--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="4485" windowWidth="12120" windowHeight="5070"/>
+    <workbookView xWindow="-15" yWindow="4485" windowWidth="11055" windowHeight="5055"/>
   </bookViews>
   <sheets>
     <sheet name="順豐出口" sheetId="4" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11978" uniqueCount="8739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12032" uniqueCount="8773">
   <si>
     <t>麒安科技有限公司</t>
   </si>
@@ -30829,6 +30829,142 @@
   </si>
   <si>
     <t>0422086880#35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>97219279</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>楷嘉電子股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.12.31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WBBL2024081769</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>友良高科技紡織股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二04679</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119.03.24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114.03.26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電話</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>慢溫事業有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二04680</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>062211393#23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>劉小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>長頴國際貿易有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二04681</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新杰資訊科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二04682</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>時曄科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二04683</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0229188958#118</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台灣愛喜益科技有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二04684</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>117.03.31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0282266477#207</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>榮創能源科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二04685</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>035976988#16593</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>戴小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匯彩科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二04686</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0222980099#112</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>何小姐</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -30961,7 +31097,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -31064,12 +31200,35 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="38">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -31728,7 +31887,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:J2123"/>
+  <dimension ref="A1:J2132"/>
   <sheetFormatPr defaultRowHeight="21.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" style="5" customWidth="1"/>
@@ -40859,7 +41018,7 @@
         <v>3318</v>
       </c>
     </row>
-    <row r="612" spans="1:8" ht="24" customHeight="1">
+    <row r="612" spans="1:8" ht="24.2" customHeight="1">
       <c r="A612" s="5" t="s">
         <v>878</v>
       </c>
@@ -72861,112 +73020,325 @@
         <v>8709</v>
       </c>
     </row>
+    <row r="2124" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2124" s="5" t="s">
+        <v>8740</v>
+      </c>
+      <c r="B2124" s="3" t="s">
+        <v>8739</v>
+      </c>
+      <c r="C2124" s="34" t="s">
+        <v>8742</v>
+      </c>
+      <c r="D2124" s="1" t="s">
+        <v>8741</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2125" s="12" t="s">
+        <v>8743</v>
+      </c>
+      <c r="B2125" s="7">
+        <v>79838241</v>
+      </c>
+      <c r="C2125" s="6" t="s">
+        <v>8744</v>
+      </c>
+      <c r="D2125" s="6" t="s">
+        <v>8745</v>
+      </c>
+      <c r="F2125" s="6" t="s">
+        <v>8746</v>
+      </c>
+      <c r="G2125" s="6" t="s">
+        <v>8747</v>
+      </c>
+      <c r="I2125" s="32"/>
+    </row>
+    <row r="2126" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2126" s="12" t="s">
+        <v>8748</v>
+      </c>
+      <c r="B2126" s="7">
+        <v>24926184</v>
+      </c>
+      <c r="C2126" s="6" t="s">
+        <v>8749</v>
+      </c>
+      <c r="D2126" s="6" t="s">
+        <v>8745</v>
+      </c>
+      <c r="F2126" s="6" t="s">
+        <v>8746</v>
+      </c>
+      <c r="G2126" s="6" t="s">
+        <v>8747</v>
+      </c>
+      <c r="H2126" s="6" t="s">
+        <v>8750</v>
+      </c>
+      <c r="I2126" s="32" t="s">
+        <v>8751</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2127" s="12" t="s">
+        <v>8752</v>
+      </c>
+      <c r="B2127" s="7">
+        <v>93369894</v>
+      </c>
+      <c r="C2127" s="6" t="s">
+        <v>8753</v>
+      </c>
+      <c r="D2127" s="6" t="s">
+        <v>8745</v>
+      </c>
+      <c r="F2127" s="6" t="s">
+        <v>8746</v>
+      </c>
+      <c r="G2127" s="6" t="s">
+        <v>8747</v>
+      </c>
+      <c r="I2127" s="32"/>
+    </row>
+    <row r="2128" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2128" s="12" t="s">
+        <v>8754</v>
+      </c>
+      <c r="B2128" s="7">
+        <v>29166887</v>
+      </c>
+      <c r="C2128" s="6" t="s">
+        <v>8755</v>
+      </c>
+      <c r="D2128" s="6" t="s">
+        <v>8745</v>
+      </c>
+      <c r="F2128" s="6" t="s">
+        <v>8746</v>
+      </c>
+      <c r="G2128" s="6" t="s">
+        <v>8747</v>
+      </c>
+      <c r="I2128" s="32"/>
+    </row>
+    <row r="2129" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2129" s="12" t="s">
+        <v>8756</v>
+      </c>
+      <c r="B2129" s="7">
+        <v>54014332</v>
+      </c>
+      <c r="C2129" s="6" t="s">
+        <v>8757</v>
+      </c>
+      <c r="D2129" s="6" t="s">
+        <v>8745</v>
+      </c>
+      <c r="F2129" s="6" t="s">
+        <v>8746</v>
+      </c>
+      <c r="G2129" s="6" t="s">
+        <v>8747</v>
+      </c>
+      <c r="H2129" s="6" t="s">
+        <v>8758</v>
+      </c>
+      <c r="I2129" s="32" t="s">
+        <v>8759</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2130" s="12" t="s">
+        <v>8760</v>
+      </c>
+      <c r="B2130" s="7">
+        <v>25089142</v>
+      </c>
+      <c r="C2130" s="6" t="s">
+        <v>8761</v>
+      </c>
+      <c r="D2130" s="6" t="s">
+        <v>8762</v>
+      </c>
+      <c r="F2130" s="6" t="s">
+        <v>8746</v>
+      </c>
+      <c r="G2130" s="6" t="s">
+        <v>8747</v>
+      </c>
+      <c r="H2130" s="6" t="s">
+        <v>8763</v>
+      </c>
+      <c r="I2130" s="32" t="s">
+        <v>8764</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2131" s="12" t="s">
+        <v>8765</v>
+      </c>
+      <c r="B2131" s="7">
+        <v>70634323</v>
+      </c>
+      <c r="C2131" s="6" t="s">
+        <v>8766</v>
+      </c>
+      <c r="D2131" s="6" t="s">
+        <v>8745</v>
+      </c>
+      <c r="F2131" s="6" t="s">
+        <v>8746</v>
+      </c>
+      <c r="G2131" s="6" t="s">
+        <v>8747</v>
+      </c>
+      <c r="H2131" s="6" t="s">
+        <v>8767</v>
+      </c>
+      <c r="I2131" s="32" t="s">
+        <v>8768</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2132" s="12" t="s">
+        <v>8769</v>
+      </c>
+      <c r="B2132" s="7">
+        <v>54726923</v>
+      </c>
+      <c r="C2132" s="6" t="s">
+        <v>8770</v>
+      </c>
+      <c r="D2132" s="6" t="s">
+        <v>8745</v>
+      </c>
+      <c r="F2132" s="6" t="s">
+        <v>8746</v>
+      </c>
+      <c r="G2132" s="6" t="s">
+        <v>8747</v>
+      </c>
+      <c r="H2132" s="6" t="s">
+        <v>8771</v>
+      </c>
+      <c r="I2132" s="32" t="s">
+        <v>8772</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2022:A2033">
-    <cfRule type="duplicateValues" dxfId="35" priority="81" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="86" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2068:A2075">
-    <cfRule type="duplicateValues" dxfId="34" priority="72" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="77" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2068:B2075">
-    <cfRule type="duplicateValues" dxfId="33" priority="71" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="76" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2076:A2086">
-    <cfRule type="duplicateValues" dxfId="32" priority="55" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="60" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2076:B2086">
-    <cfRule type="duplicateValues" dxfId="31" priority="54" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="59" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2108">
-    <cfRule type="duplicateValues" dxfId="30" priority="44" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="49" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2108">
-    <cfRule type="duplicateValues" dxfId="29" priority="42" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="43" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="47" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="48" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2087">
-    <cfRule type="duplicateValues" dxfId="27" priority="41" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="46" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2087">
-    <cfRule type="duplicateValues" dxfId="26" priority="40" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="45" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2088">
-    <cfRule type="duplicateValues" dxfId="25" priority="39" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="44" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2088">
-    <cfRule type="duplicateValues" dxfId="24" priority="38" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="43" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2089">
-    <cfRule type="duplicateValues" dxfId="23" priority="37" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="42" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2089">
-    <cfRule type="duplicateValues" dxfId="22" priority="36" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="41" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2090">
-    <cfRule type="duplicateValues" dxfId="21" priority="35" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="40" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2090">
-    <cfRule type="duplicateValues" dxfId="20" priority="34" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="39" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2091">
-    <cfRule type="duplicateValues" dxfId="19" priority="33" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="38" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2091">
-    <cfRule type="duplicateValues" dxfId="18" priority="32" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="37" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2092">
-    <cfRule type="duplicateValues" dxfId="17" priority="31" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="36" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2092">
-    <cfRule type="duplicateValues" dxfId="16" priority="30" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="35" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2093">
-    <cfRule type="duplicateValues" dxfId="15" priority="29" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="34" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2093">
-    <cfRule type="duplicateValues" dxfId="14" priority="28" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="33" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2094">
-    <cfRule type="duplicateValues" dxfId="13" priority="27" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="32" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2094">
-    <cfRule type="duplicateValues" dxfId="12" priority="26" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="31" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2095">
+    <cfRule type="duplicateValues" dxfId="13" priority="30" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2095">
+    <cfRule type="duplicateValues" dxfId="12" priority="29" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2096:A2099">
     <cfRule type="duplicateValues" dxfId="11" priority="25" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2095">
+  <conditionalFormatting sqref="B2096:B2099">
     <cfRule type="duplicateValues" dxfId="10" priority="24" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2096:A2099">
-    <cfRule type="duplicateValues" dxfId="9" priority="20" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2096:B2099">
-    <cfRule type="duplicateValues" dxfId="8" priority="19" stopIfTrue="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A2100:A2107">
-    <cfRule type="duplicateValues" dxfId="7" priority="12" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="17" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2100:B2107">
-    <cfRule type="duplicateValues" dxfId="6" priority="11" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="16" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2124:A65536 A2034:A2067 A1:A2021">
-    <cfRule type="duplicateValues" dxfId="5" priority="82" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2124 A2034:A2067 A1:A2021 A2133:A65536">
+    <cfRule type="duplicateValues" dxfId="7" priority="87" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2124:B65536 B1:B2067">
-    <cfRule type="duplicateValues" dxfId="4" priority="87" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2124 B1:B2067 B2133:B65536">
+    <cfRule type="duplicateValues" dxfId="6" priority="92" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2109:A2116">
+    <cfRule type="duplicateValues" dxfId="5" priority="12" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2109:B2116">
+    <cfRule type="duplicateValues" dxfId="4" priority="11" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2117:A2123">
     <cfRule type="duplicateValues" dxfId="3" priority="7" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2109:B2116">
+  <conditionalFormatting sqref="B2117:B2123">
     <cfRule type="duplicateValues" dxfId="2" priority="6" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2117:A2123">
+  <conditionalFormatting sqref="A2125:A2132">
     <cfRule type="duplicateValues" dxfId="1" priority="2" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2117:B2123">
+  <conditionalFormatting sqref="B2125:B2132">
     <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">

--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="4485" windowWidth="11055" windowHeight="5055"/>
+    <workbookView xWindow="-15" yWindow="4530" windowWidth="11055" windowHeight="5010"/>
   </bookViews>
   <sheets>
     <sheet name="順豐出口" sheetId="4" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12032" uniqueCount="8773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12093" uniqueCount="8800">
   <si>
     <t>麒安科技有限公司</t>
   </si>
@@ -30965,6 +30965,91 @@
   </si>
   <si>
     <t>何小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05143647</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>穎特力欣股份有限公司</t>
+  </si>
+  <si>
+    <t>億克斯有限公司</t>
+  </si>
+  <si>
+    <t>立晟科技有限公司</t>
+  </si>
+  <si>
+    <t>霖宏科技股份有限公司</t>
+  </si>
+  <si>
+    <t>勤誠興業股份有限公司</t>
+  </si>
+  <si>
+    <t>勤鋒精密股份有限公司</t>
+  </si>
+  <si>
+    <t>登康美有限公司</t>
+  </si>
+  <si>
+    <t>台灣電緣股份有限公司</t>
+  </si>
+  <si>
+    <t>優克美科技股份有限公司</t>
+  </si>
+  <si>
+    <t>昱達利工業股份有限公司</t>
+  </si>
+  <si>
+    <t>威翔航空科技股份有限公司</t>
+  </si>
+  <si>
+    <t>鑫創科技股份有限公司</t>
+  </si>
+  <si>
+    <t>114業二06265</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二06266</t>
+  </si>
+  <si>
+    <t>114業二06267</t>
+  </si>
+  <si>
+    <t>114業二06268</t>
+  </si>
+  <si>
+    <t>114業二06269</t>
+  </si>
+  <si>
+    <t>114業二06270</t>
+  </si>
+  <si>
+    <t>114業二06271</t>
+  </si>
+  <si>
+    <t>114業二06272</t>
+  </si>
+  <si>
+    <t>114業二06273</t>
+  </si>
+  <si>
+    <t>114業二06274</t>
+  </si>
+  <si>
+    <t>114業二06275</t>
+  </si>
+  <si>
+    <t>114業二06276</t>
+  </si>
+  <si>
+    <t>119.03.31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114.04.07</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -31097,7 +31182,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -31203,12 +31288,48 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="38">
+  <dxfs count="41">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -31887,7 +32008,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:J2132"/>
+  <dimension ref="A1:J2144"/>
   <sheetFormatPr defaultRowHeight="21.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" style="5" customWidth="1"/>
@@ -72611,38 +72732,41 @@
         <v>8660</v>
       </c>
     </row>
-    <row r="2108" spans="1:9" s="31" customFormat="1" ht="21.95" customHeight="1">
-      <c r="A2108" s="30" t="s">
-        <v>8573</v>
-      </c>
-      <c r="B2108" s="30">
-        <v>52693448</v>
-      </c>
-      <c r="C2108" s="30" t="s">
-        <v>8571</v>
-      </c>
-      <c r="D2108" s="30" t="s">
-        <v>8572</v>
-      </c>
-      <c r="E2108" s="31" t="s">
-        <v>8574</v>
-      </c>
-      <c r="F2108" s="31" t="s">
-        <v>8575</v>
-      </c>
-      <c r="G2108" s="31" t="s">
-        <v>3798</v>
+    <row r="2108" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2108" s="12" t="s">
+        <v>8673</v>
+      </c>
+      <c r="B2108" s="7">
+        <v>35928595</v>
+      </c>
+      <c r="C2108" s="6" t="s">
+        <v>8674</v>
+      </c>
+      <c r="D2108" s="6" t="s">
+        <v>8675</v>
+      </c>
+      <c r="F2108" s="6" t="s">
+        <v>8676</v>
+      </c>
+      <c r="G2108" s="6" t="s">
+        <v>8677</v>
+      </c>
+      <c r="H2108" s="6" t="s">
+        <v>8678</v>
+      </c>
+      <c r="I2108" s="32" t="s">
+        <v>8679</v>
       </c>
     </row>
     <row r="2109" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2109" s="12" t="s">
-        <v>8673</v>
+        <v>8680</v>
       </c>
       <c r="B2109" s="7">
-        <v>35928595</v>
+        <v>57132939</v>
       </c>
       <c r="C2109" s="6" t="s">
-        <v>8674</v>
+        <v>8681</v>
       </c>
       <c r="D2109" s="6" t="s">
         <v>8675</v>
@@ -72654,21 +72778,21 @@
         <v>8677</v>
       </c>
       <c r="H2109" s="6" t="s">
-        <v>8678</v>
+        <v>8682</v>
       </c>
       <c r="I2109" s="32" t="s">
-        <v>8679</v>
+        <v>8683</v>
       </c>
     </row>
     <row r="2110" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2110" s="12" t="s">
-        <v>8680</v>
+        <v>8684</v>
       </c>
       <c r="B2110" s="7">
-        <v>57132939</v>
+        <v>28112723</v>
       </c>
       <c r="C2110" s="6" t="s">
-        <v>8681</v>
+        <v>8685</v>
       </c>
       <c r="D2110" s="6" t="s">
         <v>8675</v>
@@ -72677,24 +72801,24 @@
         <v>8676</v>
       </c>
       <c r="G2110" s="6" t="s">
-        <v>8677</v>
+        <v>8686</v>
       </c>
       <c r="H2110" s="6" t="s">
-        <v>8682</v>
+        <v>8687</v>
       </c>
       <c r="I2110" s="32" t="s">
-        <v>8683</v>
+        <v>8688</v>
       </c>
     </row>
     <row r="2111" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2111" s="12" t="s">
-        <v>8684</v>
+        <v>8689</v>
       </c>
       <c r="B2111" s="7">
-        <v>28112723</v>
+        <v>90784186</v>
       </c>
       <c r="C2111" s="6" t="s">
-        <v>8685</v>
+        <v>8690</v>
       </c>
       <c r="D2111" s="6" t="s">
         <v>8675</v>
@@ -72703,24 +72827,24 @@
         <v>8676</v>
       </c>
       <c r="G2111" s="6" t="s">
-        <v>8686</v>
+        <v>8677</v>
       </c>
       <c r="H2111" s="6" t="s">
-        <v>8687</v>
+        <v>8691</v>
       </c>
       <c r="I2111" s="32" t="s">
-        <v>8688</v>
+        <v>8692</v>
       </c>
     </row>
     <row r="2112" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2112" s="12" t="s">
-        <v>8689</v>
+        <v>8693</v>
       </c>
       <c r="B2112" s="7">
-        <v>90784186</v>
+        <v>28877776</v>
       </c>
       <c r="C2112" s="6" t="s">
-        <v>8690</v>
+        <v>8694</v>
       </c>
       <c r="D2112" s="6" t="s">
         <v>8675</v>
@@ -72732,21 +72856,19 @@
         <v>8677</v>
       </c>
       <c r="H2112" s="6" t="s">
-        <v>8691</v>
-      </c>
-      <c r="I2112" s="32" t="s">
-        <v>8692</v>
-      </c>
+        <v>8695</v>
+      </c>
+      <c r="I2112" s="32"/>
     </row>
     <row r="2113" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2113" s="12" t="s">
-        <v>8693</v>
+        <v>8696</v>
       </c>
       <c r="B2113" s="7">
-        <v>28877776</v>
+        <v>16541523</v>
       </c>
       <c r="C2113" s="6" t="s">
-        <v>8694</v>
+        <v>8697</v>
       </c>
       <c r="D2113" s="6" t="s">
         <v>8675</v>
@@ -72758,19 +72880,21 @@
         <v>8677</v>
       </c>
       <c r="H2113" s="6" t="s">
-        <v>8695</v>
-      </c>
-      <c r="I2113" s="32"/>
+        <v>8698</v>
+      </c>
+      <c r="I2113" s="32" t="s">
+        <v>8692</v>
+      </c>
     </row>
     <row r="2114" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2114" s="12" t="s">
-        <v>8696</v>
+        <v>8699</v>
       </c>
       <c r="B2114" s="7">
-        <v>16541523</v>
+        <v>12733681</v>
       </c>
       <c r="C2114" s="6" t="s">
-        <v>8697</v>
+        <v>8700</v>
       </c>
       <c r="D2114" s="6" t="s">
         <v>8675</v>
@@ -72782,21 +72906,21 @@
         <v>8677</v>
       </c>
       <c r="H2114" s="6" t="s">
-        <v>8698</v>
+        <v>8701</v>
       </c>
       <c r="I2114" s="32" t="s">
-        <v>8692</v>
+        <v>8702</v>
       </c>
     </row>
     <row r="2115" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2115" s="12" t="s">
-        <v>8699</v>
+        <v>8703</v>
       </c>
       <c r="B2115" s="7">
-        <v>12733681</v>
+        <v>34783798</v>
       </c>
       <c r="C2115" s="6" t="s">
-        <v>8700</v>
+        <v>8704</v>
       </c>
       <c r="D2115" s="6" t="s">
         <v>8675</v>
@@ -72808,48 +72932,48 @@
         <v>8677</v>
       </c>
       <c r="H2115" s="6" t="s">
-        <v>8701</v>
-      </c>
-      <c r="I2115" s="32" t="s">
-        <v>8702</v>
-      </c>
+        <v>8705</v>
+      </c>
+      <c r="I2115" s="32"/>
     </row>
     <row r="2116" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2116" s="12" t="s">
-        <v>8703</v>
+        <v>8712</v>
       </c>
       <c r="B2116" s="7">
-        <v>34783798</v>
+        <v>54503893</v>
       </c>
       <c r="C2116" s="6" t="s">
-        <v>8704</v>
+        <v>8713</v>
       </c>
       <c r="D2116" s="6" t="s">
-        <v>8675</v>
+        <v>8714</v>
       </c>
       <c r="F2116" s="6" t="s">
-        <v>8676</v>
+        <v>8715</v>
       </c>
       <c r="G2116" s="6" t="s">
-        <v>8677</v>
+        <v>8716</v>
       </c>
       <c r="H2116" s="6" t="s">
-        <v>8705</v>
-      </c>
-      <c r="I2116" s="32"/>
+        <v>8717</v>
+      </c>
+      <c r="I2116" s="32" t="s">
+        <v>8706</v>
+      </c>
     </row>
     <row r="2117" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2117" s="12" t="s">
-        <v>8712</v>
+        <v>8718</v>
       </c>
       <c r="B2117" s="7">
-        <v>54503893</v>
+        <v>13004319</v>
       </c>
       <c r="C2117" s="6" t="s">
-        <v>8713</v>
+        <v>8719</v>
       </c>
       <c r="D2117" s="6" t="s">
-        <v>8714</v>
+        <v>8720</v>
       </c>
       <c r="F2117" s="6" t="s">
         <v>8715</v>
@@ -72858,24 +72982,24 @@
         <v>8716</v>
       </c>
       <c r="H2117" s="6" t="s">
-        <v>8717</v>
+        <v>8721</v>
       </c>
       <c r="I2117" s="32" t="s">
-        <v>8706</v>
+        <v>8707</v>
       </c>
     </row>
     <row r="2118" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2118" s="12" t="s">
-        <v>8718</v>
+        <v>8722</v>
       </c>
       <c r="B2118" s="7">
-        <v>13004319</v>
+        <v>35892013</v>
       </c>
       <c r="C2118" s="6" t="s">
-        <v>8719</v>
+        <v>8723</v>
       </c>
       <c r="D2118" s="6" t="s">
-        <v>8720</v>
+        <v>8724</v>
       </c>
       <c r="F2118" s="6" t="s">
         <v>8715</v>
@@ -72884,24 +73008,24 @@
         <v>8716</v>
       </c>
       <c r="H2118" s="6" t="s">
-        <v>8721</v>
+        <v>8725</v>
       </c>
       <c r="I2118" s="32" t="s">
-        <v>8707</v>
+        <v>8708</v>
       </c>
     </row>
     <row r="2119" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2119" s="12" t="s">
-        <v>8722</v>
+        <v>8726</v>
       </c>
       <c r="B2119" s="7">
-        <v>35892013</v>
+        <v>54138621</v>
       </c>
       <c r="C2119" s="6" t="s">
-        <v>8723</v>
+        <v>8727</v>
       </c>
       <c r="D2119" s="6" t="s">
-        <v>8724</v>
+        <v>8720</v>
       </c>
       <c r="F2119" s="6" t="s">
         <v>8715</v>
@@ -72910,21 +73034,21 @@
         <v>8716</v>
       </c>
       <c r="H2119" s="6" t="s">
-        <v>8725</v>
+        <v>8728</v>
       </c>
       <c r="I2119" s="32" t="s">
-        <v>8708</v>
+        <v>8709</v>
       </c>
     </row>
     <row r="2120" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2120" s="12" t="s">
-        <v>8726</v>
+        <v>8729</v>
       </c>
       <c r="B2120" s="7">
-        <v>54138621</v>
+        <v>96770218</v>
       </c>
       <c r="C2120" s="6" t="s">
-        <v>8727</v>
+        <v>8730</v>
       </c>
       <c r="D2120" s="6" t="s">
         <v>8720</v>
@@ -72936,21 +73060,21 @@
         <v>8716</v>
       </c>
       <c r="H2120" s="6" t="s">
-        <v>8728</v>
+        <v>8731</v>
       </c>
       <c r="I2120" s="32" t="s">
-        <v>8709</v>
+        <v>8710</v>
       </c>
     </row>
     <row r="2121" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2121" s="12" t="s">
-        <v>8729</v>
+        <v>8732</v>
       </c>
       <c r="B2121" s="7">
-        <v>96770218</v>
+        <v>79962796</v>
       </c>
       <c r="C2121" s="6" t="s">
-        <v>8730</v>
+        <v>8733</v>
       </c>
       <c r="D2121" s="6" t="s">
         <v>8720</v>
@@ -72962,24 +73086,24 @@
         <v>8716</v>
       </c>
       <c r="H2121" s="6" t="s">
-        <v>8731</v>
+        <v>8734</v>
       </c>
       <c r="I2121" s="32" t="s">
-        <v>8710</v>
+        <v>8711</v>
       </c>
     </row>
     <row r="2122" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2122" s="12" t="s">
-        <v>8732</v>
+        <v>8735</v>
       </c>
       <c r="B2122" s="7">
-        <v>79962796</v>
+        <v>54398652</v>
       </c>
       <c r="C2122" s="6" t="s">
-        <v>8733</v>
+        <v>8736</v>
       </c>
       <c r="D2122" s="6" t="s">
-        <v>8720</v>
+        <v>8737</v>
       </c>
       <c r="F2122" s="6" t="s">
         <v>8715</v>
@@ -72988,61 +73112,56 @@
         <v>8716</v>
       </c>
       <c r="H2122" s="6" t="s">
-        <v>8734</v>
+        <v>8738</v>
       </c>
       <c r="I2122" s="32" t="s">
-        <v>8711</v>
-      </c>
-    </row>
-    <row r="2123" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
-      <c r="A2123" s="12" t="s">
-        <v>8735</v>
-      </c>
-      <c r="B2123" s="7">
-        <v>54398652</v>
-      </c>
-      <c r="C2123" s="6" t="s">
-        <v>8736</v>
-      </c>
-      <c r="D2123" s="6" t="s">
-        <v>8737</v>
-      </c>
-      <c r="F2123" s="6" t="s">
-        <v>8715</v>
-      </c>
-      <c r="G2123" s="6" t="s">
-        <v>8716</v>
-      </c>
-      <c r="H2123" s="6" t="s">
-        <v>8738</v>
-      </c>
-      <c r="I2123" s="32" t="s">
         <v>8709</v>
       </c>
     </row>
-    <row r="2124" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2124" s="5" t="s">
+    <row r="2123" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2123" s="5" t="s">
         <v>8740</v>
       </c>
-      <c r="B2124" s="3" t="s">
+      <c r="B2123" s="3" t="s">
         <v>8739</v>
       </c>
-      <c r="C2124" s="34" t="s">
+      <c r="C2123" s="34" t="s">
         <v>8742</v>
       </c>
-      <c r="D2124" s="1" t="s">
+      <c r="D2123" s="1" t="s">
         <v>8741</v>
       </c>
+    </row>
+    <row r="2124" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2124" s="12" t="s">
+        <v>8743</v>
+      </c>
+      <c r="B2124" s="7">
+        <v>79838241</v>
+      </c>
+      <c r="C2124" s="6" t="s">
+        <v>8744</v>
+      </c>
+      <c r="D2124" s="6" t="s">
+        <v>8745</v>
+      </c>
+      <c r="F2124" s="6" t="s">
+        <v>8746</v>
+      </c>
+      <c r="G2124" s="6" t="s">
+        <v>8747</v>
+      </c>
+      <c r="I2124" s="32"/>
     </row>
     <row r="2125" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2125" s="12" t="s">
-        <v>8743</v>
+        <v>8748</v>
       </c>
       <c r="B2125" s="7">
-        <v>79838241</v>
+        <v>24926184</v>
       </c>
       <c r="C2125" s="6" t="s">
-        <v>8744</v>
+        <v>8749</v>
       </c>
       <c r="D2125" s="6" t="s">
         <v>8745</v>
@@ -73053,17 +73172,22 @@
       <c r="G2125" s="6" t="s">
         <v>8747</v>
       </c>
-      <c r="I2125" s="32"/>
+      <c r="H2125" s="6" t="s">
+        <v>8750</v>
+      </c>
+      <c r="I2125" s="32" t="s">
+        <v>8751</v>
+      </c>
     </row>
     <row r="2126" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2126" s="12" t="s">
-        <v>8748</v>
+        <v>8752</v>
       </c>
       <c r="B2126" s="7">
-        <v>24926184</v>
+        <v>93369894</v>
       </c>
       <c r="C2126" s="6" t="s">
-        <v>8749</v>
+        <v>8753</v>
       </c>
       <c r="D2126" s="6" t="s">
         <v>8745</v>
@@ -73074,22 +73198,17 @@
       <c r="G2126" s="6" t="s">
         <v>8747</v>
       </c>
-      <c r="H2126" s="6" t="s">
-        <v>8750</v>
-      </c>
-      <c r="I2126" s="32" t="s">
-        <v>8751</v>
-      </c>
+      <c r="I2126" s="32"/>
     </row>
     <row r="2127" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2127" s="12" t="s">
-        <v>8752</v>
+        <v>8754</v>
       </c>
       <c r="B2127" s="7">
-        <v>93369894</v>
+        <v>29166887</v>
       </c>
       <c r="C2127" s="6" t="s">
-        <v>8753</v>
+        <v>8755</v>
       </c>
       <c r="D2127" s="6" t="s">
         <v>8745</v>
@@ -73104,13 +73223,13 @@
     </row>
     <row r="2128" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2128" s="12" t="s">
-        <v>8754</v>
+        <v>8756</v>
       </c>
       <c r="B2128" s="7">
-        <v>29166887</v>
+        <v>54014332</v>
       </c>
       <c r="C2128" s="6" t="s">
-        <v>8755</v>
+        <v>8757</v>
       </c>
       <c r="D2128" s="6" t="s">
         <v>8745</v>
@@ -73121,20 +73240,25 @@
       <c r="G2128" s="6" t="s">
         <v>8747</v>
       </c>
-      <c r="I2128" s="32"/>
+      <c r="H2128" s="6" t="s">
+        <v>8758</v>
+      </c>
+      <c r="I2128" s="32" t="s">
+        <v>8759</v>
+      </c>
     </row>
     <row r="2129" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2129" s="12" t="s">
-        <v>8756</v>
+        <v>8760</v>
       </c>
       <c r="B2129" s="7">
-        <v>54014332</v>
+        <v>25089142</v>
       </c>
       <c r="C2129" s="6" t="s">
-        <v>8757</v>
+        <v>8761</v>
       </c>
       <c r="D2129" s="6" t="s">
-        <v>8745</v>
+        <v>8762</v>
       </c>
       <c r="F2129" s="6" t="s">
         <v>8746</v>
@@ -73143,24 +73267,24 @@
         <v>8747</v>
       </c>
       <c r="H2129" s="6" t="s">
-        <v>8758</v>
+        <v>8763</v>
       </c>
       <c r="I2129" s="32" t="s">
-        <v>8759</v>
+        <v>8764</v>
       </c>
     </row>
     <row r="2130" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2130" s="12" t="s">
-        <v>8760</v>
+        <v>8765</v>
       </c>
       <c r="B2130" s="7">
-        <v>25089142</v>
+        <v>70634323</v>
       </c>
       <c r="C2130" s="6" t="s">
-        <v>8761</v>
+        <v>8766</v>
       </c>
       <c r="D2130" s="6" t="s">
-        <v>8762</v>
+        <v>8745</v>
       </c>
       <c r="F2130" s="6" t="s">
         <v>8746</v>
@@ -73169,21 +73293,21 @@
         <v>8747</v>
       </c>
       <c r="H2130" s="6" t="s">
-        <v>8763</v>
+        <v>8767</v>
       </c>
       <c r="I2130" s="32" t="s">
-        <v>8764</v>
+        <v>8768</v>
       </c>
     </row>
     <row r="2131" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2131" s="12" t="s">
-        <v>8765</v>
+        <v>8769</v>
       </c>
       <c r="B2131" s="7">
-        <v>70634323</v>
+        <v>54726923</v>
       </c>
       <c r="C2131" s="6" t="s">
-        <v>8766</v>
+        <v>8770</v>
       </c>
       <c r="D2131" s="6" t="s">
         <v>8745</v>
@@ -73195,151 +73319,395 @@
         <v>8747</v>
       </c>
       <c r="H2131" s="6" t="s">
-        <v>8767</v>
+        <v>8771</v>
       </c>
       <c r="I2131" s="32" t="s">
-        <v>8768</v>
-      </c>
-    </row>
-    <row r="2132" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
-      <c r="A2132" s="12" t="s">
-        <v>8769</v>
-      </c>
-      <c r="B2132" s="7">
-        <v>54726923</v>
-      </c>
-      <c r="C2132" s="6" t="s">
-        <v>8770</v>
-      </c>
-      <c r="D2132" s="6" t="s">
-        <v>8745</v>
-      </c>
-      <c r="F2132" s="6" t="s">
-        <v>8746</v>
-      </c>
-      <c r="G2132" s="6" t="s">
-        <v>8747</v>
-      </c>
-      <c r="H2132" s="6" t="s">
-        <v>8771</v>
-      </c>
-      <c r="I2132" s="32" t="s">
         <v>8772</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:9" s="31" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2132" s="30" t="s">
+        <v>8573</v>
+      </c>
+      <c r="B2132" s="30">
+        <v>52693448</v>
+      </c>
+      <c r="C2132" s="30" t="s">
+        <v>8571</v>
+      </c>
+      <c r="D2132" s="30" t="s">
+        <v>8572</v>
+      </c>
+      <c r="E2132" s="31" t="s">
+        <v>8574</v>
+      </c>
+      <c r="F2132" s="31" t="s">
+        <v>8575</v>
+      </c>
+      <c r="G2132" s="31" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2133" s="35" t="s">
+        <v>8774</v>
+      </c>
+      <c r="B2133" s="35">
+        <v>96799025</v>
+      </c>
+      <c r="C2133" s="35" t="s">
+        <v>8786</v>
+      </c>
+      <c r="D2133" s="35" t="s">
+        <v>8798</v>
+      </c>
+      <c r="F2133" s="1" t="s">
+        <v>8799</v>
+      </c>
+      <c r="G2133" s="6" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2134" s="35" t="s">
+        <v>8775</v>
+      </c>
+      <c r="B2134" s="35">
+        <v>82914313</v>
+      </c>
+      <c r="C2134" s="35" t="s">
+        <v>8787</v>
+      </c>
+      <c r="D2134" s="35" t="s">
+        <v>8798</v>
+      </c>
+      <c r="F2134" s="1" t="s">
+        <v>8799</v>
+      </c>
+      <c r="G2134" s="6" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2135" s="35" t="s">
+        <v>8776</v>
+      </c>
+      <c r="B2135" s="35">
+        <v>28043986</v>
+      </c>
+      <c r="C2135" s="35" t="s">
+        <v>8788</v>
+      </c>
+      <c r="D2135" s="35" t="s">
+        <v>8798</v>
+      </c>
+      <c r="F2135" s="1" t="s">
+        <v>8799</v>
+      </c>
+      <c r="G2135" s="6" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2136" s="35" t="s">
+        <v>8777</v>
+      </c>
+      <c r="B2136" s="35">
+        <v>89396770</v>
+      </c>
+      <c r="C2136" s="35" t="s">
+        <v>8789</v>
+      </c>
+      <c r="D2136" s="35" t="s">
+        <v>8798</v>
+      </c>
+      <c r="F2136" s="1" t="s">
+        <v>8799</v>
+      </c>
+      <c r="G2136" s="6" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2137" s="35" t="s">
+        <v>8778</v>
+      </c>
+      <c r="B2137" s="36" t="s">
+        <v>8773</v>
+      </c>
+      <c r="C2137" s="35" t="s">
+        <v>8790</v>
+      </c>
+      <c r="D2137" s="35" t="s">
+        <v>8798</v>
+      </c>
+      <c r="F2137" s="1" t="s">
+        <v>8799</v>
+      </c>
+      <c r="G2137" s="6" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2138" s="35" t="s">
+        <v>8779</v>
+      </c>
+      <c r="B2138" s="35">
+        <v>83483376</v>
+      </c>
+      <c r="C2138" s="35" t="s">
+        <v>8791</v>
+      </c>
+      <c r="D2138" s="35" t="s">
+        <v>8798</v>
+      </c>
+      <c r="F2138" s="1" t="s">
+        <v>8799</v>
+      </c>
+      <c r="G2138" s="6" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2139" s="35" t="s">
+        <v>8780</v>
+      </c>
+      <c r="B2139" s="35">
+        <v>28339685</v>
+      </c>
+      <c r="C2139" s="35" t="s">
+        <v>8792</v>
+      </c>
+      <c r="D2139" s="35" t="s">
+        <v>8798</v>
+      </c>
+      <c r="F2139" s="1" t="s">
+        <v>8799</v>
+      </c>
+      <c r="G2139" s="6" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2140" s="35" t="s">
+        <v>8781</v>
+      </c>
+      <c r="B2140" s="35">
+        <v>59214274</v>
+      </c>
+      <c r="C2140" s="35" t="s">
+        <v>8793</v>
+      </c>
+      <c r="D2140" s="35" t="s">
+        <v>8798</v>
+      </c>
+      <c r="F2140" s="1" t="s">
+        <v>8799</v>
+      </c>
+      <c r="G2140" s="6" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2141" s="35" t="s">
+        <v>8782</v>
+      </c>
+      <c r="B2141" s="35">
+        <v>53137700</v>
+      </c>
+      <c r="C2141" s="35" t="s">
+        <v>8794</v>
+      </c>
+      <c r="D2141" s="35" t="s">
+        <v>8798</v>
+      </c>
+      <c r="F2141" s="1" t="s">
+        <v>8799</v>
+      </c>
+      <c r="G2141" s="6" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2142" s="35" t="s">
+        <v>8783</v>
+      </c>
+      <c r="B2142" s="35">
+        <v>84070747</v>
+      </c>
+      <c r="C2142" s="35" t="s">
+        <v>8795</v>
+      </c>
+      <c r="D2142" s="35" t="s">
+        <v>8798</v>
+      </c>
+      <c r="F2142" s="1" t="s">
+        <v>8799</v>
+      </c>
+      <c r="G2142" s="6" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2143" s="35" t="s">
+        <v>8784</v>
+      </c>
+      <c r="B2143" s="35">
+        <v>54135526</v>
+      </c>
+      <c r="C2143" s="35" t="s">
+        <v>8796</v>
+      </c>
+      <c r="D2143" s="35" t="s">
+        <v>8798</v>
+      </c>
+      <c r="F2143" s="1" t="s">
+        <v>8799</v>
+      </c>
+      <c r="G2143" s="6" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2144" s="35" t="s">
+        <v>8785</v>
+      </c>
+      <c r="B2144" s="35">
+        <v>16766959</v>
+      </c>
+      <c r="C2144" s="35" t="s">
+        <v>8797</v>
+      </c>
+      <c r="D2144" s="35" t="s">
+        <v>8798</v>
+      </c>
+      <c r="F2144" s="1" t="s">
+        <v>8799</v>
+      </c>
+      <c r="G2144" s="6" t="s">
+        <v>3798</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2022:A2033">
-    <cfRule type="duplicateValues" dxfId="37" priority="86" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="89" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2068:A2075">
-    <cfRule type="duplicateValues" dxfId="36" priority="77" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="80" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2068:B2075">
-    <cfRule type="duplicateValues" dxfId="35" priority="76" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="79" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2076:A2086">
-    <cfRule type="duplicateValues" dxfId="34" priority="60" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="63" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2076:B2086">
-    <cfRule type="duplicateValues" dxfId="33" priority="59" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="62" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2108">
+  <conditionalFormatting sqref="B2132">
+    <cfRule type="duplicateValues" dxfId="35" priority="52" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2132">
+    <cfRule type="duplicateValues" dxfId="34" priority="50" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="51" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2087">
     <cfRule type="duplicateValues" dxfId="32" priority="49" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2108">
-    <cfRule type="duplicateValues" dxfId="31" priority="47" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="48" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2087">
+    <cfRule type="duplicateValues" dxfId="31" priority="48" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2087">
+  <conditionalFormatting sqref="A2088">
+    <cfRule type="duplicateValues" dxfId="30" priority="47" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2088">
     <cfRule type="duplicateValues" dxfId="29" priority="46" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2087">
+  <conditionalFormatting sqref="A2089">
     <cfRule type="duplicateValues" dxfId="28" priority="45" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2088">
+  <conditionalFormatting sqref="B2089">
     <cfRule type="duplicateValues" dxfId="27" priority="44" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2088">
+  <conditionalFormatting sqref="A2090">
     <cfRule type="duplicateValues" dxfId="26" priority="43" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2089">
+  <conditionalFormatting sqref="B2090">
     <cfRule type="duplicateValues" dxfId="25" priority="42" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2089">
+  <conditionalFormatting sqref="A2091">
     <cfRule type="duplicateValues" dxfId="24" priority="41" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2090">
+  <conditionalFormatting sqref="B2091">
     <cfRule type="duplicateValues" dxfId="23" priority="40" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2090">
+  <conditionalFormatting sqref="A2092">
     <cfRule type="duplicateValues" dxfId="22" priority="39" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2091">
+  <conditionalFormatting sqref="B2092">
     <cfRule type="duplicateValues" dxfId="21" priority="38" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2091">
+  <conditionalFormatting sqref="A2093">
     <cfRule type="duplicateValues" dxfId="20" priority="37" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2092">
+  <conditionalFormatting sqref="B2093">
     <cfRule type="duplicateValues" dxfId="19" priority="36" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2092">
+  <conditionalFormatting sqref="A2094">
     <cfRule type="duplicateValues" dxfId="18" priority="35" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2093">
+  <conditionalFormatting sqref="B2094">
     <cfRule type="duplicateValues" dxfId="17" priority="34" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2093">
+  <conditionalFormatting sqref="A2095">
     <cfRule type="duplicateValues" dxfId="16" priority="33" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2094">
+  <conditionalFormatting sqref="B2095">
     <cfRule type="duplicateValues" dxfId="15" priority="32" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2094">
-    <cfRule type="duplicateValues" dxfId="14" priority="31" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2095">
-    <cfRule type="duplicateValues" dxfId="13" priority="30" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2095">
-    <cfRule type="duplicateValues" dxfId="12" priority="29" stopIfTrue="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A2096:A2099">
-    <cfRule type="duplicateValues" dxfId="11" priority="25" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="28" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2096:B2099">
-    <cfRule type="duplicateValues" dxfId="10" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="27" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2100:A2107">
-    <cfRule type="duplicateValues" dxfId="9" priority="17" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="20" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2100:B2107">
-    <cfRule type="duplicateValues" dxfId="8" priority="16" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="19" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2124 A2034:A2067 A1:A2021 A2133:A65536">
-    <cfRule type="duplicateValues" dxfId="7" priority="87" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2145:A65536 A2123 A2034:A2067 A1:A2021">
+    <cfRule type="duplicateValues" dxfId="10" priority="90" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2124 B1:B2067 B2133:B65536">
-    <cfRule type="duplicateValues" dxfId="6" priority="92" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2145:B65536 B2123 B1:B2067">
+    <cfRule type="duplicateValues" dxfId="9" priority="95" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2109:A2116">
-    <cfRule type="duplicateValues" dxfId="5" priority="12" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2108:A2115">
+    <cfRule type="duplicateValues" dxfId="8" priority="15" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2109:B2116">
-    <cfRule type="duplicateValues" dxfId="4" priority="11" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2108:B2115">
+    <cfRule type="duplicateValues" dxfId="7" priority="14" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2117:A2123">
-    <cfRule type="duplicateValues" dxfId="3" priority="7" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2116:A2122">
+    <cfRule type="duplicateValues" dxfId="6" priority="10" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2117:B2123">
-    <cfRule type="duplicateValues" dxfId="2" priority="6" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2116:B2122">
+    <cfRule type="duplicateValues" dxfId="5" priority="9" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2125:A2132">
-    <cfRule type="duplicateValues" dxfId="1" priority="2" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2124:A2131">
+    <cfRule type="duplicateValues" dxfId="4" priority="5" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2125:B2132">
-    <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2124:B2131">
+    <cfRule type="duplicateValues" dxfId="3" priority="4" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2133:B2144">
+    <cfRule type="duplicateValues" dxfId="2" priority="3" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2133:B2144">
+    <cfRule type="duplicateValues" dxfId="1" priority="1" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1190:G1200 G314:G674 G676:G703 G251:G312 G705:G1187 G2:G249">
@@ -73354,7 +73722,7 @@
     <hyperlink ref="H2088" r:id="rId5"/>
     <hyperlink ref="H2090" r:id="rId6"/>
     <hyperlink ref="H2100" r:id="rId7"/>
-    <hyperlink ref="H2111" r:id="rId8"/>
+    <hyperlink ref="H2110" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>

--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12093" uniqueCount="8800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12111" uniqueCount="8825">
   <si>
     <t>麒安科技有限公司</t>
   </si>
@@ -30972,84 +30972,207 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>0425601948</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>207/陳小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>穎特力欣股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二06265</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119.03.31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114.04.07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電話</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>億克斯有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二06266</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>立晟科技有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二06267</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>063319500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12/郭小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>霖宏科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二06268</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>052216696</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>勤誠興業股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二06269</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119.03.31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114.04.07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電話</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>勤鋒精密股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二06270</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119.03.31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114.04.07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電話</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>登康美有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二06271</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>062399068</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>34/呂小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>台灣電緣股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二06272</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>047580966</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>409/張小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>優克美科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二06273</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>047278869</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>283/江小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>昱達利工業股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二06274</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0226236855</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29/薛小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>威翔航空科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二06275</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0424618885</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1103/林小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>鑫創科技股份有限公司</t>
-  </si>
-  <si>
-    <t>114業二06265</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>114業二06266</t>
-  </si>
-  <si>
-    <t>114業二06267</t>
-  </si>
-  <si>
-    <t>114業二06268</t>
-  </si>
-  <si>
-    <t>114業二06269</t>
-  </si>
-  <si>
-    <t>114業二06270</t>
-  </si>
-  <si>
-    <t>114業二06271</t>
-  </si>
-  <si>
-    <t>114業二06272</t>
-  </si>
-  <si>
-    <t>114業二06273</t>
-  </si>
-  <si>
-    <t>114業二06274</t>
-  </si>
-  <si>
-    <t>114業二06275</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>114業二06276</t>
-  </si>
-  <si>
-    <t>119.03.31</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>114.04.07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>035586568</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1601/林小姐</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -31182,7 +31305,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -31288,18 +31411,82 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="41">
+  <dxfs count="48">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -73348,366 +73535,446 @@
         <v>3798</v>
       </c>
     </row>
-    <row r="2133" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2133" s="35" t="s">
+    <row r="2133" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2133" s="12" t="s">
+        <v>8776</v>
+      </c>
+      <c r="B2133" s="7">
+        <v>96799025</v>
+      </c>
+      <c r="C2133" s="6" t="s">
+        <v>8777</v>
+      </c>
+      <c r="D2133" s="6" t="s">
+        <v>8778</v>
+      </c>
+      <c r="F2133" s="6" t="s">
+        <v>8779</v>
+      </c>
+      <c r="G2133" s="6" t="s">
+        <v>8780</v>
+      </c>
+      <c r="I2133" s="32"/>
+    </row>
+    <row r="2134" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2134" s="12" t="s">
+        <v>8781</v>
+      </c>
+      <c r="B2134" s="7">
+        <v>82914313</v>
+      </c>
+      <c r="C2134" s="6" t="s">
+        <v>8782</v>
+      </c>
+      <c r="D2134" s="6" t="s">
+        <v>8778</v>
+      </c>
+      <c r="F2134" s="6" t="s">
+        <v>8779</v>
+      </c>
+      <c r="G2134" s="6" t="s">
+        <v>8780</v>
+      </c>
+      <c r="H2134" s="6" t="s">
         <v>8774</v>
       </c>
-      <c r="B2133" s="35">
-        <v>96799025</v>
-      </c>
-      <c r="C2133" s="35" t="s">
+      <c r="I2134" s="32" t="s">
+        <v>8775</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2135" s="12" t="s">
+        <v>8783</v>
+      </c>
+      <c r="B2135" s="7">
+        <v>28043986</v>
+      </c>
+      <c r="C2135" s="6" t="s">
+        <v>8784</v>
+      </c>
+      <c r="D2135" s="6" t="s">
+        <v>8778</v>
+      </c>
+      <c r="F2135" s="6" t="s">
+        <v>8779</v>
+      </c>
+      <c r="G2135" s="6" t="s">
+        <v>8780</v>
+      </c>
+      <c r="H2135" s="6" t="s">
+        <v>8785</v>
+      </c>
+      <c r="I2135" s="32" t="s">
         <v>8786</v>
       </c>
-      <c r="D2133" s="35" t="s">
+    </row>
+    <row r="2136" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2136" s="12" t="s">
+        <v>8787</v>
+      </c>
+      <c r="B2136" s="7">
+        <v>89396770</v>
+      </c>
+      <c r="C2136" s="6" t="s">
+        <v>8788</v>
+      </c>
+      <c r="D2136" s="6" t="s">
+        <v>8778</v>
+      </c>
+      <c r="F2136" s="6" t="s">
+        <v>8779</v>
+      </c>
+      <c r="G2136" s="6" t="s">
+        <v>8780</v>
+      </c>
+      <c r="H2136" s="6" t="s">
+        <v>8789</v>
+      </c>
+      <c r="I2136" s="32" t="s">
+        <v>8790</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2137" s="12" t="s">
+        <v>8791</v>
+      </c>
+      <c r="B2137" s="7" t="s">
+        <v>8773</v>
+      </c>
+      <c r="C2137" s="6" t="s">
+        <v>8792</v>
+      </c>
+      <c r="D2137" s="6" t="s">
+        <v>8793</v>
+      </c>
+      <c r="F2137" s="6" t="s">
+        <v>8794</v>
+      </c>
+      <c r="G2137" s="6" t="s">
+        <v>8795</v>
+      </c>
+      <c r="I2137" s="32"/>
+    </row>
+    <row r="2138" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2138" s="12" t="s">
+        <v>8796</v>
+      </c>
+      <c r="B2138" s="7">
+        <v>83483376</v>
+      </c>
+      <c r="C2138" s="6" t="s">
+        <v>8797</v>
+      </c>
+      <c r="D2138" s="6" t="s">
         <v>8798</v>
       </c>
-      <c r="F2133" s="1" t="s">
+      <c r="F2138" s="6" t="s">
         <v>8799</v>
       </c>
-      <c r="G2133" s="6" t="s">
-        <v>3798</v>
-      </c>
-    </row>
-    <row r="2134" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2134" s="35" t="s">
-        <v>8775</v>
-      </c>
-      <c r="B2134" s="35">
-        <v>82914313</v>
-      </c>
-      <c r="C2134" s="35" t="s">
-        <v>8787</v>
-      </c>
-      <c r="D2134" s="35" t="s">
+      <c r="G2138" s="6" t="s">
+        <v>8800</v>
+      </c>
+      <c r="I2138" s="32"/>
+    </row>
+    <row r="2139" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2139" s="12" t="s">
+        <v>8801</v>
+      </c>
+      <c r="B2139" s="7">
+        <v>28339685</v>
+      </c>
+      <c r="C2139" s="6" t="s">
+        <v>8802</v>
+      </c>
+      <c r="D2139" s="6" t="s">
         <v>8798</v>
       </c>
-      <c r="F2134" s="1" t="s">
+      <c r="F2139" s="6" t="s">
         <v>8799</v>
       </c>
-      <c r="G2134" s="6" t="s">
-        <v>3798</v>
-      </c>
-    </row>
-    <row r="2135" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2135" s="35" t="s">
-        <v>8776</v>
-      </c>
-      <c r="B2135" s="35">
-        <v>28043986</v>
-      </c>
-      <c r="C2135" s="35" t="s">
-        <v>8788</v>
-      </c>
-      <c r="D2135" s="35" t="s">
+      <c r="G2139" s="6" t="s">
+        <v>8800</v>
+      </c>
+      <c r="H2139" s="6" t="s">
+        <v>8803</v>
+      </c>
+      <c r="I2139" s="32" t="s">
+        <v>8804</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2140" s="12" t="s">
+        <v>8805</v>
+      </c>
+      <c r="B2140" s="7">
+        <v>59214274</v>
+      </c>
+      <c r="C2140" s="6" t="s">
+        <v>8806</v>
+      </c>
+      <c r="D2140" s="6" t="s">
         <v>8798</v>
       </c>
-      <c r="F2135" s="1" t="s">
+      <c r="F2140" s="6" t="s">
         <v>8799</v>
       </c>
-      <c r="G2135" s="6" t="s">
-        <v>3798</v>
-      </c>
-    </row>
-    <row r="2136" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2136" s="35" t="s">
-        <v>8777</v>
-      </c>
-      <c r="B2136" s="35">
-        <v>89396770</v>
-      </c>
-      <c r="C2136" s="35" t="s">
-        <v>8789</v>
-      </c>
-      <c r="D2136" s="35" t="s">
+      <c r="G2140" s="6" t="s">
+        <v>8800</v>
+      </c>
+      <c r="H2140" s="6" t="s">
+        <v>8807</v>
+      </c>
+      <c r="I2140" s="32" t="s">
+        <v>8808</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2141" s="12" t="s">
+        <v>8809</v>
+      </c>
+      <c r="B2141" s="7">
+        <v>53137700</v>
+      </c>
+      <c r="C2141" s="6" t="s">
+        <v>8810</v>
+      </c>
+      <c r="D2141" s="6" t="s">
         <v>8798</v>
       </c>
-      <c r="F2136" s="1" t="s">
+      <c r="F2141" s="6" t="s">
         <v>8799</v>
       </c>
-      <c r="G2136" s="6" t="s">
-        <v>3798</v>
-      </c>
-    </row>
-    <row r="2137" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2137" s="35" t="s">
+      <c r="G2141" s="6" t="s">
+        <v>8800</v>
+      </c>
+      <c r="H2141" s="6" t="s">
+        <v>8811</v>
+      </c>
+      <c r="I2141" s="32" t="s">
+        <v>8812</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2142" s="12" t="s">
+        <v>8813</v>
+      </c>
+      <c r="B2142" s="7">
+        <v>84070747</v>
+      </c>
+      <c r="C2142" s="6" t="s">
+        <v>8814</v>
+      </c>
+      <c r="D2142" s="6" t="s">
         <v>8778</v>
       </c>
-      <c r="B2137" s="36" t="s">
-        <v>8773</v>
-      </c>
-      <c r="C2137" s="35" t="s">
-        <v>8790</v>
-      </c>
-      <c r="D2137" s="35" t="s">
-        <v>8798</v>
-      </c>
-      <c r="F2137" s="1" t="s">
-        <v>8799</v>
-      </c>
-      <c r="G2137" s="6" t="s">
-        <v>3798</v>
-      </c>
-    </row>
-    <row r="2138" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2138" s="35" t="s">
+      <c r="F2142" s="6" t="s">
         <v>8779</v>
       </c>
-      <c r="B2138" s="35">
-        <v>83483376</v>
-      </c>
-      <c r="C2138" s="35" t="s">
-        <v>8791</v>
-      </c>
-      <c r="D2138" s="35" t="s">
-        <v>8798</v>
-      </c>
-      <c r="F2138" s="1" t="s">
-        <v>8799</v>
-      </c>
-      <c r="G2138" s="6" t="s">
-        <v>3798</v>
-      </c>
-    </row>
-    <row r="2139" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2139" s="35" t="s">
+      <c r="G2142" s="6" t="s">
         <v>8780</v>
       </c>
-      <c r="B2139" s="35">
-        <v>28339685</v>
-      </c>
-      <c r="C2139" s="35" t="s">
-        <v>8792</v>
-      </c>
-      <c r="D2139" s="35" t="s">
-        <v>8798</v>
-      </c>
-      <c r="F2139" s="1" t="s">
-        <v>8799</v>
-      </c>
-      <c r="G2139" s="6" t="s">
-        <v>3798</v>
-      </c>
-    </row>
-    <row r="2140" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2140" s="35" t="s">
-        <v>8781</v>
-      </c>
-      <c r="B2140" s="35">
-        <v>59214274</v>
-      </c>
-      <c r="C2140" s="35" t="s">
-        <v>8793</v>
-      </c>
-      <c r="D2140" s="35" t="s">
-        <v>8798</v>
-      </c>
-      <c r="F2140" s="1" t="s">
-        <v>8799</v>
-      </c>
-      <c r="G2140" s="6" t="s">
-        <v>3798</v>
-      </c>
-    </row>
-    <row r="2141" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2141" s="35" t="s">
-        <v>8782</v>
-      </c>
-      <c r="B2141" s="35">
-        <v>53137700</v>
-      </c>
-      <c r="C2141" s="35" t="s">
-        <v>8794</v>
-      </c>
-      <c r="D2141" s="35" t="s">
-        <v>8798</v>
-      </c>
-      <c r="F2141" s="1" t="s">
-        <v>8799</v>
-      </c>
-      <c r="G2141" s="6" t="s">
-        <v>3798</v>
-      </c>
-    </row>
-    <row r="2142" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2142" s="35" t="s">
-        <v>8783</v>
-      </c>
-      <c r="B2142" s="35">
-        <v>84070747</v>
-      </c>
-      <c r="C2142" s="35" t="s">
-        <v>8795</v>
-      </c>
-      <c r="D2142" s="35" t="s">
-        <v>8798</v>
-      </c>
-      <c r="F2142" s="1" t="s">
-        <v>8799</v>
-      </c>
-      <c r="G2142" s="6" t="s">
-        <v>3798</v>
-      </c>
-    </row>
-    <row r="2143" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2143" s="35" t="s">
-        <v>8784</v>
-      </c>
-      <c r="B2143" s="35">
+      <c r="H2142" s="6" t="s">
+        <v>8815</v>
+      </c>
+      <c r="I2142" s="32" t="s">
+        <v>8816</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2143" s="12" t="s">
+        <v>8817</v>
+      </c>
+      <c r="B2143" s="7">
         <v>54135526</v>
       </c>
-      <c r="C2143" s="35" t="s">
-        <v>8796</v>
-      </c>
-      <c r="D2143" s="35" t="s">
-        <v>8798</v>
-      </c>
-      <c r="F2143" s="1" t="s">
-        <v>8799</v>
+      <c r="C2143" s="6" t="s">
+        <v>8818</v>
+      </c>
+      <c r="D2143" s="6" t="s">
+        <v>8778</v>
+      </c>
+      <c r="F2143" s="6" t="s">
+        <v>8779</v>
       </c>
       <c r="G2143" s="6" t="s">
-        <v>3798</v>
-      </c>
-    </row>
-    <row r="2144" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2144" s="35" t="s">
-        <v>8785</v>
-      </c>
-      <c r="B2144" s="35">
+        <v>8780</v>
+      </c>
+      <c r="H2143" s="6" t="s">
+        <v>8819</v>
+      </c>
+      <c r="I2143" s="32" t="s">
+        <v>8820</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2144" s="12" t="s">
+        <v>8821</v>
+      </c>
+      <c r="B2144" s="7">
         <v>16766959</v>
       </c>
-      <c r="C2144" s="35" t="s">
-        <v>8797</v>
-      </c>
-      <c r="D2144" s="35" t="s">
-        <v>8798</v>
-      </c>
-      <c r="F2144" s="1" t="s">
-        <v>8799</v>
+      <c r="C2144" s="6" t="s">
+        <v>8822</v>
+      </c>
+      <c r="D2144" s="6" t="s">
+        <v>8778</v>
+      </c>
+      <c r="F2144" s="6" t="s">
+        <v>8779</v>
       </c>
       <c r="G2144" s="6" t="s">
-        <v>3798</v>
+        <v>8780</v>
+      </c>
+      <c r="H2144" s="6" t="s">
+        <v>8823</v>
+      </c>
+      <c r="I2144" s="32" t="s">
+        <v>8824</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2022:A2033">
-    <cfRule type="duplicateValues" dxfId="40" priority="89" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="102" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2068:A2075">
-    <cfRule type="duplicateValues" dxfId="39" priority="80" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="93" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2068:B2075">
-    <cfRule type="duplicateValues" dxfId="38" priority="79" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="92" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2076:A2086">
-    <cfRule type="duplicateValues" dxfId="37" priority="63" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="76" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2076:B2086">
-    <cfRule type="duplicateValues" dxfId="36" priority="62" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="75" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2132">
-    <cfRule type="duplicateValues" dxfId="35" priority="52" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="65" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2132">
-    <cfRule type="duplicateValues" dxfId="34" priority="50" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="51" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="63" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="64" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2087">
-    <cfRule type="duplicateValues" dxfId="32" priority="49" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="62" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2087">
-    <cfRule type="duplicateValues" dxfId="31" priority="48" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="61" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2088">
-    <cfRule type="duplicateValues" dxfId="30" priority="47" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="60" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2088">
-    <cfRule type="duplicateValues" dxfId="29" priority="46" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="59" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2089">
-    <cfRule type="duplicateValues" dxfId="28" priority="45" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="58" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2089">
-    <cfRule type="duplicateValues" dxfId="27" priority="44" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="57" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2090">
-    <cfRule type="duplicateValues" dxfId="26" priority="43" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="56" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2090">
-    <cfRule type="duplicateValues" dxfId="25" priority="42" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="55" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2091">
-    <cfRule type="duplicateValues" dxfId="24" priority="41" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="54" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2091">
-    <cfRule type="duplicateValues" dxfId="23" priority="40" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="53" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2092">
-    <cfRule type="duplicateValues" dxfId="22" priority="39" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="52" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2092">
-    <cfRule type="duplicateValues" dxfId="21" priority="38" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="51" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2093">
-    <cfRule type="duplicateValues" dxfId="20" priority="37" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="50" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2093">
-    <cfRule type="duplicateValues" dxfId="19" priority="36" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="49" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2094">
-    <cfRule type="duplicateValues" dxfId="18" priority="35" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="48" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2094">
-    <cfRule type="duplicateValues" dxfId="17" priority="34" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="47" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2095">
-    <cfRule type="duplicateValues" dxfId="16" priority="33" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="46" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2095">
-    <cfRule type="duplicateValues" dxfId="15" priority="32" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="45" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2096:A2099">
-    <cfRule type="duplicateValues" dxfId="14" priority="28" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="41" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2096:B2099">
-    <cfRule type="duplicateValues" dxfId="13" priority="27" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="40" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2100:A2107">
-    <cfRule type="duplicateValues" dxfId="12" priority="20" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="33" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2100:B2107">
-    <cfRule type="duplicateValues" dxfId="11" priority="19" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="32" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2145:A65536 A2123 A2034:A2067 A1:A2021">
-    <cfRule type="duplicateValues" dxfId="10" priority="90" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="103" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2145:B65536 B2123 B1:B2067">
-    <cfRule type="duplicateValues" dxfId="9" priority="95" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="108" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2108:A2115">
-    <cfRule type="duplicateValues" dxfId="8" priority="15" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="28" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2108:B2115">
-    <cfRule type="duplicateValues" dxfId="7" priority="14" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="27" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2116:A2122">
+    <cfRule type="duplicateValues" dxfId="13" priority="23" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2116:B2122">
+    <cfRule type="duplicateValues" dxfId="12" priority="22" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2124:A2131">
+    <cfRule type="duplicateValues" dxfId="11" priority="18" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2124:B2131">
+    <cfRule type="duplicateValues" dxfId="10" priority="17" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2133">
+    <cfRule type="duplicateValues" dxfId="9" priority="13" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2133">
+    <cfRule type="duplicateValues" dxfId="8" priority="12" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2134">
+    <cfRule type="duplicateValues" dxfId="7" priority="11" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2134">
     <cfRule type="duplicateValues" dxfId="6" priority="10" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2116:B2122">
+  <conditionalFormatting sqref="A2135">
     <cfRule type="duplicateValues" dxfId="5" priority="9" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2124:A2131">
-    <cfRule type="duplicateValues" dxfId="4" priority="5" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2135">
+    <cfRule type="duplicateValues" dxfId="4" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2124:B2131">
+  <conditionalFormatting sqref="A2136:A2141">
     <cfRule type="duplicateValues" dxfId="3" priority="4" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2133:B2144">
+  <conditionalFormatting sqref="B2136:B2141">
     <cfRule type="duplicateValues" dxfId="2" priority="3" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2133:B2144">
-    <cfRule type="duplicateValues" dxfId="1" priority="1" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2142:A2144">
+    <cfRule type="duplicateValues" dxfId="1" priority="2" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2142:B2144">
+    <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1190:G1200 G314:G674 G676:G703 G251:G312 G705:G1187 G2:G249">

--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12111" uniqueCount="8825">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12115" uniqueCount="8829">
   <si>
     <t>麒安科技有限公司</t>
   </si>
@@ -31173,6 +31173,22 @@
   </si>
   <si>
     <t>1601/林小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>84521378</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WBBL2025024165</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119.02.21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聯新電子股份有限公司</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -32195,7 +32211,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:J2144"/>
+  <dimension ref="A1:J2145"/>
   <sheetFormatPr defaultRowHeight="21.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" style="5" customWidth="1"/>
@@ -73830,6 +73846,20 @@
       </c>
       <c r="I2144" s="32" t="s">
         <v>8824</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A2145" s="5" t="s">
+        <v>8828</v>
+      </c>
+      <c r="B2145" s="3" t="s">
+        <v>8825</v>
+      </c>
+      <c r="C2145" s="1" t="s">
+        <v>8826</v>
+      </c>
+      <c r="D2145" s="1" t="s">
+        <v>8827</v>
       </c>
     </row>
   </sheetData>

--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12115" uniqueCount="8829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12352" uniqueCount="8982">
   <si>
     <t>麒安科技有限公司</t>
   </si>
@@ -31176,20 +31176,475 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>84521378</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>淩雲科技股份有限公司</t>
+  </si>
+  <si>
+    <t>嘉和半導體股份有限公司</t>
+  </si>
+  <si>
+    <t>嘉達企業有限公司</t>
+  </si>
+  <si>
+    <t>育林有限公司</t>
+  </si>
+  <si>
+    <t>坤載企業有限公司</t>
+  </si>
+  <si>
+    <t>乙威科技國際有限公司</t>
+  </si>
+  <si>
+    <t>華新科技股份有限公司</t>
+  </si>
+  <si>
+    <t>上益旺股份有限公司</t>
+  </si>
+  <si>
+    <t>聯新電子股份有限公司</t>
+  </si>
+  <si>
+    <t>加高電子股份有限公司</t>
+  </si>
+  <si>
+    <t>毅騰科技有限公司</t>
+  </si>
+  <si>
+    <t>東捷科技股份有限公司</t>
+  </si>
+  <si>
+    <t>富祐鴻科技股份有限公司</t>
+  </si>
+  <si>
+    <t>宇仁醫療器材科技股份有限公司</t>
+  </si>
+  <si>
+    <t>華通儀器股份有限公司</t>
+  </si>
+  <si>
+    <t>百甯股份有限公司</t>
+  </si>
+  <si>
+    <t>台灣特洛奇資訊有限公司</t>
+  </si>
+  <si>
+    <t>尚立光電股份有限公司</t>
+  </si>
+  <si>
+    <t>海昌電子股份有限公司</t>
+  </si>
+  <si>
+    <t>前源科技股份有限公司</t>
+  </si>
+  <si>
+    <t>凰騰股份有限公司</t>
+  </si>
+  <si>
+    <t>晶遠光學工程股份有限公司</t>
+  </si>
+  <si>
+    <t>聯恩電子有限公司</t>
+  </si>
+  <si>
+    <t>嵩富機械廠股份有限公司</t>
+  </si>
+  <si>
+    <t>方見科技股份有限公司</t>
+  </si>
+  <si>
+    <t>宜星科技有限公司</t>
+  </si>
+  <si>
+    <t>易智聯有限公司</t>
+  </si>
+  <si>
+    <t>奈司特技術股份有限公司</t>
+  </si>
+  <si>
+    <t>香港商施華洛世奇有限公司台灣分公司</t>
+  </si>
+  <si>
+    <t>漢鈞科技股份有限公司</t>
+  </si>
+  <si>
+    <t>捷科泰亞股份有限公司</t>
+  </si>
+  <si>
+    <t>凌智博爾股份有限公司</t>
+  </si>
+  <si>
+    <t>貫旭企業有限公司</t>
+  </si>
+  <si>
+    <t>御頂科技有限公司</t>
+  </si>
+  <si>
+    <t>安富利科技股份有限公司</t>
+  </si>
+  <si>
+    <t>鼎豐技研有限公司</t>
+  </si>
+  <si>
+    <t>凌巨科技股份有限公司</t>
+  </si>
+  <si>
+    <t>紳泰科技股份有限公司</t>
+  </si>
+  <si>
+    <t>香港商美康雅香港有限公司台灣分公司</t>
+  </si>
+  <si>
+    <t>盈助興業股份有限公司</t>
+  </si>
+  <si>
+    <t>文顥電子股份有限公司</t>
+  </si>
+  <si>
+    <t>合鈺科技有限公司</t>
+  </si>
+  <si>
+    <t>立方航電股份有限公司</t>
+  </si>
+  <si>
+    <t>台星科股份有限公司</t>
+  </si>
+  <si>
+    <t>翱昇科技股份有限公司</t>
+  </si>
+  <si>
+    <t>信廣精密機械維修有限公司</t>
+  </si>
+  <si>
+    <t>大賽璐台灣股份有限公司</t>
+  </si>
+  <si>
+    <t>元晶太陽能科技股份有限公司</t>
+  </si>
+  <si>
+    <t>孫維陽</t>
+  </si>
+  <si>
+    <t>亞琦化粧品股份有限公司</t>
+  </si>
+  <si>
+    <t>大銀微系統股份有限公司</t>
+  </si>
+  <si>
+    <t>中南創發股份有限公司</t>
+  </si>
+  <si>
+    <t>亞奇雷科技股份有限公司</t>
+  </si>
+  <si>
+    <t>威力沛科技有限公司</t>
+  </si>
+  <si>
+    <t>將大科技股份有限公司</t>
+  </si>
+  <si>
+    <t>復成船舶機械工程有限公司</t>
+  </si>
+  <si>
+    <t>美喆國際企業股份有限公司</t>
+  </si>
+  <si>
+    <t>F125449741</t>
+  </si>
+  <si>
+    <t>WBBL2025034477</t>
+  </si>
+  <si>
+    <t>WBBL2025034436</t>
+  </si>
+  <si>
+    <t>WBBL2025034325</t>
+  </si>
+  <si>
+    <t>WBBL2025034264</t>
+  </si>
+  <si>
+    <t>WBBL2025024228</t>
+  </si>
+  <si>
+    <t>WBBL2025024229</t>
+  </si>
+  <si>
+    <t>WBBL2025024164</t>
   </si>
   <si>
     <t>WBBL2025024165</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WBBL2025013888</t>
+  </si>
+  <si>
+    <t>WBBL2025013870</t>
+  </si>
+  <si>
+    <t>WBBL2025013833</t>
+  </si>
+  <si>
+    <t>WBBL2025013795</t>
+  </si>
+  <si>
+    <t>WBBL2025013598</t>
+  </si>
+  <si>
+    <t>WBBL2024123183</t>
+  </si>
+  <si>
+    <t>WBBL2024123130</t>
+  </si>
+  <si>
+    <t>WBBL2024123074</t>
+  </si>
+  <si>
+    <t>WBBL2024112998</t>
+  </si>
+  <si>
+    <t>WBBL2024112997</t>
+  </si>
+  <si>
+    <t>WBBL2024112813</t>
+  </si>
+  <si>
+    <t>WBBL2024112739</t>
+  </si>
+  <si>
+    <t>WBBL2024112740</t>
+  </si>
+  <si>
+    <t>WBBL2024112741</t>
+  </si>
+  <si>
+    <t>WBBL2024112614</t>
+  </si>
+  <si>
+    <t>WBBL2024102306</t>
+  </si>
+  <si>
+    <t>WBBL2024102235</t>
+  </si>
+  <si>
+    <t>WBBL2024091878</t>
+  </si>
+  <si>
+    <t>WBBL2024091837</t>
+  </si>
+  <si>
+    <t>WBBL2024081763</t>
+  </si>
+  <si>
+    <t>WBBL2024081711</t>
+  </si>
+  <si>
+    <t>WBBL2024061101</t>
+  </si>
+  <si>
+    <t>WBBL2024061055</t>
+  </si>
+  <si>
+    <t>WBBL2024060914</t>
+  </si>
+  <si>
+    <t>WBBL2024060915</t>
+  </si>
+  <si>
+    <t>WBBL2024050777</t>
+  </si>
+  <si>
+    <t>WBBL2024050778</t>
+  </si>
+  <si>
+    <t>WBBL2024050671</t>
+  </si>
+  <si>
+    <t>WBBL2024050620</t>
+  </si>
+  <si>
+    <t>WBBL2024040260</t>
+  </si>
+  <si>
+    <t>WBBL2024030020</t>
+  </si>
+  <si>
+    <t>WBBL2024039983</t>
+  </si>
+  <si>
+    <t>WBBL2024029667</t>
+  </si>
+  <si>
+    <t>WBBL2024029642</t>
+  </si>
+  <si>
+    <t>WBBL2024029641</t>
+  </si>
+  <si>
+    <t>WBBL2024029640</t>
+  </si>
+  <si>
+    <t>WBBL2024029614</t>
+  </si>
+  <si>
+    <t>WBBL2024029599</t>
+  </si>
+  <si>
+    <t>WBBL2024029467</t>
+  </si>
+  <si>
+    <t>WBBL2024029414</t>
+  </si>
+  <si>
+    <t>WBBL2023128762</t>
+  </si>
+  <si>
+    <t>WBBL2023128499</t>
+  </si>
+  <si>
+    <t>WBBL2023128457</t>
+  </si>
+  <si>
+    <t>WBBL2023128458</t>
+  </si>
+  <si>
+    <t>WBBL2023035347</t>
+  </si>
+  <si>
+    <t>WBBL2023035236</t>
+  </si>
+  <si>
+    <t>WBBL2023025143</t>
+  </si>
+  <si>
+    <t>WBBL2022124551</t>
+  </si>
+  <si>
+    <t>WBBL2022113770</t>
+  </si>
+  <si>
+    <t>119.03.18</t>
+  </si>
+  <si>
+    <t>119.03.23</t>
+  </si>
+  <si>
+    <t>119.03.10</t>
+  </si>
+  <si>
+    <t>118.03.06</t>
+  </si>
+  <si>
+    <t>119.02.26</t>
+  </si>
+  <si>
+    <t>119.03.20</t>
+  </si>
+  <si>
+    <t>119.01.31</t>
   </si>
   <si>
     <t>119.02.21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>聯新電子股份有限公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119.01.24</t>
+  </si>
+  <si>
+    <t>119.01.22</t>
+  </si>
+  <si>
+    <t>119.01.21</t>
+  </si>
+  <si>
+    <t>119.01.16</t>
+  </si>
+  <si>
+    <t>119.01.04</t>
+  </si>
+  <si>
+    <t>114.12.10</t>
+  </si>
+  <si>
+    <t>118.12.04</t>
+  </si>
+  <si>
+    <t>118.11.30</t>
+  </si>
+  <si>
+    <t>118.11.12</t>
+  </si>
+  <si>
+    <t>118.11.07</t>
+  </si>
+  <si>
+    <t>117.10.11</t>
+  </si>
+  <si>
+    <t>118.11.05</t>
+  </si>
+  <si>
+    <t>118.09.06</t>
+  </si>
+  <si>
+    <t>118.09.18</t>
+  </si>
+  <si>
+    <t>114.08.22</t>
+  </si>
+  <si>
+    <t>118.06.28</t>
+  </si>
+  <si>
+    <t>118.06.24</t>
+  </si>
+  <si>
+    <t>115.12.29</t>
+  </si>
+  <si>
+    <t>118.06.11</t>
+  </si>
+  <si>
+    <t>115.05.16</t>
+  </si>
+  <si>
+    <t>118.04.16</t>
+  </si>
+  <si>
+    <t>118.02.27</t>
+  </si>
+  <si>
+    <t>118.03.07</t>
+  </si>
+  <si>
+    <t>114.02.26</t>
+  </si>
+  <si>
+    <t>118.02.23</t>
+  </si>
+  <si>
+    <t>117.07.07</t>
+  </si>
+  <si>
+    <t>118.02.17</t>
+  </si>
+  <si>
+    <t>118.02.04</t>
+  </si>
+  <si>
+    <t>117.12.10</t>
+  </si>
+  <si>
+    <t>113.12.31</t>
+  </si>
+  <si>
+    <t>117.03.08</t>
+  </si>
+  <si>
+    <t>117.02.28</t>
+  </si>
+  <si>
+    <t>116.02.20</t>
+  </si>
+  <si>
+    <t>112.12.31</t>
   </si>
 </sst>
 </file>
@@ -32211,7 +32666,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:J2145"/>
+  <dimension ref="A1:J2204"/>
   <sheetFormatPr defaultRowHeight="21.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" style="5" customWidth="1"/>
@@ -73848,18 +74303,1024 @@
         <v>8824</v>
       </c>
     </row>
-    <row r="2145" spans="1:4" ht="21.95" customHeight="1">
+    <row r="2145" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2145" s="5" t="s">
+        <v>8825</v>
+      </c>
+      <c r="B2145" s="3">
+        <v>13025089</v>
+      </c>
+      <c r="C2145" s="1" t="s">
+        <v>8883</v>
+      </c>
+      <c r="D2145" s="1" t="s">
+        <v>8940</v>
+      </c>
+      <c r="E2145" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2146" s="5" t="s">
+        <v>8826</v>
+      </c>
+      <c r="B2146" s="3">
+        <v>42942664</v>
+      </c>
+      <c r="C2146" s="1" t="s">
+        <v>8884</v>
+      </c>
+      <c r="D2146" s="1" t="s">
+        <v>8941</v>
+      </c>
+      <c r="E2146" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2147" s="5" t="s">
+        <v>8827</v>
+      </c>
+      <c r="B2147" s="3">
+        <v>90895471</v>
+      </c>
+      <c r="C2147" s="1" t="s">
+        <v>8885</v>
+      </c>
+      <c r="D2147" s="1" t="s">
+        <v>8942</v>
+      </c>
+      <c r="E2147" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2148" s="5" t="s">
         <v>8828</v>
       </c>
-      <c r="B2145" s="3" t="s">
-        <v>8825</v>
-      </c>
-      <c r="C2145" s="1" t="s">
-        <v>8826</v>
-      </c>
-      <c r="D2145" s="1" t="s">
-        <v>8827</v>
+      <c r="B2148" s="3">
+        <v>30926062</v>
+      </c>
+      <c r="C2148" s="1" t="s">
+        <v>8886</v>
+      </c>
+      <c r="D2148" s="1" t="s">
+        <v>8943</v>
+      </c>
+      <c r="E2148" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2149" s="5" t="s">
+        <v>8829</v>
+      </c>
+      <c r="B2149" s="3">
+        <v>90780816</v>
+      </c>
+      <c r="C2149" s="1" t="s">
+        <v>8887</v>
+      </c>
+      <c r="D2149" s="1" t="s">
+        <v>8944</v>
+      </c>
+      <c r="E2149" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2150" s="5" t="s">
+        <v>8830</v>
+      </c>
+      <c r="B2150" s="3">
+        <v>54252501</v>
+      </c>
+      <c r="C2150" s="1" t="s">
+        <v>8888</v>
+      </c>
+      <c r="D2150" s="1" t="s">
+        <v>8945</v>
+      </c>
+      <c r="E2150" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2151" s="5" t="s">
+        <v>8832</v>
+      </c>
+      <c r="B2151" s="3">
+        <v>83591516</v>
+      </c>
+      <c r="C2151" s="1" t="s">
+        <v>8889</v>
+      </c>
+      <c r="D2151" s="1" t="s">
+        <v>8946</v>
+      </c>
+      <c r="E2151" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2152" s="5" t="s">
+        <v>8833</v>
+      </c>
+      <c r="B2152" s="3">
+        <v>84521378</v>
+      </c>
+      <c r="C2152" s="1" t="s">
+        <v>8890</v>
+      </c>
+      <c r="D2152" s="1" t="s">
+        <v>8947</v>
+      </c>
+      <c r="E2152" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2153" s="5" t="s">
+        <v>8834</v>
+      </c>
+      <c r="B2153" s="3">
+        <v>75914885</v>
+      </c>
+      <c r="C2153" s="1" t="s">
+        <v>8891</v>
+      </c>
+      <c r="D2153" s="1" t="s">
+        <v>8948</v>
+      </c>
+      <c r="E2153" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2154" s="5" t="s">
+        <v>8835</v>
+      </c>
+      <c r="B2154" s="3">
+        <v>85091972</v>
+      </c>
+      <c r="C2154" s="1" t="s">
+        <v>8892</v>
+      </c>
+      <c r="D2154" s="1" t="s">
+        <v>8949</v>
+      </c>
+      <c r="E2154" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2155" s="5" t="s">
+        <v>8836</v>
+      </c>
+      <c r="B2155" s="3">
+        <v>16491312</v>
+      </c>
+      <c r="C2155" s="1" t="s">
+        <v>8893</v>
+      </c>
+      <c r="D2155" s="1" t="s">
+        <v>8950</v>
+      </c>
+      <c r="E2155" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2156" s="5" t="s">
+        <v>8837</v>
+      </c>
+      <c r="B2156" s="3">
+        <v>89649769</v>
+      </c>
+      <c r="C2156" s="1" t="s">
+        <v>8894</v>
+      </c>
+      <c r="D2156" s="1" t="s">
+        <v>8951</v>
+      </c>
+      <c r="E2156" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2157" s="5" t="s">
+        <v>8838</v>
+      </c>
+      <c r="B2157" s="3">
+        <v>16980249</v>
+      </c>
+      <c r="C2157" s="1" t="s">
+        <v>8895</v>
+      </c>
+      <c r="D2157" s="1" t="s">
+        <v>8952</v>
+      </c>
+      <c r="E2157" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2158" s="5" t="s">
+        <v>8839</v>
+      </c>
+      <c r="B2158" s="3">
+        <v>16690537</v>
+      </c>
+      <c r="C2158" s="1" t="s">
+        <v>8896</v>
+      </c>
+      <c r="D2158" s="1" t="s">
+        <v>8953</v>
+      </c>
+      <c r="E2158" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2159" s="5" t="s">
+        <v>8840</v>
+      </c>
+      <c r="B2159" s="3">
+        <v>42751762</v>
+      </c>
+      <c r="C2159" s="1" t="s">
+        <v>8897</v>
+      </c>
+      <c r="D2159" s="1" t="s">
+        <v>4169</v>
+      </c>
+      <c r="E2159" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2160" s="5" t="s">
+        <v>8841</v>
+      </c>
+      <c r="B2160" s="3">
+        <v>54705407</v>
+      </c>
+      <c r="C2160" s="1" t="s">
+        <v>8898</v>
+      </c>
+      <c r="D2160" s="1" t="s">
+        <v>8954</v>
+      </c>
+      <c r="E2160" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2161" s="5" t="s">
+        <v>8842</v>
+      </c>
+      <c r="B2161" s="3">
+        <v>24439184</v>
+      </c>
+      <c r="C2161" s="1" t="s">
+        <v>8890</v>
+      </c>
+      <c r="D2161" s="1" t="s">
+        <v>8947</v>
+      </c>
+      <c r="E2161" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2162" s="5" t="s">
+        <v>8843</v>
+      </c>
+      <c r="B2162" s="3">
+        <v>81464351</v>
+      </c>
+      <c r="C2162" s="1" t="s">
+        <v>8899</v>
+      </c>
+      <c r="D2162" s="1" t="s">
+        <v>4169</v>
+      </c>
+      <c r="E2162" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2163" s="5" t="s">
+        <v>8843</v>
+      </c>
+      <c r="B2163" s="3">
+        <v>81464351</v>
+      </c>
+      <c r="C2163" s="1" t="s">
+        <v>8900</v>
+      </c>
+      <c r="D2163" s="1" t="s">
+        <v>4169</v>
+      </c>
+      <c r="E2163" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2164" s="5" t="s">
+        <v>8844</v>
+      </c>
+      <c r="B2164" s="3">
+        <v>70803848</v>
+      </c>
+      <c r="C2164" s="1" t="s">
+        <v>8901</v>
+      </c>
+      <c r="D2164" s="1" t="s">
+        <v>8955</v>
+      </c>
+      <c r="E2164" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2165" s="5" t="s">
+        <v>8845</v>
+      </c>
+      <c r="B2165" s="3">
+        <v>83222751</v>
+      </c>
+      <c r="C2165" s="1" t="s">
+        <v>8902</v>
+      </c>
+      <c r="D2165" s="1" t="s">
+        <v>4169</v>
+      </c>
+      <c r="E2165" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2166" s="5" t="s">
+        <v>8846</v>
+      </c>
+      <c r="B2166" s="3">
+        <v>89819285</v>
+      </c>
+      <c r="C2166" s="1" t="s">
+        <v>8903</v>
+      </c>
+      <c r="D2166" s="1" t="s">
+        <v>8956</v>
+      </c>
+      <c r="E2166" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2167" s="5" t="s">
+        <v>8847</v>
+      </c>
+      <c r="B2167" s="3">
+        <v>28102979</v>
+      </c>
+      <c r="C2167" s="1" t="s">
+        <v>8904</v>
+      </c>
+      <c r="D2167" s="1" t="s">
+        <v>8956</v>
+      </c>
+      <c r="E2167" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2168" s="5" t="s">
+        <v>8848</v>
+      </c>
+      <c r="B2168" s="3">
+        <v>55841816</v>
+      </c>
+      <c r="C2168" s="1" t="s">
+        <v>8905</v>
+      </c>
+      <c r="D2168" s="1" t="s">
+        <v>8957</v>
+      </c>
+      <c r="E2168" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2169" s="5" t="s">
+        <v>8849</v>
+      </c>
+      <c r="B2169" s="3">
+        <v>90369060</v>
+      </c>
+      <c r="C2169" s="1" t="s">
+        <v>8890</v>
+      </c>
+      <c r="D2169" s="1" t="s">
+        <v>8947</v>
+      </c>
+      <c r="E2169" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2170" s="5" t="s">
+        <v>8850</v>
+      </c>
+      <c r="B2170" s="3">
+        <v>24775171</v>
+      </c>
+      <c r="C2170" s="1" t="s">
+        <v>8906</v>
+      </c>
+      <c r="D2170" s="1" t="s">
+        <v>8958</v>
+      </c>
+      <c r="E2170" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2171" s="5" t="s">
+        <v>8851</v>
+      </c>
+      <c r="B2171" s="3">
+        <v>54979243</v>
+      </c>
+      <c r="C2171" s="1" t="s">
+        <v>8907</v>
+      </c>
+      <c r="D2171" s="1" t="s">
+        <v>8959</v>
+      </c>
+      <c r="E2171" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2172" s="5" t="s">
+        <v>8852</v>
+      </c>
+      <c r="B2172" s="3">
+        <v>54127434</v>
+      </c>
+      <c r="C2172" s="1" t="s">
+        <v>8908</v>
+      </c>
+      <c r="D2172" s="1" t="s">
+        <v>8960</v>
+      </c>
+      <c r="E2172" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2173" s="5" t="s">
+        <v>8853</v>
+      </c>
+      <c r="B2173" s="3">
+        <v>70757485</v>
+      </c>
+      <c r="C2173" s="1" t="s">
+        <v>8909</v>
+      </c>
+      <c r="D2173" s="1" t="s">
+        <v>8961</v>
+      </c>
+      <c r="E2173" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2174" s="5" t="s">
+        <v>8854</v>
+      </c>
+      <c r="B2174" s="3">
+        <v>53288988</v>
+      </c>
+      <c r="C2174" s="1" t="s">
+        <v>8910</v>
+      </c>
+      <c r="D2174" s="1" t="s">
+        <v>8962</v>
+      </c>
+      <c r="E2174" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2175" s="5" t="s">
+        <v>8855</v>
+      </c>
+      <c r="B2175" s="3">
+        <v>12661194</v>
+      </c>
+      <c r="C2175" s="1" t="s">
+        <v>8911</v>
+      </c>
+      <c r="D2175" s="1" t="s">
+        <v>4955</v>
+      </c>
+      <c r="E2175" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2176" s="5" t="s">
+        <v>8856</v>
+      </c>
+      <c r="B2176" s="3">
+        <v>66632506</v>
+      </c>
+      <c r="C2176" s="1" t="s">
+        <v>8890</v>
+      </c>
+      <c r="D2176" s="1" t="s">
+        <v>8947</v>
+      </c>
+      <c r="E2176" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2177" s="5" t="s">
+        <v>8857</v>
+      </c>
+      <c r="B2177" s="3">
+        <v>28589212</v>
+      </c>
+      <c r="C2177" s="1" t="s">
+        <v>8912</v>
+      </c>
+      <c r="D2177" s="1" t="s">
+        <v>8963</v>
+      </c>
+      <c r="E2177" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2178" s="5" t="s">
+        <v>8858</v>
+      </c>
+      <c r="B2178" s="3">
+        <v>24714891</v>
+      </c>
+      <c r="C2178" s="1" t="s">
+        <v>8913</v>
+      </c>
+      <c r="D2178" s="1" t="s">
+        <v>8964</v>
+      </c>
+      <c r="E2178" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2179" s="5" t="s">
+        <v>8859</v>
+      </c>
+      <c r="B2179" s="3">
+        <v>89405911</v>
+      </c>
+      <c r="C2179" s="1" t="s">
+        <v>8914</v>
+      </c>
+      <c r="D2179" s="1" t="s">
+        <v>8965</v>
+      </c>
+      <c r="E2179" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2180" s="5" t="s">
+        <v>8860</v>
+      </c>
+      <c r="B2180" s="3">
+        <v>54786196</v>
+      </c>
+      <c r="C2180" s="1" t="s">
+        <v>8915</v>
+      </c>
+      <c r="D2180" s="1" t="s">
+        <v>8966</v>
+      </c>
+      <c r="E2180" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2181" s="5" t="s">
+        <v>8861</v>
+      </c>
+      <c r="B2181" s="3">
+        <v>16432742</v>
+      </c>
+      <c r="C2181" s="1" t="s">
+        <v>8916</v>
+      </c>
+      <c r="D2181" s="1" t="s">
+        <v>5049</v>
+      </c>
+      <c r="E2181" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2182" s="5" t="s">
+        <v>8861</v>
+      </c>
+      <c r="B2182" s="3">
+        <v>16432742</v>
+      </c>
+      <c r="C2182" s="1" t="s">
+        <v>8917</v>
+      </c>
+      <c r="D2182" s="1" t="s">
+        <v>5049</v>
+      </c>
+      <c r="E2182" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2183" s="5" t="s">
+        <v>8862</v>
+      </c>
+      <c r="B2183" s="3">
+        <v>50787813</v>
+      </c>
+      <c r="C2183" s="1" t="s">
+        <v>8918</v>
+      </c>
+      <c r="D2183" s="1" t="s">
+        <v>8967</v>
+      </c>
+      <c r="E2183" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2184" s="5" t="s">
+        <v>8863</v>
+      </c>
+      <c r="B2184" s="3">
+        <v>54378282</v>
+      </c>
+      <c r="C2184" s="1" t="s">
+        <v>8919</v>
+      </c>
+      <c r="D2184" s="1" t="s">
+        <v>7063</v>
+      </c>
+      <c r="E2184" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2185" s="5" t="s">
+        <v>8864</v>
+      </c>
+      <c r="B2185" s="3">
+        <v>59196156</v>
+      </c>
+      <c r="C2185" s="1" t="s">
+        <v>8920</v>
+      </c>
+      <c r="D2185" s="1" t="s">
+        <v>8968</v>
+      </c>
+      <c r="E2185" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2186" s="5" t="s">
+        <v>8865</v>
+      </c>
+      <c r="B2186" s="3">
+        <v>96860766</v>
+      </c>
+      <c r="C2186" s="1" t="s">
+        <v>8921</v>
+      </c>
+      <c r="D2186" s="1" t="s">
+        <v>6741</v>
+      </c>
+      <c r="E2186" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2187" s="5" t="s">
+        <v>8866</v>
+      </c>
+      <c r="B2187" s="3">
+        <v>93626394</v>
+      </c>
+      <c r="C2187" s="1" t="s">
+        <v>8922</v>
+      </c>
+      <c r="D2187" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E2187" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2188" s="5" t="s">
+        <v>8867</v>
+      </c>
+      <c r="B2188" s="3">
+        <v>93624327</v>
+      </c>
+      <c r="C2188" s="1" t="s">
+        <v>8923</v>
+      </c>
+      <c r="D2188" s="1" t="s">
+        <v>8969</v>
+      </c>
+      <c r="E2188" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2189" s="5" t="s">
+        <v>8868</v>
+      </c>
+      <c r="B2189" s="3">
+        <v>70552666</v>
+      </c>
+      <c r="C2189" s="1" t="s">
+        <v>8924</v>
+      </c>
+      <c r="D2189" s="1" t="s">
+        <v>8970</v>
+      </c>
+      <c r="E2189" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2190" s="5" t="s">
+        <v>8868</v>
+      </c>
+      <c r="B2190" s="3">
+        <v>70552666</v>
+      </c>
+      <c r="C2190" s="1" t="s">
+        <v>8925</v>
+      </c>
+      <c r="D2190" s="1" t="s">
+        <v>8970</v>
+      </c>
+      <c r="E2190" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2191" s="5" t="s">
+        <v>8869</v>
+      </c>
+      <c r="B2191" s="3">
+        <v>54861011</v>
+      </c>
+      <c r="C2191" s="1" t="s">
+        <v>8926</v>
+      </c>
+      <c r="D2191" s="1" t="s">
+        <v>8971</v>
+      </c>
+      <c r="E2191" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2192" s="5" t="s">
+        <v>8870</v>
+      </c>
+      <c r="B2192" s="3">
+        <v>42777783</v>
+      </c>
+      <c r="C2192" s="1" t="s">
+        <v>8927</v>
+      </c>
+      <c r="D2192" s="1" t="s">
+        <v>8972</v>
+      </c>
+      <c r="E2192" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2193" s="5" t="s">
+        <v>8871</v>
+      </c>
+      <c r="B2193" s="3">
+        <v>42986774</v>
+      </c>
+      <c r="C2193" s="1" t="s">
+        <v>8928</v>
+      </c>
+      <c r="D2193" s="1" t="s">
+        <v>8973</v>
+      </c>
+      <c r="E2193" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2194" s="5" t="s">
+        <v>8872</v>
+      </c>
+      <c r="B2194" s="3">
+        <v>28997300</v>
+      </c>
+      <c r="C2194" s="1" t="s">
+        <v>8929</v>
+      </c>
+      <c r="D2194" s="1" t="s">
+        <v>8974</v>
+      </c>
+      <c r="E2194" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2195" s="5" t="s">
+        <v>8873</v>
+      </c>
+      <c r="B2195" s="3" t="s">
+        <v>8882</v>
+      </c>
+      <c r="C2195" s="1" t="s">
+        <v>8930</v>
+      </c>
+      <c r="D2195" s="1" t="s">
+        <v>8975</v>
+      </c>
+      <c r="E2195" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2196" s="5" t="s">
+        <v>8874</v>
+      </c>
+      <c r="B2196" s="3">
+        <v>1879651</v>
+      </c>
+      <c r="C2196" s="1" t="s">
+        <v>8931</v>
+      </c>
+      <c r="D2196" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E2196" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2197" s="5" t="s">
+        <v>8875</v>
+      </c>
+      <c r="B2197" s="3">
+        <v>97413843</v>
+      </c>
+      <c r="C2197" s="1" t="s">
+        <v>8932</v>
+      </c>
+      <c r="D2197" s="1" t="s">
+        <v>8976</v>
+      </c>
+      <c r="E2197" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2198" s="5" t="s">
+        <v>8876</v>
+      </c>
+      <c r="B2198" s="3">
+        <v>53110738</v>
+      </c>
+      <c r="C2198" s="1" t="s">
+        <v>8933</v>
+      </c>
+      <c r="D2198" s="1" t="s">
+        <v>8977</v>
+      </c>
+      <c r="E2198" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2199" s="5" t="s">
+        <v>8877</v>
+      </c>
+      <c r="B2199" s="3">
+        <v>50890128</v>
+      </c>
+      <c r="C2199" s="1" t="s">
+        <v>8934</v>
+      </c>
+      <c r="D2199" s="1" t="s">
+        <v>6015</v>
+      </c>
+      <c r="E2199" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2200" s="5" t="s">
+        <v>8878</v>
+      </c>
+      <c r="B2200" s="3">
+        <v>54223936</v>
+      </c>
+      <c r="C2200" s="1" t="s">
+        <v>8935</v>
+      </c>
+      <c r="D2200" s="1" t="s">
+        <v>8978</v>
+      </c>
+      <c r="E2200" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2201" s="5" t="s">
+        <v>8879</v>
+      </c>
+      <c r="B2201" s="3">
+        <v>83479268</v>
+      </c>
+      <c r="C2201" s="1" t="s">
+        <v>8936</v>
+      </c>
+      <c r="D2201" s="1" t="s">
+        <v>8979</v>
+      </c>
+      <c r="E2201" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2202" s="5" t="s">
+        <v>8880</v>
+      </c>
+      <c r="B2202" s="3">
+        <v>22298960</v>
+      </c>
+      <c r="C2202" s="1" t="s">
+        <v>8937</v>
+      </c>
+      <c r="D2202" s="1" t="s">
+        <v>8980</v>
+      </c>
+      <c r="E2202" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2203" s="5" t="s">
+        <v>8831</v>
+      </c>
+      <c r="B2203" s="3">
+        <v>19004316</v>
+      </c>
+      <c r="C2203" s="1" t="s">
+        <v>8938</v>
+      </c>
+      <c r="D2203" s="1" t="s">
+        <v>8981</v>
+      </c>
+      <c r="E2203" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A2204" s="5" t="s">
+        <v>8881</v>
+      </c>
+      <c r="B2204" s="3">
+        <v>30974752</v>
+      </c>
+      <c r="C2204" s="1" t="s">
+        <v>8939</v>
+      </c>
+      <c r="D2204" s="1" t="s">
+        <v>5872</v>
+      </c>
+      <c r="E2204" s="1" t="s">
+        <v>3940</v>
       </c>
     </row>
   </sheetData>

--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12352" uniqueCount="8982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12377" uniqueCount="8994">
   <si>
     <t>麒安科技有限公司</t>
   </si>
@@ -31645,6 +31645,45 @@
   </si>
   <si>
     <t>112.12.31</t>
+  </si>
+  <si>
+    <t>星騏國際有限公司</t>
+  </si>
+  <si>
+    <t>東庚企業股份有限公司</t>
+  </si>
+  <si>
+    <t>精聯電子股份有限公司</t>
+  </si>
+  <si>
+    <t>貿連科技有限公司</t>
+  </si>
+  <si>
+    <t>114業二06277</t>
+  </si>
+  <si>
+    <t>114業二06278</t>
+  </si>
+  <si>
+    <t>114業二06279</t>
+  </si>
+  <si>
+    <t>114業二06280</t>
+  </si>
+  <si>
+    <t>114業二06281</t>
+  </si>
+  <si>
+    <t>119.04.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119.04.07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114.04.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -31887,7 +31926,27 @@
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="48">
+  <dxfs count="50">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -32666,7 +32725,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:J2204"/>
+  <dimension ref="A1:J2209"/>
   <sheetFormatPr defaultRowHeight="21.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" style="5" customWidth="1"/>
@@ -75119,7 +75178,7 @@
         <v>3940</v>
       </c>
     </row>
-    <row r="2193" spans="1:5" ht="21.95" customHeight="1">
+    <row r="2193" spans="1:7" ht="21.95" customHeight="1">
       <c r="A2193" s="5" t="s">
         <v>8871</v>
       </c>
@@ -75136,7 +75195,7 @@
         <v>3940</v>
       </c>
     </row>
-    <row r="2194" spans="1:5" ht="21.95" customHeight="1">
+    <row r="2194" spans="1:7" ht="21.95" customHeight="1">
       <c r="A2194" s="5" t="s">
         <v>8872</v>
       </c>
@@ -75153,7 +75212,7 @@
         <v>3940</v>
       </c>
     </row>
-    <row r="2195" spans="1:5" ht="21.95" customHeight="1">
+    <row r="2195" spans="1:7" ht="21.95" customHeight="1">
       <c r="A2195" s="5" t="s">
         <v>8873</v>
       </c>
@@ -75170,7 +75229,7 @@
         <v>3940</v>
       </c>
     </row>
-    <row r="2196" spans="1:5" ht="21.95" customHeight="1">
+    <row r="2196" spans="1:7" ht="21.95" customHeight="1">
       <c r="A2196" s="5" t="s">
         <v>8874</v>
       </c>
@@ -75187,7 +75246,7 @@
         <v>3940</v>
       </c>
     </row>
-    <row r="2197" spans="1:5" ht="21.95" customHeight="1">
+    <row r="2197" spans="1:7" ht="21.95" customHeight="1">
       <c r="A2197" s="5" t="s">
         <v>8875</v>
       </c>
@@ -75204,7 +75263,7 @@
         <v>3940</v>
       </c>
     </row>
-    <row r="2198" spans="1:5" ht="21.95" customHeight="1">
+    <row r="2198" spans="1:7" ht="21.95" customHeight="1">
       <c r="A2198" s="5" t="s">
         <v>8876</v>
       </c>
@@ -75221,7 +75280,7 @@
         <v>3940</v>
       </c>
     </row>
-    <row r="2199" spans="1:5" ht="21.95" customHeight="1">
+    <row r="2199" spans="1:7" ht="21.95" customHeight="1">
       <c r="A2199" s="5" t="s">
         <v>8877</v>
       </c>
@@ -75238,7 +75297,7 @@
         <v>3940</v>
       </c>
     </row>
-    <row r="2200" spans="1:5" ht="21.95" customHeight="1">
+    <row r="2200" spans="1:7" ht="21.95" customHeight="1">
       <c r="A2200" s="5" t="s">
         <v>8878</v>
       </c>
@@ -75255,7 +75314,7 @@
         <v>3940</v>
       </c>
     </row>
-    <row r="2201" spans="1:5" ht="21.95" customHeight="1">
+    <row r="2201" spans="1:7" ht="21.95" customHeight="1">
       <c r="A2201" s="5" t="s">
         <v>8879</v>
       </c>
@@ -75272,7 +75331,7 @@
         <v>3940</v>
       </c>
     </row>
-    <row r="2202" spans="1:5" ht="21.95" customHeight="1">
+    <row r="2202" spans="1:7" ht="21.95" customHeight="1">
       <c r="A2202" s="5" t="s">
         <v>8880</v>
       </c>
@@ -75289,7 +75348,7 @@
         <v>3940</v>
       </c>
     </row>
-    <row r="2203" spans="1:5" ht="21.95" customHeight="1">
+    <row r="2203" spans="1:7" ht="21.95" customHeight="1">
       <c r="A2203" s="5" t="s">
         <v>8831</v>
       </c>
@@ -75306,7 +75365,7 @@
         <v>3940</v>
       </c>
     </row>
-    <row r="2204" spans="1:5" ht="21.95" customHeight="1">
+    <row r="2204" spans="1:7" ht="21.95" customHeight="1">
       <c r="A2204" s="5" t="s">
         <v>8881</v>
       </c>
@@ -75321,151 +75380,257 @@
       </c>
       <c r="E2204" s="1" t="s">
         <v>3940</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A2205" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2205" s="3">
+        <v>22099322</v>
+      </c>
+      <c r="C2205" s="1" t="s">
+        <v>8986</v>
+      </c>
+      <c r="D2205" s="1" t="s">
+        <v>8991</v>
+      </c>
+      <c r="F2205" s="1" t="s">
+        <v>8993</v>
+      </c>
+      <c r="G2205" s="1" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A2206" s="5" t="s">
+        <v>8982</v>
+      </c>
+      <c r="B2206" s="3">
+        <v>90272116</v>
+      </c>
+      <c r="C2206" s="1" t="s">
+        <v>8987</v>
+      </c>
+      <c r="D2206" s="1" t="s">
+        <v>8992</v>
+      </c>
+      <c r="F2206" s="1" t="s">
+        <v>8993</v>
+      </c>
+      <c r="G2206" s="1" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A2207" s="5" t="s">
+        <v>8983</v>
+      </c>
+      <c r="B2207" s="3">
+        <v>22491655</v>
+      </c>
+      <c r="C2207" s="1" t="s">
+        <v>8988</v>
+      </c>
+      <c r="D2207" s="1" t="s">
+        <v>8992</v>
+      </c>
+      <c r="F2207" s="1" t="s">
+        <v>8993</v>
+      </c>
+      <c r="G2207" s="1" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A2208" s="5" t="s">
+        <v>8984</v>
+      </c>
+      <c r="B2208" s="3">
+        <v>28913512</v>
+      </c>
+      <c r="C2208" s="1" t="s">
+        <v>8989</v>
+      </c>
+      <c r="D2208" s="1" t="s">
+        <v>8992</v>
+      </c>
+      <c r="F2208" s="1" t="s">
+        <v>8993</v>
+      </c>
+      <c r="G2208" s="1" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A2209" s="5" t="s">
+        <v>8985</v>
+      </c>
+      <c r="B2209" s="3">
+        <v>50856590</v>
+      </c>
+      <c r="C2209" s="1" t="s">
+        <v>8990</v>
+      </c>
+      <c r="D2209" s="1" t="s">
+        <v>8992</v>
+      </c>
+      <c r="F2209" s="1" t="s">
+        <v>8993</v>
+      </c>
+      <c r="G2209" s="1" t="s">
+        <v>3798</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2022:A2033">
-    <cfRule type="duplicateValues" dxfId="47" priority="102" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="107" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2068:A2075">
-    <cfRule type="duplicateValues" dxfId="46" priority="93" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="98" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2068:B2075">
-    <cfRule type="duplicateValues" dxfId="45" priority="92" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="97" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2076:A2086">
-    <cfRule type="duplicateValues" dxfId="44" priority="76" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="81" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2076:B2086">
-    <cfRule type="duplicateValues" dxfId="43" priority="75" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="80" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2132">
-    <cfRule type="duplicateValues" dxfId="42" priority="65" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="70" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2132">
-    <cfRule type="duplicateValues" dxfId="41" priority="63" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="64" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="68" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="69" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2087">
-    <cfRule type="duplicateValues" dxfId="39" priority="62" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="67" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2087">
-    <cfRule type="duplicateValues" dxfId="38" priority="61" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="66" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2088">
-    <cfRule type="duplicateValues" dxfId="37" priority="60" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="65" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2088">
-    <cfRule type="duplicateValues" dxfId="36" priority="59" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="64" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2089">
-    <cfRule type="duplicateValues" dxfId="35" priority="58" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="63" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2089">
-    <cfRule type="duplicateValues" dxfId="34" priority="57" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="62" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2090">
-    <cfRule type="duplicateValues" dxfId="33" priority="56" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="61" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2090">
-    <cfRule type="duplicateValues" dxfId="32" priority="55" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="60" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2091">
-    <cfRule type="duplicateValues" dxfId="31" priority="54" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="59" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2091">
-    <cfRule type="duplicateValues" dxfId="30" priority="53" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="58" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2092">
-    <cfRule type="duplicateValues" dxfId="29" priority="52" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="57" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2092">
-    <cfRule type="duplicateValues" dxfId="28" priority="51" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="56" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2093">
-    <cfRule type="duplicateValues" dxfId="27" priority="50" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="55" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2093">
-    <cfRule type="duplicateValues" dxfId="26" priority="49" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="54" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2094">
-    <cfRule type="duplicateValues" dxfId="25" priority="48" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="53" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2094">
-    <cfRule type="duplicateValues" dxfId="24" priority="47" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="52" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2095">
+    <cfRule type="duplicateValues" dxfId="25" priority="51" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2095">
+    <cfRule type="duplicateValues" dxfId="24" priority="50" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2096:A2099">
     <cfRule type="duplicateValues" dxfId="23" priority="46" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2095">
+  <conditionalFormatting sqref="B2096:B2099">
     <cfRule type="duplicateValues" dxfId="22" priority="45" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2096:A2099">
-    <cfRule type="duplicateValues" dxfId="21" priority="41" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2096:B2099">
-    <cfRule type="duplicateValues" dxfId="20" priority="40" stopIfTrue="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A2100:A2107">
-    <cfRule type="duplicateValues" dxfId="19" priority="33" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="38" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2100:B2107">
-    <cfRule type="duplicateValues" dxfId="18" priority="32" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="37" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2145:A65536 A2123 A2034:A2067 A1:A2021">
-    <cfRule type="duplicateValues" dxfId="17" priority="103" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2145:A2204 A2123 A2034:A2067 A1:A2021 A2210:A65536">
+    <cfRule type="duplicateValues" dxfId="19" priority="108" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2145:B65536 B2123 B1:B2067">
-    <cfRule type="duplicateValues" dxfId="16" priority="108" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2145:B2204 B2123 B1:B2067 B2210:B65536">
+    <cfRule type="duplicateValues" dxfId="18" priority="113" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2108:A2115">
+    <cfRule type="duplicateValues" dxfId="17" priority="33" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2108:B2115">
+    <cfRule type="duplicateValues" dxfId="16" priority="32" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2116:A2122">
     <cfRule type="duplicateValues" dxfId="15" priority="28" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2108:B2115">
+  <conditionalFormatting sqref="B2116:B2122">
     <cfRule type="duplicateValues" dxfId="14" priority="27" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2116:A2122">
+  <conditionalFormatting sqref="A2124:A2131">
     <cfRule type="duplicateValues" dxfId="13" priority="23" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2116:B2122">
+  <conditionalFormatting sqref="B2124:B2131">
     <cfRule type="duplicateValues" dxfId="12" priority="22" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2124:A2131">
+  <conditionalFormatting sqref="A2133">
     <cfRule type="duplicateValues" dxfId="11" priority="18" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2124:B2131">
+  <conditionalFormatting sqref="B2133">
     <cfRule type="duplicateValues" dxfId="10" priority="17" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2133">
-    <cfRule type="duplicateValues" dxfId="9" priority="13" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2133">
-    <cfRule type="duplicateValues" dxfId="8" priority="12" stopIfTrue="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A2134">
-    <cfRule type="duplicateValues" dxfId="7" priority="11" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="16" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2134">
-    <cfRule type="duplicateValues" dxfId="6" priority="10" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="15" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2135">
+    <cfRule type="duplicateValues" dxfId="7" priority="14" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2135">
+    <cfRule type="duplicateValues" dxfId="6" priority="13" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2136:A2141">
     <cfRule type="duplicateValues" dxfId="5" priority="9" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2135">
+  <conditionalFormatting sqref="B2136:B2141">
     <cfRule type="duplicateValues" dxfId="4" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2136:A2141">
-    <cfRule type="duplicateValues" dxfId="3" priority="4" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2136:B2141">
-    <cfRule type="duplicateValues" dxfId="2" priority="3" stopIfTrue="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A2142:A2144">
-    <cfRule type="duplicateValues" dxfId="1" priority="2" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="7" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2142:B2144">
-    <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2205:A2209">
+    <cfRule type="duplicateValues" dxfId="1" priority="1" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2205:B2209">
+    <cfRule type="duplicateValues" dxfId="0" priority="2" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1190:G1200 G314:G674 G676:G703 G251:G312 G705:G1187 G2:G249">

--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12462" uniqueCount="9040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12516" uniqueCount="9087">
   <si>
     <t>麒安科技有限公司</t>
   </si>
@@ -30158,14 +30158,14 @@
     <t>114業二02918</t>
   </si>
   <si>
-    <t>115.02.17</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>遠創智慧股份有限公司</t>
   </si>
   <si>
-    <t>印章有問題</t>
+    <t>天心工業股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二02909</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -30173,18 +30173,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>天心工業股份有限公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>114業二02909</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>119.02.20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>電話</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -31812,35 +31800,223 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>114.04.17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119.04.11</t>
+  </si>
+  <si>
+    <t>115.09.30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>117.12.07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0425693976</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>61/曹小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>032888899</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>174/蔡小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>033248320</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李先生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119.04.14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114.04.17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電話</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0277087199</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>280/唐小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>115.12.31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0286483000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>306/吳小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0423590169</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12/劉小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0228090899</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甄小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>076165203</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鐘先生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0229995010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>63306/吳小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>郵件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aerowu@socle-tech.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吳先生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>119.04.15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>115.12.31</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>114.04.17</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>吳先生</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aerowu@socle-tech.com</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>119.04.11</t>
-  </si>
-  <si>
-    <t>115.09.30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>117.12.07</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>電話</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>033591777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>294/黃小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>東典光電科技股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119.04.14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0426578118</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>318/蔡小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>039908671</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>035981328</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>森思股份有限公司</t>
+  </si>
+  <si>
+    <t>24934868</t>
+  </si>
+  <si>
+    <t>WBBL2025044850</t>
+  </si>
+  <si>
+    <t>119.04.24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>博立恆科技有限公司</t>
+  </si>
+  <si>
+    <t>提思創意有限公司</t>
+  </si>
+  <si>
+    <t>聯野國際有限公司</t>
+  </si>
+  <si>
+    <t>亨諳股份有限公司</t>
+  </si>
+  <si>
+    <t>橋牧科技股份有限公司</t>
+  </si>
+  <si>
+    <t>114業二07681</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二07682</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二07683</t>
+  </si>
+  <si>
+    <t>114業二07684</t>
+  </si>
+  <si>
+    <t>114業二07685</t>
+  </si>
+  <si>
+    <t>115.04.21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119.04.21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>117.12.31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119.04.25</t>
   </si>
 </sst>
 </file>
@@ -31919,7 +32095,7 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -31929,12 +32105,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -31972,7 +32142,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -32063,12 +32233,6 @@
     <xf numFmtId="186" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -32078,10 +32242,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -32089,7 +32253,117 @@
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="59">
+  <dxfs count="70">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -32978,7 +33252,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:J2224"/>
+  <dimension ref="A1:J2230"/>
   <sheetFormatPr defaultRowHeight="21.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" style="5" customWidth="1"/>
@@ -44862,7 +45136,7 @@
         <v>5956</v>
       </c>
       <c r="D795" s="1" t="s">
-        <v>9038</v>
+        <v>9031</v>
       </c>
       <c r="F795" s="1" t="s">
         <v>5961</v>
@@ -62422,7 +62696,7 @@
         <v>6091</v>
       </c>
       <c r="D1670" s="1" t="s">
-        <v>9039</v>
+        <v>9032</v>
       </c>
       <c r="F1670" s="1" t="s">
         <v>6102</v>
@@ -68474,16 +68748,16 @@
     </row>
     <row r="1905" spans="1:9" ht="21.95" customHeight="1">
       <c r="A1905" s="5" t="s">
-        <v>8668</v>
+        <v>8665</v>
       </c>
       <c r="B1905" s="3" t="s">
+        <v>8664</v>
+      </c>
+      <c r="C1905" s="1" t="s">
+        <v>8666</v>
+      </c>
+      <c r="D1905" s="1" t="s">
         <v>8667</v>
-      </c>
-      <c r="C1905" s="1" t="s">
-        <v>8669</v>
-      </c>
-      <c r="D1905" s="1" t="s">
-        <v>8670</v>
       </c>
       <c r="E1905" s="1" t="s">
         <v>3508</v>
@@ -73158,1475 +73432,1469 @@
     </row>
     <row r="2087" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2087" s="12" t="s">
-        <v>8574</v>
+        <v>8571</v>
       </c>
       <c r="B2087" s="7">
         <v>52259079</v>
       </c>
       <c r="C2087" s="6" t="s">
-        <v>8575</v>
+        <v>8572</v>
       </c>
       <c r="D2087" s="6" t="s">
         <v>8566</v>
       </c>
       <c r="F2087" s="6" t="s">
+        <v>8573</v>
+      </c>
+      <c r="G2087" s="6" t="s">
+        <v>8574</v>
+      </c>
+      <c r="H2087" s="6" t="s">
+        <v>8575</v>
+      </c>
+      <c r="I2087" s="6" t="s">
         <v>8576</v>
-      </c>
-      <c r="G2087" s="6" t="s">
-        <v>8577</v>
-      </c>
-      <c r="H2087" s="6" t="s">
-        <v>8578</v>
-      </c>
-      <c r="I2087" s="6" t="s">
-        <v>8579</v>
       </c>
     </row>
     <row r="2088" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2088" s="12" t="s">
-        <v>8580</v>
+        <v>8577</v>
       </c>
       <c r="B2088" s="7">
         <v>86828303</v>
       </c>
       <c r="C2088" s="6" t="s">
-        <v>8581</v>
+        <v>8578</v>
       </c>
       <c r="D2088" s="6" t="s">
         <v>8567</v>
       </c>
       <c r="F2088" s="6" t="s">
-        <v>8576</v>
+        <v>8573</v>
       </c>
       <c r="G2088" s="6" t="s">
-        <v>8582</v>
+        <v>8579</v>
       </c>
       <c r="H2088" s="6" t="s">
-        <v>8583</v>
+        <v>8580</v>
       </c>
       <c r="I2088" s="6" t="s">
-        <v>8584</v>
+        <v>8581</v>
       </c>
     </row>
     <row r="2089" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2089" s="12" t="s">
-        <v>8585</v>
+        <v>8582</v>
       </c>
       <c r="B2089" s="7">
         <v>27457023</v>
       </c>
       <c r="C2089" s="6" t="s">
-        <v>8586</v>
+        <v>8583</v>
       </c>
       <c r="D2089" s="6" t="s">
         <v>8567</v>
       </c>
       <c r="F2089" s="6" t="s">
+        <v>8573</v>
+      </c>
+      <c r="G2089" s="6" t="s">
+        <v>8574</v>
+      </c>
+      <c r="H2089" s="6" t="s">
+        <v>8584</v>
+      </c>
+      <c r="I2089" s="6" t="s">
         <v>8576</v>
-      </c>
-      <c r="G2089" s="6" t="s">
-        <v>8577</v>
-      </c>
-      <c r="H2089" s="6" t="s">
-        <v>8587</v>
-      </c>
-      <c r="I2089" s="6" t="s">
-        <v>8579</v>
       </c>
     </row>
     <row r="2090" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2090" s="12" t="s">
-        <v>8588</v>
+        <v>8585</v>
       </c>
       <c r="B2090" s="7">
         <v>23503047</v>
       </c>
       <c r="C2090" s="6" t="s">
-        <v>8589</v>
+        <v>8586</v>
       </c>
       <c r="D2090" s="6" t="s">
         <v>8567</v>
       </c>
       <c r="F2090" s="6" t="s">
-        <v>8576</v>
+        <v>8573</v>
       </c>
       <c r="G2090" s="6" t="s">
-        <v>8582</v>
+        <v>8579</v>
       </c>
       <c r="H2090" s="6" t="s">
-        <v>8590</v>
+        <v>8587</v>
       </c>
       <c r="I2090" s="6" t="s">
-        <v>8591</v>
+        <v>8588</v>
       </c>
     </row>
     <row r="2091" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2091" s="12" t="s">
-        <v>8592</v>
+        <v>8589</v>
       </c>
       <c r="B2091" s="7">
         <v>43704649</v>
       </c>
       <c r="C2091" s="6" t="s">
-        <v>8593</v>
+        <v>8590</v>
       </c>
       <c r="D2091" s="6" t="s">
         <v>8567</v>
       </c>
       <c r="F2091" s="6" t="s">
-        <v>8576</v>
+        <v>8573</v>
       </c>
       <c r="G2091" s="6" t="s">
-        <v>8577</v>
+        <v>8574</v>
       </c>
       <c r="H2091" s="6" t="s">
-        <v>8594</v>
+        <v>8591</v>
       </c>
       <c r="I2091" s="6" t="s">
-        <v>8595</v>
+        <v>8592</v>
       </c>
     </row>
     <row r="2092" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2092" s="12" t="s">
-        <v>8596</v>
+        <v>8593</v>
       </c>
       <c r="B2092" s="7">
         <v>53740840</v>
       </c>
       <c r="C2092" s="6" t="s">
-        <v>8597</v>
+        <v>8594</v>
       </c>
       <c r="D2092" s="6" t="s">
         <v>8567</v>
       </c>
       <c r="F2092" s="6" t="s">
-        <v>8576</v>
+        <v>8573</v>
       </c>
       <c r="G2092" s="6" t="s">
-        <v>8577</v>
+        <v>8574</v>
       </c>
       <c r="H2092" s="6" t="s">
-        <v>8598</v>
+        <v>8595</v>
       </c>
       <c r="I2092" s="6" t="s">
-        <v>8599</v>
+        <v>8596</v>
       </c>
     </row>
     <row r="2093" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2093" s="12" t="s">
-        <v>8600</v>
+        <v>8597</v>
       </c>
       <c r="B2093" s="7">
         <v>56619737</v>
       </c>
       <c r="C2093" s="6" t="s">
-        <v>8601</v>
+        <v>8598</v>
       </c>
       <c r="D2093" s="6" t="s">
         <v>8567</v>
       </c>
       <c r="F2093" s="6" t="s">
+        <v>8573</v>
+      </c>
+      <c r="G2093" s="6" t="s">
+        <v>8574</v>
+      </c>
+      <c r="H2093" s="6" t="s">
+        <v>8599</v>
+      </c>
+      <c r="I2093" s="6" t="s">
         <v>8576</v>
-      </c>
-      <c r="G2093" s="6" t="s">
-        <v>8577</v>
-      </c>
-      <c r="H2093" s="6" t="s">
-        <v>8602</v>
-      </c>
-      <c r="I2093" s="6" t="s">
-        <v>8579</v>
       </c>
     </row>
     <row r="2094" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2094" s="12" t="s">
-        <v>8603</v>
+        <v>8600</v>
       </c>
       <c r="B2094" s="7">
         <v>24808757</v>
       </c>
       <c r="C2094" s="6" t="s">
-        <v>8604</v>
+        <v>8601</v>
       </c>
       <c r="D2094" s="6" t="s">
         <v>8567</v>
       </c>
       <c r="F2094" s="6" t="s">
-        <v>8576</v>
+        <v>8573</v>
       </c>
       <c r="G2094" s="6" t="s">
-        <v>8577</v>
+        <v>8574</v>
       </c>
       <c r="H2094" s="6" t="s">
-        <v>8605</v>
+        <v>8602</v>
       </c>
       <c r="I2094" s="6" t="s">
-        <v>8606</v>
+        <v>8603</v>
       </c>
     </row>
     <row r="2095" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2095" s="12" t="s">
-        <v>8607</v>
+        <v>8604</v>
       </c>
       <c r="B2095" s="7">
         <v>27472283</v>
       </c>
       <c r="C2095" s="6" t="s">
-        <v>8608</v>
+        <v>8605</v>
       </c>
       <c r="D2095" s="6" t="s">
         <v>8568</v>
       </c>
       <c r="F2095" s="6" t="s">
+        <v>8573</v>
+      </c>
+      <c r="G2095" s="6" t="s">
+        <v>8574</v>
+      </c>
+      <c r="H2095" s="6" t="s">
+        <v>8606</v>
+      </c>
+      <c r="I2095" s="6" t="s">
         <v>8576</v>
-      </c>
-      <c r="G2095" s="6" t="s">
-        <v>8577</v>
-      </c>
-      <c r="H2095" s="6" t="s">
-        <v>8609</v>
-      </c>
-      <c r="I2095" s="6" t="s">
-        <v>8579</v>
       </c>
     </row>
     <row r="2096" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2096" s="12" t="s">
-        <v>8612</v>
+        <v>8609</v>
       </c>
       <c r="B2096" s="7">
         <v>29033965</v>
       </c>
       <c r="C2096" s="6" t="s">
-        <v>8613</v>
+        <v>8610</v>
       </c>
       <c r="D2096" s="6" t="s">
-        <v>8610</v>
+        <v>8607</v>
       </c>
       <c r="F2096" s="6" t="s">
-        <v>8614</v>
+        <v>8611</v>
       </c>
       <c r="G2096" s="6" t="s">
-        <v>8615</v>
+        <v>8612</v>
       </c>
       <c r="H2096" s="6" t="s">
-        <v>8629</v>
+        <v>8626</v>
       </c>
       <c r="I2096" s="6" t="s">
-        <v>8628</v>
+        <v>8625</v>
       </c>
     </row>
     <row r="2097" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2097" s="12" t="s">
-        <v>8616</v>
+        <v>8613</v>
       </c>
       <c r="B2097" s="7">
         <v>53594184</v>
       </c>
       <c r="C2097" s="6" t="s">
-        <v>8617</v>
+        <v>8614</v>
       </c>
       <c r="D2097" s="6" t="s">
+        <v>8608</v>
+      </c>
+      <c r="F2097" s="6" t="s">
         <v>8611</v>
       </c>
-      <c r="F2097" s="6" t="s">
-        <v>8614</v>
-      </c>
       <c r="G2097" s="6" t="s">
-        <v>8615</v>
+        <v>8612</v>
       </c>
       <c r="H2097" s="6" t="s">
-        <v>8630</v>
+        <v>8627</v>
       </c>
       <c r="I2097" s="6" t="s">
-        <v>8631</v>
+        <v>8628</v>
       </c>
     </row>
     <row r="2098" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2098" s="12" t="s">
-        <v>8618</v>
+        <v>8615</v>
       </c>
       <c r="B2098" s="7">
         <v>42622374</v>
       </c>
       <c r="C2098" s="6" t="s">
-        <v>8619</v>
+        <v>8616</v>
       </c>
       <c r="D2098" s="6" t="s">
-        <v>8610</v>
+        <v>8607</v>
       </c>
       <c r="F2098" s="6" t="s">
-        <v>8614</v>
+        <v>8611</v>
       </c>
       <c r="G2098" s="6" t="s">
-        <v>8615</v>
+        <v>8612</v>
       </c>
       <c r="H2098" s="6" t="s">
-        <v>8620</v>
+        <v>8617</v>
       </c>
       <c r="I2098" s="6" t="s">
-        <v>8632</v>
+        <v>8629</v>
       </c>
     </row>
     <row r="2099" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2099" s="12" t="s">
-        <v>8621</v>
+        <v>8618</v>
       </c>
       <c r="B2099" s="7">
         <v>96002575</v>
       </c>
       <c r="C2099" s="6" t="s">
-        <v>8622</v>
+        <v>8619</v>
       </c>
       <c r="D2099" s="6" t="s">
-        <v>8610</v>
+        <v>8607</v>
       </c>
       <c r="F2099" s="6" t="s">
-        <v>8614</v>
+        <v>8611</v>
       </c>
       <c r="G2099" s="6" t="s">
-        <v>8615</v>
+        <v>8612</v>
       </c>
       <c r="H2099" s="6" t="s">
-        <v>8634</v>
-      </c>
-      <c r="I2099" s="32" t="s">
-        <v>8633</v>
+        <v>8631</v>
+      </c>
+      <c r="I2099" s="30" t="s">
+        <v>8630</v>
       </c>
     </row>
     <row r="2100" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2100" s="12" t="s">
-        <v>8635</v>
+        <v>8632</v>
       </c>
       <c r="B2100" s="7">
         <v>89672698</v>
       </c>
       <c r="C2100" s="6" t="s">
-        <v>8636</v>
+        <v>8633</v>
       </c>
       <c r="D2100" s="6" t="s">
-        <v>8626</v>
+        <v>8623</v>
       </c>
       <c r="F2100" s="6" t="s">
-        <v>8637</v>
+        <v>8634</v>
       </c>
       <c r="G2100" s="6" t="s">
-        <v>8656</v>
-      </c>
-      <c r="H2100" s="33" t="s">
-        <v>8666</v>
-      </c>
-      <c r="I2100" s="32" t="s">
-        <v>8657</v>
+        <v>8653</v>
+      </c>
+      <c r="H2100" s="31" t="s">
+        <v>8663</v>
+      </c>
+      <c r="I2100" s="30" t="s">
+        <v>8654</v>
       </c>
     </row>
     <row r="2101" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2101" s="12" t="s">
-        <v>8639</v>
+        <v>8636</v>
       </c>
       <c r="B2101" s="7">
         <v>55794222</v>
       </c>
       <c r="C2101" s="6" t="s">
-        <v>8640</v>
+        <v>8637</v>
       </c>
       <c r="D2101" s="6" t="s">
-        <v>8627</v>
+        <v>8624</v>
       </c>
       <c r="F2101" s="6" t="s">
-        <v>8637</v>
+        <v>8634</v>
       </c>
       <c r="G2101" s="6" t="s">
-        <v>8638</v>
+        <v>8635</v>
       </c>
       <c r="H2101" s="6" t="s">
-        <v>8664</v>
-      </c>
-      <c r="I2101" s="32" t="s">
-        <v>8663</v>
+        <v>8661</v>
+      </c>
+      <c r="I2101" s="30" t="s">
+        <v>8660</v>
       </c>
     </row>
     <row r="2102" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2102" s="12" t="s">
-        <v>8641</v>
+        <v>8638</v>
       </c>
       <c r="B2102" s="7">
         <v>27774061</v>
       </c>
       <c r="C2102" s="6" t="s">
-        <v>8623</v>
+        <v>8620</v>
       </c>
       <c r="D2102" s="6" t="s">
-        <v>8627</v>
+        <v>8624</v>
       </c>
       <c r="F2102" s="6" t="s">
-        <v>8637</v>
+        <v>8634</v>
       </c>
       <c r="G2102" s="6" t="s">
-        <v>8638</v>
+        <v>8635</v>
       </c>
       <c r="H2102" s="6" t="s">
-        <v>8642</v>
-      </c>
-      <c r="I2102" s="32" t="s">
-        <v>8662</v>
+        <v>8639</v>
+      </c>
+      <c r="I2102" s="30" t="s">
+        <v>8659</v>
       </c>
     </row>
     <row r="2103" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2103" s="12" t="s">
-        <v>8643</v>
+        <v>8640</v>
       </c>
       <c r="B2103" s="7">
         <v>66652410</v>
       </c>
       <c r="C2103" s="6" t="s">
+        <v>8621</v>
+      </c>
+      <c r="D2103" s="6" t="s">
         <v>8624</v>
       </c>
-      <c r="D2103" s="6" t="s">
-        <v>8627</v>
-      </c>
       <c r="F2103" s="6" t="s">
-        <v>8637</v>
+        <v>8634</v>
       </c>
       <c r="G2103" s="6" t="s">
-        <v>8638</v>
+        <v>8635</v>
       </c>
       <c r="H2103" s="6" t="s">
-        <v>8644</v>
-      </c>
-      <c r="I2103" s="32" t="s">
-        <v>8661</v>
+        <v>8641</v>
+      </c>
+      <c r="I2103" s="30" t="s">
+        <v>8658</v>
       </c>
     </row>
     <row r="2104" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2104" s="12" t="s">
-        <v>8645</v>
+        <v>8642</v>
       </c>
       <c r="B2104" s="7">
         <v>25171389</v>
       </c>
       <c r="C2104" s="6" t="s">
-        <v>8646</v>
+        <v>8643</v>
       </c>
       <c r="D2104" s="6" t="s">
-        <v>8627</v>
+        <v>8624</v>
       </c>
       <c r="F2104" s="6" t="s">
-        <v>8637</v>
+        <v>8634</v>
       </c>
       <c r="G2104" s="6" t="s">
-        <v>8638</v>
+        <v>8635</v>
       </c>
       <c r="H2104" s="6" t="s">
-        <v>8647</v>
-      </c>
-      <c r="I2104" s="32" t="s">
-        <v>8660</v>
+        <v>8644</v>
+      </c>
+      <c r="I2104" s="30" t="s">
+        <v>8657</v>
       </c>
     </row>
     <row r="2105" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2105" s="12" t="s">
-        <v>8648</v>
+        <v>8645</v>
       </c>
       <c r="B2105" s="7">
         <v>55731769</v>
       </c>
       <c r="C2105" s="6" t="s">
-        <v>8649</v>
+        <v>8646</v>
       </c>
       <c r="D2105" s="6" t="s">
-        <v>8627</v>
+        <v>8624</v>
       </c>
       <c r="F2105" s="6" t="s">
-        <v>8637</v>
+        <v>8634</v>
       </c>
       <c r="G2105" s="6" t="s">
-        <v>8638</v>
+        <v>8635</v>
       </c>
       <c r="H2105" s="6" t="s">
-        <v>8650</v>
-      </c>
-      <c r="I2105" s="32" t="s">
-        <v>8659</v>
+        <v>8647</v>
+      </c>
+      <c r="I2105" s="30" t="s">
+        <v>8656</v>
       </c>
     </row>
     <row r="2106" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2106" s="12" t="s">
-        <v>8651</v>
+        <v>8648</v>
       </c>
       <c r="B2106" s="7">
         <v>16444732</v>
       </c>
       <c r="C2106" s="6" t="s">
-        <v>8652</v>
+        <v>8649</v>
       </c>
       <c r="D2106" s="6" t="s">
-        <v>8627</v>
+        <v>8624</v>
       </c>
       <c r="F2106" s="6" t="s">
-        <v>8637</v>
+        <v>8634</v>
       </c>
       <c r="G2106" s="6" t="s">
-        <v>8638</v>
+        <v>8635</v>
       </c>
       <c r="H2106" s="6" t="s">
-        <v>8653</v>
-      </c>
-      <c r="I2106" s="32" t="s">
-        <v>8665</v>
+        <v>8650</v>
+      </c>
+      <c r="I2106" s="30" t="s">
+        <v>8662</v>
       </c>
     </row>
     <row r="2107" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2107" s="12" t="s">
-        <v>8654</v>
+        <v>8651</v>
       </c>
       <c r="B2107" s="7">
         <v>94025314</v>
       </c>
       <c r="C2107" s="6" t="s">
-        <v>8625</v>
+        <v>8622</v>
       </c>
       <c r="D2107" s="6" t="s">
-        <v>8627</v>
+        <v>8624</v>
       </c>
       <c r="F2107" s="6" t="s">
-        <v>8637</v>
+        <v>8634</v>
       </c>
       <c r="G2107" s="6" t="s">
-        <v>8638</v>
+        <v>8635</v>
       </c>
       <c r="H2107" s="6" t="s">
+        <v>8652</v>
+      </c>
+      <c r="I2107" s="30" t="s">
         <v>8655</v>
-      </c>
-      <c r="I2107" s="32" t="s">
-        <v>8658</v>
       </c>
     </row>
     <row r="2108" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2108" s="12" t="s">
-        <v>8671</v>
+        <v>8668</v>
       </c>
       <c r="B2108" s="7">
         <v>35928595</v>
       </c>
       <c r="C2108" s="6" t="s">
+        <v>8669</v>
+      </c>
+      <c r="D2108" s="6" t="s">
+        <v>8670</v>
+      </c>
+      <c r="F2108" s="6" t="s">
+        <v>8671</v>
+      </c>
+      <c r="G2108" s="6" t="s">
         <v>8672</v>
       </c>
-      <c r="D2108" s="6" t="s">
+      <c r="H2108" s="6" t="s">
         <v>8673</v>
       </c>
-      <c r="F2108" s="6" t="s">
+      <c r="I2108" s="30" t="s">
         <v>8674</v>
-      </c>
-      <c r="G2108" s="6" t="s">
-        <v>8675</v>
-      </c>
-      <c r="H2108" s="6" t="s">
-        <v>8676</v>
-      </c>
-      <c r="I2108" s="32" t="s">
-        <v>8677</v>
       </c>
     </row>
     <row r="2109" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2109" s="12" t="s">
-        <v>8678</v>
+        <v>8675</v>
       </c>
       <c r="B2109" s="7">
         <v>57132939</v>
       </c>
       <c r="C2109" s="6" t="s">
-        <v>8679</v>
+        <v>8676</v>
       </c>
       <c r="D2109" s="6" t="s">
-        <v>8673</v>
+        <v>8670</v>
       </c>
       <c r="F2109" s="6" t="s">
-        <v>8674</v>
+        <v>8671</v>
       </c>
       <c r="G2109" s="6" t="s">
-        <v>8675</v>
+        <v>8672</v>
       </c>
       <c r="H2109" s="6" t="s">
-        <v>8680</v>
-      </c>
-      <c r="I2109" s="32" t="s">
-        <v>8681</v>
+        <v>8677</v>
+      </c>
+      <c r="I2109" s="30" t="s">
+        <v>8678</v>
       </c>
     </row>
     <row r="2110" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2110" s="12" t="s">
-        <v>8682</v>
+        <v>8679</v>
       </c>
       <c r="B2110" s="7">
         <v>28112723</v>
       </c>
       <c r="C2110" s="6" t="s">
+        <v>8680</v>
+      </c>
+      <c r="D2110" s="6" t="s">
+        <v>8670</v>
+      </c>
+      <c r="F2110" s="6" t="s">
+        <v>8671</v>
+      </c>
+      <c r="G2110" s="6" t="s">
+        <v>8681</v>
+      </c>
+      <c r="H2110" s="6" t="s">
+        <v>8682</v>
+      </c>
+      <c r="I2110" s="30" t="s">
         <v>8683</v>
-      </c>
-      <c r="D2110" s="6" t="s">
-        <v>8673</v>
-      </c>
-      <c r="F2110" s="6" t="s">
-        <v>8674</v>
-      </c>
-      <c r="G2110" s="6" t="s">
-        <v>8684</v>
-      </c>
-      <c r="H2110" s="6" t="s">
-        <v>8685</v>
-      </c>
-      <c r="I2110" s="32" t="s">
-        <v>8686</v>
       </c>
     </row>
     <row r="2111" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2111" s="12" t="s">
-        <v>8687</v>
+        <v>8684</v>
       </c>
       <c r="B2111" s="7">
         <v>90784186</v>
       </c>
       <c r="C2111" s="6" t="s">
-        <v>8688</v>
+        <v>8685</v>
       </c>
       <c r="D2111" s="6" t="s">
-        <v>8673</v>
+        <v>8670</v>
       </c>
       <c r="F2111" s="6" t="s">
-        <v>8674</v>
+        <v>8671</v>
       </c>
       <c r="G2111" s="6" t="s">
-        <v>8675</v>
+        <v>8672</v>
       </c>
       <c r="H2111" s="6" t="s">
-        <v>8689</v>
-      </c>
-      <c r="I2111" s="32" t="s">
-        <v>8690</v>
+        <v>8686</v>
+      </c>
+      <c r="I2111" s="30" t="s">
+        <v>8687</v>
       </c>
     </row>
     <row r="2112" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2112" s="12" t="s">
-        <v>8691</v>
+        <v>8688</v>
       </c>
       <c r="B2112" s="7">
         <v>28877776</v>
       </c>
       <c r="C2112" s="6" t="s">
-        <v>8692</v>
+        <v>8689</v>
       </c>
       <c r="D2112" s="6" t="s">
-        <v>8673</v>
+        <v>8670</v>
       </c>
       <c r="F2112" s="6" t="s">
-        <v>8674</v>
+        <v>8671</v>
       </c>
       <c r="G2112" s="6" t="s">
-        <v>8675</v>
+        <v>8672</v>
       </c>
       <c r="H2112" s="6" t="s">
-        <v>8693</v>
-      </c>
-      <c r="I2112" s="32"/>
+        <v>8690</v>
+      </c>
+      <c r="I2112" s="30"/>
     </row>
     <row r="2113" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2113" s="12" t="s">
-        <v>8694</v>
+        <v>8691</v>
       </c>
       <c r="B2113" s="7">
         <v>16541523</v>
       </c>
       <c r="C2113" s="6" t="s">
-        <v>8695</v>
+        <v>8692</v>
       </c>
       <c r="D2113" s="6" t="s">
-        <v>8673</v>
+        <v>8670</v>
       </c>
       <c r="F2113" s="6" t="s">
-        <v>8674</v>
+        <v>8671</v>
       </c>
       <c r="G2113" s="6" t="s">
-        <v>8675</v>
+        <v>8672</v>
       </c>
       <c r="H2113" s="6" t="s">
-        <v>8696</v>
-      </c>
-      <c r="I2113" s="32" t="s">
-        <v>8690</v>
+        <v>8693</v>
+      </c>
+      <c r="I2113" s="30" t="s">
+        <v>8687</v>
       </c>
     </row>
     <row r="2114" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2114" s="12" t="s">
-        <v>8697</v>
+        <v>8694</v>
       </c>
       <c r="B2114" s="7">
         <v>12733681</v>
       </c>
       <c r="C2114" s="6" t="s">
-        <v>8698</v>
+        <v>8695</v>
       </c>
       <c r="D2114" s="6" t="s">
-        <v>8673</v>
+        <v>8670</v>
       </c>
       <c r="F2114" s="6" t="s">
-        <v>8674</v>
+        <v>8671</v>
       </c>
       <c r="G2114" s="6" t="s">
-        <v>8675</v>
+        <v>8672</v>
       </c>
       <c r="H2114" s="6" t="s">
-        <v>8699</v>
-      </c>
-      <c r="I2114" s="32" t="s">
-        <v>8700</v>
+        <v>8696</v>
+      </c>
+      <c r="I2114" s="30" t="s">
+        <v>8697</v>
       </c>
     </row>
     <row r="2115" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2115" s="12" t="s">
-        <v>8701</v>
+        <v>8698</v>
       </c>
       <c r="B2115" s="7">
         <v>34783798</v>
       </c>
       <c r="C2115" s="6" t="s">
-        <v>8702</v>
+        <v>8699</v>
       </c>
       <c r="D2115" s="6" t="s">
-        <v>8673</v>
+        <v>8670</v>
       </c>
       <c r="F2115" s="6" t="s">
-        <v>8674</v>
+        <v>8671</v>
       </c>
       <c r="G2115" s="6" t="s">
-        <v>8675</v>
+        <v>8672</v>
       </c>
       <c r="H2115" s="6" t="s">
-        <v>8703</v>
-      </c>
-      <c r="I2115" s="32"/>
+        <v>8700</v>
+      </c>
+      <c r="I2115" s="30"/>
     </row>
     <row r="2116" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2116" s="12" t="s">
-        <v>8710</v>
+        <v>8707</v>
       </c>
       <c r="B2116" s="7">
         <v>54503893</v>
       </c>
       <c r="C2116" s="6" t="s">
+        <v>8708</v>
+      </c>
+      <c r="D2116" s="6" t="s">
+        <v>8709</v>
+      </c>
+      <c r="F2116" s="6" t="s">
+        <v>8710</v>
+      </c>
+      <c r="G2116" s="6" t="s">
         <v>8711</v>
       </c>
-      <c r="D2116" s="6" t="s">
+      <c r="H2116" s="6" t="s">
         <v>8712</v>
       </c>
-      <c r="F2116" s="6" t="s">
-        <v>8713</v>
-      </c>
-      <c r="G2116" s="6" t="s">
-        <v>8714</v>
-      </c>
-      <c r="H2116" s="6" t="s">
-        <v>8715</v>
-      </c>
-      <c r="I2116" s="32" t="s">
-        <v>8704</v>
+      <c r="I2116" s="30" t="s">
+        <v>8701</v>
       </c>
     </row>
     <row r="2117" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2117" s="12" t="s">
-        <v>8716</v>
+        <v>8713</v>
       </c>
       <c r="B2117" s="7">
         <v>13004319</v>
       </c>
       <c r="C2117" s="6" t="s">
-        <v>8717</v>
+        <v>8714</v>
       </c>
       <c r="D2117" s="6" t="s">
-        <v>8718</v>
+        <v>8715</v>
       </c>
       <c r="F2117" s="6" t="s">
-        <v>8713</v>
+        <v>8710</v>
       </c>
       <c r="G2117" s="6" t="s">
-        <v>8714</v>
+        <v>8711</v>
       </c>
       <c r="H2117" s="6" t="s">
-        <v>8719</v>
-      </c>
-      <c r="I2117" s="32" t="s">
-        <v>8705</v>
+        <v>8716</v>
+      </c>
+      <c r="I2117" s="30" t="s">
+        <v>8702</v>
       </c>
     </row>
     <row r="2118" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2118" s="12" t="s">
-        <v>8720</v>
+        <v>8717</v>
       </c>
       <c r="B2118" s="7">
         <v>35892013</v>
       </c>
       <c r="C2118" s="6" t="s">
-        <v>8721</v>
+        <v>8718</v>
       </c>
       <c r="D2118" s="6" t="s">
-        <v>8722</v>
+        <v>8719</v>
       </c>
       <c r="F2118" s="6" t="s">
-        <v>8713</v>
+        <v>8710</v>
       </c>
       <c r="G2118" s="6" t="s">
-        <v>8714</v>
+        <v>8711</v>
       </c>
       <c r="H2118" s="6" t="s">
-        <v>8723</v>
-      </c>
-      <c r="I2118" s="32" t="s">
-        <v>8706</v>
+        <v>8720</v>
+      </c>
+      <c r="I2118" s="30" t="s">
+        <v>8703</v>
       </c>
     </row>
     <row r="2119" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2119" s="12" t="s">
-        <v>8724</v>
+        <v>8721</v>
       </c>
       <c r="B2119" s="7">
         <v>54138621</v>
       </c>
       <c r="C2119" s="6" t="s">
-        <v>8725</v>
+        <v>8722</v>
       </c>
       <c r="D2119" s="6" t="s">
-        <v>8718</v>
+        <v>8715</v>
       </c>
       <c r="F2119" s="6" t="s">
-        <v>8713</v>
+        <v>8710</v>
       </c>
       <c r="G2119" s="6" t="s">
-        <v>8714</v>
+        <v>8711</v>
       </c>
       <c r="H2119" s="6" t="s">
-        <v>8726</v>
-      </c>
-      <c r="I2119" s="32" t="s">
-        <v>8707</v>
+        <v>8723</v>
+      </c>
+      <c r="I2119" s="30" t="s">
+        <v>8704</v>
       </c>
     </row>
     <row r="2120" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2120" s="12" t="s">
-        <v>8727</v>
+        <v>8724</v>
       </c>
       <c r="B2120" s="7">
         <v>96770218</v>
       </c>
       <c r="C2120" s="6" t="s">
-        <v>8728</v>
+        <v>8725</v>
       </c>
       <c r="D2120" s="6" t="s">
-        <v>8718</v>
+        <v>8715</v>
       </c>
       <c r="F2120" s="6" t="s">
-        <v>8713</v>
+        <v>8710</v>
       </c>
       <c r="G2120" s="6" t="s">
-        <v>8714</v>
+        <v>8711</v>
       </c>
       <c r="H2120" s="6" t="s">
-        <v>8729</v>
-      </c>
-      <c r="I2120" s="32" t="s">
-        <v>8708</v>
+        <v>8726</v>
+      </c>
+      <c r="I2120" s="30" t="s">
+        <v>8705</v>
       </c>
     </row>
     <row r="2121" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2121" s="12" t="s">
-        <v>8730</v>
+        <v>8727</v>
       </c>
       <c r="B2121" s="7">
         <v>79962796</v>
       </c>
       <c r="C2121" s="6" t="s">
-        <v>8731</v>
+        <v>8728</v>
       </c>
       <c r="D2121" s="6" t="s">
-        <v>8718</v>
+        <v>8715</v>
       </c>
       <c r="F2121" s="6" t="s">
-        <v>8713</v>
+        <v>8710</v>
       </c>
       <c r="G2121" s="6" t="s">
-        <v>8714</v>
+        <v>8711</v>
       </c>
       <c r="H2121" s="6" t="s">
-        <v>8732</v>
-      </c>
-      <c r="I2121" s="32" t="s">
-        <v>8709</v>
+        <v>8729</v>
+      </c>
+      <c r="I2121" s="30" t="s">
+        <v>8706</v>
       </c>
     </row>
     <row r="2122" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2122" s="12" t="s">
-        <v>8733</v>
+        <v>8730</v>
       </c>
       <c r="B2122" s="7">
         <v>54398652</v>
       </c>
       <c r="C2122" s="6" t="s">
-        <v>8734</v>
+        <v>8731</v>
       </c>
       <c r="D2122" s="6" t="s">
-        <v>8735</v>
+        <v>8732</v>
       </c>
       <c r="F2122" s="6" t="s">
-        <v>8713</v>
+        <v>8710</v>
       </c>
       <c r="G2122" s="6" t="s">
-        <v>8714</v>
+        <v>8711</v>
       </c>
       <c r="H2122" s="6" t="s">
-        <v>8736</v>
-      </c>
-      <c r="I2122" s="32" t="s">
-        <v>8707</v>
+        <v>8733</v>
+      </c>
+      <c r="I2122" s="30" t="s">
+        <v>8704</v>
       </c>
     </row>
     <row r="2123" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2123" s="5" t="s">
-        <v>8738</v>
+        <v>8735</v>
       </c>
       <c r="B2123" s="3" t="s">
+        <v>8734</v>
+      </c>
+      <c r="C2123" s="32" t="s">
         <v>8737</v>
       </c>
-      <c r="C2123" s="34" t="s">
-        <v>8740</v>
-      </c>
       <c r="D2123" s="1" t="s">
-        <v>8739</v>
+        <v>8736</v>
       </c>
     </row>
     <row r="2124" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2124" s="12" t="s">
-        <v>8741</v>
+        <v>8738</v>
       </c>
       <c r="B2124" s="7">
         <v>79838241</v>
       </c>
       <c r="C2124" s="6" t="s">
+        <v>8739</v>
+      </c>
+      <c r="D2124" s="6" t="s">
+        <v>8740</v>
+      </c>
+      <c r="F2124" s="6" t="s">
+        <v>8741</v>
+      </c>
+      <c r="G2124" s="6" t="s">
         <v>8742</v>
       </c>
-      <c r="D2124" s="6" t="s">
-        <v>8743</v>
-      </c>
-      <c r="F2124" s="6" t="s">
-        <v>8744</v>
-      </c>
-      <c r="G2124" s="6" t="s">
-        <v>8745</v>
-      </c>
-      <c r="I2124" s="32"/>
+      <c r="I2124" s="30"/>
     </row>
     <row r="2125" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2125" s="12" t="s">
-        <v>8746</v>
+        <v>8743</v>
       </c>
       <c r="B2125" s="7">
         <v>24926184</v>
       </c>
       <c r="C2125" s="6" t="s">
-        <v>8747</v>
+        <v>8744</v>
       </c>
       <c r="D2125" s="6" t="s">
-        <v>8743</v>
+        <v>8740</v>
       </c>
       <c r="F2125" s="6" t="s">
-        <v>8744</v>
+        <v>8741</v>
       </c>
       <c r="G2125" s="6" t="s">
+        <v>8742</v>
+      </c>
+      <c r="H2125" s="6" t="s">
         <v>8745</v>
       </c>
-      <c r="H2125" s="6" t="s">
-        <v>8748</v>
-      </c>
-      <c r="I2125" s="32" t="s">
-        <v>8749</v>
+      <c r="I2125" s="30" t="s">
+        <v>8746</v>
       </c>
     </row>
     <row r="2126" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2126" s="12" t="s">
-        <v>8750</v>
+        <v>8747</v>
       </c>
       <c r="B2126" s="7">
         <v>93369894</v>
       </c>
       <c r="C2126" s="6" t="s">
-        <v>8751</v>
+        <v>8748</v>
       </c>
       <c r="D2126" s="6" t="s">
-        <v>8743</v>
+        <v>8740</v>
       </c>
       <c r="F2126" s="6" t="s">
-        <v>8744</v>
+        <v>8741</v>
       </c>
       <c r="G2126" s="6" t="s">
-        <v>8745</v>
-      </c>
-      <c r="I2126" s="32"/>
+        <v>8742</v>
+      </c>
+      <c r="I2126" s="30"/>
     </row>
     <row r="2127" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2127" s="12" t="s">
-        <v>8752</v>
+        <v>8749</v>
       </c>
       <c r="B2127" s="7">
         <v>29166887</v>
       </c>
       <c r="C2127" s="6" t="s">
-        <v>8753</v>
+        <v>8750</v>
       </c>
       <c r="D2127" s="6" t="s">
-        <v>8743</v>
+        <v>8740</v>
       </c>
       <c r="F2127" s="6" t="s">
-        <v>8744</v>
+        <v>8741</v>
       </c>
       <c r="G2127" s="6" t="s">
-        <v>8745</v>
-      </c>
-      <c r="I2127" s="32"/>
+        <v>8742</v>
+      </c>
+      <c r="I2127" s="30"/>
     </row>
     <row r="2128" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2128" s="12" t="s">
-        <v>8754</v>
+        <v>8751</v>
       </c>
       <c r="B2128" s="7">
         <v>54014332</v>
       </c>
       <c r="C2128" s="6" t="s">
-        <v>8755</v>
+        <v>8752</v>
       </c>
       <c r="D2128" s="6" t="s">
-        <v>8743</v>
+        <v>8740</v>
       </c>
       <c r="F2128" s="6" t="s">
-        <v>8744</v>
+        <v>8741</v>
       </c>
       <c r="G2128" s="6" t="s">
-        <v>8745</v>
+        <v>8742</v>
       </c>
       <c r="H2128" s="6" t="s">
-        <v>8756</v>
-      </c>
-      <c r="I2128" s="32" t="s">
-        <v>8757</v>
+        <v>8753</v>
+      </c>
+      <c r="I2128" s="30" t="s">
+        <v>8754</v>
       </c>
     </row>
     <row r="2129" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2129" s="12" t="s">
-        <v>8758</v>
+        <v>8755</v>
       </c>
       <c r="B2129" s="7">
         <v>25089142</v>
       </c>
       <c r="C2129" s="6" t="s">
+        <v>8756</v>
+      </c>
+      <c r="D2129" s="6" t="s">
+        <v>8757</v>
+      </c>
+      <c r="F2129" s="6" t="s">
+        <v>8741</v>
+      </c>
+      <c r="G2129" s="6" t="s">
+        <v>8742</v>
+      </c>
+      <c r="H2129" s="6" t="s">
+        <v>8758</v>
+      </c>
+      <c r="I2129" s="30" t="s">
         <v>8759</v>
-      </c>
-      <c r="D2129" s="6" t="s">
-        <v>8760</v>
-      </c>
-      <c r="F2129" s="6" t="s">
-        <v>8744</v>
-      </c>
-      <c r="G2129" s="6" t="s">
-        <v>8745</v>
-      </c>
-      <c r="H2129" s="6" t="s">
-        <v>8761</v>
-      </c>
-      <c r="I2129" s="32" t="s">
-        <v>8762</v>
       </c>
     </row>
     <row r="2130" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2130" s="12" t="s">
-        <v>8763</v>
+        <v>8760</v>
       </c>
       <c r="B2130" s="7">
         <v>70634323</v>
       </c>
       <c r="C2130" s="6" t="s">
-        <v>8764</v>
+        <v>8761</v>
       </c>
       <c r="D2130" s="6" t="s">
-        <v>8743</v>
+        <v>8740</v>
       </c>
       <c r="F2130" s="6" t="s">
-        <v>8744</v>
+        <v>8741</v>
       </c>
       <c r="G2130" s="6" t="s">
-        <v>8745</v>
+        <v>8742</v>
       </c>
       <c r="H2130" s="6" t="s">
-        <v>8765</v>
-      </c>
-      <c r="I2130" s="32" t="s">
-        <v>8766</v>
+        <v>8762</v>
+      </c>
+      <c r="I2130" s="30" t="s">
+        <v>8763</v>
       </c>
     </row>
     <row r="2131" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2131" s="12" t="s">
-        <v>8767</v>
+        <v>8764</v>
       </c>
       <c r="B2131" s="7">
         <v>54726923</v>
       </c>
       <c r="C2131" s="6" t="s">
-        <v>8768</v>
+        <v>8765</v>
       </c>
       <c r="D2131" s="6" t="s">
-        <v>8743</v>
+        <v>8740</v>
       </c>
       <c r="F2131" s="6" t="s">
-        <v>8744</v>
+        <v>8741</v>
       </c>
       <c r="G2131" s="6" t="s">
-        <v>8745</v>
+        <v>8742</v>
       </c>
       <c r="H2131" s="6" t="s">
-        <v>8769</v>
-      </c>
-      <c r="I2131" s="32" t="s">
-        <v>8770</v>
-      </c>
-    </row>
-    <row r="2132" spans="1:9" s="31" customFormat="1" ht="21.95" customHeight="1">
-      <c r="A2132" s="30" t="s">
-        <v>8571</v>
-      </c>
-      <c r="B2132" s="30">
-        <v>52693448</v>
-      </c>
-      <c r="C2132" s="30" t="s">
-        <v>8569</v>
-      </c>
-      <c r="D2132" s="30" t="s">
-        <v>8570</v>
-      </c>
-      <c r="E2132" s="31" t="s">
-        <v>8572</v>
-      </c>
-      <c r="F2132" s="31" t="s">
-        <v>8573</v>
-      </c>
-      <c r="G2132" s="31" t="s">
-        <v>3798</v>
-      </c>
+        <v>8766</v>
+      </c>
+      <c r="I2131" s="30" t="s">
+        <v>8767</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2132" s="12" t="s">
+        <v>8771</v>
+      </c>
+      <c r="B2132" s="7">
+        <v>96799025</v>
+      </c>
+      <c r="C2132" s="6" t="s">
+        <v>8772</v>
+      </c>
+      <c r="D2132" s="6" t="s">
+        <v>8773</v>
+      </c>
+      <c r="F2132" s="6" t="s">
+        <v>8774</v>
+      </c>
+      <c r="G2132" s="6" t="s">
+        <v>8775</v>
+      </c>
+      <c r="I2132" s="30"/>
     </row>
     <row r="2133" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2133" s="12" t="s">
+        <v>8776</v>
+      </c>
+      <c r="B2133" s="7">
+        <v>82914313</v>
+      </c>
+      <c r="C2133" s="6" t="s">
+        <v>8777</v>
+      </c>
+      <c r="D2133" s="6" t="s">
+        <v>8773</v>
+      </c>
+      <c r="F2133" s="6" t="s">
         <v>8774</v>
       </c>
-      <c r="B2133" s="7">
-        <v>96799025</v>
-      </c>
-      <c r="C2133" s="6" t="s">
+      <c r="G2133" s="6" t="s">
         <v>8775</v>
       </c>
-      <c r="D2133" s="6" t="s">
-        <v>8776</v>
-      </c>
-      <c r="F2133" s="6" t="s">
-        <v>8777</v>
-      </c>
-      <c r="G2133" s="6" t="s">
-        <v>8778</v>
-      </c>
-      <c r="I2133" s="32"/>
+      <c r="H2133" s="6" t="s">
+        <v>8769</v>
+      </c>
+      <c r="I2133" s="30" t="s">
+        <v>8770</v>
+      </c>
     </row>
     <row r="2134" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2134" s="12" t="s">
+        <v>8778</v>
+      </c>
+      <c r="B2134" s="7">
+        <v>28043986</v>
+      </c>
+      <c r="C2134" s="6" t="s">
         <v>8779</v>
       </c>
-      <c r="B2134" s="7">
-        <v>82914313</v>
-      </c>
-      <c r="C2134" s="6" t="s">
+      <c r="D2134" s="6" t="s">
+        <v>8773</v>
+      </c>
+      <c r="F2134" s="6" t="s">
+        <v>8774</v>
+      </c>
+      <c r="G2134" s="6" t="s">
+        <v>8775</v>
+      </c>
+      <c r="H2134" s="6" t="s">
         <v>8780</v>
       </c>
-      <c r="D2134" s="6" t="s">
-        <v>8776</v>
-      </c>
-      <c r="F2134" s="6" t="s">
-        <v>8777</v>
-      </c>
-      <c r="G2134" s="6" t="s">
-        <v>8778</v>
-      </c>
-      <c r="H2134" s="6" t="s">
-        <v>8772</v>
-      </c>
-      <c r="I2134" s="32" t="s">
-        <v>8773</v>
+      <c r="I2134" s="30" t="s">
+        <v>8781</v>
       </c>
     </row>
     <row r="2135" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2135" s="12" t="s">
-        <v>8781</v>
+        <v>8782</v>
       </c>
       <c r="B2135" s="7">
-        <v>28043986</v>
+        <v>89396770</v>
       </c>
       <c r="C2135" s="6" t="s">
-        <v>8782</v>
+        <v>8783</v>
       </c>
       <c r="D2135" s="6" t="s">
-        <v>8776</v>
+        <v>8773</v>
       </c>
       <c r="F2135" s="6" t="s">
-        <v>8777</v>
+        <v>8774</v>
       </c>
       <c r="G2135" s="6" t="s">
-        <v>8778</v>
+        <v>8775</v>
       </c>
       <c r="H2135" s="6" t="s">
-        <v>8783</v>
-      </c>
-      <c r="I2135" s="32" t="s">
         <v>8784</v>
+      </c>
+      <c r="I2135" s="30" t="s">
+        <v>8785</v>
       </c>
     </row>
     <row r="2136" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2136" s="12" t="s">
-        <v>8785</v>
-      </c>
-      <c r="B2136" s="7">
-        <v>89396770</v>
+        <v>8786</v>
+      </c>
+      <c r="B2136" s="7" t="s">
+        <v>8768</v>
       </c>
       <c r="C2136" s="6" t="s">
-        <v>8786</v>
+        <v>8787</v>
       </c>
       <c r="D2136" s="6" t="s">
-        <v>8776</v>
+        <v>8788</v>
       </c>
       <c r="F2136" s="6" t="s">
-        <v>8777</v>
+        <v>8789</v>
       </c>
       <c r="G2136" s="6" t="s">
-        <v>8778</v>
-      </c>
-      <c r="H2136" s="6" t="s">
-        <v>8787</v>
-      </c>
-      <c r="I2136" s="32" t="s">
-        <v>8788</v>
-      </c>
+        <v>8790</v>
+      </c>
+      <c r="I2136" s="30"/>
     </row>
     <row r="2137" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2137" s="12" t="s">
-        <v>8789</v>
-      </c>
-      <c r="B2137" s="7" t="s">
-        <v>8771</v>
+        <v>8791</v>
+      </c>
+      <c r="B2137" s="7">
+        <v>83483376</v>
       </c>
       <c r="C2137" s="6" t="s">
-        <v>8790</v>
+        <v>8792</v>
       </c>
       <c r="D2137" s="6" t="s">
-        <v>8791</v>
+        <v>8793</v>
       </c>
       <c r="F2137" s="6" t="s">
-        <v>8792</v>
+        <v>8794</v>
       </c>
       <c r="G2137" s="6" t="s">
-        <v>8793</v>
-      </c>
-      <c r="I2137" s="32"/>
+        <v>8795</v>
+      </c>
+      <c r="I2137" s="30"/>
     </row>
     <row r="2138" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2138" s="12" t="s">
+        <v>8796</v>
+      </c>
+      <c r="B2138" s="7">
+        <v>28339685</v>
+      </c>
+      <c r="C2138" s="6" t="s">
+        <v>8797</v>
+      </c>
+      <c r="D2138" s="6" t="s">
+        <v>8793</v>
+      </c>
+      <c r="F2138" s="6" t="s">
         <v>8794</v>
       </c>
-      <c r="B2138" s="7">
-        <v>83483376</v>
-      </c>
-      <c r="C2138" s="6" t="s">
+      <c r="G2138" s="6" t="s">
         <v>8795</v>
       </c>
-      <c r="D2138" s="6" t="s">
-        <v>8796</v>
-      </c>
-      <c r="F2138" s="6" t="s">
-        <v>8797</v>
-      </c>
-      <c r="G2138" s="6" t="s">
+      <c r="H2138" s="6" t="s">
         <v>8798</v>
       </c>
-      <c r="I2138" s="32"/>
+      <c r="I2138" s="30" t="s">
+        <v>8799</v>
+      </c>
     </row>
     <row r="2139" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2139" s="12" t="s">
-        <v>8799</v>
+        <v>8800</v>
       </c>
       <c r="B2139" s="7">
-        <v>28339685</v>
+        <v>59214274</v>
       </c>
       <c r="C2139" s="6" t="s">
-        <v>8800</v>
+        <v>8801</v>
       </c>
       <c r="D2139" s="6" t="s">
-        <v>8796</v>
+        <v>8793</v>
       </c>
       <c r="F2139" s="6" t="s">
-        <v>8797</v>
+        <v>8794</v>
       </c>
       <c r="G2139" s="6" t="s">
-        <v>8798</v>
+        <v>8795</v>
       </c>
       <c r="H2139" s="6" t="s">
-        <v>8801</v>
-      </c>
-      <c r="I2139" s="32" t="s">
         <v>8802</v>
+      </c>
+      <c r="I2139" s="30" t="s">
+        <v>8803</v>
       </c>
     </row>
     <row r="2140" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2140" s="12" t="s">
-        <v>8803</v>
+        <v>8804</v>
       </c>
       <c r="B2140" s="7">
-        <v>59214274</v>
+        <v>53137700</v>
       </c>
       <c r="C2140" s="6" t="s">
-        <v>8804</v>
+        <v>8805</v>
       </c>
       <c r="D2140" s="6" t="s">
-        <v>8796</v>
+        <v>8793</v>
       </c>
       <c r="F2140" s="6" t="s">
-        <v>8797</v>
+        <v>8794</v>
       </c>
       <c r="G2140" s="6" t="s">
-        <v>8798</v>
+        <v>8795</v>
       </c>
       <c r="H2140" s="6" t="s">
-        <v>8805</v>
-      </c>
-      <c r="I2140" s="32" t="s">
         <v>8806</v>
+      </c>
+      <c r="I2140" s="30" t="s">
+        <v>8807</v>
       </c>
     </row>
     <row r="2141" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2141" s="12" t="s">
-        <v>8807</v>
+        <v>8808</v>
       </c>
       <c r="B2141" s="7">
-        <v>53137700</v>
+        <v>84070747</v>
       </c>
       <c r="C2141" s="6" t="s">
-        <v>8808</v>
+        <v>8809</v>
       </c>
       <c r="D2141" s="6" t="s">
-        <v>8796</v>
+        <v>8773</v>
       </c>
       <c r="F2141" s="6" t="s">
-        <v>8797</v>
+        <v>8774</v>
       </c>
       <c r="G2141" s="6" t="s">
-        <v>8798</v>
+        <v>8775</v>
       </c>
       <c r="H2141" s="6" t="s">
-        <v>8809</v>
-      </c>
-      <c r="I2141" s="32" t="s">
         <v>8810</v>
+      </c>
+      <c r="I2141" s="30" t="s">
+        <v>8811</v>
       </c>
     </row>
     <row r="2142" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2142" s="12" t="s">
-        <v>8811</v>
+        <v>8812</v>
       </c>
       <c r="B2142" s="7">
-        <v>84070747</v>
+        <v>54135526</v>
       </c>
       <c r="C2142" s="6" t="s">
-        <v>8812</v>
+        <v>8813</v>
       </c>
       <c r="D2142" s="6" t="s">
-        <v>8776</v>
+        <v>8773</v>
       </c>
       <c r="F2142" s="6" t="s">
-        <v>8777</v>
+        <v>8774</v>
       </c>
       <c r="G2142" s="6" t="s">
-        <v>8778</v>
+        <v>8775</v>
       </c>
       <c r="H2142" s="6" t="s">
-        <v>8813</v>
-      </c>
-      <c r="I2142" s="32" t="s">
         <v>8814</v>
+      </c>
+      <c r="I2142" s="30" t="s">
+        <v>8815</v>
       </c>
     </row>
     <row r="2143" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
       <c r="A2143" s="12" t="s">
-        <v>8815</v>
+        <v>8816</v>
       </c>
       <c r="B2143" s="7">
-        <v>54135526</v>
+        <v>16766959</v>
       </c>
       <c r="C2143" s="6" t="s">
-        <v>8816</v>
+        <v>8817</v>
       </c>
       <c r="D2143" s="6" t="s">
-        <v>8776</v>
+        <v>8773</v>
       </c>
       <c r="F2143" s="6" t="s">
-        <v>8777</v>
+        <v>8774</v>
       </c>
       <c r="G2143" s="6" t="s">
-        <v>8778</v>
+        <v>8775</v>
       </c>
       <c r="H2143" s="6" t="s">
-        <v>8817</v>
-      </c>
-      <c r="I2143" s="32" t="s">
         <v>8818</v>
       </c>
-    </row>
-    <row r="2144" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1">
-      <c r="A2144" s="12" t="s">
+      <c r="I2143" s="30" t="s">
         <v>8819</v>
       </c>
-      <c r="B2144" s="7">
-        <v>16766959</v>
-      </c>
-      <c r="C2144" s="6" t="s">
+    </row>
+    <row r="2144" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2144" s="5" t="s">
         <v>8820</v>
       </c>
-      <c r="D2144" s="6" t="s">
-        <v>8776</v>
-      </c>
-      <c r="F2144" s="6" t="s">
-        <v>8777</v>
-      </c>
-      <c r="G2144" s="6" t="s">
-        <v>8778</v>
-      </c>
-      <c r="H2144" s="6" t="s">
-        <v>8821</v>
-      </c>
-      <c r="I2144" s="32" t="s">
-        <v>8822</v>
+      <c r="B2144" s="3">
+        <v>13025089</v>
+      </c>
+      <c r="C2144" s="1" t="s">
+        <v>8878</v>
+      </c>
+      <c r="D2144" s="1" t="s">
+        <v>8935</v>
+      </c>
+      <c r="E2144" s="1" t="s">
+        <v>3940</v>
       </c>
     </row>
     <row r="2145" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2145" s="5" t="s">
-        <v>8823</v>
+        <v>8821</v>
       </c>
       <c r="B2145" s="3">
-        <v>13025089</v>
+        <v>42942664</v>
       </c>
       <c r="C2145" s="1" t="s">
-        <v>8881</v>
+        <v>8879</v>
       </c>
       <c r="D2145" s="1" t="s">
-        <v>8938</v>
+        <v>8936</v>
       </c>
       <c r="E2145" s="1" t="s">
         <v>3940</v>
@@ -74634,16 +74902,16 @@
     </row>
     <row r="2146" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2146" s="5" t="s">
-        <v>8824</v>
+        <v>8822</v>
       </c>
       <c r="B2146" s="3">
-        <v>42942664</v>
+        <v>90895471</v>
       </c>
       <c r="C2146" s="1" t="s">
-        <v>8882</v>
+        <v>8880</v>
       </c>
       <c r="D2146" s="1" t="s">
-        <v>8939</v>
+        <v>8937</v>
       </c>
       <c r="E2146" s="1" t="s">
         <v>3940</v>
@@ -74651,16 +74919,16 @@
     </row>
     <row r="2147" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2147" s="5" t="s">
-        <v>8825</v>
+        <v>8823</v>
       </c>
       <c r="B2147" s="3">
-        <v>90895471</v>
+        <v>30926062</v>
       </c>
       <c r="C2147" s="1" t="s">
-        <v>8883</v>
+        <v>8881</v>
       </c>
       <c r="D2147" s="1" t="s">
-        <v>8940</v>
+        <v>8938</v>
       </c>
       <c r="E2147" s="1" t="s">
         <v>3940</v>
@@ -74668,16 +74936,16 @@
     </row>
     <row r="2148" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2148" s="5" t="s">
-        <v>8826</v>
+        <v>8824</v>
       </c>
       <c r="B2148" s="3">
-        <v>30926062</v>
+        <v>90780816</v>
       </c>
       <c r="C2148" s="1" t="s">
-        <v>8884</v>
+        <v>8882</v>
       </c>
       <c r="D2148" s="1" t="s">
-        <v>8941</v>
+        <v>8939</v>
       </c>
       <c r="E2148" s="1" t="s">
         <v>3940</v>
@@ -74685,16 +74953,16 @@
     </row>
     <row r="2149" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2149" s="5" t="s">
-        <v>8827</v>
+        <v>8825</v>
       </c>
       <c r="B2149" s="3">
-        <v>90780816</v>
+        <v>54252501</v>
       </c>
       <c r="C2149" s="1" t="s">
-        <v>8885</v>
+        <v>8883</v>
       </c>
       <c r="D2149" s="1" t="s">
-        <v>8942</v>
+        <v>8940</v>
       </c>
       <c r="E2149" s="1" t="s">
         <v>3940</v>
@@ -74702,16 +74970,16 @@
     </row>
     <row r="2150" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2150" s="5" t="s">
-        <v>8828</v>
+        <v>8827</v>
       </c>
       <c r="B2150" s="3">
-        <v>54252501</v>
+        <v>83591516</v>
       </c>
       <c r="C2150" s="1" t="s">
-        <v>8886</v>
+        <v>8884</v>
       </c>
       <c r="D2150" s="1" t="s">
-        <v>8943</v>
+        <v>8941</v>
       </c>
       <c r="E2150" s="1" t="s">
         <v>3940</v>
@@ -74719,16 +74987,16 @@
     </row>
     <row r="2151" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2151" s="5" t="s">
-        <v>8830</v>
+        <v>8828</v>
       </c>
       <c r="B2151" s="3">
-        <v>83591516</v>
+        <v>84521378</v>
       </c>
       <c r="C2151" s="1" t="s">
-        <v>8887</v>
+        <v>8885</v>
       </c>
       <c r="D2151" s="1" t="s">
-        <v>8944</v>
+        <v>8942</v>
       </c>
       <c r="E2151" s="1" t="s">
         <v>3940</v>
@@ -74736,16 +75004,16 @@
     </row>
     <row r="2152" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2152" s="5" t="s">
-        <v>8831</v>
+        <v>8829</v>
       </c>
       <c r="B2152" s="3">
-        <v>84521378</v>
+        <v>75914885</v>
       </c>
       <c r="C2152" s="1" t="s">
-        <v>8888</v>
+        <v>8886</v>
       </c>
       <c r="D2152" s="1" t="s">
-        <v>8945</v>
+        <v>8943</v>
       </c>
       <c r="E2152" s="1" t="s">
         <v>3940</v>
@@ -74753,16 +75021,16 @@
     </row>
     <row r="2153" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2153" s="5" t="s">
-        <v>8832</v>
+        <v>8830</v>
       </c>
       <c r="B2153" s="3">
-        <v>75914885</v>
+        <v>85091972</v>
       </c>
       <c r="C2153" s="1" t="s">
-        <v>8889</v>
+        <v>8887</v>
       </c>
       <c r="D2153" s="1" t="s">
-        <v>8946</v>
+        <v>8944</v>
       </c>
       <c r="E2153" s="1" t="s">
         <v>3940</v>
@@ -74770,16 +75038,16 @@
     </row>
     <row r="2154" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2154" s="5" t="s">
-        <v>8833</v>
+        <v>8831</v>
       </c>
       <c r="B2154" s="3">
-        <v>85091972</v>
+        <v>16491312</v>
       </c>
       <c r="C2154" s="1" t="s">
-        <v>8890</v>
+        <v>8888</v>
       </c>
       <c r="D2154" s="1" t="s">
-        <v>8947</v>
+        <v>8945</v>
       </c>
       <c r="E2154" s="1" t="s">
         <v>3940</v>
@@ -74787,16 +75055,16 @@
     </row>
     <row r="2155" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2155" s="5" t="s">
-        <v>8834</v>
+        <v>8832</v>
       </c>
       <c r="B2155" s="3">
-        <v>16491312</v>
+        <v>89649769</v>
       </c>
       <c r="C2155" s="1" t="s">
-        <v>8891</v>
+        <v>8889</v>
       </c>
       <c r="D2155" s="1" t="s">
-        <v>8948</v>
+        <v>8946</v>
       </c>
       <c r="E2155" s="1" t="s">
         <v>3940</v>
@@ -74804,16 +75072,16 @@
     </row>
     <row r="2156" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2156" s="5" t="s">
-        <v>8835</v>
+        <v>8833</v>
       </c>
       <c r="B2156" s="3">
-        <v>89649769</v>
+        <v>16980249</v>
       </c>
       <c r="C2156" s="1" t="s">
-        <v>8892</v>
+        <v>8890</v>
       </c>
       <c r="D2156" s="1" t="s">
-        <v>8949</v>
+        <v>8947</v>
       </c>
       <c r="E2156" s="1" t="s">
         <v>3940</v>
@@ -74821,16 +75089,16 @@
     </row>
     <row r="2157" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2157" s="5" t="s">
-        <v>8836</v>
+        <v>8834</v>
       </c>
       <c r="B2157" s="3">
-        <v>16980249</v>
+        <v>16690537</v>
       </c>
       <c r="C2157" s="1" t="s">
-        <v>8893</v>
+        <v>8891</v>
       </c>
       <c r="D2157" s="1" t="s">
-        <v>8950</v>
+        <v>8948</v>
       </c>
       <c r="E2157" s="1" t="s">
         <v>3940</v>
@@ -74838,16 +75106,16 @@
     </row>
     <row r="2158" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2158" s="5" t="s">
-        <v>8837</v>
+        <v>8835</v>
       </c>
       <c r="B2158" s="3">
-        <v>16690537</v>
+        <v>42751762</v>
       </c>
       <c r="C2158" s="1" t="s">
-        <v>8894</v>
+        <v>8892</v>
       </c>
       <c r="D2158" s="1" t="s">
-        <v>8951</v>
+        <v>4169</v>
       </c>
       <c r="E2158" s="1" t="s">
         <v>3940</v>
@@ -74855,16 +75123,16 @@
     </row>
     <row r="2159" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2159" s="5" t="s">
-        <v>8838</v>
+        <v>8836</v>
       </c>
       <c r="B2159" s="3">
-        <v>42751762</v>
+        <v>54705407</v>
       </c>
       <c r="C2159" s="1" t="s">
-        <v>8895</v>
+        <v>8893</v>
       </c>
       <c r="D2159" s="1" t="s">
-        <v>4169</v>
+        <v>8949</v>
       </c>
       <c r="E2159" s="1" t="s">
         <v>3940</v>
@@ -74872,16 +75140,16 @@
     </row>
     <row r="2160" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2160" s="5" t="s">
-        <v>8839</v>
+        <v>8837</v>
       </c>
       <c r="B2160" s="3">
-        <v>54705407</v>
+        <v>24439184</v>
       </c>
       <c r="C2160" s="1" t="s">
-        <v>8896</v>
+        <v>8885</v>
       </c>
       <c r="D2160" s="1" t="s">
-        <v>8952</v>
+        <v>8942</v>
       </c>
       <c r="E2160" s="1" t="s">
         <v>3940</v>
@@ -74889,16 +75157,16 @@
     </row>
     <row r="2161" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2161" s="5" t="s">
-        <v>8840</v>
+        <v>8838</v>
       </c>
       <c r="B2161" s="3">
-        <v>24439184</v>
+        <v>81464351</v>
       </c>
       <c r="C2161" s="1" t="s">
-        <v>8888</v>
+        <v>8894</v>
       </c>
       <c r="D2161" s="1" t="s">
-        <v>8945</v>
+        <v>4169</v>
       </c>
       <c r="E2161" s="1" t="s">
         <v>3940</v>
@@ -74906,13 +75174,13 @@
     </row>
     <row r="2162" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2162" s="5" t="s">
-        <v>8841</v>
+        <v>8838</v>
       </c>
       <c r="B2162" s="3">
         <v>81464351</v>
       </c>
       <c r="C2162" s="1" t="s">
-        <v>8897</v>
+        <v>8895</v>
       </c>
       <c r="D2162" s="1" t="s">
         <v>4169</v>
@@ -74923,16 +75191,16 @@
     </row>
     <row r="2163" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2163" s="5" t="s">
-        <v>8841</v>
+        <v>8839</v>
       </c>
       <c r="B2163" s="3">
-        <v>81464351</v>
+        <v>70803848</v>
       </c>
       <c r="C2163" s="1" t="s">
-        <v>8898</v>
+        <v>8896</v>
       </c>
       <c r="D2163" s="1" t="s">
-        <v>4169</v>
+        <v>8950</v>
       </c>
       <c r="E2163" s="1" t="s">
         <v>3940</v>
@@ -74940,16 +75208,16 @@
     </row>
     <row r="2164" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2164" s="5" t="s">
-        <v>8842</v>
+        <v>8840</v>
       </c>
       <c r="B2164" s="3">
-        <v>70803848</v>
+        <v>83222751</v>
       </c>
       <c r="C2164" s="1" t="s">
-        <v>8899</v>
+        <v>8897</v>
       </c>
       <c r="D2164" s="1" t="s">
-        <v>8953</v>
+        <v>4169</v>
       </c>
       <c r="E2164" s="1" t="s">
         <v>3940</v>
@@ -74957,16 +75225,16 @@
     </row>
     <row r="2165" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2165" s="5" t="s">
-        <v>8843</v>
+        <v>8841</v>
       </c>
       <c r="B2165" s="3">
-        <v>83222751</v>
+        <v>89819285</v>
       </c>
       <c r="C2165" s="1" t="s">
-        <v>8900</v>
+        <v>8898</v>
       </c>
       <c r="D2165" s="1" t="s">
-        <v>4169</v>
+        <v>8951</v>
       </c>
       <c r="E2165" s="1" t="s">
         <v>3940</v>
@@ -74974,16 +75242,16 @@
     </row>
     <row r="2166" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2166" s="5" t="s">
-        <v>8844</v>
+        <v>8842</v>
       </c>
       <c r="B2166" s="3">
-        <v>89819285</v>
+        <v>28102979</v>
       </c>
       <c r="C2166" s="1" t="s">
-        <v>8901</v>
+        <v>8899</v>
       </c>
       <c r="D2166" s="1" t="s">
-        <v>8954</v>
+        <v>8951</v>
       </c>
       <c r="E2166" s="1" t="s">
         <v>3940</v>
@@ -74991,16 +75259,16 @@
     </row>
     <row r="2167" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2167" s="5" t="s">
-        <v>8845</v>
+        <v>8843</v>
       </c>
       <c r="B2167" s="3">
-        <v>28102979</v>
+        <v>55841816</v>
       </c>
       <c r="C2167" s="1" t="s">
-        <v>8902</v>
+        <v>8900</v>
       </c>
       <c r="D2167" s="1" t="s">
-        <v>8954</v>
+        <v>8952</v>
       </c>
       <c r="E2167" s="1" t="s">
         <v>3940</v>
@@ -75008,16 +75276,16 @@
     </row>
     <row r="2168" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2168" s="5" t="s">
-        <v>8846</v>
+        <v>8844</v>
       </c>
       <c r="B2168" s="3">
-        <v>55841816</v>
+        <v>90369060</v>
       </c>
       <c r="C2168" s="1" t="s">
-        <v>8903</v>
+        <v>8885</v>
       </c>
       <c r="D2168" s="1" t="s">
-        <v>8955</v>
+        <v>8942</v>
       </c>
       <c r="E2168" s="1" t="s">
         <v>3940</v>
@@ -75025,16 +75293,16 @@
     </row>
     <row r="2169" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2169" s="5" t="s">
-        <v>8847</v>
+        <v>8845</v>
       </c>
       <c r="B2169" s="3">
-        <v>90369060</v>
+        <v>24775171</v>
       </c>
       <c r="C2169" s="1" t="s">
-        <v>8888</v>
+        <v>8901</v>
       </c>
       <c r="D2169" s="1" t="s">
-        <v>8945</v>
+        <v>8953</v>
       </c>
       <c r="E2169" s="1" t="s">
         <v>3940</v>
@@ -75042,16 +75310,16 @@
     </row>
     <row r="2170" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2170" s="5" t="s">
-        <v>8848</v>
+        <v>8846</v>
       </c>
       <c r="B2170" s="3">
-        <v>24775171</v>
+        <v>54979243</v>
       </c>
       <c r="C2170" s="1" t="s">
-        <v>8904</v>
+        <v>8902</v>
       </c>
       <c r="D2170" s="1" t="s">
-        <v>8956</v>
+        <v>8954</v>
       </c>
       <c r="E2170" s="1" t="s">
         <v>3940</v>
@@ -75059,16 +75327,16 @@
     </row>
     <row r="2171" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2171" s="5" t="s">
-        <v>8849</v>
+        <v>8847</v>
       </c>
       <c r="B2171" s="3">
-        <v>54979243</v>
+        <v>54127434</v>
       </c>
       <c r="C2171" s="1" t="s">
-        <v>8905</v>
+        <v>8903</v>
       </c>
       <c r="D2171" s="1" t="s">
-        <v>8957</v>
+        <v>8955</v>
       </c>
       <c r="E2171" s="1" t="s">
         <v>3940</v>
@@ -75076,16 +75344,16 @@
     </row>
     <row r="2172" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2172" s="5" t="s">
-        <v>8850</v>
+        <v>8848</v>
       </c>
       <c r="B2172" s="3">
-        <v>54127434</v>
+        <v>70757485</v>
       </c>
       <c r="C2172" s="1" t="s">
-        <v>8906</v>
+        <v>8904</v>
       </c>
       <c r="D2172" s="1" t="s">
-        <v>8958</v>
+        <v>8956</v>
       </c>
       <c r="E2172" s="1" t="s">
         <v>3940</v>
@@ -75093,16 +75361,16 @@
     </row>
     <row r="2173" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2173" s="5" t="s">
-        <v>8851</v>
+        <v>8849</v>
       </c>
       <c r="B2173" s="3">
-        <v>70757485</v>
+        <v>53288988</v>
       </c>
       <c r="C2173" s="1" t="s">
-        <v>8907</v>
+        <v>8905</v>
       </c>
       <c r="D2173" s="1" t="s">
-        <v>8959</v>
+        <v>8957</v>
       </c>
       <c r="E2173" s="1" t="s">
         <v>3940</v>
@@ -75110,16 +75378,16 @@
     </row>
     <row r="2174" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2174" s="5" t="s">
-        <v>8852</v>
+        <v>8850</v>
       </c>
       <c r="B2174" s="3">
-        <v>53288988</v>
+        <v>12661194</v>
       </c>
       <c r="C2174" s="1" t="s">
-        <v>8908</v>
+        <v>8906</v>
       </c>
       <c r="D2174" s="1" t="s">
-        <v>8960</v>
+        <v>4955</v>
       </c>
       <c r="E2174" s="1" t="s">
         <v>3940</v>
@@ -75127,16 +75395,16 @@
     </row>
     <row r="2175" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2175" s="5" t="s">
-        <v>8853</v>
+        <v>8851</v>
       </c>
       <c r="B2175" s="3">
-        <v>12661194</v>
+        <v>66632506</v>
       </c>
       <c r="C2175" s="1" t="s">
-        <v>8909</v>
+        <v>8885</v>
       </c>
       <c r="D2175" s="1" t="s">
-        <v>4955</v>
+        <v>8942</v>
       </c>
       <c r="E2175" s="1" t="s">
         <v>3940</v>
@@ -75144,16 +75412,16 @@
     </row>
     <row r="2176" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2176" s="5" t="s">
-        <v>8854</v>
+        <v>8852</v>
       </c>
       <c r="B2176" s="3">
-        <v>66632506</v>
+        <v>28589212</v>
       </c>
       <c r="C2176" s="1" t="s">
-        <v>8888</v>
+        <v>8907</v>
       </c>
       <c r="D2176" s="1" t="s">
-        <v>8945</v>
+        <v>8958</v>
       </c>
       <c r="E2176" s="1" t="s">
         <v>3940</v>
@@ -75161,16 +75429,16 @@
     </row>
     <row r="2177" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2177" s="5" t="s">
-        <v>8855</v>
+        <v>8853</v>
       </c>
       <c r="B2177" s="3">
-        <v>28589212</v>
+        <v>24714891</v>
       </c>
       <c r="C2177" s="1" t="s">
-        <v>8910</v>
+        <v>8908</v>
       </c>
       <c r="D2177" s="1" t="s">
-        <v>8961</v>
+        <v>8959</v>
       </c>
       <c r="E2177" s="1" t="s">
         <v>3940</v>
@@ -75178,16 +75446,16 @@
     </row>
     <row r="2178" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2178" s="5" t="s">
-        <v>8856</v>
+        <v>8854</v>
       </c>
       <c r="B2178" s="3">
-        <v>24714891</v>
+        <v>89405911</v>
       </c>
       <c r="C2178" s="1" t="s">
-        <v>8911</v>
+        <v>8909</v>
       </c>
       <c r="D2178" s="1" t="s">
-        <v>8962</v>
+        <v>8960</v>
       </c>
       <c r="E2178" s="1" t="s">
         <v>3940</v>
@@ -75195,16 +75463,16 @@
     </row>
     <row r="2179" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2179" s="5" t="s">
-        <v>8857</v>
+        <v>8855</v>
       </c>
       <c r="B2179" s="3">
-        <v>89405911</v>
+        <v>54786196</v>
       </c>
       <c r="C2179" s="1" t="s">
-        <v>8912</v>
+        <v>8910</v>
       </c>
       <c r="D2179" s="1" t="s">
-        <v>8963</v>
+        <v>8961</v>
       </c>
       <c r="E2179" s="1" t="s">
         <v>3940</v>
@@ -75212,16 +75480,16 @@
     </row>
     <row r="2180" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2180" s="5" t="s">
-        <v>8858</v>
+        <v>8856</v>
       </c>
       <c r="B2180" s="3">
-        <v>54786196</v>
+        <v>16432742</v>
       </c>
       <c r="C2180" s="1" t="s">
-        <v>8913</v>
+        <v>8911</v>
       </c>
       <c r="D2180" s="1" t="s">
-        <v>8964</v>
+        <v>5049</v>
       </c>
       <c r="E2180" s="1" t="s">
         <v>3940</v>
@@ -75229,13 +75497,13 @@
     </row>
     <row r="2181" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2181" s="5" t="s">
-        <v>8859</v>
+        <v>8856</v>
       </c>
       <c r="B2181" s="3">
         <v>16432742</v>
       </c>
       <c r="C2181" s="1" t="s">
-        <v>8914</v>
+        <v>8912</v>
       </c>
       <c r="D2181" s="1" t="s">
         <v>5049</v>
@@ -75246,16 +75514,16 @@
     </row>
     <row r="2182" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2182" s="5" t="s">
-        <v>8859</v>
+        <v>8857</v>
       </c>
       <c r="B2182" s="3">
-        <v>16432742</v>
+        <v>50787813</v>
       </c>
       <c r="C2182" s="1" t="s">
-        <v>8915</v>
+        <v>8913</v>
       </c>
       <c r="D2182" s="1" t="s">
-        <v>5049</v>
+        <v>8962</v>
       </c>
       <c r="E2182" s="1" t="s">
         <v>3940</v>
@@ -75263,16 +75531,16 @@
     </row>
     <row r="2183" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2183" s="5" t="s">
-        <v>8860</v>
+        <v>8858</v>
       </c>
       <c r="B2183" s="3">
-        <v>50787813</v>
+        <v>54378282</v>
       </c>
       <c r="C2183" s="1" t="s">
-        <v>8916</v>
+        <v>8914</v>
       </c>
       <c r="D2183" s="1" t="s">
-        <v>8965</v>
+        <v>7061</v>
       </c>
       <c r="E2183" s="1" t="s">
         <v>3940</v>
@@ -75280,16 +75548,16 @@
     </row>
     <row r="2184" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2184" s="5" t="s">
-        <v>8861</v>
+        <v>8859</v>
       </c>
       <c r="B2184" s="3">
-        <v>54378282</v>
+        <v>59196156</v>
       </c>
       <c r="C2184" s="1" t="s">
-        <v>8917</v>
+        <v>8915</v>
       </c>
       <c r="D2184" s="1" t="s">
-        <v>7061</v>
+        <v>8963</v>
       </c>
       <c r="E2184" s="1" t="s">
         <v>3940</v>
@@ -75297,16 +75565,16 @@
     </row>
     <row r="2185" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2185" s="5" t="s">
-        <v>8862</v>
+        <v>8860</v>
       </c>
       <c r="B2185" s="3">
-        <v>59196156</v>
+        <v>96860766</v>
       </c>
       <c r="C2185" s="1" t="s">
-        <v>8918</v>
+        <v>8916</v>
       </c>
       <c r="D2185" s="1" t="s">
-        <v>8966</v>
+        <v>6739</v>
       </c>
       <c r="E2185" s="1" t="s">
         <v>3940</v>
@@ -75314,16 +75582,16 @@
     </row>
     <row r="2186" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2186" s="5" t="s">
-        <v>8863</v>
+        <v>8861</v>
       </c>
       <c r="B2186" s="3">
-        <v>96860766</v>
+        <v>93626394</v>
       </c>
       <c r="C2186" s="1" t="s">
-        <v>8919</v>
+        <v>8917</v>
       </c>
       <c r="D2186" s="1" t="s">
-        <v>6739</v>
+        <v>367</v>
       </c>
       <c r="E2186" s="1" t="s">
         <v>3940</v>
@@ -75331,16 +75599,16 @@
     </row>
     <row r="2187" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2187" s="5" t="s">
-        <v>8864</v>
+        <v>8862</v>
       </c>
       <c r="B2187" s="3">
-        <v>93626394</v>
+        <v>93624327</v>
       </c>
       <c r="C2187" s="1" t="s">
-        <v>8920</v>
+        <v>8918</v>
       </c>
       <c r="D2187" s="1" t="s">
-        <v>367</v>
+        <v>8964</v>
       </c>
       <c r="E2187" s="1" t="s">
         <v>3940</v>
@@ -75348,16 +75616,16 @@
     </row>
     <row r="2188" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2188" s="5" t="s">
-        <v>8865</v>
+        <v>8863</v>
       </c>
       <c r="B2188" s="3">
-        <v>93624327</v>
+        <v>70552666</v>
       </c>
       <c r="C2188" s="1" t="s">
-        <v>8921</v>
+        <v>8919</v>
       </c>
       <c r="D2188" s="1" t="s">
-        <v>8967</v>
+        <v>8965</v>
       </c>
       <c r="E2188" s="1" t="s">
         <v>3940</v>
@@ -75365,16 +75633,16 @@
     </row>
     <row r="2189" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2189" s="5" t="s">
-        <v>8866</v>
+        <v>8863</v>
       </c>
       <c r="B2189" s="3">
         <v>70552666</v>
       </c>
       <c r="C2189" s="1" t="s">
-        <v>8922</v>
+        <v>8920</v>
       </c>
       <c r="D2189" s="1" t="s">
-        <v>8968</v>
+        <v>8965</v>
       </c>
       <c r="E2189" s="1" t="s">
         <v>3940</v>
@@ -75382,16 +75650,16 @@
     </row>
     <row r="2190" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2190" s="5" t="s">
-        <v>8866</v>
+        <v>8864</v>
       </c>
       <c r="B2190" s="3">
-        <v>70552666</v>
+        <v>54861011</v>
       </c>
       <c r="C2190" s="1" t="s">
-        <v>8923</v>
+        <v>8921</v>
       </c>
       <c r="D2190" s="1" t="s">
-        <v>8968</v>
+        <v>8966</v>
       </c>
       <c r="E2190" s="1" t="s">
         <v>3940</v>
@@ -75399,16 +75667,16 @@
     </row>
     <row r="2191" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2191" s="5" t="s">
-        <v>8867</v>
+        <v>8865</v>
       </c>
       <c r="B2191" s="3">
-        <v>54861011</v>
+        <v>42777783</v>
       </c>
       <c r="C2191" s="1" t="s">
-        <v>8924</v>
+        <v>8922</v>
       </c>
       <c r="D2191" s="1" t="s">
-        <v>8969</v>
+        <v>8967</v>
       </c>
       <c r="E2191" s="1" t="s">
         <v>3940</v>
@@ -75416,16 +75684,16 @@
     </row>
     <row r="2192" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2192" s="5" t="s">
-        <v>8868</v>
+        <v>8866</v>
       </c>
       <c r="B2192" s="3">
-        <v>42777783</v>
+        <v>42986774</v>
       </c>
       <c r="C2192" s="1" t="s">
-        <v>8925</v>
+        <v>8923</v>
       </c>
       <c r="D2192" s="1" t="s">
-        <v>8970</v>
+        <v>8968</v>
       </c>
       <c r="E2192" s="1" t="s">
         <v>3940</v>
@@ -75433,16 +75701,16 @@
     </row>
     <row r="2193" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2193" s="5" t="s">
-        <v>8869</v>
+        <v>8867</v>
       </c>
       <c r="B2193" s="3">
-        <v>42986774</v>
+        <v>28997300</v>
       </c>
       <c r="C2193" s="1" t="s">
-        <v>8926</v>
+        <v>8924</v>
       </c>
       <c r="D2193" s="1" t="s">
-        <v>8971</v>
+        <v>8969</v>
       </c>
       <c r="E2193" s="1" t="s">
         <v>3940</v>
@@ -75450,16 +75718,16 @@
     </row>
     <row r="2194" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2194" s="5" t="s">
-        <v>8870</v>
-      </c>
-      <c r="B2194" s="3">
-        <v>28997300</v>
+        <v>8868</v>
+      </c>
+      <c r="B2194" s="3" t="s">
+        <v>8877</v>
       </c>
       <c r="C2194" s="1" t="s">
-        <v>8927</v>
+        <v>8925</v>
       </c>
       <c r="D2194" s="1" t="s">
-        <v>8972</v>
+        <v>8970</v>
       </c>
       <c r="E2194" s="1" t="s">
         <v>3940</v>
@@ -75467,16 +75735,16 @@
     </row>
     <row r="2195" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2195" s="5" t="s">
-        <v>8871</v>
-      </c>
-      <c r="B2195" s="3" t="s">
-        <v>8880</v>
+        <v>8869</v>
+      </c>
+      <c r="B2195" s="3">
+        <v>1879651</v>
       </c>
       <c r="C2195" s="1" t="s">
-        <v>8928</v>
+        <v>8926</v>
       </c>
       <c r="D2195" s="1" t="s">
-        <v>8973</v>
+        <v>367</v>
       </c>
       <c r="E2195" s="1" t="s">
         <v>3940</v>
@@ -75484,16 +75752,16 @@
     </row>
     <row r="2196" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2196" s="5" t="s">
-        <v>8872</v>
+        <v>8870</v>
       </c>
       <c r="B2196" s="3">
-        <v>1879651</v>
+        <v>97413843</v>
       </c>
       <c r="C2196" s="1" t="s">
-        <v>8929</v>
+        <v>8927</v>
       </c>
       <c r="D2196" s="1" t="s">
-        <v>367</v>
+        <v>8971</v>
       </c>
       <c r="E2196" s="1" t="s">
         <v>3940</v>
@@ -75501,16 +75769,16 @@
     </row>
     <row r="2197" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2197" s="5" t="s">
-        <v>8873</v>
+        <v>8871</v>
       </c>
       <c r="B2197" s="3">
-        <v>97413843</v>
+        <v>53110738</v>
       </c>
       <c r="C2197" s="1" t="s">
-        <v>8930</v>
+        <v>8928</v>
       </c>
       <c r="D2197" s="1" t="s">
-        <v>8974</v>
+        <v>8972</v>
       </c>
       <c r="E2197" s="1" t="s">
         <v>3940</v>
@@ -75518,16 +75786,16 @@
     </row>
     <row r="2198" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2198" s="5" t="s">
-        <v>8874</v>
+        <v>8872</v>
       </c>
       <c r="B2198" s="3">
-        <v>53110738</v>
+        <v>50890128</v>
       </c>
       <c r="C2198" s="1" t="s">
-        <v>8931</v>
+        <v>8929</v>
       </c>
       <c r="D2198" s="1" t="s">
-        <v>8975</v>
+        <v>6014</v>
       </c>
       <c r="E2198" s="1" t="s">
         <v>3940</v>
@@ -75535,16 +75803,16 @@
     </row>
     <row r="2199" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2199" s="5" t="s">
-        <v>8875</v>
+        <v>8873</v>
       </c>
       <c r="B2199" s="3">
-        <v>50890128</v>
+        <v>54223936</v>
       </c>
       <c r="C2199" s="1" t="s">
-        <v>8932</v>
+        <v>8930</v>
       </c>
       <c r="D2199" s="1" t="s">
-        <v>6014</v>
+        <v>8973</v>
       </c>
       <c r="E2199" s="1" t="s">
         <v>3940</v>
@@ -75552,16 +75820,16 @@
     </row>
     <row r="2200" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2200" s="5" t="s">
-        <v>8876</v>
+        <v>8874</v>
       </c>
       <c r="B2200" s="3">
-        <v>54223936</v>
+        <v>83479268</v>
       </c>
       <c r="C2200" s="1" t="s">
-        <v>8933</v>
+        <v>8931</v>
       </c>
       <c r="D2200" s="1" t="s">
-        <v>8976</v>
+        <v>8974</v>
       </c>
       <c r="E2200" s="1" t="s">
         <v>3940</v>
@@ -75569,16 +75837,16 @@
     </row>
     <row r="2201" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2201" s="5" t="s">
-        <v>8877</v>
+        <v>8875</v>
       </c>
       <c r="B2201" s="3">
-        <v>83479268</v>
+        <v>22298960</v>
       </c>
       <c r="C2201" s="1" t="s">
-        <v>8934</v>
+        <v>8932</v>
       </c>
       <c r="D2201" s="1" t="s">
-        <v>8977</v>
+        <v>8975</v>
       </c>
       <c r="E2201" s="1" t="s">
         <v>3940</v>
@@ -75586,16 +75854,16 @@
     </row>
     <row r="2202" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2202" s="5" t="s">
-        <v>8878</v>
+        <v>8826</v>
       </c>
       <c r="B2202" s="3">
-        <v>22298960</v>
+        <v>19004316</v>
       </c>
       <c r="C2202" s="1" t="s">
-        <v>8935</v>
+        <v>8933</v>
       </c>
       <c r="D2202" s="1" t="s">
-        <v>8978</v>
+        <v>8976</v>
       </c>
       <c r="E2202" s="1" t="s">
         <v>3940</v>
@@ -75603,16 +75871,16 @@
     </row>
     <row r="2203" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2203" s="5" t="s">
-        <v>8829</v>
+        <v>8876</v>
       </c>
       <c r="B2203" s="3">
-        <v>19004316</v>
+        <v>30974752</v>
       </c>
       <c r="C2203" s="1" t="s">
-        <v>8936</v>
+        <v>8934</v>
       </c>
       <c r="D2203" s="1" t="s">
-        <v>8979</v>
+        <v>5872</v>
       </c>
       <c r="E2203" s="1" t="s">
         <v>3940</v>
@@ -75620,619 +75888,854 @@
     </row>
     <row r="2204" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2204" s="5" t="s">
-        <v>8879</v>
+        <v>135</v>
       </c>
       <c r="B2204" s="3">
-        <v>30974752</v>
+        <v>22099322</v>
       </c>
       <c r="C2204" s="1" t="s">
-        <v>8937</v>
+        <v>8981</v>
       </c>
       <c r="D2204" s="1" t="s">
-        <v>5872</v>
-      </c>
-      <c r="E2204" s="1" t="s">
-        <v>3940</v>
+        <v>8986</v>
+      </c>
+      <c r="F2204" s="1" t="s">
+        <v>8988</v>
+      </c>
+      <c r="G2204" s="1" t="s">
+        <v>3798</v>
+      </c>
+      <c r="H2204" s="24" t="s">
+        <v>8989</v>
+      </c>
+      <c r="I2204" s="1" t="s">
+        <v>8990</v>
       </c>
     </row>
     <row r="2205" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2205" s="5" t="s">
-        <v>135</v>
+        <v>8977</v>
       </c>
       <c r="B2205" s="3">
-        <v>22099322</v>
+        <v>90272116</v>
       </c>
       <c r="C2205" s="1" t="s">
-        <v>8984</v>
+        <v>8982</v>
       </c>
       <c r="D2205" s="1" t="s">
-        <v>8989</v>
+        <v>8987</v>
       </c>
       <c r="F2205" s="1" t="s">
-        <v>8991</v>
+        <v>8988</v>
       </c>
       <c r="G2205" s="1" t="s">
         <v>3798</v>
       </c>
       <c r="H2205" s="24" t="s">
-        <v>8992</v>
+        <v>8997</v>
       </c>
       <c r="I2205" s="1" t="s">
-        <v>8993</v>
+        <v>8998</v>
       </c>
     </row>
     <row r="2206" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2206" s="5" t="s">
-        <v>8980</v>
+        <v>8978</v>
       </c>
       <c r="B2206" s="3">
-        <v>90272116</v>
+        <v>22491655</v>
       </c>
       <c r="C2206" s="1" t="s">
-        <v>8985</v>
+        <v>8983</v>
       </c>
       <c r="D2206" s="1" t="s">
-        <v>8990</v>
+        <v>8987</v>
       </c>
       <c r="F2206" s="1" t="s">
-        <v>8991</v>
+        <v>8988</v>
       </c>
       <c r="G2206" s="1" t="s">
         <v>3798</v>
       </c>
       <c r="H2206" s="24" t="s">
-        <v>9000</v>
+        <v>8993</v>
       </c>
       <c r="I2206" s="1" t="s">
-        <v>9001</v>
+        <v>8994</v>
       </c>
     </row>
     <row r="2207" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2207" s="5" t="s">
-        <v>8981</v>
+        <v>8979</v>
       </c>
       <c r="B2207" s="3">
-        <v>22491655</v>
+        <v>28913512</v>
       </c>
       <c r="C2207" s="1" t="s">
-        <v>8986</v>
+        <v>8984</v>
       </c>
       <c r="D2207" s="1" t="s">
-        <v>8990</v>
+        <v>8987</v>
       </c>
       <c r="F2207" s="1" t="s">
-        <v>8991</v>
+        <v>8988</v>
       </c>
       <c r="G2207" s="1" t="s">
         <v>3798</v>
       </c>
       <c r="H2207" s="24" t="s">
-        <v>8996</v>
+        <v>8991</v>
       </c>
       <c r="I2207" s="1" t="s">
-        <v>8997</v>
+        <v>8992</v>
       </c>
     </row>
     <row r="2208" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2208" s="5" t="s">
-        <v>8982</v>
+        <v>8980</v>
       </c>
       <c r="B2208" s="3">
-        <v>28913512</v>
+        <v>50856590</v>
       </c>
       <c r="C2208" s="1" t="s">
+        <v>8985</v>
+      </c>
+      <c r="D2208" s="1" t="s">
         <v>8987</v>
       </c>
-      <c r="D2208" s="1" t="s">
-        <v>8990</v>
-      </c>
       <c r="F2208" s="1" t="s">
-        <v>8991</v>
+        <v>8988</v>
       </c>
       <c r="G2208" s="1" t="s">
         <v>3798</v>
       </c>
       <c r="H2208" s="24" t="s">
-        <v>8994</v>
+        <v>8995</v>
       </c>
       <c r="I2208" s="1" t="s">
-        <v>8995</v>
+        <v>8996</v>
       </c>
     </row>
     <row r="2209" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2209" s="5" t="s">
-        <v>8983</v>
+        <v>8999</v>
       </c>
       <c r="B2209" s="3">
-        <v>50856590</v>
+        <v>42633891</v>
       </c>
       <c r="C2209" s="1" t="s">
-        <v>8988</v>
+        <v>9000</v>
       </c>
       <c r="D2209" s="1" t="s">
-        <v>8990</v>
-      </c>
-      <c r="F2209" s="1" t="s">
-        <v>8991</v>
-      </c>
-      <c r="G2209" s="1" t="s">
-        <v>3798</v>
-      </c>
-      <c r="H2209" s="24" t="s">
-        <v>8998</v>
-      </c>
-      <c r="I2209" s="1" t="s">
-        <v>8999</v>
+        <v>9030</v>
+      </c>
+      <c r="E2209" s="1" t="s">
+        <v>3940</v>
       </c>
     </row>
     <row r="2210" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2210" s="5" t="s">
+        <v>9001</v>
+      </c>
+      <c r="B2210" s="3">
+        <v>54659163</v>
+      </c>
+      <c r="C2210" s="1" t="s">
+        <v>9013</v>
+      </c>
+      <c r="D2210" s="1" t="s">
+        <v>9064</v>
+      </c>
+      <c r="F2210" s="1" t="s">
+        <v>9059</v>
+      </c>
+      <c r="G2210" s="1" t="s">
+        <v>9060</v>
+      </c>
+      <c r="H2210" s="1" t="s">
+        <v>9065</v>
+      </c>
+      <c r="I2210" s="1" t="s">
+        <v>9066</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2211" s="5" t="s">
         <v>9002</v>
       </c>
-      <c r="B2210" s="3">
-        <v>42633891</v>
-      </c>
-      <c r="C2210" s="1" t="s">
-        <v>9003</v>
-      </c>
-      <c r="D2210" s="1" t="s">
-        <v>9037</v>
-      </c>
-    </row>
-    <row r="2211" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2211" s="35" t="s">
-        <v>9004</v>
-      </c>
-      <c r="B2211" s="35">
-        <v>54659163</v>
-      </c>
-      <c r="C2211" s="35" t="s">
-        <v>9016</v>
-      </c>
-      <c r="D2211" s="35" t="s">
-        <v>9030</v>
+      <c r="B2211" s="3">
+        <v>80315002</v>
+      </c>
+      <c r="C2211" s="1" t="s">
+        <v>9014</v>
+      </c>
+      <c r="D2211" s="1" t="s">
+        <v>9027</v>
       </c>
       <c r="F2211" s="1" t="s">
-        <v>9034</v>
+        <v>9029</v>
       </c>
       <c r="G2211" s="1" t="s">
         <v>3798</v>
       </c>
+      <c r="H2211" s="1" t="s">
+        <v>9037</v>
+      </c>
+      <c r="I2211" s="1" t="s">
+        <v>9038</v>
+      </c>
     </row>
     <row r="2212" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2212" s="35" t="s">
-        <v>9005</v>
-      </c>
-      <c r="B2212" s="35">
-        <v>80315002</v>
-      </c>
-      <c r="C2212" s="35" t="s">
-        <v>9017</v>
-      </c>
-      <c r="D2212" s="35" t="s">
-        <v>9030</v>
+      <c r="A2212" s="5" t="s">
+        <v>9003</v>
+      </c>
+      <c r="B2212" s="3">
+        <v>36255511</v>
+      </c>
+      <c r="C2212" s="1" t="s">
+        <v>9015</v>
+      </c>
+      <c r="D2212" s="1" t="s">
+        <v>9027</v>
       </c>
       <c r="F2212" s="1" t="s">
-        <v>9034</v>
+        <v>9029</v>
       </c>
       <c r="G2212" s="1" t="s">
         <v>3798</v>
       </c>
+      <c r="H2212" s="1" t="s">
+        <v>9035</v>
+      </c>
+      <c r="I2212" s="1" t="s">
+        <v>9036</v>
+      </c>
     </row>
     <row r="2213" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2213" s="35" t="s">
-        <v>9006</v>
-      </c>
-      <c r="B2213" s="35">
-        <v>36255511</v>
-      </c>
-      <c r="C2213" s="35" t="s">
-        <v>9018</v>
-      </c>
-      <c r="D2213" s="35" t="s">
-        <v>9030</v>
+      <c r="A2213" s="5" t="s">
+        <v>9004</v>
+      </c>
+      <c r="B2213" s="3">
+        <v>61770000</v>
+      </c>
+      <c r="C2213" s="1" t="s">
+        <v>9016</v>
+      </c>
+      <c r="D2213" s="1" t="s">
+        <v>9028</v>
       </c>
       <c r="F2213" s="1" t="s">
-        <v>9034</v>
+        <v>9029</v>
       </c>
       <c r="G2213" s="1" t="s">
         <v>3798</v>
       </c>
+      <c r="H2213" s="1" t="s">
+        <v>9033</v>
+      </c>
+      <c r="I2213" s="1" t="s">
+        <v>9034</v>
+      </c>
     </row>
     <row r="2214" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2214" s="35" t="s">
+      <c r="A2214" s="5" t="s">
+        <v>9005</v>
+      </c>
+      <c r="B2214" s="3">
+        <v>70730016</v>
+      </c>
+      <c r="C2214" s="1" t="s">
+        <v>9017</v>
+      </c>
+      <c r="D2214" s="1" t="s">
+        <v>9058</v>
+      </c>
+      <c r="F2214" s="1" t="s">
+        <v>9059</v>
+      </c>
+      <c r="G2214" s="1" t="s">
+        <v>9060</v>
+      </c>
+      <c r="H2214" s="1" t="s">
+        <v>9061</v>
+      </c>
+      <c r="I2214" s="1" t="s">
+        <v>9062</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2215" s="5" t="s">
+        <v>9006</v>
+      </c>
+      <c r="B2215" s="3">
+        <v>28962344</v>
+      </c>
+      <c r="C2215" s="1" t="s">
+        <v>9018</v>
+      </c>
+      <c r="D2215" s="1" t="s">
+        <v>9039</v>
+      </c>
+      <c r="F2215" s="1" t="s">
+        <v>9040</v>
+      </c>
+      <c r="G2215" s="1" t="s">
+        <v>9041</v>
+      </c>
+      <c r="H2215" s="1" t="s">
+        <v>9042</v>
+      </c>
+      <c r="I2215" s="1" t="s">
+        <v>9043</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2216" s="5" t="s">
         <v>9007</v>
       </c>
-      <c r="B2214" s="35">
-        <v>61770000</v>
-      </c>
-      <c r="C2214" s="35" t="s">
+      <c r="B2216" s="3">
+        <v>20879786</v>
+      </c>
+      <c r="C2216" s="1" t="s">
         <v>9019</v>
       </c>
-      <c r="D2214" s="35" t="s">
-        <v>9031</v>
-      </c>
-      <c r="F2214" s="1" t="s">
-        <v>9034</v>
-      </c>
-      <c r="G2214" s="1" t="s">
+      <c r="D2216" s="1" t="s">
+        <v>9044</v>
+      </c>
+      <c r="F2216" s="1" t="s">
+        <v>9040</v>
+      </c>
+      <c r="G2216" s="1" t="s">
+        <v>9041</v>
+      </c>
+      <c r="H2216" s="1" t="s">
+        <v>9045</v>
+      </c>
+      <c r="I2216" s="1" t="s">
+        <v>9046</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2217" s="5" t="s">
+        <v>9008</v>
+      </c>
+      <c r="B2217" s="3">
+        <v>28860819</v>
+      </c>
+      <c r="C2217" s="1" t="s">
+        <v>9020</v>
+      </c>
+      <c r="D2217" s="1" t="s">
+        <v>9064</v>
+      </c>
+      <c r="F2217" s="1" t="s">
+        <v>9059</v>
+      </c>
+      <c r="G2217" s="1" t="s">
+        <v>9060</v>
+      </c>
+      <c r="H2217" s="1" t="s">
+        <v>9068</v>
+      </c>
+      <c r="I2217" s="1">
+        <v>7820</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2218" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2218" s="3">
+        <v>50827271</v>
+      </c>
+      <c r="C2218" s="1" t="s">
+        <v>9021</v>
+      </c>
+      <c r="D2218" s="1" t="s">
+        <v>9039</v>
+      </c>
+      <c r="F2218" s="1" t="s">
+        <v>9040</v>
+      </c>
+      <c r="G2218" s="1" t="s">
+        <v>9041</v>
+      </c>
+      <c r="H2218" s="1" t="s">
+        <v>9047</v>
+      </c>
+      <c r="I2218" s="1" t="s">
+        <v>9048</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2219" s="5" t="s">
+        <v>9009</v>
+      </c>
+      <c r="B2219" s="3">
+        <v>90706387</v>
+      </c>
+      <c r="C2219" s="1" t="s">
+        <v>9022</v>
+      </c>
+      <c r="D2219" s="1" t="s">
+        <v>9039</v>
+      </c>
+      <c r="F2219" s="1" t="s">
+        <v>9040</v>
+      </c>
+      <c r="G2219" s="1" t="s">
+        <v>9041</v>
+      </c>
+      <c r="H2219" s="1" t="s">
+        <v>9049</v>
+      </c>
+      <c r="I2219" s="1" t="s">
+        <v>9050</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2220" s="5" t="s">
+        <v>9010</v>
+      </c>
+      <c r="B2220" s="3">
+        <v>89147766</v>
+      </c>
+      <c r="C2220" s="1" t="s">
+        <v>9023</v>
+      </c>
+      <c r="D2220" s="1" t="s">
+        <v>9039</v>
+      </c>
+      <c r="F2220" s="1" t="s">
+        <v>9040</v>
+      </c>
+      <c r="G2220" s="1" t="s">
+        <v>9041</v>
+      </c>
+      <c r="H2220" s="1" t="s">
+        <v>9051</v>
+      </c>
+      <c r="I2220" s="1" t="s">
+        <v>9052</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2221" s="5" t="s">
+        <v>9011</v>
+      </c>
+      <c r="B2221" s="3">
+        <v>27577420</v>
+      </c>
+      <c r="C2221" s="1" t="s">
+        <v>9024</v>
+      </c>
+      <c r="D2221" s="1" t="s">
+        <v>9039</v>
+      </c>
+      <c r="F2221" s="1" t="s">
+        <v>9040</v>
+      </c>
+      <c r="G2221" s="1" t="s">
+        <v>9041</v>
+      </c>
+      <c r="H2221" s="1" t="s">
+        <v>9053</v>
+      </c>
+      <c r="I2221" s="1" t="s">
+        <v>9054</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2222" s="5" t="s">
+        <v>9063</v>
+      </c>
+      <c r="B2222" s="3">
+        <v>70507419</v>
+      </c>
+      <c r="C2222" s="1" t="s">
+        <v>9025</v>
+      </c>
+      <c r="D2222" s="1" t="s">
+        <v>9064</v>
+      </c>
+      <c r="F2222" s="1" t="s">
+        <v>9059</v>
+      </c>
+      <c r="G2222" s="1" t="s">
+        <v>9060</v>
+      </c>
+      <c r="H2222" s="24" t="s">
+        <v>9067</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2223" s="5" t="s">
+        <v>9012</v>
+      </c>
+      <c r="B2223" s="3">
+        <v>54269279</v>
+      </c>
+      <c r="C2223" s="1" t="s">
+        <v>9026</v>
+      </c>
+      <c r="D2223" s="1" t="s">
+        <v>9039</v>
+      </c>
+      <c r="F2223" s="1" t="s">
+        <v>9040</v>
+      </c>
+      <c r="G2223" s="1" t="s">
+        <v>9055</v>
+      </c>
+      <c r="H2223" s="1" t="s">
+        <v>9056</v>
+      </c>
+      <c r="I2223" s="1" t="s">
+        <v>9057</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2224" s="2" t="s">
+        <v>9069</v>
+      </c>
+      <c r="B2224" s="3" t="s">
+        <v>9070</v>
+      </c>
+      <c r="C2224" s="1" t="s">
+        <v>9071</v>
+      </c>
+      <c r="D2224" s="1" t="s">
+        <v>9086</v>
+      </c>
+      <c r="E2224" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:7" s="6" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A2225" s="33" t="s">
+        <v>8570</v>
+      </c>
+      <c r="B2225" s="33">
+        <v>52693448</v>
+      </c>
+      <c r="C2225" s="33" t="s">
+        <v>8569</v>
+      </c>
+      <c r="D2225" s="34" t="s">
+        <v>9083</v>
+      </c>
+      <c r="F2225" s="6" t="s">
+        <v>9072</v>
+      </c>
+      <c r="G2225" s="6" t="s">
         <v>3798</v>
       </c>
     </row>
-    <row r="2215" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2215" s="35" t="s">
-        <v>9008</v>
-      </c>
-      <c r="B2215" s="35">
-        <v>70730016</v>
-      </c>
-      <c r="C2215" s="35" t="s">
-        <v>9020</v>
-      </c>
-      <c r="D2215" s="35" t="s">
-        <v>9032</v>
-      </c>
-      <c r="F2215" s="1" t="s">
-        <v>9034</v>
-      </c>
-      <c r="G2215" s="1" t="s">
+    <row r="2226" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A2226" s="34" t="s">
+        <v>9073</v>
+      </c>
+      <c r="B2226" s="34">
+        <v>82842114</v>
+      </c>
+      <c r="C2226" s="34" t="s">
+        <v>9078</v>
+      </c>
+      <c r="D2226" s="34" t="s">
+        <v>9083</v>
+      </c>
+      <c r="F2226" s="6" t="s">
+        <v>9072</v>
+      </c>
+      <c r="G2226" s="6" t="s">
         <v>3798</v>
       </c>
     </row>
-    <row r="2216" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2216" s="35" t="s">
-        <v>9009</v>
-      </c>
-      <c r="B2216" s="35">
-        <v>28962344</v>
-      </c>
-      <c r="C2216" s="35" t="s">
-        <v>9021</v>
-      </c>
-      <c r="D2216" s="35" t="s">
-        <v>9030</v>
-      </c>
-      <c r="F2216" s="1" t="s">
-        <v>9034</v>
-      </c>
-      <c r="G2216" s="1" t="s">
+    <row r="2227" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A2227" s="34" t="s">
+        <v>9074</v>
+      </c>
+      <c r="B2227" s="34">
+        <v>93841128</v>
+      </c>
+      <c r="C2227" s="34" t="s">
+        <v>9079</v>
+      </c>
+      <c r="D2227" s="34" t="s">
+        <v>9084</v>
+      </c>
+      <c r="F2227" s="6" t="s">
+        <v>9072</v>
+      </c>
+      <c r="G2227" s="6" t="s">
         <v>3798</v>
       </c>
     </row>
-    <row r="2217" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2217" s="35" t="s">
-        <v>9010</v>
-      </c>
-      <c r="B2217" s="35">
-        <v>20879786</v>
-      </c>
-      <c r="C2217" s="35" t="s">
-        <v>9022</v>
-      </c>
-      <c r="D2217" s="35" t="s">
-        <v>9033</v>
-      </c>
-      <c r="F2217" s="1" t="s">
-        <v>9034</v>
-      </c>
-      <c r="G2217" s="1" t="s">
+    <row r="2228" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A2228" s="34" t="s">
+        <v>9075</v>
+      </c>
+      <c r="B2228" s="34">
+        <v>23935404</v>
+      </c>
+      <c r="C2228" s="34" t="s">
+        <v>9080</v>
+      </c>
+      <c r="D2228" s="34" t="s">
+        <v>9084</v>
+      </c>
+      <c r="F2228" s="6" t="s">
+        <v>9072</v>
+      </c>
+      <c r="G2228" s="6" t="s">
         <v>3798</v>
       </c>
     </row>
-    <row r="2218" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2218" s="35" t="s">
-        <v>9011</v>
-      </c>
-      <c r="B2218" s="35">
-        <v>28860819</v>
-      </c>
-      <c r="C2218" s="35" t="s">
-        <v>9023</v>
-      </c>
-      <c r="D2218" s="35" t="s">
-        <v>9030</v>
-      </c>
-      <c r="F2218" s="1" t="s">
-        <v>9034</v>
-      </c>
-      <c r="G2218" s="1" t="s">
+    <row r="2229" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A2229" s="34" t="s">
+        <v>9076</v>
+      </c>
+      <c r="B2229" s="34">
+        <v>86226301</v>
+      </c>
+      <c r="C2229" s="34" t="s">
+        <v>9081</v>
+      </c>
+      <c r="D2229" s="34" t="s">
+        <v>9085</v>
+      </c>
+      <c r="F2229" s="6" t="s">
+        <v>9072</v>
+      </c>
+      <c r="G2229" s="6" t="s">
         <v>3798</v>
       </c>
     </row>
-    <row r="2219" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2219" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="B2219" s="35">
-        <v>50827271</v>
-      </c>
-      <c r="C2219" s="35" t="s">
-        <v>9024</v>
-      </c>
-      <c r="D2219" s="35" t="s">
-        <v>9030</v>
-      </c>
-      <c r="F2219" s="1" t="s">
-        <v>9034</v>
-      </c>
-      <c r="G2219" s="1" t="s">
+    <row r="2230" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A2230" s="34" t="s">
+        <v>9077</v>
+      </c>
+      <c r="B2230" s="34">
+        <v>23500409</v>
+      </c>
+      <c r="C2230" s="34" t="s">
+        <v>9082</v>
+      </c>
+      <c r="D2230" s="34" t="s">
+        <v>9084</v>
+      </c>
+      <c r="F2230" s="6" t="s">
+        <v>9072</v>
+      </c>
+      <c r="G2230" s="6" t="s">
         <v>3798</v>
-      </c>
-    </row>
-    <row r="2220" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2220" s="35" t="s">
-        <v>9012</v>
-      </c>
-      <c r="B2220" s="35">
-        <v>90706387</v>
-      </c>
-      <c r="C2220" s="35" t="s">
-        <v>9025</v>
-      </c>
-      <c r="D2220" s="35" t="s">
-        <v>9030</v>
-      </c>
-      <c r="F2220" s="1" t="s">
-        <v>9034</v>
-      </c>
-      <c r="G2220" s="1" t="s">
-        <v>3798</v>
-      </c>
-    </row>
-    <row r="2221" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2221" s="35" t="s">
-        <v>9013</v>
-      </c>
-      <c r="B2221" s="35">
-        <v>89147766</v>
-      </c>
-      <c r="C2221" s="35" t="s">
-        <v>9026</v>
-      </c>
-      <c r="D2221" s="35" t="s">
-        <v>9030</v>
-      </c>
-      <c r="F2221" s="1" t="s">
-        <v>9034</v>
-      </c>
-      <c r="G2221" s="1" t="s">
-        <v>3798</v>
-      </c>
-    </row>
-    <row r="2222" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2222" s="35" t="s">
-        <v>9014</v>
-      </c>
-      <c r="B2222" s="35">
-        <v>27577420</v>
-      </c>
-      <c r="C2222" s="35" t="s">
-        <v>9027</v>
-      </c>
-      <c r="D2222" s="35" t="s">
-        <v>9030</v>
-      </c>
-      <c r="F2222" s="1" t="s">
-        <v>9034</v>
-      </c>
-      <c r="G2222" s="1" t="s">
-        <v>3798</v>
-      </c>
-    </row>
-    <row r="2223" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2223" s="35" t="s">
-        <v>493</v>
-      </c>
-      <c r="B2223" s="35">
-        <v>70507419</v>
-      </c>
-      <c r="C2223" s="35" t="s">
-        <v>9028</v>
-      </c>
-      <c r="D2223" s="35" t="s">
-        <v>9030</v>
-      </c>
-      <c r="F2223" s="1" t="s">
-        <v>9034</v>
-      </c>
-      <c r="G2223" s="1" t="s">
-        <v>3798</v>
-      </c>
-    </row>
-    <row r="2224" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2224" s="36" t="s">
-        <v>9015</v>
-      </c>
-      <c r="B2224" s="36">
-        <v>54269279</v>
-      </c>
-      <c r="C2224" s="36" t="s">
-        <v>9029</v>
-      </c>
-      <c r="D2224" s="35" t="s">
-        <v>9030</v>
-      </c>
-      <c r="F2224" s="1" t="s">
-        <v>9034</v>
-      </c>
-      <c r="G2224" s="6" t="s">
-        <v>8582</v>
-      </c>
-      <c r="H2224" s="22" t="s">
-        <v>9036</v>
-      </c>
-      <c r="I2224" s="1" t="s">
-        <v>9035</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2022:A2033">
-    <cfRule type="duplicateValues" dxfId="58" priority="116" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="139" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2068:A2075">
-    <cfRule type="duplicateValues" dxfId="57" priority="107" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="130" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2068:B2075">
-    <cfRule type="duplicateValues" dxfId="56" priority="106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="129" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2076:A2086">
+    <cfRule type="duplicateValues" dxfId="66" priority="113" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2076:B2086">
+    <cfRule type="duplicateValues" dxfId="65" priority="112" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2087">
+    <cfRule type="duplicateValues" dxfId="64" priority="99" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2087">
+    <cfRule type="duplicateValues" dxfId="63" priority="98" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2088">
+    <cfRule type="duplicateValues" dxfId="62" priority="97" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2088">
+    <cfRule type="duplicateValues" dxfId="61" priority="96" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2089">
+    <cfRule type="duplicateValues" dxfId="60" priority="95" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2089">
+    <cfRule type="duplicateValues" dxfId="59" priority="94" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2090">
+    <cfRule type="duplicateValues" dxfId="58" priority="93" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2090">
+    <cfRule type="duplicateValues" dxfId="57" priority="92" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2091">
+    <cfRule type="duplicateValues" dxfId="56" priority="91" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2091">
     <cfRule type="duplicateValues" dxfId="55" priority="90" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2076:B2086">
+  <conditionalFormatting sqref="A2092">
     <cfRule type="duplicateValues" dxfId="54" priority="89" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2132">
-    <cfRule type="duplicateValues" dxfId="53" priority="79" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2092">
+    <cfRule type="duplicateValues" dxfId="53" priority="88" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2093">
+    <cfRule type="duplicateValues" dxfId="52" priority="87" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2093">
+    <cfRule type="duplicateValues" dxfId="51" priority="86" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2094">
+    <cfRule type="duplicateValues" dxfId="50" priority="85" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2094">
+    <cfRule type="duplicateValues" dxfId="49" priority="84" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2095">
+    <cfRule type="duplicateValues" dxfId="48" priority="83" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2095">
+    <cfRule type="duplicateValues" dxfId="47" priority="82" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2096:A2099">
+    <cfRule type="duplicateValues" dxfId="46" priority="78" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2096:B2099">
+    <cfRule type="duplicateValues" dxfId="45" priority="77" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2100:A2107">
+    <cfRule type="duplicateValues" dxfId="44" priority="70" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2100:B2107">
+    <cfRule type="duplicateValues" dxfId="43" priority="69" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2231:A65536 A2144:A2203 A2123 A2034:A2067 A1:A2021 A2209">
+    <cfRule type="duplicateValues" dxfId="42" priority="140" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2144:B2203 B2123 B1:B2067 B2209 B2224 B2231:B65536">
+    <cfRule type="duplicateValues" dxfId="41" priority="145" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2108:A2115">
+    <cfRule type="duplicateValues" dxfId="40" priority="65" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2108:B2115">
+    <cfRule type="duplicateValues" dxfId="39" priority="64" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2116:A2122">
+    <cfRule type="duplicateValues" dxfId="38" priority="60" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2116:B2122">
+    <cfRule type="duplicateValues" dxfId="37" priority="59" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2124:A2131">
+    <cfRule type="duplicateValues" dxfId="36" priority="55" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2124:B2131">
+    <cfRule type="duplicateValues" dxfId="35" priority="54" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2132">
+    <cfRule type="duplicateValues" dxfId="34" priority="50" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2132">
-    <cfRule type="duplicateValues" dxfId="52" priority="77" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="78" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2087">
-    <cfRule type="duplicateValues" dxfId="50" priority="76" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2087">
-    <cfRule type="duplicateValues" dxfId="49" priority="75" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2088">
-    <cfRule type="duplicateValues" dxfId="48" priority="74" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2088">
-    <cfRule type="duplicateValues" dxfId="47" priority="73" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2089">
-    <cfRule type="duplicateValues" dxfId="46" priority="72" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2089">
-    <cfRule type="duplicateValues" dxfId="45" priority="71" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2090">
-    <cfRule type="duplicateValues" dxfId="44" priority="70" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2090">
-    <cfRule type="duplicateValues" dxfId="43" priority="69" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2091">
-    <cfRule type="duplicateValues" dxfId="42" priority="68" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2091">
-    <cfRule type="duplicateValues" dxfId="41" priority="67" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2092">
-    <cfRule type="duplicateValues" dxfId="40" priority="66" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2092">
-    <cfRule type="duplicateValues" dxfId="39" priority="65" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2093">
-    <cfRule type="duplicateValues" dxfId="38" priority="64" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2093">
-    <cfRule type="duplicateValues" dxfId="37" priority="63" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2094">
-    <cfRule type="duplicateValues" dxfId="36" priority="62" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2094">
-    <cfRule type="duplicateValues" dxfId="35" priority="61" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2095">
-    <cfRule type="duplicateValues" dxfId="34" priority="60" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2095">
-    <cfRule type="duplicateValues" dxfId="33" priority="59" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2096:A2099">
-    <cfRule type="duplicateValues" dxfId="32" priority="55" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2096:B2099">
-    <cfRule type="duplicateValues" dxfId="31" priority="54" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2100:A2107">
-    <cfRule type="duplicateValues" dxfId="30" priority="47" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2100:B2107">
-    <cfRule type="duplicateValues" dxfId="29" priority="46" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2145:A2204 A2123 A2034:A2067 A1:A2021 A2210 A2225:A65536">
-    <cfRule type="duplicateValues" dxfId="28" priority="117" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2145:B2204 B2123 B1:B2067 B2210 B2225:B65536">
-    <cfRule type="duplicateValues" dxfId="27" priority="122" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2108:A2115">
-    <cfRule type="duplicateValues" dxfId="26" priority="42" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2108:B2115">
-    <cfRule type="duplicateValues" dxfId="25" priority="41" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2116:A2122">
-    <cfRule type="duplicateValues" dxfId="24" priority="37" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2116:B2122">
-    <cfRule type="duplicateValues" dxfId="23" priority="36" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2124:A2131">
-    <cfRule type="duplicateValues" dxfId="22" priority="32" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2124:B2131">
-    <cfRule type="duplicateValues" dxfId="21" priority="31" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="49" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2133">
-    <cfRule type="duplicateValues" dxfId="20" priority="27" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="48" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2133">
-    <cfRule type="duplicateValues" dxfId="19" priority="26" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="47" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2134">
-    <cfRule type="duplicateValues" dxfId="18" priority="25" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="46" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2134">
-    <cfRule type="duplicateValues" dxfId="17" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="45" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2135">
-    <cfRule type="duplicateValues" dxfId="16" priority="23" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2135:A2140">
+    <cfRule type="duplicateValues" dxfId="28" priority="41" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2135">
-    <cfRule type="duplicateValues" dxfId="15" priority="22" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2135:B2140">
+    <cfRule type="duplicateValues" dxfId="27" priority="40" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2136:A2141">
-    <cfRule type="duplicateValues" dxfId="14" priority="18" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2141:A2143">
+    <cfRule type="duplicateValues" dxfId="26" priority="39" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2136:B2141">
-    <cfRule type="duplicateValues" dxfId="13" priority="17" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2141:B2143">
+    <cfRule type="duplicateValues" dxfId="25" priority="38" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2142:A2144">
-    <cfRule type="duplicateValues" dxfId="12" priority="16" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2204:A2208">
+    <cfRule type="duplicateValues" dxfId="24" priority="33" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2142:B2144">
-    <cfRule type="duplicateValues" dxfId="11" priority="15" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2204:B2208">
+    <cfRule type="duplicateValues" dxfId="23" priority="34" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2205:A2209">
+  <conditionalFormatting sqref="A2211:A2213">
+    <cfRule type="duplicateValues" dxfId="22" priority="22" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2211:B2213">
+    <cfRule type="duplicateValues" dxfId="21" priority="23" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2215:A2216">
+    <cfRule type="duplicateValues" dxfId="20" priority="20" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2215:B2216">
+    <cfRule type="duplicateValues" dxfId="19" priority="21" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2218:A2221">
+    <cfRule type="duplicateValues" dxfId="18" priority="18" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2218:B2221">
+    <cfRule type="duplicateValues" dxfId="17" priority="19" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2223">
+    <cfRule type="duplicateValues" dxfId="16" priority="16" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2223">
+    <cfRule type="duplicateValues" dxfId="15" priority="17" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2214">
+    <cfRule type="duplicateValues" dxfId="14" priority="14" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2214">
+    <cfRule type="duplicateValues" dxfId="13" priority="15" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2222">
+    <cfRule type="duplicateValues" dxfId="12" priority="12" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2222">
+    <cfRule type="duplicateValues" dxfId="11" priority="13" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2210">
     <cfRule type="duplicateValues" dxfId="10" priority="10" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2205:B2209">
+  <conditionalFormatting sqref="B2210">
     <cfRule type="duplicateValues" dxfId="9" priority="11" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2224">
-    <cfRule type="duplicateValues" dxfId="8" priority="9" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2217">
+    <cfRule type="duplicateValues" dxfId="8" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2224">
-    <cfRule type="duplicateValues" dxfId="7" priority="7" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="8" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2217">
+    <cfRule type="duplicateValues" dxfId="7" priority="9" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2211:B2219">
+  <conditionalFormatting sqref="A2224">
+    <cfRule type="duplicateValues" dxfId="6" priority="7" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2225">
     <cfRule type="duplicateValues" dxfId="5" priority="6" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2211:B2219">
+  <conditionalFormatting sqref="B2225">
     <cfRule type="duplicateValues" dxfId="4" priority="4" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="3" priority="5" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2220:B2223">
+  <conditionalFormatting sqref="B2226:B2230">
     <cfRule type="duplicateValues" dxfId="2" priority="3" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2220:B2223">
+  <conditionalFormatting sqref="B2226:B2230">
     <cfRule type="duplicateValues" dxfId="1" priority="1" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="0" priority="2" stopIfTrue="1"/>
   </conditionalFormatting>
@@ -76250,7 +76753,7 @@
     <hyperlink ref="H2090" r:id="rId6"/>
     <hyperlink ref="H2100" r:id="rId7"/>
     <hyperlink ref="H2110" r:id="rId8"/>
-    <hyperlink ref="H2224" r:id="rId9"/>
+    <hyperlink ref="H2223" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>

--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="4620" windowWidth="11055" windowHeight="4920"/>
+    <workbookView xWindow="-15" yWindow="4665" windowWidth="11055" windowHeight="4875"/>
   </bookViews>
   <sheets>
     <sheet name="順豐出口" sheetId="4" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12516" uniqueCount="9087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12623" uniqueCount="9154">
   <si>
     <t>麒安科技有限公司</t>
   </si>
@@ -32017,6 +32017,240 @@
   </si>
   <si>
     <t>119.04.25</t>
+  </si>
+  <si>
+    <t>0277106666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5173/高先生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0987567555</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>楊先生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0277337050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101/徐小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0423893383</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>108/洪小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0492332527</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>簡先生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0424725191</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紀小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>97104831</t>
+  </si>
+  <si>
+    <t>世廷股份有限公司</t>
+  </si>
+  <si>
+    <t>WBBL2025044919</t>
+  </si>
+  <si>
+    <t>遠視界科技股份有限公司</t>
+  </si>
+  <si>
+    <t>恩詠有限公司</t>
+  </si>
+  <si>
+    <t>普泰光電股份有限公司</t>
+  </si>
+  <si>
+    <t>東森得易購股份有限公司</t>
+  </si>
+  <si>
+    <t>利拉進出口有限公司</t>
+  </si>
+  <si>
+    <t>興太有限公司</t>
+  </si>
+  <si>
+    <t>迅德興業股份有限公司</t>
+  </si>
+  <si>
+    <t>德克斯精密有限公司</t>
+  </si>
+  <si>
+    <t>碩頂精密工業股份有限公司</t>
+  </si>
+  <si>
+    <t>悅群電子股份有限公司</t>
+  </si>
+  <si>
+    <t>德誠接合科技有限公司</t>
+  </si>
+  <si>
+    <t>立寰科技股份有限公司</t>
+  </si>
+  <si>
+    <t>展緻企業有限公司</t>
+  </si>
+  <si>
+    <t>上奕國際股份有限公司</t>
+  </si>
+  <si>
+    <t>加金企業股份有限公司</t>
+  </si>
+  <si>
+    <t>114業二07686</t>
+  </si>
+  <si>
+    <t>114業二07687</t>
+  </si>
+  <si>
+    <t>114業二07688</t>
+  </si>
+  <si>
+    <t>114業二07689</t>
+  </si>
+  <si>
+    <t>114業二07690</t>
+  </si>
+  <si>
+    <t>114業二07691</t>
+  </si>
+  <si>
+    <t>114業二07692</t>
+  </si>
+  <si>
+    <t>114業二07693</t>
+  </si>
+  <si>
+    <t>114業二07694</t>
+  </si>
+  <si>
+    <t>114業二07695</t>
+  </si>
+  <si>
+    <t>114業二07696</t>
+  </si>
+  <si>
+    <t>114業二07697</t>
+  </si>
+  <si>
+    <t>114業二07698</t>
+  </si>
+  <si>
+    <t>114業二07699</t>
+  </si>
+  <si>
+    <t>114業二07700</t>
+  </si>
+  <si>
+    <t>119.04.28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>118.04.20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>117.04.20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119.04.30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119.05.02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0963041181</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0226721114</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃先生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0224653566</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0226822974</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>55/蕭小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>033554556</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>623/郭小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0226580206</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7017/吳小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0437072558</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2265/陳小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0282278586</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>106/吳小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119.04.28</t>
   </si>
 </sst>
 </file>
@@ -32026,7 +32260,7 @@
   <numFmts count="1">
     <numFmt numFmtId="186" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <name val="新細明體"/>
@@ -32055,13 +32289,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="標楷體"/>
-      <family val="4"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <name val="標楷體"/>
       <family val="4"/>
       <charset val="136"/>
@@ -32142,7 +32369,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -32170,7 +32397,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -32185,22 +32412,22 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -32242,38 +32469,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="70">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="68">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -33252,7 +33453,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:J2230"/>
+  <dimension ref="A1:J2246"/>
   <sheetFormatPr defaultRowHeight="21.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" style="5" customWidth="1"/>
@@ -76411,332 +76612,728 @@
         <v>3940</v>
       </c>
     </row>
-    <row r="2225" spans="1:7" s="6" customFormat="1" ht="21.95" customHeight="1">
-      <c r="A2225" s="33" t="s">
+    <row r="2225" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2225" s="2" t="s">
         <v>8570</v>
       </c>
-      <c r="B2225" s="33">
+      <c r="B2225" s="3">
         <v>52693448</v>
       </c>
-      <c r="C2225" s="33" t="s">
+      <c r="C2225" s="1" t="s">
         <v>8569</v>
       </c>
-      <c r="D2225" s="34" t="s">
+      <c r="D2225" s="1" t="s">
         <v>9083</v>
       </c>
-      <c r="F2225" s="6" t="s">
+      <c r="F2225" s="1" t="s">
         <v>9072</v>
       </c>
-      <c r="G2225" s="6" t="s">
+      <c r="G2225" s="1" t="s">
         <v>3798</v>
       </c>
-    </row>
-    <row r="2226" spans="1:7" ht="21.95" customHeight="1">
-      <c r="A2226" s="34" t="s">
+      <c r="H2225" s="1" t="s">
+        <v>9087</v>
+      </c>
+      <c r="I2225" s="1" t="s">
+        <v>9088</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2226" s="2" t="s">
         <v>9073</v>
       </c>
-      <c r="B2226" s="34">
+      <c r="B2226" s="3">
         <v>82842114</v>
       </c>
-      <c r="C2226" s="34" t="s">
+      <c r="C2226" s="1" t="s">
         <v>9078</v>
       </c>
-      <c r="D2226" s="34" t="s">
+      <c r="D2226" s="1" t="s">
         <v>9083</v>
       </c>
-      <c r="F2226" s="6" t="s">
+      <c r="F2226" s="1" t="s">
         <v>9072</v>
       </c>
-      <c r="G2226" s="6" t="s">
+      <c r="G2226" s="1" t="s">
         <v>3798</v>
       </c>
-    </row>
-    <row r="2227" spans="1:7" ht="21.95" customHeight="1">
-      <c r="A2227" s="34" t="s">
+      <c r="H2226" s="1" t="s">
+        <v>9089</v>
+      </c>
+      <c r="I2226" s="1" t="s">
+        <v>9090</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2227" s="2" t="s">
         <v>9074</v>
       </c>
-      <c r="B2227" s="34">
+      <c r="B2227" s="3">
         <v>93841128</v>
       </c>
-      <c r="C2227" s="34" t="s">
+      <c r="C2227" s="1" t="s">
         <v>9079</v>
       </c>
-      <c r="D2227" s="34" t="s">
+      <c r="D2227" s="1" t="s">
         <v>9084</v>
       </c>
-      <c r="F2227" s="6" t="s">
+      <c r="F2227" s="1" t="s">
         <v>9072</v>
       </c>
-      <c r="G2227" s="6" t="s">
+      <c r="G2227" s="1" t="s">
         <v>3798</v>
       </c>
-    </row>
-    <row r="2228" spans="1:7" ht="21.95" customHeight="1">
-      <c r="A2228" s="34" t="s">
+      <c r="H2227" s="1" t="s">
+        <v>9091</v>
+      </c>
+      <c r="I2227" s="1" t="s">
+        <v>9092</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2228" s="2" t="s">
         <v>9075</v>
       </c>
-      <c r="B2228" s="34">
+      <c r="B2228" s="3">
         <v>23935404</v>
       </c>
-      <c r="C2228" s="34" t="s">
+      <c r="C2228" s="1" t="s">
         <v>9080</v>
       </c>
-      <c r="D2228" s="34" t="s">
+      <c r="D2228" s="1" t="s">
         <v>9084</v>
       </c>
-      <c r="F2228" s="6" t="s">
+      <c r="F2228" s="1" t="s">
         <v>9072</v>
       </c>
-      <c r="G2228" s="6" t="s">
+      <c r="G2228" s="1" t="s">
         <v>3798</v>
       </c>
-    </row>
-    <row r="2229" spans="1:7" ht="21.95" customHeight="1">
-      <c r="A2229" s="34" t="s">
+      <c r="H2228" s="1" t="s">
+        <v>9093</v>
+      </c>
+      <c r="I2228" s="1" t="s">
+        <v>9094</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2229" s="2" t="s">
         <v>9076</v>
       </c>
-      <c r="B2229" s="34">
+      <c r="B2229" s="3">
         <v>86226301</v>
       </c>
-      <c r="C2229" s="34" t="s">
+      <c r="C2229" s="1" t="s">
         <v>9081</v>
       </c>
-      <c r="D2229" s="34" t="s">
+      <c r="D2229" s="1" t="s">
         <v>9085</v>
       </c>
-      <c r="F2229" s="6" t="s">
+      <c r="F2229" s="1" t="s">
         <v>9072</v>
       </c>
-      <c r="G2229" s="6" t="s">
+      <c r="G2229" s="1" t="s">
         <v>3798</v>
       </c>
-    </row>
-    <row r="2230" spans="1:7" ht="21.95" customHeight="1">
-      <c r="A2230" s="34" t="s">
+      <c r="H2229" s="1" t="s">
+        <v>9095</v>
+      </c>
+      <c r="I2229" s="1" t="s">
+        <v>9096</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2230" s="2" t="s">
         <v>9077</v>
       </c>
-      <c r="B2230" s="34">
+      <c r="B2230" s="3">
         <v>23500409</v>
       </c>
-      <c r="C2230" s="34" t="s">
+      <c r="C2230" s="1" t="s">
         <v>9082</v>
       </c>
-      <c r="D2230" s="34" t="s">
+      <c r="D2230" s="1" t="s">
         <v>9084</v>
       </c>
-      <c r="F2230" s="6" t="s">
+      <c r="F2230" s="1" t="s">
         <v>9072</v>
       </c>
-      <c r="G2230" s="6" t="s">
+      <c r="G2230" s="1" t="s">
+        <v>3798</v>
+      </c>
+      <c r="H2230" s="1" t="s">
+        <v>9097</v>
+      </c>
+      <c r="I2230" s="1" t="s">
+        <v>9098</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2231" s="5" t="s">
+        <v>9100</v>
+      </c>
+      <c r="B2231" s="3" t="s">
+        <v>9099</v>
+      </c>
+      <c r="C2231" s="1" t="s">
+        <v>9101</v>
+      </c>
+      <c r="D2231" s="1" t="s">
+        <v>9153</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2232" s="5" t="s">
+        <v>9102</v>
+      </c>
+      <c r="B2232" s="3">
+        <v>94038633</v>
+      </c>
+      <c r="C2232" s="1" t="s">
+        <v>9117</v>
+      </c>
+      <c r="D2232" s="1" t="s">
+        <v>9132</v>
+      </c>
+      <c r="F2232" s="1" t="s">
+        <v>9135</v>
+      </c>
+      <c r="G2232" s="1" t="s">
+        <v>3798</v>
+      </c>
+      <c r="H2232" s="1" t="s">
+        <v>9149</v>
+      </c>
+      <c r="I2232" s="1" t="s">
+        <v>9150</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2233" s="5" t="s">
+        <v>9103</v>
+      </c>
+      <c r="B2233" s="3">
+        <v>90300788</v>
+      </c>
+      <c r="C2233" s="1" t="s">
+        <v>9118</v>
+      </c>
+      <c r="D2233" s="1" t="s">
+        <v>9132</v>
+      </c>
+      <c r="F2233" s="1" t="s">
+        <v>9135</v>
+      </c>
+      <c r="G2233" s="1" t="s">
+        <v>3798</v>
+      </c>
+      <c r="H2233" s="1" t="s">
+        <v>9139</v>
+      </c>
+      <c r="I2233" s="1" t="s">
+        <v>9140</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2234" s="5" t="s">
+        <v>9104</v>
+      </c>
+      <c r="B2234" s="3">
+        <v>28173988</v>
+      </c>
+      <c r="C2234" s="1" t="s">
+        <v>9119</v>
+      </c>
+      <c r="D2234" s="1" t="s">
+        <v>9133</v>
+      </c>
+      <c r="F2234" s="1" t="s">
+        <v>9135</v>
+      </c>
+      <c r="G2234" s="1" t="s">
+        <v>3798</v>
+      </c>
+      <c r="H2234" s="1" t="s">
+        <v>9147</v>
+      </c>
+      <c r="I2234" s="1" t="s">
+        <v>9148</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2235" s="5" t="s">
+        <v>9105</v>
+      </c>
+      <c r="B2235" s="3">
+        <v>22456427</v>
+      </c>
+      <c r="C2235" s="1" t="s">
+        <v>9120</v>
+      </c>
+      <c r="D2235" s="1" t="s">
+        <v>9134</v>
+      </c>
+      <c r="F2235" s="1" t="s">
+        <v>9135</v>
+      </c>
+      <c r="G2235" s="1" t="s">
+        <v>8579</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2236" s="5" t="s">
+        <v>9106</v>
+      </c>
+      <c r="B2236" s="3">
+        <v>83136192</v>
+      </c>
+      <c r="C2236" s="1" t="s">
+        <v>9121</v>
+      </c>
+      <c r="D2236" s="1" t="s">
+        <v>9132</v>
+      </c>
+      <c r="F2236" s="1" t="s">
+        <v>9135</v>
+      </c>
+      <c r="G2236" s="1" t="s">
+        <v>3798</v>
+      </c>
+      <c r="H2236" s="1" t="s">
+        <v>9141</v>
+      </c>
+      <c r="I2236" s="1" t="s">
+        <v>9142</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2237" s="5" t="s">
+        <v>9107</v>
+      </c>
+      <c r="B2237" s="3">
+        <v>95486215</v>
+      </c>
+      <c r="C2237" s="1" t="s">
+        <v>9122</v>
+      </c>
+      <c r="D2237" s="1" t="s">
+        <v>9132</v>
+      </c>
+      <c r="F2237" s="1" t="s">
+        <v>9135</v>
+      </c>
+      <c r="G2237" s="1" t="s">
+        <v>3798</v>
+      </c>
+      <c r="H2237" s="1" t="s">
+        <v>9137</v>
+      </c>
+      <c r="I2237" s="1" t="s">
+        <v>9138</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2238" s="5" t="s">
+        <v>9108</v>
+      </c>
+      <c r="B2238" s="3">
+        <v>22133530</v>
+      </c>
+      <c r="C2238" s="1" t="s">
+        <v>9123</v>
+      </c>
+      <c r="D2238" s="1" t="s">
+        <v>9132</v>
+      </c>
+      <c r="F2238" s="1" t="s">
+        <v>9135</v>
+      </c>
+      <c r="G2238" s="1" t="s">
+        <v>3798</v>
+      </c>
+      <c r="H2238" s="1" t="s">
+        <v>9145</v>
+      </c>
+      <c r="I2238" s="1" t="s">
+        <v>9146</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2239" s="5" t="s">
+        <v>9109</v>
+      </c>
+      <c r="B2239" s="3">
+        <v>53907876</v>
+      </c>
+      <c r="C2239" s="1" t="s">
+        <v>9124</v>
+      </c>
+      <c r="D2239" s="1" t="s">
+        <v>9132</v>
+      </c>
+      <c r="F2239" s="1" t="s">
+        <v>9136</v>
+      </c>
+      <c r="G2239" s="1" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2240" s="5" t="s">
+        <v>9110</v>
+      </c>
+      <c r="B2240" s="3">
+        <v>23476816</v>
+      </c>
+      <c r="C2240" s="1" t="s">
+        <v>9125</v>
+      </c>
+      <c r="D2240" s="1" t="s">
+        <v>9132</v>
+      </c>
+      <c r="F2240" s="1" t="s">
+        <v>9136</v>
+      </c>
+      <c r="G2240" s="1" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2241" s="5" t="s">
+        <v>9111</v>
+      </c>
+      <c r="B2241" s="3">
+        <v>80577650</v>
+      </c>
+      <c r="C2241" s="1" t="s">
+        <v>9126</v>
+      </c>
+      <c r="D2241" s="1" t="s">
+        <v>9132</v>
+      </c>
+      <c r="F2241" s="1" t="s">
+        <v>9135</v>
+      </c>
+      <c r="G2241" s="1" t="s">
+        <v>3798</v>
+      </c>
+      <c r="H2241" s="1" t="s">
+        <v>9151</v>
+      </c>
+      <c r="I2241" s="1" t="s">
+        <v>9152</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2242" s="5" t="s">
+        <v>9112</v>
+      </c>
+      <c r="B2242" s="3">
+        <v>42565541</v>
+      </c>
+      <c r="C2242" s="1" t="s">
+        <v>9127</v>
+      </c>
+      <c r="D2242" s="1" t="s">
+        <v>9132</v>
+      </c>
+      <c r="F2242" s="1" t="s">
+        <v>9136</v>
+      </c>
+      <c r="G2242" s="1" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2243" s="5" t="s">
+        <v>9113</v>
+      </c>
+      <c r="B2243" s="3">
+        <v>80567479</v>
+      </c>
+      <c r="C2243" s="1" t="s">
+        <v>9128</v>
+      </c>
+      <c r="D2243" s="1" t="s">
+        <v>9132</v>
+      </c>
+      <c r="F2243" s="1" t="s">
+        <v>9135</v>
+      </c>
+      <c r="G2243" s="1" t="s">
+        <v>8579</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2244" s="5" t="s">
+        <v>9114</v>
+      </c>
+      <c r="B2244" s="3">
+        <v>23548017</v>
+      </c>
+      <c r="C2244" s="1" t="s">
+        <v>9129</v>
+      </c>
+      <c r="D2244" s="1" t="s">
+        <v>9132</v>
+      </c>
+      <c r="F2244" s="1" t="s">
+        <v>9135</v>
+      </c>
+      <c r="G2244" s="1" t="s">
+        <v>3798</v>
+      </c>
+      <c r="H2244" s="1" t="s">
+        <v>9143</v>
+      </c>
+      <c r="I2244" s="1" t="s">
+        <v>9144</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2245" s="5" t="s">
+        <v>9115</v>
+      </c>
+      <c r="B2245" s="3">
+        <v>83249941</v>
+      </c>
+      <c r="C2245" s="1" t="s">
+        <v>9130</v>
+      </c>
+      <c r="D2245" s="1" t="s">
+        <v>9132</v>
+      </c>
+      <c r="F2245" s="1" t="s">
+        <v>9136</v>
+      </c>
+      <c r="G2245" s="1" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2246" s="5" t="s">
+        <v>9116</v>
+      </c>
+      <c r="B2246" s="3">
+        <v>34136126</v>
+      </c>
+      <c r="C2246" s="1" t="s">
+        <v>9131</v>
+      </c>
+      <c r="D2246" s="1" t="s">
+        <v>9132</v>
+      </c>
+      <c r="F2246" s="1" t="s">
+        <v>9136</v>
+      </c>
+      <c r="G2246" s="1" t="s">
         <v>3798</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2022:A2033">
-    <cfRule type="duplicateValues" dxfId="69" priority="139" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="149" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2068:A2075">
-    <cfRule type="duplicateValues" dxfId="68" priority="130" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="140" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2068:B2075">
-    <cfRule type="duplicateValues" dxfId="67" priority="129" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="139" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2076:A2086">
-    <cfRule type="duplicateValues" dxfId="66" priority="113" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="123" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2076:B2086">
-    <cfRule type="duplicateValues" dxfId="65" priority="112" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="122" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2087">
-    <cfRule type="duplicateValues" dxfId="64" priority="99" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="109" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2087">
-    <cfRule type="duplicateValues" dxfId="63" priority="98" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="108" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2088">
-    <cfRule type="duplicateValues" dxfId="62" priority="97" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="107" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2088">
-    <cfRule type="duplicateValues" dxfId="61" priority="96" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="106" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2089">
-    <cfRule type="duplicateValues" dxfId="60" priority="95" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="105" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2089">
-    <cfRule type="duplicateValues" dxfId="59" priority="94" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="104" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2090">
-    <cfRule type="duplicateValues" dxfId="58" priority="93" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="103" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2090">
-    <cfRule type="duplicateValues" dxfId="57" priority="92" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="102" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2091">
-    <cfRule type="duplicateValues" dxfId="56" priority="91" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="101" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2091">
-    <cfRule type="duplicateValues" dxfId="55" priority="90" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="100" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2092">
-    <cfRule type="duplicateValues" dxfId="54" priority="89" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="99" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2092">
-    <cfRule type="duplicateValues" dxfId="53" priority="88" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="98" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2093">
-    <cfRule type="duplicateValues" dxfId="52" priority="87" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="97" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2093">
-    <cfRule type="duplicateValues" dxfId="51" priority="86" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="96" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2094">
-    <cfRule type="duplicateValues" dxfId="50" priority="85" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="95" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2094">
-    <cfRule type="duplicateValues" dxfId="49" priority="84" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="94" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2095">
-    <cfRule type="duplicateValues" dxfId="48" priority="83" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="93" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2095">
-    <cfRule type="duplicateValues" dxfId="47" priority="82" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="92" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2096:A2099">
-    <cfRule type="duplicateValues" dxfId="46" priority="78" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="88" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2096:B2099">
-    <cfRule type="duplicateValues" dxfId="45" priority="77" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="87" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2100:A2107">
-    <cfRule type="duplicateValues" dxfId="44" priority="70" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="80" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2100:B2107">
-    <cfRule type="duplicateValues" dxfId="43" priority="69" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="79" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2231:A65536 A2144:A2203 A2123 A2034:A2067 A1:A2021 A2209">
-    <cfRule type="duplicateValues" dxfId="42" priority="140" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2231 A2144:A2203 A2123 A2034:A2067 A1:A2021 A2209 A2247:A65536">
+    <cfRule type="duplicateValues" dxfId="40" priority="150" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2144:B2203 B2123 B1:B2067 B2209 B2224 B2231:B65536">
-    <cfRule type="duplicateValues" dxfId="41" priority="145" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2144:B2203 B2123 B1:B2067 B2209 B2224 B2231 B2247:B65536">
+    <cfRule type="duplicateValues" dxfId="39" priority="155" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2108:A2115">
-    <cfRule type="duplicateValues" dxfId="40" priority="65" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="75" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2108:B2115">
-    <cfRule type="duplicateValues" dxfId="39" priority="64" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="74" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2116:A2122">
-    <cfRule type="duplicateValues" dxfId="38" priority="60" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="70" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2116:B2122">
-    <cfRule type="duplicateValues" dxfId="37" priority="59" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="69" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2124:A2131">
-    <cfRule type="duplicateValues" dxfId="36" priority="55" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="65" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2124:B2131">
-    <cfRule type="duplicateValues" dxfId="35" priority="54" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="64" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2132">
-    <cfRule type="duplicateValues" dxfId="34" priority="50" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="60" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2132">
-    <cfRule type="duplicateValues" dxfId="33" priority="49" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="59" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2133">
-    <cfRule type="duplicateValues" dxfId="32" priority="48" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="58" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2133">
-    <cfRule type="duplicateValues" dxfId="31" priority="47" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="57" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2134">
-    <cfRule type="duplicateValues" dxfId="30" priority="46" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="56" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2134">
-    <cfRule type="duplicateValues" dxfId="29" priority="45" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="55" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2135:A2140">
-    <cfRule type="duplicateValues" dxfId="28" priority="41" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="51" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2135:B2140">
-    <cfRule type="duplicateValues" dxfId="27" priority="40" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="50" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2141:A2143">
-    <cfRule type="duplicateValues" dxfId="26" priority="39" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="49" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2141:B2143">
-    <cfRule type="duplicateValues" dxfId="25" priority="38" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="48" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2204:A2208">
-    <cfRule type="duplicateValues" dxfId="24" priority="33" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="43" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2204:B2208">
-    <cfRule type="duplicateValues" dxfId="23" priority="34" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="44" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2211:A2213">
-    <cfRule type="duplicateValues" dxfId="22" priority="22" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="32" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2211:B2213">
-    <cfRule type="duplicateValues" dxfId="21" priority="23" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="33" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2215:A2216">
-    <cfRule type="duplicateValues" dxfId="20" priority="20" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="30" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2215:B2216">
-    <cfRule type="duplicateValues" dxfId="19" priority="21" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="31" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2218:A2221">
-    <cfRule type="duplicateValues" dxfId="18" priority="18" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="28" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2218:B2221">
-    <cfRule type="duplicateValues" dxfId="17" priority="19" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="29" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2223">
-    <cfRule type="duplicateValues" dxfId="16" priority="16" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="26" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2223">
-    <cfRule type="duplicateValues" dxfId="15" priority="17" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="27" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2214">
-    <cfRule type="duplicateValues" dxfId="14" priority="14" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="24" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2214">
-    <cfRule type="duplicateValues" dxfId="13" priority="15" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="25" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2222">
-    <cfRule type="duplicateValues" dxfId="12" priority="12" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="22" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2222">
-    <cfRule type="duplicateValues" dxfId="11" priority="13" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="23" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2210">
-    <cfRule type="duplicateValues" dxfId="10" priority="10" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="20" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2210">
-    <cfRule type="duplicateValues" dxfId="9" priority="11" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="21" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2217">
-    <cfRule type="duplicateValues" dxfId="8" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="18" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2217">
-    <cfRule type="duplicateValues" dxfId="7" priority="9" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="19" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2224">
-    <cfRule type="duplicateValues" dxfId="6" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="17" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2225">
-    <cfRule type="duplicateValues" dxfId="5" priority="6" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2225:B2230">
+    <cfRule type="duplicateValues" dxfId="3" priority="10" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2225">
-    <cfRule type="duplicateValues" dxfId="4" priority="4" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="5" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2225:A2230">
+    <cfRule type="duplicateValues" dxfId="2" priority="9" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2226:B2230">
-    <cfRule type="duplicateValues" dxfId="2" priority="3" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2232:A2246">
+    <cfRule type="duplicateValues" dxfId="1" priority="1" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2226:B2230">
-    <cfRule type="duplicateValues" dxfId="1" priority="1" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2232:B2246">
     <cfRule type="duplicateValues" dxfId="0" priority="2" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">

--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="4665" windowWidth="11055" windowHeight="4875"/>
+    <workbookView xWindow="-15" yWindow="4710" windowWidth="11055" windowHeight="4830"/>
   </bookViews>
   <sheets>
     <sheet name="順豐出口" sheetId="4" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12623" uniqueCount="9154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12658" uniqueCount="9170">
   <si>
     <t>麒安科技有限公司</t>
   </si>
@@ -32251,6 +32251,56 @@
   </si>
   <si>
     <t>119.04.28</t>
+  </si>
+  <si>
+    <t>澳洲商摩爾斯微有限公司台灣分公司</t>
+  </si>
+  <si>
+    <t>恆品企業股份有限公司</t>
+  </si>
+  <si>
+    <t>友德國際股份有限公司</t>
+  </si>
+  <si>
+    <t>英屬維京群島商嘉皇有限公司台灣分公司</t>
+  </si>
+  <si>
+    <t>兆發科技股份有限公司</t>
+  </si>
+  <si>
+    <t>台灣穗高科技股份有限公司</t>
+  </si>
+  <si>
+    <t>福珞爾台灣股份有限公司</t>
+  </si>
+  <si>
+    <t>114業二07701</t>
+  </si>
+  <si>
+    <t>114業二07702</t>
+  </si>
+  <si>
+    <t>114業二07703</t>
+  </si>
+  <si>
+    <t>114業二07704</t>
+  </si>
+  <si>
+    <t>114業二07705</t>
+  </si>
+  <si>
+    <t>114業二07706</t>
+  </si>
+  <si>
+    <t>114業二07707</t>
+  </si>
+  <si>
+    <t>119.05.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119.05.08</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -32258,9 +32308,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="186" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
+    <numFmt numFmtId="176" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <name val="新細明體"/>
@@ -32321,6 +32371,13 @@
       <family val="4"/>
       <charset val="136"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <name val="標楷體"/>
+      <family val="4"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -32369,7 +32426,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -32457,7 +32514,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="186" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -32469,12 +32526,45 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="68">
+  <dxfs count="71">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -33453,7 +33543,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:J2246"/>
+  <dimension ref="A1:J2253"/>
   <sheetFormatPr defaultRowHeight="21.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" style="5" customWidth="1"/>
@@ -77130,210 +77220,357 @@
         <v>3798</v>
       </c>
     </row>
+    <row r="2247" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2247" s="33" t="s">
+        <v>9154</v>
+      </c>
+      <c r="B2247" s="33">
+        <v>95448326</v>
+      </c>
+      <c r="C2247" s="33" t="s">
+        <v>9161</v>
+      </c>
+      <c r="D2247" s="33" t="s">
+        <v>9168</v>
+      </c>
+      <c r="F2247" s="1" t="s">
+        <v>9169</v>
+      </c>
+      <c r="G2247" s="1" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2248" s="33" t="s">
+        <v>9155</v>
+      </c>
+      <c r="B2248" s="33">
+        <v>84820811</v>
+      </c>
+      <c r="C2248" s="33" t="s">
+        <v>9162</v>
+      </c>
+      <c r="D2248" s="33" t="s">
+        <v>9168</v>
+      </c>
+      <c r="F2248" s="1" t="s">
+        <v>9169</v>
+      </c>
+      <c r="G2248" s="1" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2249" s="33" t="s">
+        <v>9156</v>
+      </c>
+      <c r="B2249" s="33">
+        <v>12682542</v>
+      </c>
+      <c r="C2249" s="33" t="s">
+        <v>9163</v>
+      </c>
+      <c r="D2249" s="33" t="s">
+        <v>9168</v>
+      </c>
+      <c r="F2249" s="1" t="s">
+        <v>9169</v>
+      </c>
+      <c r="G2249" s="1" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2250" s="33" t="s">
+        <v>9157</v>
+      </c>
+      <c r="B2250" s="33">
+        <v>94078959</v>
+      </c>
+      <c r="C2250" s="33" t="s">
+        <v>9164</v>
+      </c>
+      <c r="D2250" s="33" t="s">
+        <v>9168</v>
+      </c>
+      <c r="F2250" s="1" t="s">
+        <v>9169</v>
+      </c>
+      <c r="G2250" s="1" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2251" s="33" t="s">
+        <v>9158</v>
+      </c>
+      <c r="B2251" s="33">
+        <v>27816750</v>
+      </c>
+      <c r="C2251" s="33" t="s">
+        <v>9165</v>
+      </c>
+      <c r="D2251" s="33" t="s">
+        <v>9168</v>
+      </c>
+      <c r="F2251" s="1" t="s">
+        <v>9169</v>
+      </c>
+      <c r="G2251" s="1" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2252" s="33" t="s">
+        <v>9159</v>
+      </c>
+      <c r="B2252" s="33">
+        <v>80347834</v>
+      </c>
+      <c r="C2252" s="33" t="s">
+        <v>9166</v>
+      </c>
+      <c r="D2252" s="33" t="s">
+        <v>9168</v>
+      </c>
+      <c r="F2252" s="1" t="s">
+        <v>9169</v>
+      </c>
+      <c r="G2252" s="1" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2253" s="33" t="s">
+        <v>9160</v>
+      </c>
+      <c r="B2253" s="33">
+        <v>82926198</v>
+      </c>
+      <c r="C2253" s="33" t="s">
+        <v>9167</v>
+      </c>
+      <c r="D2253" s="33" t="s">
+        <v>9168</v>
+      </c>
+      <c r="F2253" s="1" t="s">
+        <v>9169</v>
+      </c>
+      <c r="G2253" s="1" t="s">
+        <v>3798</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2022:A2033">
-    <cfRule type="duplicateValues" dxfId="67" priority="149" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="152" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2068:A2075">
-    <cfRule type="duplicateValues" dxfId="66" priority="140" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="143" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2068:B2075">
-    <cfRule type="duplicateValues" dxfId="65" priority="139" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="142" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2076:A2086">
-    <cfRule type="duplicateValues" dxfId="64" priority="123" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="126" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2076:B2086">
-    <cfRule type="duplicateValues" dxfId="63" priority="122" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="125" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2087">
+    <cfRule type="duplicateValues" dxfId="65" priority="112" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2087">
+    <cfRule type="duplicateValues" dxfId="64" priority="111" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2088">
+    <cfRule type="duplicateValues" dxfId="63" priority="110" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2088">
     <cfRule type="duplicateValues" dxfId="62" priority="109" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2087">
+  <conditionalFormatting sqref="A2089">
     <cfRule type="duplicateValues" dxfId="61" priority="108" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2088">
+  <conditionalFormatting sqref="B2089">
     <cfRule type="duplicateValues" dxfId="60" priority="107" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2088">
+  <conditionalFormatting sqref="A2090">
     <cfRule type="duplicateValues" dxfId="59" priority="106" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2089">
+  <conditionalFormatting sqref="B2090">
     <cfRule type="duplicateValues" dxfId="58" priority="105" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2089">
+  <conditionalFormatting sqref="A2091">
     <cfRule type="duplicateValues" dxfId="57" priority="104" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2090">
+  <conditionalFormatting sqref="B2091">
     <cfRule type="duplicateValues" dxfId="56" priority="103" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2090">
+  <conditionalFormatting sqref="A2092">
     <cfRule type="duplicateValues" dxfId="55" priority="102" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2091">
+  <conditionalFormatting sqref="B2092">
     <cfRule type="duplicateValues" dxfId="54" priority="101" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2091">
+  <conditionalFormatting sqref="A2093">
     <cfRule type="duplicateValues" dxfId="53" priority="100" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2092">
+  <conditionalFormatting sqref="B2093">
     <cfRule type="duplicateValues" dxfId="52" priority="99" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2092">
+  <conditionalFormatting sqref="A2094">
     <cfRule type="duplicateValues" dxfId="51" priority="98" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2093">
+  <conditionalFormatting sqref="B2094">
     <cfRule type="duplicateValues" dxfId="50" priority="97" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2093">
+  <conditionalFormatting sqref="A2095">
     <cfRule type="duplicateValues" dxfId="49" priority="96" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2094">
+  <conditionalFormatting sqref="B2095">
     <cfRule type="duplicateValues" dxfId="48" priority="95" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2094">
-    <cfRule type="duplicateValues" dxfId="47" priority="94" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2095">
-    <cfRule type="duplicateValues" dxfId="46" priority="93" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2095">
-    <cfRule type="duplicateValues" dxfId="45" priority="92" stopIfTrue="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A2096:A2099">
-    <cfRule type="duplicateValues" dxfId="44" priority="88" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="91" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2096:B2099">
-    <cfRule type="duplicateValues" dxfId="43" priority="87" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="90" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2100:A2107">
-    <cfRule type="duplicateValues" dxfId="42" priority="80" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="83" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2100:B2107">
-    <cfRule type="duplicateValues" dxfId="41" priority="79" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="82" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2231 A2144:A2203 A2123 A2034:A2067 A1:A2021 A2209 A2247:A65536">
-    <cfRule type="duplicateValues" dxfId="40" priority="150" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2231 A2144:A2203 A2123 A2034:A2067 A1:A2021 A2209 A2254:A65536">
+    <cfRule type="duplicateValues" dxfId="43" priority="153" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2144:B2203 B2123 B1:B2067 B2209 B2224 B2231 B2247:B65536">
-    <cfRule type="duplicateValues" dxfId="39" priority="155" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2144:B2203 B2123 B1:B2067 B2209 B2224 B2231 B2254:B65536">
+    <cfRule type="duplicateValues" dxfId="42" priority="158" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2108:A2115">
-    <cfRule type="duplicateValues" dxfId="38" priority="75" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="78" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2108:B2115">
-    <cfRule type="duplicateValues" dxfId="37" priority="74" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="77" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2116:A2122">
-    <cfRule type="duplicateValues" dxfId="36" priority="70" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="73" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2116:B2122">
-    <cfRule type="duplicateValues" dxfId="35" priority="69" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="72" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2124:A2131">
-    <cfRule type="duplicateValues" dxfId="34" priority="65" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="68" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2124:B2131">
-    <cfRule type="duplicateValues" dxfId="33" priority="64" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="67" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2132">
+    <cfRule type="duplicateValues" dxfId="35" priority="63" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2132">
+    <cfRule type="duplicateValues" dxfId="34" priority="62" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2133">
+    <cfRule type="duplicateValues" dxfId="33" priority="61" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2133">
     <cfRule type="duplicateValues" dxfId="32" priority="60" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2132">
+  <conditionalFormatting sqref="A2134">
     <cfRule type="duplicateValues" dxfId="31" priority="59" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2133">
+  <conditionalFormatting sqref="B2134">
     <cfRule type="duplicateValues" dxfId="30" priority="58" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2133">
-    <cfRule type="duplicateValues" dxfId="29" priority="57" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2135:A2140">
+    <cfRule type="duplicateValues" dxfId="29" priority="54" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2134">
-    <cfRule type="duplicateValues" dxfId="28" priority="56" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2135:B2140">
+    <cfRule type="duplicateValues" dxfId="28" priority="53" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2134">
-    <cfRule type="duplicateValues" dxfId="27" priority="55" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2141:A2143">
+    <cfRule type="duplicateValues" dxfId="27" priority="52" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2135:A2140">
+  <conditionalFormatting sqref="B2141:B2143">
     <cfRule type="duplicateValues" dxfId="26" priority="51" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2135:B2140">
-    <cfRule type="duplicateValues" dxfId="25" priority="50" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2141:A2143">
-    <cfRule type="duplicateValues" dxfId="24" priority="49" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2141:B2143">
-    <cfRule type="duplicateValues" dxfId="23" priority="48" stopIfTrue="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A2204:A2208">
-    <cfRule type="duplicateValues" dxfId="22" priority="43" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="46" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2204:B2208">
-    <cfRule type="duplicateValues" dxfId="21" priority="44" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="47" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2211:A2213">
-    <cfRule type="duplicateValues" dxfId="20" priority="32" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="35" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2211:B2213">
-    <cfRule type="duplicateValues" dxfId="19" priority="33" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="36" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2215:A2216">
-    <cfRule type="duplicateValues" dxfId="18" priority="30" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="33" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2215:B2216">
-    <cfRule type="duplicateValues" dxfId="17" priority="31" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="34" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2218:A2221">
-    <cfRule type="duplicateValues" dxfId="16" priority="28" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="31" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2218:B2221">
-    <cfRule type="duplicateValues" dxfId="15" priority="29" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="32" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2223">
-    <cfRule type="duplicateValues" dxfId="14" priority="26" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="29" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2223">
-    <cfRule type="duplicateValues" dxfId="13" priority="27" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="30" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2214">
-    <cfRule type="duplicateValues" dxfId="12" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="27" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2214">
-    <cfRule type="duplicateValues" dxfId="11" priority="25" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="28" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2222">
-    <cfRule type="duplicateValues" dxfId="10" priority="22" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="25" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2222">
-    <cfRule type="duplicateValues" dxfId="9" priority="23" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="26" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2210">
-    <cfRule type="duplicateValues" dxfId="8" priority="20" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="23" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2210">
-    <cfRule type="duplicateValues" dxfId="7" priority="21" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="24" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2217">
-    <cfRule type="duplicateValues" dxfId="6" priority="18" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="21" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2217">
-    <cfRule type="duplicateValues" dxfId="5" priority="19" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="22" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2224">
-    <cfRule type="duplicateValues" dxfId="4" priority="17" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="20" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2225:B2230">
-    <cfRule type="duplicateValues" dxfId="3" priority="10" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="13" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2225:A2230">
-    <cfRule type="duplicateValues" dxfId="2" priority="9" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="12" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2232:A2246">
-    <cfRule type="duplicateValues" dxfId="1" priority="1" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2232:B2246">
+    <cfRule type="duplicateValues" dxfId="3" priority="5" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2247:B2253">
+    <cfRule type="duplicateValues" dxfId="2" priority="3" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2247:B2253">
+    <cfRule type="duplicateValues" dxfId="1" priority="1" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="0" priority="2" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">

--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12658" uniqueCount="9170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12682" uniqueCount="9190">
   <si>
     <t>麒安科技有限公司</t>
   </si>
@@ -32295,12 +32295,87 @@
     <t>114業二07707</t>
   </si>
   <si>
+    <t>0222436177</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>801/游小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>036018088</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>315/蔡小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>065050560</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6183/林小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0937352299</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>劉小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0227993339</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0425233716</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0938011856</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>119.05.05</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>119.05.08</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電話</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WBBL2025055048</t>
+  </si>
+  <si>
+    <t>WBBL2025055063</t>
+  </si>
+  <si>
+    <t>東鴻新世紀有限公司</t>
+  </si>
+  <si>
+    <t>119.05.08</t>
+  </si>
+  <si>
+    <t>114.05.31</t>
   </si>
 </sst>
 </file>
@@ -32310,7 +32385,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <name val="新細明體"/>
@@ -32371,13 +32446,6 @@
       <family val="4"/>
       <charset val="136"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <name val="標楷體"/>
-      <family val="4"/>
-      <charset val="136"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -32426,7 +32494,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -32526,15 +32594,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="71">
+  <dxfs count="72">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -33543,7 +33618,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:J2253"/>
+  <dimension ref="A1:J2255"/>
   <sheetFormatPr defaultRowHeight="21.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" style="5" customWidth="1"/>
@@ -77221,360 +77296,441 @@
       </c>
     </row>
     <row r="2247" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2247" s="33" t="s">
+      <c r="A2247" s="5" t="s">
         <v>9154</v>
       </c>
-      <c r="B2247" s="33">
+      <c r="B2247" s="3">
         <v>95448326</v>
       </c>
-      <c r="C2247" s="33" t="s">
+      <c r="C2247" s="1" t="s">
         <v>9161</v>
       </c>
-      <c r="D2247" s="33" t="s">
+      <c r="D2247" s="1" t="s">
+        <v>9182</v>
+      </c>
+      <c r="F2247" s="1" t="s">
+        <v>9183</v>
+      </c>
+      <c r="G2247" s="1" t="s">
+        <v>9184</v>
+      </c>
+      <c r="H2247" s="1" t="s">
+        <v>9180</v>
+      </c>
+      <c r="I2247" s="1" t="s">
+        <v>9181</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2248" s="5" t="s">
+        <v>9155</v>
+      </c>
+      <c r="B2248" s="3">
+        <v>84820811</v>
+      </c>
+      <c r="C2248" s="1" t="s">
+        <v>9162</v>
+      </c>
+      <c r="D2248" s="1" t="s">
+        <v>9182</v>
+      </c>
+      <c r="F2248" s="1" t="s">
+        <v>9183</v>
+      </c>
+      <c r="G2248" s="1" t="s">
+        <v>9184</v>
+      </c>
+      <c r="H2248" s="1" t="s">
+        <v>9178</v>
+      </c>
+      <c r="I2248" s="1" t="s">
+        <v>9179</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2249" s="5" t="s">
+        <v>9156</v>
+      </c>
+      <c r="B2249" s="3">
+        <v>12682542</v>
+      </c>
+      <c r="C2249" s="1" t="s">
+        <v>9163</v>
+      </c>
+      <c r="D2249" s="1" t="s">
+        <v>9182</v>
+      </c>
+      <c r="F2249" s="1" t="s">
+        <v>9183</v>
+      </c>
+      <c r="G2249" s="1" t="s">
+        <v>9184</v>
+      </c>
+      <c r="H2249" s="1" t="s">
+        <v>9176</v>
+      </c>
+      <c r="I2249" s="1" t="s">
+        <v>9177</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2250" s="5" t="s">
+        <v>9157</v>
+      </c>
+      <c r="B2250" s="3">
+        <v>94078959</v>
+      </c>
+      <c r="C2250" s="1" t="s">
+        <v>9164</v>
+      </c>
+      <c r="D2250" s="1" t="s">
+        <v>9182</v>
+      </c>
+      <c r="F2250" s="1" t="s">
+        <v>9183</v>
+      </c>
+      <c r="G2250" s="1" t="s">
+        <v>9184</v>
+      </c>
+      <c r="H2250" s="1" t="s">
         <v>9168</v>
       </c>
-      <c r="F2247" s="1" t="s">
+      <c r="I2250" s="1" t="s">
         <v>9169</v>
       </c>
-      <c r="G2247" s="1" t="s">
-        <v>3798</v>
-      </c>
-    </row>
-    <row r="2248" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2248" s="33" t="s">
-        <v>9155</v>
-      </c>
-      <c r="B2248" s="33">
-        <v>84820811</v>
-      </c>
-      <c r="C2248" s="33" t="s">
-        <v>9162</v>
-      </c>
-      <c r="D2248" s="33" t="s">
-        <v>9168</v>
-      </c>
-      <c r="F2248" s="1" t="s">
-        <v>9169</v>
-      </c>
-      <c r="G2248" s="1" t="s">
-        <v>3798</v>
-      </c>
-    </row>
-    <row r="2249" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2249" s="33" t="s">
-        <v>9156</v>
-      </c>
-      <c r="B2249" s="33">
-        <v>12682542</v>
-      </c>
-      <c r="C2249" s="33" t="s">
-        <v>9163</v>
-      </c>
-      <c r="D2249" s="33" t="s">
-        <v>9168</v>
-      </c>
-      <c r="F2249" s="1" t="s">
-        <v>9169</v>
-      </c>
-      <c r="G2249" s="1" t="s">
-        <v>3798</v>
-      </c>
-    </row>
-    <row r="2250" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2250" s="33" t="s">
-        <v>9157</v>
-      </c>
-      <c r="B2250" s="33">
-        <v>94078959</v>
-      </c>
-      <c r="C2250" s="33" t="s">
-        <v>9164</v>
-      </c>
-      <c r="D2250" s="33" t="s">
-        <v>9168</v>
-      </c>
-      <c r="F2250" s="1" t="s">
-        <v>9169</v>
-      </c>
-      <c r="G2250" s="1" t="s">
-        <v>3798</v>
-      </c>
     </row>
     <row r="2251" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2251" s="33" t="s">
+      <c r="A2251" s="5" t="s">
         <v>9158</v>
       </c>
-      <c r="B2251" s="33">
+      <c r="B2251" s="3">
         <v>27816750</v>
       </c>
-      <c r="C2251" s="33" t="s">
+      <c r="C2251" s="1" t="s">
         <v>9165</v>
       </c>
-      <c r="D2251" s="33" t="s">
-        <v>9168</v>
+      <c r="D2251" s="1" t="s">
+        <v>9182</v>
       </c>
       <c r="F2251" s="1" t="s">
-        <v>9169</v>
+        <v>9183</v>
       </c>
       <c r="G2251" s="1" t="s">
-        <v>3798</v>
+        <v>9184</v>
+      </c>
+      <c r="H2251" s="1" t="s">
+        <v>9170</v>
+      </c>
+      <c r="I2251" s="1" t="s">
+        <v>9171</v>
       </c>
     </row>
     <row r="2252" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2252" s="33" t="s">
+      <c r="A2252" s="5" t="s">
         <v>9159</v>
       </c>
-      <c r="B2252" s="33">
+      <c r="B2252" s="3">
         <v>80347834</v>
       </c>
-      <c r="C2252" s="33" t="s">
+      <c r="C2252" s="1" t="s">
         <v>9166</v>
       </c>
-      <c r="D2252" s="33" t="s">
-        <v>9168</v>
+      <c r="D2252" s="1" t="s">
+        <v>9182</v>
       </c>
       <c r="F2252" s="1" t="s">
-        <v>9169</v>
+        <v>9183</v>
       </c>
       <c r="G2252" s="1" t="s">
-        <v>3798</v>
+        <v>9184</v>
+      </c>
+      <c r="H2252" s="1" t="s">
+        <v>9172</v>
+      </c>
+      <c r="I2252" s="1" t="s">
+        <v>9173</v>
       </c>
     </row>
     <row r="2253" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2253" s="33" t="s">
+      <c r="A2253" s="5" t="s">
         <v>9160</v>
       </c>
-      <c r="B2253" s="33">
+      <c r="B2253" s="3">
         <v>82926198</v>
       </c>
-      <c r="C2253" s="33" t="s">
+      <c r="C2253" s="1" t="s">
         <v>9167</v>
       </c>
-      <c r="D2253" s="33" t="s">
-        <v>9168</v>
+      <c r="D2253" s="1" t="s">
+        <v>9182</v>
       </c>
       <c r="F2253" s="1" t="s">
-        <v>9169</v>
+        <v>9183</v>
       </c>
       <c r="G2253" s="1" t="s">
-        <v>3798</v>
+        <v>9184</v>
+      </c>
+      <c r="H2253" s="1" t="s">
+        <v>9174</v>
+      </c>
+      <c r="I2253" s="1" t="s">
+        <v>9175</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2254" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2254" s="3" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C2254" s="1" t="s">
+        <v>9186</v>
+      </c>
+      <c r="D2254" s="1" t="s">
+        <v>9188</v>
+      </c>
+      <c r="E2254" s="1" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2255" s="5" t="s">
+        <v>9187</v>
+      </c>
+      <c r="B2255" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C2255" s="1" t="s">
+        <v>9185</v>
+      </c>
+      <c r="D2255" s="1" t="s">
+        <v>9189</v>
+      </c>
+      <c r="E2255" s="1" t="s">
+        <v>3940</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2022:A2033">
-    <cfRule type="duplicateValues" dxfId="70" priority="152" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="156" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2068:A2075">
-    <cfRule type="duplicateValues" dxfId="69" priority="143" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="147" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2068:B2075">
-    <cfRule type="duplicateValues" dxfId="68" priority="142" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="146" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2076:A2086">
-    <cfRule type="duplicateValues" dxfId="67" priority="126" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="130" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2076:B2086">
-    <cfRule type="duplicateValues" dxfId="66" priority="125" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="129" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2087">
-    <cfRule type="duplicateValues" dxfId="65" priority="112" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="116" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2087">
-    <cfRule type="duplicateValues" dxfId="64" priority="111" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="115" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2088">
-    <cfRule type="duplicateValues" dxfId="63" priority="110" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="114" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2088">
-    <cfRule type="duplicateValues" dxfId="62" priority="109" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="113" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2089">
-    <cfRule type="duplicateValues" dxfId="61" priority="108" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="112" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2089">
-    <cfRule type="duplicateValues" dxfId="60" priority="107" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="111" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2090">
-    <cfRule type="duplicateValues" dxfId="59" priority="106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="110" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2090">
-    <cfRule type="duplicateValues" dxfId="58" priority="105" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="109" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2091">
-    <cfRule type="duplicateValues" dxfId="57" priority="104" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="108" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2091">
-    <cfRule type="duplicateValues" dxfId="56" priority="103" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="107" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2092">
-    <cfRule type="duplicateValues" dxfId="55" priority="102" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="106" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2092">
-    <cfRule type="duplicateValues" dxfId="54" priority="101" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="105" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2093">
-    <cfRule type="duplicateValues" dxfId="53" priority="100" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="104" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2093">
-    <cfRule type="duplicateValues" dxfId="52" priority="99" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="103" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2094">
-    <cfRule type="duplicateValues" dxfId="51" priority="98" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="102" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2094">
-    <cfRule type="duplicateValues" dxfId="50" priority="97" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="101" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2095">
-    <cfRule type="duplicateValues" dxfId="49" priority="96" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="100" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2095">
+    <cfRule type="duplicateValues" dxfId="49" priority="99" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2096:A2099">
     <cfRule type="duplicateValues" dxfId="48" priority="95" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2096:A2099">
-    <cfRule type="duplicateValues" dxfId="47" priority="91" stopIfTrue="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B2096:B2099">
-    <cfRule type="duplicateValues" dxfId="46" priority="90" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="94" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2100:A2107">
-    <cfRule type="duplicateValues" dxfId="45" priority="83" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="87" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2100:B2107">
-    <cfRule type="duplicateValues" dxfId="44" priority="82" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="86" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2231 A2144:A2203 A2123 A2034:A2067 A1:A2021 A2209 A2254:A65536">
-    <cfRule type="duplicateValues" dxfId="43" priority="153" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2231 A2144:A2203 A2123 A2034:A2067 A1:A2021 A2209 A2255:A65534">
+    <cfRule type="duplicateValues" dxfId="44" priority="157" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2144:B2203 B2123 B1:B2067 B2209 B2224 B2231 B2254:B65536">
-    <cfRule type="duplicateValues" dxfId="42" priority="158" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2144:B2203 B2123 B1:B2067 B2209 B2224 B2231 B2255:B65534">
+    <cfRule type="duplicateValues" dxfId="43" priority="162" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2108:A2115">
-    <cfRule type="duplicateValues" dxfId="41" priority="78" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="82" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2108:B2115">
+    <cfRule type="duplicateValues" dxfId="41" priority="81" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2116:A2122">
     <cfRule type="duplicateValues" dxfId="40" priority="77" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2116:A2122">
-    <cfRule type="duplicateValues" dxfId="39" priority="73" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2116:B2122">
+    <cfRule type="duplicateValues" dxfId="39" priority="76" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2116:B2122">
+  <conditionalFormatting sqref="A2124:A2131">
     <cfRule type="duplicateValues" dxfId="38" priority="72" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2124:A2131">
-    <cfRule type="duplicateValues" dxfId="37" priority="68" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2124:B2131">
+    <cfRule type="duplicateValues" dxfId="37" priority="71" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2124:B2131">
+  <conditionalFormatting sqref="A2132">
     <cfRule type="duplicateValues" dxfId="36" priority="67" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2132">
-    <cfRule type="duplicateValues" dxfId="35" priority="63" stopIfTrue="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B2132">
-    <cfRule type="duplicateValues" dxfId="34" priority="62" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="66" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2133">
-    <cfRule type="duplicateValues" dxfId="33" priority="61" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="65" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2133">
-    <cfRule type="duplicateValues" dxfId="32" priority="60" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="64" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2134">
-    <cfRule type="duplicateValues" dxfId="31" priority="59" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="63" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2134">
+    <cfRule type="duplicateValues" dxfId="31" priority="62" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2135:A2140">
     <cfRule type="duplicateValues" dxfId="30" priority="58" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2135:A2140">
-    <cfRule type="duplicateValues" dxfId="29" priority="54" stopIfTrue="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B2135:B2140">
-    <cfRule type="duplicateValues" dxfId="28" priority="53" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="57" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2141:A2143">
-    <cfRule type="duplicateValues" dxfId="27" priority="52" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="56" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2141:B2143">
-    <cfRule type="duplicateValues" dxfId="26" priority="51" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="55" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2204:A2208">
-    <cfRule type="duplicateValues" dxfId="25" priority="46" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="50" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2204:B2208">
-    <cfRule type="duplicateValues" dxfId="24" priority="47" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="51" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2211:A2213">
-    <cfRule type="duplicateValues" dxfId="23" priority="35" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="39" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2211:B2213">
-    <cfRule type="duplicateValues" dxfId="22" priority="36" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="40" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2215:A2216">
-    <cfRule type="duplicateValues" dxfId="21" priority="33" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="37" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2215:B2216">
-    <cfRule type="duplicateValues" dxfId="20" priority="34" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="38" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2218:A2221">
-    <cfRule type="duplicateValues" dxfId="19" priority="31" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="35" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2218:B2221">
-    <cfRule type="duplicateValues" dxfId="18" priority="32" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="36" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2223">
-    <cfRule type="duplicateValues" dxfId="17" priority="29" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="33" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2223">
-    <cfRule type="duplicateValues" dxfId="16" priority="30" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="34" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2214">
-    <cfRule type="duplicateValues" dxfId="15" priority="27" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="31" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2214">
-    <cfRule type="duplicateValues" dxfId="14" priority="28" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="32" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2222">
-    <cfRule type="duplicateValues" dxfId="13" priority="25" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="29" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2222">
-    <cfRule type="duplicateValues" dxfId="12" priority="26" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="30" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2210">
-    <cfRule type="duplicateValues" dxfId="11" priority="23" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="27" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2210">
-    <cfRule type="duplicateValues" dxfId="10" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="28" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2217">
-    <cfRule type="duplicateValues" dxfId="9" priority="21" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="25" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2217">
-    <cfRule type="duplicateValues" dxfId="8" priority="22" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="26" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2224">
-    <cfRule type="duplicateValues" dxfId="7" priority="20" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="24" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2225:B2230">
-    <cfRule type="duplicateValues" dxfId="6" priority="13" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="17" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2225:A2230">
-    <cfRule type="duplicateValues" dxfId="5" priority="12" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="16" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2232:A2246">
-    <cfRule type="duplicateValues" dxfId="4" priority="4" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2232:B2246">
-    <cfRule type="duplicateValues" dxfId="3" priority="5" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="9" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2247:A2253">
+    <cfRule type="duplicateValues" dxfId="3" priority="3" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2247:B2253">
-    <cfRule type="duplicateValues" dxfId="2" priority="3" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2247:B2253">
+  <conditionalFormatting sqref="A2254">
     <cfRule type="duplicateValues" dxfId="1" priority="1" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2254">
     <cfRule type="duplicateValues" dxfId="0" priority="2" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1190:G1200 G314:G674 G676:G703 G251:G312 G705:G1187 G2:G249">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1190:G1200 G314:G674 G676:G703 G251:G312 G705:G1187 G2:G249 G2254">
       <formula1>"電話,Mail"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12682" uniqueCount="9190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12741" uniqueCount="9216">
   <si>
     <t>麒安科技有限公司</t>
   </si>
@@ -31968,10 +31968,6 @@
     <t>WBBL2025044850</t>
   </si>
   <si>
-    <t>119.04.24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>博立恆科技有限公司</t>
   </si>
   <si>
@@ -32178,14 +32174,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>119.04.30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>119.05.02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0963041181</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -32355,27 +32343,127 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>電話</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WBBL2025055048</t>
+  </si>
+  <si>
+    <t>WBBL2025055063</t>
+  </si>
+  <si>
+    <t>東鴻新世紀有限公司</t>
+  </si>
+  <si>
     <t>119.05.08</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>電話</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WBBL2025055048</t>
-  </si>
-  <si>
-    <t>WBBL2025055063</t>
-  </si>
-  <si>
-    <t>東鴻新世紀有限公司</t>
+  </si>
+  <si>
+    <t>114.05.31</t>
+  </si>
+  <si>
+    <t>傑艾莉國際貿易有限公司</t>
+  </si>
+  <si>
+    <t>尚敏有限公司</t>
+  </si>
+  <si>
+    <t>航銓科技股份有限公司</t>
+  </si>
+  <si>
+    <t>睿品國際室內裝修有限公司</t>
+  </si>
+  <si>
+    <t>香港商安費諾（東亞）有限公司新竹分公司</t>
+  </si>
+  <si>
+    <t>上劦實業股份有限公司</t>
+  </si>
+  <si>
+    <t>正茂有限公司</t>
+  </si>
+  <si>
+    <t>114業二07708</t>
+  </si>
+  <si>
+    <t>114業二07709</t>
+  </si>
+  <si>
+    <t>114業二07710</t>
+  </si>
+  <si>
+    <t>114業二09145</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二09146</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114業二09147</t>
+  </si>
+  <si>
+    <t>114業二09148</t>
+  </si>
+  <si>
+    <t>114業二09149</t>
+  </si>
+  <si>
+    <t>114業二09150</t>
+  </si>
+  <si>
+    <t>114業二09151</t>
+  </si>
+  <si>
+    <t>114業二09152</t>
+  </si>
+  <si>
+    <t>頎邦科技股份有限公司-C7590</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>頎邦科技股份有限公司-CS349</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119.05.12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>119.05.08</t>
-  </si>
-  <si>
-    <t>114.05.31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elainawang@chipbond.com.tw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114.04.24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114.04.30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114.05.02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114.05.08</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114.05.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114.05.14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -32385,7 +32473,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <name val="新細明體"/>
@@ -32446,6 +32534,13 @@
       <family val="4"/>
       <charset val="136"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <name val="標楷體"/>
+      <family val="4"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -32494,7 +32589,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -32594,12 +32689,45 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="72">
+  <dxfs count="75">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -33618,7 +33746,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:J2255"/>
+  <dimension ref="A1:J2266"/>
   <sheetFormatPr defaultRowHeight="21.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" style="5" customWidth="1"/>
@@ -76771,7 +76899,7 @@
         <v>9071</v>
       </c>
       <c r="D2224" s="1" t="s">
-        <v>9086</v>
+        <v>9085</v>
       </c>
       <c r="E2224" s="1" t="s">
         <v>3940</v>
@@ -76788,258 +76916,258 @@
         <v>8569</v>
       </c>
       <c r="D2225" s="1" t="s">
-        <v>9083</v>
+        <v>9082</v>
       </c>
       <c r="F2225" s="1" t="s">
-        <v>9072</v>
+        <v>9209</v>
       </c>
       <c r="G2225" s="1" t="s">
         <v>3798</v>
       </c>
       <c r="H2225" s="1" t="s">
+        <v>9086</v>
+      </c>
+      <c r="I2225" s="1" t="s">
         <v>9087</v>
-      </c>
-      <c r="I2225" s="1" t="s">
-        <v>9088</v>
       </c>
     </row>
     <row r="2226" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2226" s="2" t="s">
-        <v>9073</v>
+        <v>9072</v>
       </c>
       <c r="B2226" s="3">
         <v>82842114</v>
       </c>
       <c r="C2226" s="1" t="s">
-        <v>9078</v>
+        <v>9077</v>
       </c>
       <c r="D2226" s="1" t="s">
-        <v>9083</v>
+        <v>9082</v>
       </c>
       <c r="F2226" s="1" t="s">
-        <v>9072</v>
+        <v>9209</v>
       </c>
       <c r="G2226" s="1" t="s">
         <v>3798</v>
       </c>
       <c r="H2226" s="1" t="s">
+        <v>9088</v>
+      </c>
+      <c r="I2226" s="1" t="s">
         <v>9089</v>
-      </c>
-      <c r="I2226" s="1" t="s">
-        <v>9090</v>
       </c>
     </row>
     <row r="2227" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2227" s="2" t="s">
-        <v>9074</v>
+        <v>9073</v>
       </c>
       <c r="B2227" s="3">
         <v>93841128</v>
       </c>
       <c r="C2227" s="1" t="s">
-        <v>9079</v>
+        <v>9078</v>
       </c>
       <c r="D2227" s="1" t="s">
-        <v>9084</v>
+        <v>9083</v>
       </c>
       <c r="F2227" s="1" t="s">
-        <v>9072</v>
+        <v>9209</v>
       </c>
       <c r="G2227" s="1" t="s">
         <v>3798</v>
       </c>
       <c r="H2227" s="1" t="s">
+        <v>9090</v>
+      </c>
+      <c r="I2227" s="1" t="s">
         <v>9091</v>
-      </c>
-      <c r="I2227" s="1" t="s">
-        <v>9092</v>
       </c>
     </row>
     <row r="2228" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2228" s="2" t="s">
-        <v>9075</v>
+        <v>9074</v>
       </c>
       <c r="B2228" s="3">
         <v>23935404</v>
       </c>
       <c r="C2228" s="1" t="s">
-        <v>9080</v>
+        <v>9079</v>
       </c>
       <c r="D2228" s="1" t="s">
-        <v>9084</v>
+        <v>9083</v>
       </c>
       <c r="F2228" s="1" t="s">
-        <v>9072</v>
+        <v>9209</v>
       </c>
       <c r="G2228" s="1" t="s">
         <v>3798</v>
       </c>
       <c r="H2228" s="1" t="s">
+        <v>9092</v>
+      </c>
+      <c r="I2228" s="1" t="s">
         <v>9093</v>
-      </c>
-      <c r="I2228" s="1" t="s">
-        <v>9094</v>
       </c>
     </row>
     <row r="2229" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2229" s="2" t="s">
-        <v>9076</v>
+        <v>9075</v>
       </c>
       <c r="B2229" s="3">
         <v>86226301</v>
       </c>
       <c r="C2229" s="1" t="s">
-        <v>9081</v>
+        <v>9080</v>
       </c>
       <c r="D2229" s="1" t="s">
-        <v>9085</v>
+        <v>9084</v>
       </c>
       <c r="F2229" s="1" t="s">
-        <v>9072</v>
+        <v>9209</v>
       </c>
       <c r="G2229" s="1" t="s">
         <v>3798</v>
       </c>
       <c r="H2229" s="1" t="s">
+        <v>9094</v>
+      </c>
+      <c r="I2229" s="1" t="s">
         <v>9095</v>
-      </c>
-      <c r="I2229" s="1" t="s">
-        <v>9096</v>
       </c>
     </row>
     <row r="2230" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2230" s="2" t="s">
-        <v>9077</v>
+        <v>9076</v>
       </c>
       <c r="B2230" s="3">
         <v>23500409</v>
       </c>
       <c r="C2230" s="1" t="s">
-        <v>9082</v>
+        <v>9081</v>
       </c>
       <c r="D2230" s="1" t="s">
-        <v>9084</v>
+        <v>9083</v>
       </c>
       <c r="F2230" s="1" t="s">
-        <v>9072</v>
+        <v>9209</v>
       </c>
       <c r="G2230" s="1" t="s">
         <v>3798</v>
       </c>
       <c r="H2230" s="1" t="s">
+        <v>9096</v>
+      </c>
+      <c r="I2230" s="1" t="s">
         <v>9097</v>
-      </c>
-      <c r="I2230" s="1" t="s">
-        <v>9098</v>
       </c>
     </row>
     <row r="2231" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2231" s="5" t="s">
+        <v>9099</v>
+      </c>
+      <c r="B2231" s="3" t="s">
+        <v>9098</v>
+      </c>
+      <c r="C2231" s="1" t="s">
         <v>9100</v>
       </c>
-      <c r="B2231" s="3" t="s">
-        <v>9099</v>
-      </c>
-      <c r="C2231" s="1" t="s">
-        <v>9101</v>
-      </c>
       <c r="D2231" s="1" t="s">
-        <v>9153</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="2232" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2232" s="5" t="s">
-        <v>9102</v>
+        <v>9101</v>
       </c>
       <c r="B2232" s="3">
         <v>94038633</v>
       </c>
       <c r="C2232" s="1" t="s">
-        <v>9117</v>
+        <v>9116</v>
       </c>
       <c r="D2232" s="1" t="s">
-        <v>9132</v>
+        <v>9131</v>
       </c>
       <c r="F2232" s="1" t="s">
-        <v>9135</v>
+        <v>9210</v>
       </c>
       <c r="G2232" s="1" t="s">
         <v>3798</v>
       </c>
       <c r="H2232" s="1" t="s">
-        <v>9149</v>
+        <v>9146</v>
       </c>
       <c r="I2232" s="1" t="s">
-        <v>9150</v>
+        <v>9147</v>
       </c>
     </row>
     <row r="2233" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2233" s="5" t="s">
-        <v>9103</v>
+        <v>9102</v>
       </c>
       <c r="B2233" s="3">
         <v>90300788</v>
       </c>
       <c r="C2233" s="1" t="s">
-        <v>9118</v>
+        <v>9117</v>
       </c>
       <c r="D2233" s="1" t="s">
-        <v>9132</v>
+        <v>9131</v>
       </c>
       <c r="F2233" s="1" t="s">
-        <v>9135</v>
+        <v>9210</v>
       </c>
       <c r="G2233" s="1" t="s">
         <v>3798</v>
       </c>
       <c r="H2233" s="1" t="s">
-        <v>9139</v>
+        <v>9136</v>
       </c>
       <c r="I2233" s="1" t="s">
-        <v>9140</v>
+        <v>9137</v>
       </c>
     </row>
     <row r="2234" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2234" s="5" t="s">
-        <v>9104</v>
+        <v>9103</v>
       </c>
       <c r="B2234" s="3">
         <v>28173988</v>
       </c>
       <c r="C2234" s="1" t="s">
-        <v>9119</v>
+        <v>9118</v>
       </c>
       <c r="D2234" s="1" t="s">
-        <v>9133</v>
+        <v>9132</v>
       </c>
       <c r="F2234" s="1" t="s">
-        <v>9135</v>
+        <v>9210</v>
       </c>
       <c r="G2234" s="1" t="s">
         <v>3798</v>
       </c>
       <c r="H2234" s="1" t="s">
-        <v>9147</v>
+        <v>9144</v>
       </c>
       <c r="I2234" s="1" t="s">
-        <v>9148</v>
+        <v>9145</v>
       </c>
     </row>
     <row r="2235" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2235" s="5" t="s">
-        <v>9105</v>
+        <v>9104</v>
       </c>
       <c r="B2235" s="3">
         <v>22456427</v>
       </c>
       <c r="C2235" s="1" t="s">
-        <v>9120</v>
+        <v>9119</v>
       </c>
       <c r="D2235" s="1" t="s">
-        <v>9134</v>
+        <v>9133</v>
       </c>
       <c r="F2235" s="1" t="s">
-        <v>9135</v>
+        <v>9210</v>
       </c>
       <c r="G2235" s="1" t="s">
         <v>8579</v>
@@ -77047,97 +77175,97 @@
     </row>
     <row r="2236" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2236" s="5" t="s">
-        <v>9106</v>
+        <v>9105</v>
       </c>
       <c r="B2236" s="3">
         <v>83136192</v>
       </c>
       <c r="C2236" s="1" t="s">
-        <v>9121</v>
+        <v>9120</v>
       </c>
       <c r="D2236" s="1" t="s">
-        <v>9132</v>
+        <v>9131</v>
       </c>
       <c r="F2236" s="1" t="s">
-        <v>9135</v>
+        <v>9210</v>
       </c>
       <c r="G2236" s="1" t="s">
         <v>3798</v>
       </c>
       <c r="H2236" s="1" t="s">
-        <v>9141</v>
+        <v>9138</v>
       </c>
       <c r="I2236" s="1" t="s">
-        <v>9142</v>
+        <v>9139</v>
       </c>
     </row>
     <row r="2237" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2237" s="5" t="s">
-        <v>9107</v>
+        <v>9106</v>
       </c>
       <c r="B2237" s="3">
         <v>95486215</v>
       </c>
       <c r="C2237" s="1" t="s">
-        <v>9122</v>
+        <v>9121</v>
       </c>
       <c r="D2237" s="1" t="s">
-        <v>9132</v>
+        <v>9131</v>
       </c>
       <c r="F2237" s="1" t="s">
-        <v>9135</v>
+        <v>9210</v>
       </c>
       <c r="G2237" s="1" t="s">
         <v>3798</v>
       </c>
       <c r="H2237" s="1" t="s">
-        <v>9137</v>
+        <v>9134</v>
       </c>
       <c r="I2237" s="1" t="s">
-        <v>9138</v>
+        <v>9135</v>
       </c>
     </row>
     <row r="2238" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2238" s="5" t="s">
-        <v>9108</v>
+        <v>9107</v>
       </c>
       <c r="B2238" s="3">
         <v>22133530</v>
       </c>
       <c r="C2238" s="1" t="s">
-        <v>9123</v>
+        <v>9122</v>
       </c>
       <c r="D2238" s="1" t="s">
-        <v>9132</v>
+        <v>9131</v>
       </c>
       <c r="F2238" s="1" t="s">
-        <v>9135</v>
+        <v>9210</v>
       </c>
       <c r="G2238" s="1" t="s">
         <v>3798</v>
       </c>
       <c r="H2238" s="1" t="s">
-        <v>9145</v>
+        <v>9142</v>
       </c>
       <c r="I2238" s="1" t="s">
-        <v>9146</v>
+        <v>9143</v>
       </c>
     </row>
     <row r="2239" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2239" s="5" t="s">
-        <v>9109</v>
+        <v>9108</v>
       </c>
       <c r="B2239" s="3">
         <v>53907876</v>
       </c>
       <c r="C2239" s="1" t="s">
-        <v>9124</v>
+        <v>9123</v>
       </c>
       <c r="D2239" s="1" t="s">
-        <v>9132</v>
+        <v>9131</v>
       </c>
       <c r="F2239" s="1" t="s">
-        <v>9136</v>
+        <v>9211</v>
       </c>
       <c r="G2239" s="1" t="s">
         <v>3798</v>
@@ -77145,19 +77273,19 @@
     </row>
     <row r="2240" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2240" s="5" t="s">
-        <v>9110</v>
+        <v>9109</v>
       </c>
       <c r="B2240" s="3">
         <v>23476816</v>
       </c>
       <c r="C2240" s="1" t="s">
-        <v>9125</v>
+        <v>9124</v>
       </c>
       <c r="D2240" s="1" t="s">
-        <v>9132</v>
+        <v>9131</v>
       </c>
       <c r="F2240" s="1" t="s">
-        <v>9136</v>
+        <v>9211</v>
       </c>
       <c r="G2240" s="1" t="s">
         <v>3798</v>
@@ -77165,45 +77293,45 @@
     </row>
     <row r="2241" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2241" s="5" t="s">
-        <v>9111</v>
+        <v>9110</v>
       </c>
       <c r="B2241" s="3">
         <v>80577650</v>
       </c>
       <c r="C2241" s="1" t="s">
-        <v>9126</v>
+        <v>9125</v>
       </c>
       <c r="D2241" s="1" t="s">
-        <v>9132</v>
+        <v>9131</v>
       </c>
       <c r="F2241" s="1" t="s">
-        <v>9135</v>
+        <v>9210</v>
       </c>
       <c r="G2241" s="1" t="s">
         <v>3798</v>
       </c>
       <c r="H2241" s="1" t="s">
-        <v>9151</v>
+        <v>9148</v>
       </c>
       <c r="I2241" s="1" t="s">
-        <v>9152</v>
+        <v>9149</v>
       </c>
     </row>
     <row r="2242" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2242" s="5" t="s">
-        <v>9112</v>
+        <v>9111</v>
       </c>
       <c r="B2242" s="3">
         <v>42565541</v>
       </c>
       <c r="C2242" s="1" t="s">
-        <v>9127</v>
+        <v>9126</v>
       </c>
       <c r="D2242" s="1" t="s">
-        <v>9132</v>
+        <v>9131</v>
       </c>
       <c r="F2242" s="1" t="s">
-        <v>9136</v>
+        <v>9211</v>
       </c>
       <c r="G2242" s="1" t="s">
         <v>3798</v>
@@ -77211,19 +77339,19 @@
     </row>
     <row r="2243" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2243" s="5" t="s">
-        <v>9113</v>
+        <v>9112</v>
       </c>
       <c r="B2243" s="3">
         <v>80567479</v>
       </c>
       <c r="C2243" s="1" t="s">
-        <v>9128</v>
+        <v>9127</v>
       </c>
       <c r="D2243" s="1" t="s">
-        <v>9132</v>
+        <v>9131</v>
       </c>
       <c r="F2243" s="1" t="s">
-        <v>9135</v>
+        <v>9210</v>
       </c>
       <c r="G2243" s="1" t="s">
         <v>8579</v>
@@ -77231,45 +77359,45 @@
     </row>
     <row r="2244" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2244" s="5" t="s">
-        <v>9114</v>
+        <v>9113</v>
       </c>
       <c r="B2244" s="3">
         <v>23548017</v>
       </c>
       <c r="C2244" s="1" t="s">
-        <v>9129</v>
+        <v>9128</v>
       </c>
       <c r="D2244" s="1" t="s">
-        <v>9132</v>
+        <v>9131</v>
       </c>
       <c r="F2244" s="1" t="s">
-        <v>9135</v>
+        <v>9210</v>
       </c>
       <c r="G2244" s="1" t="s">
         <v>3798</v>
       </c>
       <c r="H2244" s="1" t="s">
-        <v>9143</v>
+        <v>9140</v>
       </c>
       <c r="I2244" s="1" t="s">
-        <v>9144</v>
+        <v>9141</v>
       </c>
     </row>
     <row r="2245" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2245" s="5" t="s">
-        <v>9115</v>
+        <v>9114</v>
       </c>
       <c r="B2245" s="3">
         <v>83249941</v>
       </c>
       <c r="C2245" s="1" t="s">
-        <v>9130</v>
+        <v>9129</v>
       </c>
       <c r="D2245" s="1" t="s">
-        <v>9132</v>
+        <v>9131</v>
       </c>
       <c r="F2245" s="1" t="s">
-        <v>9136</v>
+        <v>9211</v>
       </c>
       <c r="G2245" s="1" t="s">
         <v>3798</v>
@@ -77277,19 +77405,19 @@
     </row>
     <row r="2246" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2246" s="5" t="s">
-        <v>9116</v>
+        <v>9115</v>
       </c>
       <c r="B2246" s="3">
         <v>34136126</v>
       </c>
       <c r="C2246" s="1" t="s">
+        <v>9130</v>
+      </c>
+      <c r="D2246" s="1" t="s">
         <v>9131</v>
       </c>
-      <c r="D2246" s="1" t="s">
-        <v>9132</v>
-      </c>
       <c r="F2246" s="1" t="s">
-        <v>9136</v>
+        <v>9211</v>
       </c>
       <c r="G2246" s="1" t="s">
         <v>3798</v>
@@ -77297,184 +77425,184 @@
     </row>
     <row r="2247" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2247" s="5" t="s">
-        <v>9154</v>
+        <v>9151</v>
       </c>
       <c r="B2247" s="3">
         <v>95448326</v>
       </c>
       <c r="C2247" s="1" t="s">
-        <v>9161</v>
+        <v>9158</v>
       </c>
       <c r="D2247" s="1" t="s">
-        <v>9182</v>
+        <v>9179</v>
       </c>
       <c r="F2247" s="1" t="s">
-        <v>9183</v>
+        <v>9212</v>
       </c>
       <c r="G2247" s="1" t="s">
-        <v>9184</v>
+        <v>9180</v>
       </c>
       <c r="H2247" s="1" t="s">
-        <v>9180</v>
+        <v>9177</v>
       </c>
       <c r="I2247" s="1" t="s">
-        <v>9181</v>
+        <v>9178</v>
       </c>
     </row>
     <row r="2248" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2248" s="5" t="s">
-        <v>9155</v>
+        <v>9152</v>
       </c>
       <c r="B2248" s="3">
         <v>84820811</v>
       </c>
       <c r="C2248" s="1" t="s">
-        <v>9162</v>
+        <v>9159</v>
       </c>
       <c r="D2248" s="1" t="s">
-        <v>9182</v>
+        <v>9179</v>
       </c>
       <c r="F2248" s="1" t="s">
-        <v>9183</v>
+        <v>9212</v>
       </c>
       <c r="G2248" s="1" t="s">
-        <v>9184</v>
+        <v>9180</v>
       </c>
       <c r="H2248" s="1" t="s">
-        <v>9178</v>
+        <v>9175</v>
       </c>
       <c r="I2248" s="1" t="s">
-        <v>9179</v>
+        <v>9176</v>
       </c>
     </row>
     <row r="2249" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2249" s="5" t="s">
-        <v>9156</v>
+        <v>9153</v>
       </c>
       <c r="B2249" s="3">
         <v>12682542</v>
       </c>
       <c r="C2249" s="1" t="s">
-        <v>9163</v>
+        <v>9160</v>
       </c>
       <c r="D2249" s="1" t="s">
-        <v>9182</v>
+        <v>9179</v>
       </c>
       <c r="F2249" s="1" t="s">
-        <v>9183</v>
+        <v>9212</v>
       </c>
       <c r="G2249" s="1" t="s">
-        <v>9184</v>
+        <v>9180</v>
       </c>
       <c r="H2249" s="1" t="s">
-        <v>9176</v>
+        <v>9173</v>
       </c>
       <c r="I2249" s="1" t="s">
-        <v>9177</v>
+        <v>9174</v>
       </c>
     </row>
     <row r="2250" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2250" s="5" t="s">
-        <v>9157</v>
+        <v>9154</v>
       </c>
       <c r="B2250" s="3">
         <v>94078959</v>
       </c>
       <c r="C2250" s="1" t="s">
-        <v>9164</v>
+        <v>9161</v>
       </c>
       <c r="D2250" s="1" t="s">
-        <v>9182</v>
+        <v>9179</v>
       </c>
       <c r="F2250" s="1" t="s">
-        <v>9183</v>
+        <v>9212</v>
       </c>
       <c r="G2250" s="1" t="s">
-        <v>9184</v>
+        <v>9180</v>
       </c>
       <c r="H2250" s="1" t="s">
-        <v>9168</v>
+        <v>9165</v>
       </c>
       <c r="I2250" s="1" t="s">
-        <v>9169</v>
+        <v>9166</v>
       </c>
     </row>
     <row r="2251" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2251" s="5" t="s">
-        <v>9158</v>
+        <v>9155</v>
       </c>
       <c r="B2251" s="3">
         <v>27816750</v>
       </c>
       <c r="C2251" s="1" t="s">
-        <v>9165</v>
+        <v>9162</v>
       </c>
       <c r="D2251" s="1" t="s">
-        <v>9182</v>
+        <v>9179</v>
       </c>
       <c r="F2251" s="1" t="s">
-        <v>9183</v>
+        <v>9212</v>
       </c>
       <c r="G2251" s="1" t="s">
-        <v>9184</v>
+        <v>9180</v>
       </c>
       <c r="H2251" s="1" t="s">
-        <v>9170</v>
+        <v>9167</v>
       </c>
       <c r="I2251" s="1" t="s">
-        <v>9171</v>
+        <v>9168</v>
       </c>
     </row>
     <row r="2252" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2252" s="5" t="s">
-        <v>9159</v>
+        <v>9156</v>
       </c>
       <c r="B2252" s="3">
         <v>80347834</v>
       </c>
       <c r="C2252" s="1" t="s">
-        <v>9166</v>
+        <v>9163</v>
       </c>
       <c r="D2252" s="1" t="s">
-        <v>9182</v>
+        <v>9179</v>
       </c>
       <c r="F2252" s="1" t="s">
-        <v>9183</v>
+        <v>9212</v>
       </c>
       <c r="G2252" s="1" t="s">
-        <v>9184</v>
+        <v>9180</v>
       </c>
       <c r="H2252" s="1" t="s">
-        <v>9172</v>
+        <v>9169</v>
       </c>
       <c r="I2252" s="1" t="s">
-        <v>9173</v>
+        <v>9170</v>
       </c>
     </row>
     <row r="2253" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2253" s="5" t="s">
-        <v>9160</v>
+        <v>9157</v>
       </c>
       <c r="B2253" s="3">
         <v>82926198</v>
       </c>
       <c r="C2253" s="1" t="s">
-        <v>9167</v>
+        <v>9164</v>
       </c>
       <c r="D2253" s="1" t="s">
-        <v>9182</v>
+        <v>9179</v>
       </c>
       <c r="F2253" s="1" t="s">
-        <v>9183</v>
+        <v>9212</v>
       </c>
       <c r="G2253" s="1" t="s">
-        <v>9184</v>
+        <v>9180</v>
       </c>
       <c r="H2253" s="1" t="s">
-        <v>9174</v>
+        <v>9171</v>
       </c>
       <c r="I2253" s="1" t="s">
-        <v>9175</v>
+        <v>9172</v>
       </c>
     </row>
     <row r="2254" spans="1:9" ht="21.95" customHeight="1">
@@ -77485,10 +77613,10 @@
         <v>1595</v>
       </c>
       <c r="C2254" s="1" t="s">
-        <v>9186</v>
+        <v>9182</v>
       </c>
       <c r="D2254" s="1" t="s">
-        <v>9188</v>
+        <v>9184</v>
       </c>
       <c r="E2254" s="1" t="s">
         <v>3940</v>
@@ -77496,237 +77624,476 @@
     </row>
     <row r="2255" spans="1:9" ht="21.95" customHeight="1">
       <c r="A2255" s="5" t="s">
-        <v>9187</v>
+        <v>9183</v>
       </c>
       <c r="B2255" s="3" t="s">
         <v>1594</v>
       </c>
       <c r="C2255" s="1" t="s">
+        <v>9181</v>
+      </c>
+      <c r="D2255" s="1" t="s">
         <v>9185</v>
-      </c>
-      <c r="D2255" s="1" t="s">
-        <v>9189</v>
       </c>
       <c r="E2255" s="1" t="s">
         <v>3940</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A2256" s="33" t="s">
+        <v>9186</v>
+      </c>
+      <c r="B2256" s="33">
+        <v>24563182</v>
+      </c>
+      <c r="C2256" s="33" t="s">
+        <v>9193</v>
+      </c>
+      <c r="D2256" s="33" t="s">
+        <v>9206</v>
+      </c>
+      <c r="F2256" s="1" t="s">
+        <v>9213</v>
+      </c>
+      <c r="G2256" s="1" t="s">
+        <v>9180</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A2257" s="33" t="s">
+        <v>9187</v>
+      </c>
+      <c r="B2257" s="33">
+        <v>22857865</v>
+      </c>
+      <c r="C2257" s="33" t="s">
+        <v>9194</v>
+      </c>
+      <c r="D2257" s="33" t="s">
+        <v>9207</v>
+      </c>
+      <c r="F2257" s="1" t="s">
+        <v>9213</v>
+      </c>
+      <c r="G2257" s="1" t="s">
+        <v>9180</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A2258" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2258" s="33">
+        <v>56642765</v>
+      </c>
+      <c r="C2258" s="33" t="s">
+        <v>9195</v>
+      </c>
+      <c r="D2258" s="33" t="s">
+        <v>9206</v>
+      </c>
+      <c r="F2258" s="1" t="s">
+        <v>9213</v>
+      </c>
+      <c r="G2258" s="1" t="s">
+        <v>9180</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A2259" s="33" t="s">
+        <v>9188</v>
+      </c>
+      <c r="B2259" s="33">
+        <v>54570554</v>
+      </c>
+      <c r="C2259" s="33" t="s">
+        <v>9196</v>
+      </c>
+      <c r="D2259" s="33" t="s">
+        <v>9206</v>
+      </c>
+      <c r="F2259" s="1" t="s">
+        <v>9213</v>
+      </c>
+      <c r="G2259" s="1" t="s">
+        <v>9180</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A2260" s="33" t="s">
+        <v>9189</v>
+      </c>
+      <c r="B2260" s="33">
+        <v>53788554</v>
+      </c>
+      <c r="C2260" s="33" t="s">
+        <v>9197</v>
+      </c>
+      <c r="D2260" s="33" t="s">
+        <v>9206</v>
+      </c>
+      <c r="F2260" s="1" t="s">
+        <v>9213</v>
+      </c>
+      <c r="G2260" s="1" t="s">
+        <v>9180</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A2261" s="33" t="s">
+        <v>9190</v>
+      </c>
+      <c r="B2261" s="33">
+        <v>83794006</v>
+      </c>
+      <c r="C2261" s="33" t="s">
+        <v>9198</v>
+      </c>
+      <c r="D2261" s="33" t="s">
+        <v>9206</v>
+      </c>
+      <c r="F2261" s="1" t="s">
+        <v>9213</v>
+      </c>
+      <c r="G2261" s="1" t="s">
+        <v>9180</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A2262" s="33" t="s">
+        <v>9191</v>
+      </c>
+      <c r="B2262" s="33">
+        <v>30836793</v>
+      </c>
+      <c r="C2262" s="33" t="s">
+        <v>9199</v>
+      </c>
+      <c r="D2262" s="33" t="s">
+        <v>9206</v>
+      </c>
+      <c r="F2262" s="1" t="s">
+        <v>9213</v>
+      </c>
+      <c r="G2262" s="1" t="s">
+        <v>9180</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A2263" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="B2263" s="33">
+        <v>28732006</v>
+      </c>
+      <c r="C2263" s="33" t="s">
+        <v>9200</v>
+      </c>
+      <c r="D2263" s="33" t="s">
+        <v>9206</v>
+      </c>
+      <c r="F2263" s="1" t="s">
+        <v>9213</v>
+      </c>
+      <c r="G2263" s="1" t="s">
+        <v>9180</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A2264" s="33" t="s">
+        <v>9192</v>
+      </c>
+      <c r="B2264" s="33">
+        <v>53718100</v>
+      </c>
+      <c r="C2264" s="33" t="s">
+        <v>9201</v>
+      </c>
+      <c r="D2264" s="33" t="s">
+        <v>9206</v>
+      </c>
+      <c r="F2264" s="1" t="s">
+        <v>9213</v>
+      </c>
+      <c r="G2264" s="1" t="s">
+        <v>9180</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A2265" s="33" t="s">
+        <v>9204</v>
+      </c>
+      <c r="B2265" s="33">
+        <v>16130009</v>
+      </c>
+      <c r="C2265" s="33" t="s">
+        <v>9202</v>
+      </c>
+      <c r="D2265" s="33" t="s">
+        <v>9206</v>
+      </c>
+      <c r="F2265" s="1" t="s">
+        <v>9215</v>
+      </c>
+      <c r="G2265" s="1" t="s">
+        <v>8579</v>
+      </c>
+      <c r="I2265" s="1" t="s">
+        <v>9214</v>
+      </c>
+      <c r="J2265" s="22" t="s">
+        <v>9208</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:10" ht="21.95" customHeight="1">
+      <c r="A2266" s="33" t="s">
+        <v>9205</v>
+      </c>
+      <c r="B2266" s="33">
+        <v>16130009</v>
+      </c>
+      <c r="C2266" s="33" t="s">
+        <v>9203</v>
+      </c>
+      <c r="D2266" s="33" t="s">
+        <v>9206</v>
+      </c>
+      <c r="F2266" s="1" t="s">
+        <v>9215</v>
+      </c>
+      <c r="G2266" s="1" t="s">
+        <v>8579</v>
+      </c>
+      <c r="I2266" s="1" t="s">
+        <v>9214</v>
+      </c>
+      <c r="J2266" s="22" t="s">
+        <v>9208</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2022:A2033">
-    <cfRule type="duplicateValues" dxfId="71" priority="156" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="159" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2068:A2075">
-    <cfRule type="duplicateValues" dxfId="70" priority="147" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="150" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2068:B2075">
-    <cfRule type="duplicateValues" dxfId="69" priority="146" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="149" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2076:A2086">
-    <cfRule type="duplicateValues" dxfId="68" priority="130" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="133" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2076:B2086">
-    <cfRule type="duplicateValues" dxfId="67" priority="129" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="132" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2087">
+    <cfRule type="duplicateValues" dxfId="69" priority="119" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2087">
+    <cfRule type="duplicateValues" dxfId="68" priority="118" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2088">
+    <cfRule type="duplicateValues" dxfId="67" priority="117" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2088">
     <cfRule type="duplicateValues" dxfId="66" priority="116" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2087">
+  <conditionalFormatting sqref="A2089">
     <cfRule type="duplicateValues" dxfId="65" priority="115" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2088">
+  <conditionalFormatting sqref="B2089">
     <cfRule type="duplicateValues" dxfId="64" priority="114" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2088">
+  <conditionalFormatting sqref="A2090">
     <cfRule type="duplicateValues" dxfId="63" priority="113" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2089">
+  <conditionalFormatting sqref="B2090">
     <cfRule type="duplicateValues" dxfId="62" priority="112" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2089">
+  <conditionalFormatting sqref="A2091">
     <cfRule type="duplicateValues" dxfId="61" priority="111" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2090">
+  <conditionalFormatting sqref="B2091">
     <cfRule type="duplicateValues" dxfId="60" priority="110" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2090">
+  <conditionalFormatting sqref="A2092">
     <cfRule type="duplicateValues" dxfId="59" priority="109" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2091">
+  <conditionalFormatting sqref="B2092">
     <cfRule type="duplicateValues" dxfId="58" priority="108" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2091">
+  <conditionalFormatting sqref="A2093">
     <cfRule type="duplicateValues" dxfId="57" priority="107" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2092">
+  <conditionalFormatting sqref="B2093">
     <cfRule type="duplicateValues" dxfId="56" priority="106" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2092">
+  <conditionalFormatting sqref="A2094">
     <cfRule type="duplicateValues" dxfId="55" priority="105" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2093">
+  <conditionalFormatting sqref="B2094">
     <cfRule type="duplicateValues" dxfId="54" priority="104" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2093">
+  <conditionalFormatting sqref="A2095">
     <cfRule type="duplicateValues" dxfId="53" priority="103" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2094">
+  <conditionalFormatting sqref="B2095">
     <cfRule type="duplicateValues" dxfId="52" priority="102" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2094">
-    <cfRule type="duplicateValues" dxfId="51" priority="101" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2095">
-    <cfRule type="duplicateValues" dxfId="50" priority="100" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2095">
-    <cfRule type="duplicateValues" dxfId="49" priority="99" stopIfTrue="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A2096:A2099">
-    <cfRule type="duplicateValues" dxfId="48" priority="95" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="98" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2096:B2099">
-    <cfRule type="duplicateValues" dxfId="47" priority="94" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="97" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2100:A2107">
-    <cfRule type="duplicateValues" dxfId="46" priority="87" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="90" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2100:B2107">
-    <cfRule type="duplicateValues" dxfId="45" priority="86" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="89" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2231 A2144:A2203 A2123 A2034:A2067 A1:A2021 A2209 A2255:A65534">
-    <cfRule type="duplicateValues" dxfId="44" priority="157" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2231 A2144:A2203 A2123 A2034:A2067 A1:A2021 A2209 A2255 A2267:A65534">
+    <cfRule type="duplicateValues" dxfId="47" priority="160" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2144:B2203 B2123 B1:B2067 B2209 B2224 B2231 B2255:B65534">
-    <cfRule type="duplicateValues" dxfId="43" priority="162" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2144:B2203 B2123 B1:B2067 B2209 B2224 B2231 B2255 B2267:B65534">
+    <cfRule type="duplicateValues" dxfId="46" priority="165" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2108:A2115">
-    <cfRule type="duplicateValues" dxfId="42" priority="82" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="85" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2108:B2115">
-    <cfRule type="duplicateValues" dxfId="41" priority="81" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="84" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2116:A2122">
-    <cfRule type="duplicateValues" dxfId="40" priority="77" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="80" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2116:B2122">
-    <cfRule type="duplicateValues" dxfId="39" priority="76" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="79" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2124:A2131">
-    <cfRule type="duplicateValues" dxfId="38" priority="72" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="75" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2124:B2131">
-    <cfRule type="duplicateValues" dxfId="37" priority="71" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="74" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2132">
+    <cfRule type="duplicateValues" dxfId="39" priority="70" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2132">
+    <cfRule type="duplicateValues" dxfId="38" priority="69" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2133">
+    <cfRule type="duplicateValues" dxfId="37" priority="68" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2133">
     <cfRule type="duplicateValues" dxfId="36" priority="67" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2132">
+  <conditionalFormatting sqref="A2134">
     <cfRule type="duplicateValues" dxfId="35" priority="66" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2133">
+  <conditionalFormatting sqref="B2134">
     <cfRule type="duplicateValues" dxfId="34" priority="65" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2133">
-    <cfRule type="duplicateValues" dxfId="33" priority="64" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2135:A2140">
+    <cfRule type="duplicateValues" dxfId="33" priority="61" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2134">
-    <cfRule type="duplicateValues" dxfId="32" priority="63" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B2135:B2140">
+    <cfRule type="duplicateValues" dxfId="32" priority="60" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2134">
-    <cfRule type="duplicateValues" dxfId="31" priority="62" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A2141:A2143">
+    <cfRule type="duplicateValues" dxfId="31" priority="59" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2135:A2140">
+  <conditionalFormatting sqref="B2141:B2143">
     <cfRule type="duplicateValues" dxfId="30" priority="58" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2135:B2140">
-    <cfRule type="duplicateValues" dxfId="29" priority="57" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2141:A2143">
-    <cfRule type="duplicateValues" dxfId="28" priority="56" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2141:B2143">
-    <cfRule type="duplicateValues" dxfId="27" priority="55" stopIfTrue="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A2204:A2208">
-    <cfRule type="duplicateValues" dxfId="26" priority="50" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="53" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2204:B2208">
-    <cfRule type="duplicateValues" dxfId="25" priority="51" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="54" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2211:A2213">
-    <cfRule type="duplicateValues" dxfId="24" priority="39" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="42" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2211:B2213">
-    <cfRule type="duplicateValues" dxfId="23" priority="40" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="43" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2215:A2216">
-    <cfRule type="duplicateValues" dxfId="22" priority="37" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="40" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2215:B2216">
-    <cfRule type="duplicateValues" dxfId="21" priority="38" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="41" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2218:A2221">
-    <cfRule type="duplicateValues" dxfId="20" priority="35" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="38" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2218:B2221">
-    <cfRule type="duplicateValues" dxfId="19" priority="36" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="39" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2223">
-    <cfRule type="duplicateValues" dxfId="18" priority="33" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="36" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2223">
-    <cfRule type="duplicateValues" dxfId="17" priority="34" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="37" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2214">
-    <cfRule type="duplicateValues" dxfId="16" priority="31" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="34" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2214">
-    <cfRule type="duplicateValues" dxfId="15" priority="32" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="35" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2222">
-    <cfRule type="duplicateValues" dxfId="14" priority="29" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="32" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2222">
-    <cfRule type="duplicateValues" dxfId="13" priority="30" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="33" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2210">
-    <cfRule type="duplicateValues" dxfId="12" priority="27" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="30" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2210">
-    <cfRule type="duplicateValues" dxfId="11" priority="28" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="31" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2217">
-    <cfRule type="duplicateValues" dxfId="10" priority="25" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="28" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2217">
-    <cfRule type="duplicateValues" dxfId="9" priority="26" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="29" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2224">
-    <cfRule type="duplicateValues" dxfId="8" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="27" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2225:B2230">
-    <cfRule type="duplicateValues" dxfId="7" priority="17" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="20" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2225:A2230">
-    <cfRule type="duplicateValues" dxfId="6" priority="16" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="19" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2232:A2246">
-    <cfRule type="duplicateValues" dxfId="5" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="11" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2232:B2246">
-    <cfRule type="duplicateValues" dxfId="4" priority="9" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2247:A2253">
-    <cfRule type="duplicateValues" dxfId="3" priority="3" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="6" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2247:B2253">
-    <cfRule type="duplicateValues" dxfId="2" priority="4" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="7" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2254">
-    <cfRule type="duplicateValues" dxfId="1" priority="1" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2254">
+    <cfRule type="duplicateValues" dxfId="3" priority="5" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2256:B2264">
+    <cfRule type="duplicateValues" dxfId="2" priority="3" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2256:B2264">
+    <cfRule type="duplicateValues" dxfId="1" priority="1" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="0" priority="2" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
@@ -77744,9 +78111,11 @@
     <hyperlink ref="H2100" r:id="rId7"/>
     <hyperlink ref="H2110" r:id="rId8"/>
     <hyperlink ref="H2223" r:id="rId9"/>
+    <hyperlink ref="J2265" r:id="rId10"/>
+    <hyperlink ref="J2266" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>

--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -77610,7 +77610,7 @@
         <v>141</v>
       </c>
       <c r="B2254" s="3" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="C2254" s="1" t="s">
         <v>9182</v>
@@ -77627,7 +77627,7 @@
         <v>9183</v>
       </c>
       <c r="B2255" s="3" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="C2255" s="1" t="s">
         <v>9181</v>
@@ -77957,7 +77957,7 @@
   <conditionalFormatting sqref="A2231 A2144:A2203 A2123 A2034:A2067 A1:A2021 A2209 A2255 A2267:A65534">
     <cfRule type="duplicateValues" dxfId="47" priority="160" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2144:B2203 B2123 B1:B2067 B2209 B2224 B2231 B2255 B2267:B65534">
+  <conditionalFormatting sqref="B2267:B65534 B2254 B2144:B2203 B2123 B1:B2067 B2209 B2224 B2231">
     <cfRule type="duplicateValues" dxfId="46" priority="165" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2108:A2115">
@@ -78086,7 +78086,7 @@
   <conditionalFormatting sqref="A2254">
     <cfRule type="duplicateValues" dxfId="4" priority="4" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2254">
+  <conditionalFormatting sqref="B2255">
     <cfRule type="duplicateValues" dxfId="3" priority="5" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2256:B2264">

--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -31662,7 +31662,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="新細明體"/>
@@ -31710,63 +31710,27 @@
       <charset val="136"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
       <u/>
       <sz val="14"/>
-      <color indexed="12"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -31779,7 +31743,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -31789,64 +31753,37 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -32680,11 +32617,11 @@
         <v>2749</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>2753</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="5" t="s">
         <v>1461</v>
       </c>
       <c r="C33" s="3" t="s">
@@ -32694,7 +32631,7 @@
         <v>2749</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>2754</v>
       </c>
@@ -32708,7 +32645,7 @@
         <v>2749</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>2755</v>
       </c>
@@ -32722,7 +32659,7 @@
         <v>2749</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>2756</v>
       </c>
@@ -32736,7 +32673,7 @@
         <v>2749</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>2757</v>
       </c>
@@ -32750,7 +32687,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>2352</v>
       </c>
@@ -32764,7 +32701,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>4907</v>
       </c>
@@ -32790,7 +32727,7 @@
         <v>4927</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>6630</v>
       </c>
@@ -32816,7 +32753,7 @@
         <v>6667</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>6634</v>
       </c>
@@ -32842,35 +32779,33 @@
         <v>6669</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="9" t="s">
+    <row r="42" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
         <v>7178</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="4" t="s">
         <v>7177</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="3" t="s">
         <v>7159</v>
       </c>
-      <c r="D42" s="9" t="s">
+      <c r="D42" s="3" t="s">
         <v>7238</v>
       </c>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9" t="s">
+      <c r="F42" s="3" t="s">
         <v>7242</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H42" s="9" t="s">
+      <c r="H42" s="3" t="s">
         <v>7243</v>
       </c>
-      <c r="I42" s="9" t="s">
+      <c r="I42" s="3" t="s">
         <v>7244</v>
       </c>
-      <c r="J42" s="9"/>
-    </row>
-    <row r="43" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>7264</v>
       </c>
@@ -32896,7 +32831,7 @@
         <v>7296</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>2759</v>
       </c>
@@ -32910,7 +32845,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>2762</v>
       </c>
@@ -32924,7 +32859,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>2763</v>
       </c>
@@ -32938,7 +32873,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>2764</v>
       </c>
@@ -32952,7 +32887,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>2765</v>
       </c>
@@ -32966,7 +32901,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>2766</v>
       </c>
@@ -32980,7 +32915,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>2767</v>
       </c>
@@ -32994,7 +32929,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>129</v>
       </c>
@@ -33008,7 +32943,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>2408</v>
       </c>
@@ -33022,7 +32957,7 @@
         <v>2414</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>132</v>
       </c>
@@ -33036,7 +32971,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>2769</v>
       </c>
@@ -33050,7 +32985,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>2770</v>
       </c>
@@ -33064,7 +32999,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>117</v>
       </c>
@@ -33078,7 +33013,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>2771</v>
       </c>
@@ -33092,7 +33027,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>2772</v>
       </c>
@@ -33106,23 +33041,21 @@
         <v>128</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="11" t="s">
+    <row r="59" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
         <v>2773</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="4" t="s">
         <v>1299</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D59" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-    </row>
-    <row r="60" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>118</v>
       </c>
@@ -33136,7 +33069,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>2774</v>
       </c>
@@ -33150,7 +33083,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>2775</v>
       </c>
@@ -33164,7 +33097,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>2776</v>
       </c>
@@ -33178,7 +33111,7 @@
         <v>2779</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>130</v>
       </c>
@@ -33402,7 +33335,7 @@
       <c r="A78" s="3" t="s">
         <v>2785</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="B78" s="5" t="s">
         <v>1488</v>
       </c>
       <c r="C78" s="3" t="s">
@@ -33755,7 +33688,7 @@
       <c r="B103" s="4" t="s">
         <v>7450</v>
       </c>
-      <c r="C103" s="6" t="s">
+      <c r="C103" s="3" t="s">
         <v>7445</v>
       </c>
       <c r="D103" s="3" t="s">
@@ -33767,7 +33700,7 @@
       <c r="G103" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H103" s="13" t="s">
+      <c r="H103" s="7" t="s">
         <v>7466</v>
       </c>
       <c r="I103" s="3" t="s">
@@ -35218,7 +35151,7 @@
       <c r="A200" s="3" t="s">
         <v>2893</v>
       </c>
-      <c r="B200" s="7" t="s">
+      <c r="B200" s="5" t="s">
         <v>1582</v>
       </c>
       <c r="C200" s="3" t="s">
@@ -35463,7 +35396,7 @@
       <c r="I216" s="3">
         <v>2846</v>
       </c>
-      <c r="J216" s="21" t="s">
+      <c r="J216" s="13" t="s">
         <v>3906</v>
       </c>
     </row>
@@ -36228,20 +36161,18 @@
       </c>
     </row>
     <row r="264" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A264" s="11" t="s">
+      <c r="A264" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="B264" s="10" t="s">
+      <c r="B264" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="C264" s="11" t="s">
+      <c r="C264" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="D264" s="11" t="s">
+      <c r="D264" s="3" t="s">
         <v>2957</v>
       </c>
-      <c r="E264" s="12"/>
-      <c r="F264" s="12"/>
     </row>
     <row r="265" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
@@ -37735,7 +37666,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="369" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="3" t="s">
         <v>472</v>
       </c>
@@ -37749,7 +37680,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="370" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="3" t="s">
         <v>14</v>
       </c>
@@ -37763,7 +37694,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="371" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="3" t="s">
         <v>3036</v>
       </c>
@@ -37777,7 +37708,7 @@
         <v>3037</v>
       </c>
     </row>
-    <row r="372" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="3" t="s">
         <v>3038</v>
       </c>
@@ -37790,10 +37721,8 @@
       <c r="D372" s="3" t="s">
         <v>3039</v>
       </c>
-      <c r="E372" s="12"/>
-      <c r="F372" s="12"/>
-    </row>
-    <row r="373" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="373" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="3" t="s">
         <v>3040</v>
       </c>
@@ -37807,7 +37736,7 @@
         <v>3042</v>
       </c>
     </row>
-    <row r="374" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="3" t="s">
         <v>3043</v>
       </c>
@@ -37821,7 +37750,7 @@
         <v>3042</v>
       </c>
     </row>
-    <row r="375" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="3" t="s">
         <v>3044</v>
       </c>
@@ -37835,7 +37764,7 @@
         <v>3042</v>
       </c>
     </row>
-    <row r="376" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="3" t="s">
         <v>3045</v>
       </c>
@@ -37849,7 +37778,7 @@
         <v>3042</v>
       </c>
     </row>
-    <row r="377" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="3" t="s">
         <v>3046</v>
       </c>
@@ -37863,7 +37792,7 @@
         <v>3042</v>
       </c>
     </row>
-    <row r="378" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="3" t="s">
         <v>3047</v>
       </c>
@@ -37877,7 +37806,7 @@
         <v>3042</v>
       </c>
     </row>
-    <row r="379" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="3" t="s">
         <v>3048</v>
       </c>
@@ -37891,7 +37820,7 @@
         <v>3042</v>
       </c>
     </row>
-    <row r="380" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="3" t="s">
         <v>3049</v>
       </c>
@@ -37905,7 +37834,7 @@
         <v>3042</v>
       </c>
     </row>
-    <row r="381" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="3" t="s">
         <v>3050</v>
       </c>
@@ -37919,7 +37848,7 @@
         <v>3042</v>
       </c>
     </row>
-    <row r="382" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="3" t="s">
         <v>3051</v>
       </c>
@@ -37933,7 +37862,7 @@
         <v>3042</v>
       </c>
     </row>
-    <row r="383" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="3" t="s">
         <v>3052</v>
       </c>
@@ -37947,7 +37876,7 @@
         <v>3042</v>
       </c>
     </row>
-    <row r="384" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="3" t="s">
         <v>493</v>
       </c>
@@ -38532,8 +38461,6 @@
       <c r="D424" s="3" t="s">
         <v>3073</v>
       </c>
-      <c r="E424" s="12"/>
-      <c r="F424" s="12"/>
     </row>
     <row r="425" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="3" t="s">
@@ -38576,8 +38503,6 @@
       <c r="D427" s="3" t="s">
         <v>3074</v>
       </c>
-      <c r="E427" s="12"/>
-      <c r="F427" s="12"/>
     </row>
     <row r="428" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="3" t="s">
@@ -38674,8 +38599,6 @@
       <c r="D433" s="3" t="s">
         <v>3078</v>
       </c>
-      <c r="E433" s="12"/>
-      <c r="F433" s="12"/>
     </row>
     <row r="434" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="3" t="s">
@@ -38901,7 +38824,7 @@
       <c r="A448" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B448" s="7" t="s">
+      <c r="B448" s="5" t="s">
         <v>1390</v>
       </c>
       <c r="C448" s="3" t="s">
@@ -39041,7 +38964,7 @@
       <c r="A458" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="B458" s="7" t="s">
+      <c r="B458" s="5" t="s">
         <v>1738</v>
       </c>
       <c r="C458" s="3" t="s">
@@ -40212,7 +40135,7 @@
       <c r="A538" s="3" t="s">
         <v>774</v>
       </c>
-      <c r="B538" s="7" t="s">
+      <c r="B538" s="5" t="s">
         <v>1789</v>
       </c>
       <c r="C538" s="3" t="s">
@@ -40543,7 +40466,7 @@
       <c r="A561" s="3" t="s">
         <v>3109</v>
       </c>
-      <c r="B561" s="7" t="s">
+      <c r="B561" s="5" t="s">
         <v>1808</v>
       </c>
       <c r="C561" s="3" t="s">
@@ -42053,7 +41976,7 @@
       <c r="A665" s="3" t="s">
         <v>990</v>
       </c>
-      <c r="B665" s="7" t="s">
+      <c r="B665" s="5" t="s">
         <v>1886</v>
       </c>
       <c r="C665" s="3" t="s">
@@ -42373,7 +42296,7 @@
       <c r="A687" s="3" t="s">
         <v>1020</v>
       </c>
-      <c r="B687" s="7" t="s">
+      <c r="B687" s="5" t="s">
         <v>1902</v>
       </c>
       <c r="C687" s="3" t="s">
@@ -42387,7 +42310,7 @@
       <c r="A688" s="3" t="s">
         <v>1021</v>
       </c>
-      <c r="B688" s="7" t="s">
+      <c r="B688" s="5" t="s">
         <v>1400</v>
       </c>
       <c r="C688" s="3" t="s">
@@ -43675,7 +43598,7 @@
       <c r="G768" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H768" s="13" t="s">
+      <c r="H768" s="7" t="s">
         <v>4200</v>
       </c>
       <c r="I768" s="3" t="s">
@@ -43738,7 +43661,7 @@
       <c r="A771" s="3" t="s">
         <v>1155</v>
       </c>
-      <c r="B771" s="7" t="s">
+      <c r="B771" s="5" t="s">
         <v>1407</v>
       </c>
       <c r="C771" s="3" t="s">
@@ -45728,52 +45651,52 @@
       </c>
     </row>
     <row r="896" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A896" s="15" t="s">
+      <c r="A896" s="8" t="s">
         <v>2087</v>
       </c>
-      <c r="B896" s="14" t="s">
+      <c r="B896" s="9" t="s">
         <v>2314</v>
       </c>
-      <c r="C896" s="15" t="s">
+      <c r="C896" s="8" t="s">
         <v>2088</v>
       </c>
-      <c r="D896" s="15" t="s">
+      <c r="D896" s="8" t="s">
         <v>2568</v>
       </c>
-      <c r="E896" s="15"/>
-      <c r="F896" s="15"/>
+      <c r="E896" s="8"/>
+      <c r="F896" s="8"/>
     </row>
     <row r="897" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A897" s="15" t="s">
+      <c r="A897" s="8" t="s">
         <v>2091</v>
       </c>
-      <c r="B897" s="14" t="s">
+      <c r="B897" s="9" t="s">
         <v>2316</v>
       </c>
-      <c r="C897" s="15" t="s">
+      <c r="C897" s="8" t="s">
         <v>2092</v>
       </c>
-      <c r="D897" s="15" t="s">
+      <c r="D897" s="8" t="s">
         <v>2568</v>
       </c>
-      <c r="E897" s="15"/>
-      <c r="F897" s="15"/>
+      <c r="E897" s="8"/>
+      <c r="F897" s="8"/>
     </row>
     <row r="898" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A898" s="15" t="s">
+      <c r="A898" s="8" t="s">
         <v>2093</v>
       </c>
-      <c r="B898" s="14" t="s">
+      <c r="B898" s="9" t="s">
         <v>2317</v>
       </c>
-      <c r="C898" s="15" t="s">
+      <c r="C898" s="8" t="s">
         <v>2094</v>
       </c>
-      <c r="D898" s="15" t="s">
+      <c r="D898" s="8" t="s">
         <v>2568</v>
       </c>
-      <c r="E898" s="15"/>
-      <c r="F898" s="15"/>
+      <c r="E898" s="8"/>
+      <c r="F898" s="8"/>
     </row>
     <row r="899" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899" s="3" t="s">
@@ -45874,116 +45797,116 @@
       </c>
     </row>
     <row r="906" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A906" s="15" t="s">
+      <c r="A906" s="8" t="s">
         <v>2075</v>
       </c>
-      <c r="B906" s="14" t="s">
+      <c r="B906" s="9" t="s">
         <v>2308</v>
       </c>
-      <c r="C906" s="15" t="s">
+      <c r="C906" s="8" t="s">
         <v>2076</v>
       </c>
-      <c r="D906" s="15" t="s">
+      <c r="D906" s="8" t="s">
         <v>2662</v>
       </c>
-      <c r="E906" s="15"/>
-      <c r="F906" s="15"/>
+      <c r="E906" s="8"/>
+      <c r="F906" s="8"/>
     </row>
     <row r="907" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A907" s="15" t="s">
+      <c r="A907" s="8" t="s">
         <v>2079</v>
       </c>
-      <c r="B907" s="14" t="s">
+      <c r="B907" s="9" t="s">
         <v>2310</v>
       </c>
-      <c r="C907" s="15" t="s">
+      <c r="C907" s="8" t="s">
         <v>2080</v>
       </c>
-      <c r="D907" s="15" t="s">
+      <c r="D907" s="8" t="s">
         <v>2662</v>
       </c>
-      <c r="E907" s="15"/>
-      <c r="F907" s="15"/>
+      <c r="E907" s="8"/>
+      <c r="F907" s="8"/>
     </row>
     <row r="908" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A908" s="15" t="s">
+      <c r="A908" s="8" t="s">
         <v>2081</v>
       </c>
-      <c r="B908" s="14" t="s">
+      <c r="B908" s="9" t="s">
         <v>2311</v>
       </c>
-      <c r="C908" s="15" t="s">
+      <c r="C908" s="8" t="s">
         <v>2082</v>
       </c>
-      <c r="D908" s="15" t="s">
+      <c r="D908" s="8" t="s">
         <v>2662</v>
       </c>
-      <c r="E908" s="15"/>
-      <c r="F908" s="15"/>
+      <c r="E908" s="8"/>
+      <c r="F908" s="8"/>
     </row>
     <row r="909" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A909" s="15" t="s">
+      <c r="A909" s="8" t="s">
         <v>2083</v>
       </c>
-      <c r="B909" s="14" t="s">
+      <c r="B909" s="9" t="s">
         <v>2312</v>
       </c>
-      <c r="C909" s="15" t="s">
+      <c r="C909" s="8" t="s">
         <v>2084</v>
       </c>
-      <c r="D909" s="15" t="s">
+      <c r="D909" s="8" t="s">
         <v>2662</v>
       </c>
-      <c r="E909" s="15"/>
-      <c r="F909" s="15"/>
+      <c r="E909" s="8"/>
+      <c r="F909" s="8"/>
     </row>
     <row r="910" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A910" s="15" t="s">
+      <c r="A910" s="8" t="s">
         <v>2085</v>
       </c>
-      <c r="B910" s="14" t="s">
+      <c r="B910" s="9" t="s">
         <v>2313</v>
       </c>
-      <c r="C910" s="15" t="s">
+      <c r="C910" s="8" t="s">
         <v>2086</v>
       </c>
-      <c r="D910" s="15" t="s">
+      <c r="D910" s="8" t="s">
         <v>2662</v>
       </c>
-      <c r="E910" s="15"/>
-      <c r="F910" s="15"/>
+      <c r="E910" s="8"/>
+      <c r="F910" s="8"/>
     </row>
     <row r="911" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A911" s="15" t="s">
+      <c r="A911" s="8" t="s">
         <v>2089</v>
       </c>
-      <c r="B911" s="14" t="s">
+      <c r="B911" s="9" t="s">
         <v>2315</v>
       </c>
-      <c r="C911" s="15" t="s">
+      <c r="C911" s="8" t="s">
         <v>2090</v>
       </c>
-      <c r="D911" s="15" t="s">
+      <c r="D911" s="8" t="s">
         <v>2662</v>
       </c>
-      <c r="E911" s="15"/>
-      <c r="F911" s="15"/>
+      <c r="E911" s="8"/>
+      <c r="F911" s="8"/>
     </row>
     <row r="912" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A912" s="15" t="s">
+      <c r="A912" s="8" t="s">
         <v>2095</v>
       </c>
-      <c r="B912" s="14" t="s">
+      <c r="B912" s="9" t="s">
         <v>2318</v>
       </c>
-      <c r="C912" s="15" t="s">
+      <c r="C912" s="8" t="s">
         <v>2096</v>
       </c>
-      <c r="D912" s="15" t="s">
+      <c r="D912" s="8" t="s">
         <v>2662</v>
       </c>
-      <c r="E912" s="15"/>
-      <c r="F912" s="15"/>
+      <c r="E912" s="8"/>
+      <c r="F912" s="8"/>
     </row>
     <row r="913" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="3" t="s">
@@ -46028,68 +45951,68 @@
       </c>
     </row>
     <row r="916" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A916" s="15" t="s">
+      <c r="A916" s="8" t="s">
         <v>2073</v>
       </c>
-      <c r="B916" s="14" t="s">
+      <c r="B916" s="9" t="s">
         <v>2307</v>
       </c>
-      <c r="C916" s="15" t="s">
+      <c r="C916" s="8" t="s">
         <v>2074</v>
       </c>
-      <c r="D916" s="15" t="s">
+      <c r="D916" s="8" t="s">
         <v>2661</v>
       </c>
-      <c r="E916" s="15"/>
-      <c r="F916" s="15"/>
+      <c r="E916" s="8"/>
+      <c r="F916" s="8"/>
     </row>
     <row r="917" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A917" s="15" t="s">
+      <c r="A917" s="8" t="s">
         <v>2077</v>
       </c>
-      <c r="B917" s="14" t="s">
+      <c r="B917" s="9" t="s">
         <v>2309</v>
       </c>
-      <c r="C917" s="15" t="s">
+      <c r="C917" s="8" t="s">
         <v>2078</v>
       </c>
-      <c r="D917" s="15" t="s">
+      <c r="D917" s="8" t="s">
         <v>2661</v>
       </c>
-      <c r="E917" s="15"/>
-      <c r="F917" s="15"/>
+      <c r="E917" s="8"/>
+      <c r="F917" s="8"/>
     </row>
     <row r="918" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A918" s="15" t="s">
+      <c r="A918" s="8" t="s">
         <v>2068</v>
       </c>
-      <c r="B918" s="14" t="s">
+      <c r="B918" s="9" t="s">
         <v>2306</v>
       </c>
-      <c r="C918" s="15" t="s">
+      <c r="C918" s="8" t="s">
         <v>2069</v>
       </c>
-      <c r="D918" s="15" t="s">
+      <c r="D918" s="8" t="s">
         <v>2659</v>
       </c>
-      <c r="E918" s="15"/>
-      <c r="F918" s="15"/>
+      <c r="E918" s="8"/>
+      <c r="F918" s="8"/>
     </row>
     <row r="919" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A919" s="15" t="s">
+      <c r="A919" s="8" t="s">
         <v>2070</v>
       </c>
-      <c r="B919" s="14" t="s">
+      <c r="B919" s="9" t="s">
         <v>2071</v>
       </c>
-      <c r="C919" s="15" t="s">
+      <c r="C919" s="8" t="s">
         <v>2072</v>
       </c>
-      <c r="D919" s="15" t="s">
+      <c r="D919" s="8" t="s">
         <v>2660</v>
       </c>
-      <c r="E919" s="15"/>
-      <c r="F919" s="15"/>
+      <c r="E919" s="8"/>
+      <c r="F919" s="8"/>
     </row>
     <row r="920" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="3" t="s">
@@ -46134,20 +46057,20 @@
       </c>
     </row>
     <row r="923" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A923" s="15" t="s">
+      <c r="A923" s="8" t="s">
         <v>2066</v>
       </c>
-      <c r="B923" s="14" t="s">
+      <c r="B923" s="9" t="s">
         <v>2305</v>
       </c>
-      <c r="C923" s="15" t="s">
+      <c r="C923" s="8" t="s">
         <v>2067</v>
       </c>
-      <c r="D923" s="15" t="s">
+      <c r="D923" s="8" t="s">
         <v>2658</v>
       </c>
-      <c r="E923" s="15"/>
-      <c r="F923" s="15"/>
+      <c r="E923" s="8"/>
+      <c r="F923" s="8"/>
     </row>
     <row r="924" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A924" s="3" t="s">
@@ -47021,52 +46944,52 @@
       </c>
     </row>
     <row r="986" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A986" s="15" t="s">
+      <c r="A986" s="8" t="s">
         <v>2324</v>
       </c>
       <c r="B986" s="4" t="s">
         <v>2397</v>
       </c>
-      <c r="C986" s="15" t="s">
+      <c r="C986" s="8" t="s">
         <v>2325</v>
       </c>
-      <c r="D986" s="15" t="s">
+      <c r="D986" s="8" t="s">
         <v>2664</v>
       </c>
-      <c r="E986" s="15"/>
-      <c r="F986" s="15"/>
+      <c r="E986" s="8"/>
+      <c r="F986" s="8"/>
     </row>
     <row r="987" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A987" s="15" t="s">
+      <c r="A987" s="8" t="s">
         <v>2326</v>
       </c>
       <c r="B987" s="4" t="s">
         <v>2398</v>
       </c>
-      <c r="C987" s="15" t="s">
+      <c r="C987" s="8" t="s">
         <v>2327</v>
       </c>
-      <c r="D987" s="15" t="s">
+      <c r="D987" s="8" t="s">
         <v>2664</v>
       </c>
-      <c r="E987" s="15"/>
-      <c r="F987" s="15"/>
+      <c r="E987" s="8"/>
+      <c r="F987" s="8"/>
     </row>
     <row r="988" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A988" s="15" t="s">
+      <c r="A988" s="8" t="s">
         <v>2328</v>
       </c>
       <c r="B988" s="4" t="s">
         <v>2399</v>
       </c>
-      <c r="C988" s="15" t="s">
+      <c r="C988" s="8" t="s">
         <v>2329</v>
       </c>
-      <c r="D988" s="15" t="s">
+      <c r="D988" s="8" t="s">
         <v>2664</v>
       </c>
-      <c r="E988" s="15"/>
-      <c r="F988" s="15"/>
+      <c r="E988" s="8"/>
+      <c r="F988" s="8"/>
     </row>
     <row r="989" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A989" s="3" t="s">
@@ -47123,20 +47046,20 @@
       </c>
     </row>
     <row r="992" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A992" s="15" t="s">
+      <c r="A992" s="8" t="s">
         <v>2322</v>
       </c>
       <c r="B992" s="4" t="s">
         <v>2396</v>
       </c>
-      <c r="C992" s="15" t="s">
+      <c r="C992" s="8" t="s">
         <v>2323</v>
       </c>
-      <c r="D992" s="15" t="s">
+      <c r="D992" s="8" t="s">
         <v>2663</v>
       </c>
-      <c r="E992" s="15"/>
-      <c r="F992" s="15"/>
+      <c r="E992" s="8"/>
+      <c r="F992" s="8"/>
     </row>
     <row r="993" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="3" t="s">
@@ -47362,7 +47285,7 @@
         <v>3324</v>
       </c>
     </row>
-    <row r="1009" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1009" s="3" t="s">
         <v>64</v>
       </c>
@@ -47376,7 +47299,7 @@
         <v>3324</v>
       </c>
     </row>
-    <row r="1010" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1010" s="3" t="s">
         <v>2373</v>
       </c>
@@ -47390,7 +47313,7 @@
         <v>3324</v>
       </c>
     </row>
-    <row r="1011" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1011" s="3" t="s">
         <v>3326</v>
       </c>
@@ -47404,23 +47327,21 @@
         <v>3324</v>
       </c>
     </row>
-    <row r="1012" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1012" s="3" t="s">
         <v>3328</v>
       </c>
       <c r="B1012" s="4" t="s">
         <v>3329</v>
       </c>
-      <c r="C1012" s="11" t="s">
+      <c r="C1012" s="3" t="s">
         <v>2381</v>
       </c>
       <c r="D1012" s="3" t="s">
         <v>3324</v>
       </c>
-      <c r="E1012" s="12"/>
-      <c r="F1012" s="12"/>
-    </row>
-    <row r="1013" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1013" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1013" s="3" t="s">
         <v>3330</v>
       </c>
@@ -47434,7 +47355,7 @@
         <v>3324</v>
       </c>
     </row>
-    <row r="1014" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1014" s="3" t="s">
         <v>2391</v>
       </c>
@@ -47448,7 +47369,7 @@
         <v>3333</v>
       </c>
     </row>
-    <row r="1015" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1015" s="3" t="s">
         <v>3334</v>
       </c>
@@ -47462,7 +47383,7 @@
         <v>3335</v>
       </c>
     </row>
-    <row r="1016" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1016" s="3" t="s">
         <v>3336</v>
       </c>
@@ -47476,7 +47397,7 @@
         <v>3335</v>
       </c>
     </row>
-    <row r="1017" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1017" s="3" t="s">
         <v>3338</v>
       </c>
@@ -47490,7 +47411,7 @@
         <v>3335</v>
       </c>
     </row>
-    <row r="1018" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1018" s="3" t="s">
         <v>3340</v>
       </c>
@@ -47504,7 +47425,7 @@
         <v>3335</v>
       </c>
     </row>
-    <row r="1019" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1019" s="3" t="s">
         <v>3342</v>
       </c>
@@ -47518,7 +47439,7 @@
         <v>3335</v>
       </c>
     </row>
-    <row r="1020" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1020" s="3" t="s">
         <v>2393</v>
       </c>
@@ -47532,7 +47453,7 @@
         <v>3335</v>
       </c>
     </row>
-    <row r="1021" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1021" s="3" t="s">
         <v>2245</v>
       </c>
@@ -47546,7 +47467,7 @@
         <v>3345</v>
       </c>
     </row>
-    <row r="1022" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1022" s="3" t="s">
         <v>2428</v>
       </c>
@@ -47560,7 +47481,7 @@
         <v>2441</v>
       </c>
     </row>
-    <row r="1023" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1023" s="3" t="s">
         <v>2392</v>
       </c>
@@ -47574,7 +47495,7 @@
         <v>3348</v>
       </c>
     </row>
-    <row r="1024" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1024" s="3" t="s">
         <v>3349</v>
       </c>
@@ -48407,7 +48328,7 @@
       <c r="B1083" s="4">
         <v>29162926</v>
       </c>
-      <c r="C1083" s="16" t="s">
+      <c r="C1083" s="8" t="s">
         <v>2517</v>
       </c>
       <c r="D1083" s="3" t="s">
@@ -48438,7 +48359,7 @@
       <c r="B1085" s="4" t="s">
         <v>3418</v>
       </c>
-      <c r="C1085" s="16" t="s">
+      <c r="C1085" s="8" t="s">
         <v>3419</v>
       </c>
       <c r="D1085" s="3" t="s">
@@ -48469,7 +48390,7 @@
       <c r="B1087" s="4">
         <v>53876037</v>
       </c>
-      <c r="C1087" s="16" t="s">
+      <c r="C1087" s="8" t="s">
         <v>2518</v>
       </c>
       <c r="D1087" s="3" t="s">
@@ -48827,20 +48748,18 @@
       </c>
     </row>
     <row r="1113" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1113" s="11" t="s">
+      <c r="A1113" s="3" t="s">
         <v>3428</v>
       </c>
-      <c r="B1113" s="10" t="s">
+      <c r="B1113" s="4" t="s">
         <v>1397</v>
       </c>
-      <c r="C1113" s="11" t="s">
+      <c r="C1113" s="3" t="s">
         <v>3429</v>
       </c>
-      <c r="D1113" s="11" t="s">
+      <c r="D1113" s="3" t="s">
         <v>3430</v>
       </c>
-      <c r="E1113" s="11"/>
-      <c r="F1113" s="11"/>
     </row>
     <row r="1114" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1114" s="3" t="s">
@@ -50735,7 +50654,7 @@
       <c r="C1208" s="3" t="s">
         <v>3722</v>
       </c>
-      <c r="D1208" s="17" t="s">
+      <c r="D1208" s="10" t="s">
         <v>3725</v>
       </c>
       <c r="E1208" s="3" t="s">
@@ -51575,7 +51494,7 @@
       <c r="D1244" s="3" t="s">
         <v>4156</v>
       </c>
-      <c r="E1244" s="18" t="s">
+      <c r="E1244" s="11" t="s">
         <v>4166</v>
       </c>
       <c r="F1244" s="3" t="s">
@@ -51607,7 +51526,7 @@
       <c r="G1245" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1245" s="13" t="s">
+      <c r="H1245" s="7" t="s">
         <v>4196</v>
       </c>
       <c r="I1245" s="3" t="s">
@@ -52594,7 +52513,7 @@
       <c r="I1284" s="3">
         <v>718</v>
       </c>
-      <c r="J1284" s="21" t="s">
+      <c r="J1284" s="13" t="s">
         <v>4128</v>
       </c>
     </row>
@@ -52767,7 +52686,7 @@
       <c r="G1291" s="3" t="s">
         <v>4339</v>
       </c>
-      <c r="H1291" s="21" t="s">
+      <c r="H1291" s="13" t="s">
         <v>4340</v>
       </c>
       <c r="I1291" s="3" t="s">
@@ -54822,7 +54741,7 @@
       <c r="I1372" s="3" t="s">
         <v>4479</v>
       </c>
-      <c r="J1372" s="21" t="s">
+      <c r="J1372" s="13" t="s">
         <v>4730</v>
       </c>
     </row>
@@ -61317,8 +61236,8 @@
       <c r="G1627" s="3" t="s">
         <v>6151</v>
       </c>
-      <c r="H1627" s="21"/>
-      <c r="J1627" s="21" t="s">
+      <c r="H1627" s="13"/>
+      <c r="J1627" s="13" t="s">
         <v>6973</v>
       </c>
     </row>
@@ -64162,7 +64081,7 @@
       <c r="G1738" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1738" s="13" t="s">
+      <c r="H1738" s="7" t="s">
         <v>6760</v>
       </c>
       <c r="I1738" s="3" t="s">
@@ -64188,7 +64107,7 @@
       <c r="G1739" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1739" s="13" t="s">
+      <c r="H1739" s="7" t="s">
         <v>6761</v>
       </c>
       <c r="I1739" s="3" t="s">
@@ -64812,7 +64731,7 @@
       <c r="G1763" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1763" s="13" t="s">
+      <c r="H1763" s="7" t="s">
         <v>6971</v>
       </c>
       <c r="I1763" s="3" t="s">
@@ -65157,7 +65076,7 @@
         <v>7025</v>
       </c>
     </row>
-    <row r="1777" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1777" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1777" s="3" t="s">
         <v>6992</v>
       </c>
@@ -65183,7 +65102,7 @@
         <v>7031</v>
       </c>
     </row>
-    <row r="1778" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1778" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1778" s="3" t="s">
         <v>6997</v>
       </c>
@@ -65209,7 +65128,7 @@
         <v>7033</v>
       </c>
     </row>
-    <row r="1779" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1779" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1779" s="3" t="s">
         <v>6998</v>
       </c>
@@ -65235,7 +65154,7 @@
         <v>7029</v>
       </c>
     </row>
-    <row r="1780" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1780" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1780" s="3" t="s">
         <v>7048</v>
       </c>
@@ -65261,7 +65180,7 @@
         <v>7070</v>
       </c>
     </row>
-    <row r="1781" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1781" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1781" s="3" t="s">
         <v>7001</v>
       </c>
@@ -65287,7 +65206,7 @@
         <v>7036</v>
       </c>
     </row>
-    <row r="1782" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1782" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1782" s="3" t="s">
         <v>7052</v>
       </c>
@@ -65313,7 +65232,7 @@
         <v>7074</v>
       </c>
     </row>
-    <row r="1783" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1783" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1783" s="3" t="s">
         <v>7057</v>
       </c>
@@ -65339,7 +65258,7 @@
         <v>7078</v>
       </c>
     </row>
-    <row r="1784" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1784" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1784" s="3" t="s">
         <v>7018</v>
       </c>
@@ -65365,7 +65284,7 @@
         <v>7066</v>
       </c>
     </row>
-    <row r="1785" spans="1:10" s="9" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1785" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1785" s="3" t="s">
         <v>7045</v>
       </c>
@@ -65378,7 +65297,6 @@
       <c r="D1785" s="3" t="s">
         <v>7020</v>
       </c>
-      <c r="E1785" s="3"/>
       <c r="F1785" s="3" t="s">
         <v>7063</v>
       </c>
@@ -65391,9 +65309,8 @@
       <c r="I1785" s="3" t="s">
         <v>7068</v>
       </c>
-      <c r="J1785" s="3"/>
-    </row>
-    <row r="1786" spans="1:10" s="9" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1786" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1786" s="3" t="s">
         <v>7050</v>
       </c>
@@ -65406,7 +65323,6 @@
       <c r="D1786" s="3" t="s">
         <v>7020</v>
       </c>
-      <c r="E1786" s="3"/>
       <c r="F1786" s="3" t="s">
         <v>7063</v>
       </c>
@@ -65419,9 +65335,8 @@
       <c r="I1786" s="3" t="s">
         <v>7072</v>
       </c>
-      <c r="J1786" s="3"/>
-    </row>
-    <row r="1787" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1787" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1787" s="3" t="s">
         <v>7083</v>
       </c>
@@ -65447,7 +65362,7 @@
         <v>7098</v>
       </c>
     </row>
-    <row r="1788" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1788" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1788" s="3" t="s">
         <v>7105</v>
       </c>
@@ -65473,7 +65388,7 @@
         <v>7107</v>
       </c>
     </row>
-    <row r="1789" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1789" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1789" s="3" t="s">
         <v>7086</v>
       </c>
@@ -65499,7 +65414,7 @@
         <v>7100</v>
       </c>
     </row>
-    <row r="1790" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1790" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1790" s="3" t="s">
         <v>6091</v>
       </c>
@@ -65525,7 +65440,7 @@
         <v>6115</v>
       </c>
     </row>
-    <row r="1791" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1791" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1791" s="3" t="s">
         <v>7114</v>
       </c>
@@ -65551,7 +65466,7 @@
         <v>7126</v>
       </c>
     </row>
-    <row r="1792" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1792" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1792" s="3" t="s">
         <v>7115</v>
       </c>
@@ -65726,7 +65641,7 @@
       <c r="G1798" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1798" s="13" t="s">
+      <c r="H1798" s="7" t="s">
         <v>7235</v>
       </c>
       <c r="I1798" s="3" t="s">
@@ -65752,7 +65667,7 @@
       <c r="G1799" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1799" s="13" t="s">
+      <c r="H1799" s="7" t="s">
         <v>7218</v>
       </c>
       <c r="I1799" s="3" t="s">
@@ -65778,7 +65693,7 @@
       <c r="G1800" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1800" s="13" t="s">
+      <c r="H1800" s="7" t="s">
         <v>7221</v>
       </c>
       <c r="I1800" s="3" t="s">
@@ -65804,7 +65719,7 @@
       <c r="G1801" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1801" s="13" t="s">
+      <c r="H1801" s="7" t="s">
         <v>7223</v>
       </c>
       <c r="I1801" s="3" t="s">
@@ -65830,7 +65745,7 @@
       <c r="G1802" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1802" s="13" t="s">
+      <c r="H1802" s="7" t="s">
         <v>7224</v>
       </c>
       <c r="I1802" s="3" t="s">
@@ -65856,7 +65771,7 @@
       <c r="G1803" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1803" s="13" t="s">
+      <c r="H1803" s="7" t="s">
         <v>7216</v>
       </c>
       <c r="I1803" s="3" t="s">
@@ -65882,7 +65797,7 @@
       <c r="G1804" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1804" s="13" t="s">
+      <c r="H1804" s="7" t="s">
         <v>7225</v>
       </c>
       <c r="I1804" s="3" t="s">
@@ -65908,7 +65823,7 @@
       <c r="G1805" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1805" s="13" t="s">
+      <c r="H1805" s="7" t="s">
         <v>7227</v>
       </c>
       <c r="I1805" s="3" t="s">
@@ -65934,7 +65849,7 @@
       <c r="G1806" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1806" s="13" t="s">
+      <c r="H1806" s="7" t="s">
         <v>7230</v>
       </c>
       <c r="I1806" s="3" t="s">
@@ -65960,7 +65875,7 @@
       <c r="G1807" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1807" s="13" t="s">
+      <c r="H1807" s="7" t="s">
         <v>7231</v>
       </c>
       <c r="I1807" s="3" t="s">
@@ -65986,14 +65901,14 @@
       <c r="G1808" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1808" s="13" t="s">
+      <c r="H1808" s="7" t="s">
         <v>7233</v>
       </c>
       <c r="I1808" s="3" t="s">
         <v>7220</v>
       </c>
     </row>
-    <row r="1809" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1809" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1809" s="3" t="s">
         <v>6314</v>
       </c>
@@ -66019,35 +65934,33 @@
         <v>6345</v>
       </c>
     </row>
-    <row r="1810" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1810" s="9" t="s">
+    <row r="1810" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1810" s="3" t="s">
         <v>7176</v>
       </c>
-      <c r="B1810" s="8" t="s">
+      <c r="B1810" s="4" t="s">
         <v>7200</v>
       </c>
-      <c r="C1810" s="9" t="s">
+      <c r="C1810" s="3" t="s">
         <v>7158</v>
       </c>
-      <c r="D1810" s="9" t="s">
+      <c r="D1810" s="3" t="s">
         <v>7237</v>
       </c>
-      <c r="E1810" s="9"/>
-      <c r="F1810" s="9" t="s">
+      <c r="F1810" s="3" t="s">
         <v>7242</v>
       </c>
       <c r="G1810" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1810" s="9" t="s">
+      <c r="H1810" s="3" t="s">
         <v>7243</v>
       </c>
-      <c r="I1810" s="9" t="s">
+      <c r="I1810" s="3" t="s">
         <v>7244</v>
       </c>
-      <c r="J1810" s="9"/>
-    </row>
-    <row r="1811" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1811" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1811" s="3" t="s">
         <v>7342</v>
       </c>
@@ -66073,7 +65986,7 @@
         <v>7361</v>
       </c>
     </row>
-    <row r="1812" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1812" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1812" s="3" t="s">
         <v>7210</v>
       </c>
@@ -66099,7 +66012,7 @@
         <v>7250</v>
       </c>
     </row>
-    <row r="1813" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1813" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1813" s="3" t="s">
         <v>7206</v>
       </c>
@@ -66125,7 +66038,7 @@
         <v>7246</v>
       </c>
     </row>
-    <row r="1814" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1814" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1814" s="3" t="s">
         <v>7208</v>
       </c>
@@ -66151,7 +66064,7 @@
         <v>7248</v>
       </c>
     </row>
-    <row r="1815" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1815" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1815" s="3" t="s">
         <v>7212</v>
       </c>
@@ -66177,7 +66090,7 @@
         <v>7250</v>
       </c>
     </row>
-    <row r="1816" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1816" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1816" s="3" t="s">
         <v>7241</v>
       </c>
@@ -66203,7 +66116,7 @@
         <v>7253</v>
       </c>
     </row>
-    <row r="1817" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1817" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1817" s="3" t="s">
         <v>7280</v>
       </c>
@@ -66229,7 +66142,7 @@
         <v>7305</v>
       </c>
     </row>
-    <row r="1818" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1818" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1818" s="3" t="s">
         <v>7283</v>
       </c>
@@ -66255,7 +66168,7 @@
         <v>7306</v>
       </c>
     </row>
-    <row r="1819" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1819" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1819" s="3" t="s">
         <v>7286</v>
       </c>
@@ -66281,7 +66194,7 @@
         <v>7309</v>
       </c>
     </row>
-    <row r="1820" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1820" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1820" s="3" t="s">
         <v>7262</v>
       </c>
@@ -66307,7 +66220,7 @@
         <v>7294</v>
       </c>
     </row>
-    <row r="1821" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1821" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1821" s="3" t="s">
         <v>7267</v>
       </c>
@@ -66333,7 +66246,7 @@
         <v>7294</v>
       </c>
     </row>
-    <row r="1822" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1822" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1822" s="3" t="s">
         <v>7274</v>
       </c>
@@ -66360,7 +66273,7 @@
         <v>7301</v>
       </c>
     </row>
-    <row r="1823" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1823" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1823" s="3" t="s">
         <v>7272</v>
       </c>
@@ -66386,7 +66299,7 @@
         <v>7303</v>
       </c>
     </row>
-    <row r="1824" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1824" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1824" s="3" t="s">
         <v>8012</v>
       </c>
@@ -66647,7 +66560,7 @@
       <c r="G1834" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1834" s="13" t="s">
+      <c r="H1834" s="7" t="s">
         <v>7393</v>
       </c>
       <c r="I1834" s="3" t="s">
@@ -66673,7 +66586,7 @@
       <c r="G1835" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1835" s="19" t="s">
+      <c r="H1835" s="12" t="s">
         <v>7395</v>
       </c>
       <c r="I1835" s="3" t="s">
@@ -66699,7 +66612,7 @@
       <c r="G1836" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1836" s="19" t="s">
+      <c r="H1836" s="12" t="s">
         <v>7396</v>
       </c>
       <c r="I1836" s="3" t="s">
@@ -66869,7 +66782,7 @@
       <c r="B1843" s="4" t="s">
         <v>7441</v>
       </c>
-      <c r="C1843" s="6" t="s">
+      <c r="C1843" s="3" t="s">
         <v>7442</v>
       </c>
       <c r="D1843" s="3" t="s">
@@ -66907,7 +66820,7 @@
       <c r="G1844" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1844" s="13" t="s">
+      <c r="H1844" s="7" t="s">
         <v>7425</v>
       </c>
       <c r="I1844" s="3" t="s">
@@ -66944,7 +66857,7 @@
       <c r="A1846" s="3" t="s">
         <v>7417</v>
       </c>
-      <c r="B1846" s="7" t="s">
+      <c r="B1846" s="5" t="s">
         <v>7423</v>
       </c>
       <c r="C1846" s="3" t="s">
@@ -67103,7 +67016,7 @@
       <c r="B1852" s="4">
         <v>22483579</v>
       </c>
-      <c r="C1852" s="6" t="s">
+      <c r="C1852" s="3" t="s">
         <v>7443</v>
       </c>
       <c r="D1852" s="3" t="s">
@@ -67129,7 +67042,7 @@
       <c r="B1853" s="4" t="s">
         <v>7448</v>
       </c>
-      <c r="C1853" s="6" t="s">
+      <c r="C1853" s="3" t="s">
         <v>7444</v>
       </c>
       <c r="D1853" s="3" t="s">
@@ -67207,7 +67120,7 @@
       <c r="G1856" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1856" s="13" t="s">
+      <c r="H1856" s="7" t="s">
         <v>7481</v>
       </c>
       <c r="I1856" s="3" t="s">
@@ -67675,7 +67588,7 @@
       <c r="G1874" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1874" s="13" t="s">
+      <c r="H1874" s="7" t="s">
         <v>7570</v>
       </c>
       <c r="I1874" s="3" t="s">
@@ -68992,7 +68905,7 @@
       <c r="G1925" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1925" s="19" t="s">
+      <c r="H1925" s="12" t="s">
         <v>7851</v>
       </c>
       <c r="I1925" s="3" t="s">
@@ -70411,1793 +70324,1793 @@
         <v>8164</v>
       </c>
     </row>
-    <row r="1981" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1981" s="6" t="s">
+    <row r="1981" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1981" s="3" t="s">
         <v>8192</v>
       </c>
-      <c r="B1981" s="5" t="s">
+      <c r="B1981" s="4" t="s">
         <v>8191</v>
       </c>
-      <c r="C1981" s="6" t="s">
+      <c r="C1981" s="3" t="s">
         <v>8193</v>
       </c>
-      <c r="D1981" s="6" t="s">
+      <c r="D1981" s="3" t="s">
         <v>8159</v>
       </c>
-      <c r="F1981" s="6" t="s">
+      <c r="F1981" s="3" t="s">
         <v>8162</v>
       </c>
-      <c r="G1981" s="6" t="s">
+      <c r="G1981" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1981" s="6" t="s">
+      <c r="H1981" s="3" t="s">
         <v>8179</v>
       </c>
-      <c r="I1981" s="6" t="s">
+      <c r="I1981" s="3" t="s">
         <v>8180</v>
       </c>
     </row>
-    <row r="1982" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1982" s="6" t="s">
+    <row r="1982" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1982" s="3" t="s">
         <v>8195</v>
       </c>
-      <c r="B1982" s="5" t="s">
+      <c r="B1982" s="4" t="s">
         <v>8194</v>
       </c>
-      <c r="C1982" s="6" t="s">
+      <c r="C1982" s="3" t="s">
         <v>8196</v>
       </c>
-      <c r="D1982" s="6" t="s">
+      <c r="D1982" s="3" t="s">
         <v>8159</v>
       </c>
-      <c r="F1982" s="6" t="s">
+      <c r="F1982" s="3" t="s">
         <v>8162</v>
       </c>
-      <c r="G1982" s="6" t="s">
+      <c r="G1982" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1982" s="6" t="s">
+      <c r="H1982" s="3" t="s">
         <v>8181</v>
       </c>
-      <c r="I1982" s="6" t="s">
+      <c r="I1982" s="3" t="s">
         <v>8184</v>
       </c>
     </row>
-    <row r="1983" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1983" s="6" t="s">
+    <row r="1983" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1983" s="3" t="s">
         <v>8183</v>
       </c>
-      <c r="B1983" s="5" t="s">
+      <c r="B1983" s="4" t="s">
         <v>8197</v>
       </c>
-      <c r="C1983" s="6" t="s">
+      <c r="C1983" s="3" t="s">
         <v>8189</v>
       </c>
-      <c r="D1983" s="6" t="s">
+      <c r="D1983" s="3" t="s">
         <v>8159</v>
       </c>
-      <c r="F1983" s="6" t="s">
+      <c r="F1983" s="3" t="s">
         <v>8162</v>
       </c>
-      <c r="G1983" s="6" t="s">
+      <c r="G1983" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1983" s="6" t="s">
+      <c r="H1983" s="3" t="s">
         <v>8179</v>
       </c>
-      <c r="I1983" s="6" t="s">
+      <c r="I1983" s="3" t="s">
         <v>8182</v>
       </c>
     </row>
-    <row r="1984" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1984" s="6" t="s">
+    <row r="1984" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1984" s="3" t="s">
         <v>8199</v>
       </c>
-      <c r="B1984" s="5" t="s">
+      <c r="B1984" s="4" t="s">
         <v>8198</v>
       </c>
-      <c r="C1984" s="6" t="s">
+      <c r="C1984" s="3" t="s">
         <v>8200</v>
       </c>
-      <c r="D1984" s="6" t="s">
+      <c r="D1984" s="3" t="s">
         <v>8159</v>
       </c>
-      <c r="F1984" s="6" t="s">
+      <c r="F1984" s="3" t="s">
         <v>8162</v>
       </c>
-      <c r="G1984" s="6" t="s">
+      <c r="G1984" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1984" s="6" t="s">
+      <c r="H1984" s="3" t="s">
         <v>8165</v>
       </c>
-      <c r="I1984" s="6" t="s">
+      <c r="I1984" s="3" t="s">
         <v>8175</v>
       </c>
     </row>
-    <row r="1985" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1985" s="6" t="s">
+    <row r="1985" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1985" s="3" t="s">
         <v>8202</v>
       </c>
-      <c r="B1985" s="5" t="s">
+      <c r="B1985" s="4" t="s">
         <v>8201</v>
       </c>
-      <c r="C1985" s="6" t="s">
+      <c r="C1985" s="3" t="s">
         <v>8203</v>
       </c>
-      <c r="D1985" s="6" t="s">
+      <c r="D1985" s="3" t="s">
         <v>8159</v>
       </c>
-      <c r="F1985" s="6" t="s">
+      <c r="F1985" s="3" t="s">
         <v>8162</v>
       </c>
-      <c r="G1985" s="6" t="s">
+      <c r="G1985" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1985" s="6" t="s">
+      <c r="H1985" s="3" t="s">
         <v>8166</v>
       </c>
-      <c r="I1985" s="6" t="s">
+      <c r="I1985" s="3" t="s">
         <v>5351</v>
       </c>
     </row>
-    <row r="1986" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1986" s="6" t="s">
+    <row r="1986" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1986" s="3" t="s">
         <v>8205</v>
       </c>
-      <c r="B1986" s="5" t="s">
+      <c r="B1986" s="4" t="s">
         <v>8204</v>
       </c>
-      <c r="C1986" s="6" t="s">
+      <c r="C1986" s="3" t="s">
         <v>8206</v>
       </c>
-      <c r="D1986" s="6" t="s">
+      <c r="D1986" s="3" t="s">
         <v>8159</v>
       </c>
-      <c r="F1986" s="6" t="s">
+      <c r="F1986" s="3" t="s">
         <v>8162</v>
       </c>
-      <c r="G1986" s="6" t="s">
+      <c r="G1986" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1986" s="6" t="s">
+      <c r="H1986" s="3" t="s">
         <v>8167</v>
       </c>
-      <c r="I1986" s="6" t="s">
+      <c r="I1986" s="3" t="s">
         <v>8169</v>
       </c>
     </row>
-    <row r="1987" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1987" s="6" t="s">
+    <row r="1987" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1987" s="3" t="s">
         <v>8208</v>
       </c>
-      <c r="B1987" s="5" t="s">
+      <c r="B1987" s="4" t="s">
         <v>8207</v>
       </c>
-      <c r="C1987" s="6" t="s">
+      <c r="C1987" s="3" t="s">
         <v>8209</v>
       </c>
-      <c r="D1987" s="6" t="s">
+      <c r="D1987" s="3" t="s">
         <v>8159</v>
       </c>
-      <c r="F1987" s="6" t="s">
+      <c r="F1987" s="3" t="s">
         <v>8162</v>
       </c>
-      <c r="G1987" s="6" t="s">
+      <c r="G1987" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1987" s="6" t="s">
+      <c r="H1987" s="3" t="s">
         <v>8168</v>
       </c>
-      <c r="I1987" s="6" t="s">
+      <c r="I1987" s="3" t="s">
         <v>8170</v>
       </c>
     </row>
-    <row r="1988" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1988" s="6" t="s">
+    <row r="1988" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1988" s="3" t="s">
         <v>8211</v>
       </c>
-      <c r="B1988" s="5" t="s">
+      <c r="B1988" s="4" t="s">
         <v>8210</v>
       </c>
-      <c r="C1988" s="6" t="s">
+      <c r="C1988" s="3" t="s">
         <v>8212</v>
       </c>
-      <c r="D1988" s="6" t="s">
+      <c r="D1988" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="F1988" s="6" t="s">
+      <c r="F1988" s="3" t="s">
         <v>8162</v>
       </c>
-      <c r="G1988" s="6" t="s">
+      <c r="G1988" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1988" s="6" t="s">
+      <c r="H1988" s="3" t="s">
         <v>8185</v>
       </c>
-      <c r="I1988" s="6" t="s">
+      <c r="I1988" s="3" t="s">
         <v>8186</v>
       </c>
     </row>
-    <row r="1989" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1989" s="6" t="s">
+    <row r="1989" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1989" s="3" t="s">
         <v>8214</v>
       </c>
-      <c r="B1989" s="5" t="s">
+      <c r="B1989" s="4" t="s">
         <v>8213</v>
       </c>
-      <c r="C1989" s="6" t="s">
+      <c r="C1989" s="3" t="s">
         <v>8215</v>
       </c>
-      <c r="D1989" s="6" t="s">
+      <c r="D1989" s="3" t="s">
         <v>8159</v>
       </c>
-      <c r="F1989" s="6" t="s">
+      <c r="F1989" s="3" t="s">
         <v>8162</v>
       </c>
-      <c r="G1989" s="6" t="s">
+      <c r="G1989" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1989" s="6" t="s">
+      <c r="H1989" s="3" t="s">
         <v>8171</v>
       </c>
-      <c r="I1989" s="6" t="s">
+      <c r="I1989" s="3" t="s">
         <v>8172</v>
       </c>
     </row>
-    <row r="1990" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1990" s="6" t="s">
+    <row r="1990" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1990" s="3" t="s">
         <v>8217</v>
       </c>
-      <c r="B1990" s="5" t="s">
+      <c r="B1990" s="4" t="s">
         <v>8216</v>
       </c>
-      <c r="C1990" s="6" t="s">
+      <c r="C1990" s="3" t="s">
         <v>8218</v>
       </c>
-      <c r="D1990" s="6" t="s">
+      <c r="D1990" s="3" t="s">
         <v>8159</v>
       </c>
-      <c r="F1990" s="6" t="s">
+      <c r="F1990" s="3" t="s">
         <v>8162</v>
       </c>
-      <c r="G1990" s="6" t="s">
+      <c r="G1990" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1990" s="6" t="s">
+      <c r="H1990" s="3" t="s">
         <v>8173</v>
       </c>
-      <c r="I1990" s="6" t="s">
+      <c r="I1990" s="3" t="s">
         <v>8226</v>
       </c>
     </row>
-    <row r="1991" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1991" s="6" t="s">
+    <row r="1991" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1991" s="3" t="s">
         <v>8231</v>
       </c>
-      <c r="B1991" s="5" t="s">
+      <c r="B1991" s="4" t="s">
         <v>8230</v>
       </c>
-      <c r="C1991" s="6" t="s">
+      <c r="C1991" s="3" t="s">
         <v>8232</v>
       </c>
-      <c r="D1991" s="6" t="s">
+      <c r="D1991" s="3" t="s">
         <v>8159</v>
       </c>
-      <c r="F1991" s="6" t="s">
+      <c r="F1991" s="3" t="s">
         <v>8162</v>
       </c>
-      <c r="G1991" s="6" t="s">
+      <c r="G1991" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1991" s="6" t="s">
+      <c r="H1991" s="3" t="s">
         <v>8174</v>
       </c>
-      <c r="I1991" s="6" t="s">
+      <c r="I1991" s="3" t="s">
         <v>8175</v>
       </c>
     </row>
-    <row r="1992" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1992" s="6" t="s">
+    <row r="1992" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1992" s="3" t="s">
         <v>8220</v>
       </c>
-      <c r="B1992" s="5" t="s">
+      <c r="B1992" s="4" t="s">
         <v>8219</v>
       </c>
-      <c r="C1992" s="6" t="s">
+      <c r="C1992" s="3" t="s">
         <v>8221</v>
       </c>
-      <c r="D1992" s="6" t="s">
+      <c r="D1992" s="3" t="s">
         <v>8160</v>
       </c>
-      <c r="F1992" s="6" t="s">
+      <c r="F1992" s="3" t="s">
         <v>8162</v>
       </c>
-      <c r="G1992" s="6" t="s">
+      <c r="G1992" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1992" s="6" t="s">
+      <c r="H1992" s="3" t="s">
         <v>8176</v>
       </c>
-      <c r="I1992" s="6" t="s">
+      <c r="I1992" s="3" t="s">
         <v>8170</v>
       </c>
     </row>
-    <row r="1993" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1993" s="6" t="s">
+    <row r="1993" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1993" s="3" t="s">
         <v>8223</v>
       </c>
-      <c r="B1993" s="5" t="s">
+      <c r="B1993" s="4" t="s">
         <v>8222</v>
       </c>
-      <c r="C1993" s="6" t="s">
+      <c r="C1993" s="3" t="s">
         <v>8224</v>
       </c>
-      <c r="D1993" s="6" t="s">
+      <c r="D1993" s="3" t="s">
         <v>8159</v>
       </c>
-      <c r="F1993" s="6" t="s">
+      <c r="F1993" s="3" t="s">
         <v>8162</v>
       </c>
-      <c r="G1993" s="6" t="s">
+      <c r="G1993" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1993" s="6" t="s">
+      <c r="H1993" s="3" t="s">
         <v>8177</v>
       </c>
-      <c r="I1993" s="6" t="s">
+      <c r="I1993" s="3" t="s">
         <v>8164</v>
       </c>
     </row>
-    <row r="1994" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1994" s="6" t="s">
+    <row r="1994" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1994" s="3" t="s">
         <v>8228</v>
       </c>
-      <c r="B1994" s="5" t="s">
+      <c r="B1994" s="4" t="s">
         <v>8227</v>
       </c>
-      <c r="C1994" s="6" t="s">
+      <c r="C1994" s="3" t="s">
         <v>8229</v>
       </c>
-      <c r="D1994" s="6" t="s">
+      <c r="D1994" s="3" t="s">
         <v>8161</v>
       </c>
-      <c r="F1994" s="6" t="s">
+      <c r="F1994" s="3" t="s">
         <v>8162</v>
       </c>
-      <c r="G1994" s="6" t="s">
+      <c r="G1994" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H1994" s="6" t="s">
+      <c r="H1994" s="3" t="s">
         <v>8178</v>
       </c>
-      <c r="I1994" s="6" t="s">
+      <c r="I1994" s="3" t="s">
         <v>8225</v>
       </c>
     </row>
-    <row r="1995" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1995" s="6" t="s">
+    <row r="1995" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1995" s="3" t="s">
         <v>8238</v>
       </c>
-      <c r="B1995" s="5">
+      <c r="B1995" s="4">
         <v>84359591</v>
       </c>
-      <c r="C1995" s="6" t="s">
+      <c r="C1995" s="3" t="s">
         <v>8239</v>
       </c>
-      <c r="D1995" s="6" t="s">
+      <c r="D1995" s="3" t="s">
         <v>8233</v>
       </c>
-      <c r="F1995" s="6" t="s">
+      <c r="F1995" s="3" t="s">
         <v>8236</v>
       </c>
-      <c r="G1995" s="6" t="s">
+      <c r="G1995" s="3" t="s">
         <v>8237</v>
       </c>
-      <c r="H1995" s="6" t="s">
+      <c r="H1995" s="3" t="s">
         <v>8240</v>
       </c>
-      <c r="I1995" s="6" t="s">
+      <c r="I1995" s="3" t="s">
         <v>8241</v>
       </c>
     </row>
-    <row r="1996" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1996" s="6" t="s">
+    <row r="1996" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1996" s="3" t="s">
         <v>8242</v>
       </c>
-      <c r="B1996" s="5">
+      <c r="B1996" s="4">
         <v>16249702</v>
       </c>
-      <c r="C1996" s="6" t="s">
+      <c r="C1996" s="3" t="s">
         <v>8243</v>
       </c>
-      <c r="D1996" s="6" t="s">
+      <c r="D1996" s="3" t="s">
         <v>8233</v>
       </c>
-      <c r="F1996" s="6" t="s">
+      <c r="F1996" s="3" t="s">
         <v>8236</v>
       </c>
-      <c r="G1996" s="6" t="s">
+      <c r="G1996" s="3" t="s">
         <v>8237</v>
       </c>
-      <c r="H1996" s="6" t="s">
+      <c r="H1996" s="3" t="s">
         <v>8244</v>
       </c>
-      <c r="I1996" s="6" t="s">
+      <c r="I1996" s="3" t="s">
         <v>8245</v>
       </c>
     </row>
-    <row r="1997" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1997" s="6" t="s">
+    <row r="1997" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1997" s="3" t="s">
         <v>8246</v>
       </c>
-      <c r="B1997" s="5">
+      <c r="B1997" s="4">
         <v>53351335</v>
       </c>
-      <c r="C1997" s="6" t="s">
+      <c r="C1997" s="3" t="s">
         <v>8247</v>
       </c>
-      <c r="D1997" s="6" t="s">
+      <c r="D1997" s="3" t="s">
         <v>8234</v>
       </c>
-      <c r="F1997" s="6" t="s">
+      <c r="F1997" s="3" t="s">
         <v>8236</v>
       </c>
-      <c r="G1997" s="6" t="s">
+      <c r="G1997" s="3" t="s">
         <v>8237</v>
       </c>
-      <c r="H1997" s="6" t="s">
+      <c r="H1997" s="3" t="s">
         <v>8248</v>
       </c>
-      <c r="I1997" s="6" t="s">
+      <c r="I1997" s="3" t="s">
         <v>8249</v>
       </c>
     </row>
-    <row r="1998" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1998" s="6" t="s">
+    <row r="1998" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1998" s="3" t="s">
         <v>8250</v>
       </c>
-      <c r="B1998" s="5">
+      <c r="B1998" s="4">
         <v>96766306</v>
       </c>
-      <c r="C1998" s="6" t="s">
+      <c r="C1998" s="3" t="s">
         <v>8251</v>
       </c>
-      <c r="D1998" s="6" t="s">
+      <c r="D1998" s="3" t="s">
         <v>8233</v>
       </c>
-      <c r="F1998" s="6" t="s">
+      <c r="F1998" s="3" t="s">
         <v>8236</v>
       </c>
-      <c r="G1998" s="6" t="s">
+      <c r="G1998" s="3" t="s">
         <v>8237</v>
       </c>
-      <c r="H1998" s="6" t="s">
+      <c r="H1998" s="3" t="s">
         <v>8252</v>
       </c>
-      <c r="I1998" s="6" t="s">
+      <c r="I1998" s="3" t="s">
         <v>8253</v>
       </c>
     </row>
-    <row r="1999" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1999" s="6" t="s">
+    <row r="1999" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1999" s="3" t="s">
         <v>8254</v>
       </c>
-      <c r="B1999" s="5">
+      <c r="B1999" s="4">
         <v>53714239</v>
       </c>
-      <c r="C1999" s="6" t="s">
+      <c r="C1999" s="3" t="s">
         <v>8255</v>
       </c>
-      <c r="D1999" s="6" t="s">
+      <c r="D1999" s="3" t="s">
         <v>8235</v>
       </c>
-      <c r="F1999" s="6" t="s">
+      <c r="F1999" s="3" t="s">
         <v>8236</v>
       </c>
-      <c r="G1999" s="6" t="s">
+      <c r="G1999" s="3" t="s">
         <v>8237</v>
       </c>
-      <c r="H1999" s="6" t="s">
+      <c r="H1999" s="3" t="s">
         <v>8256</v>
       </c>
-      <c r="I1999" s="6" t="s">
+      <c r="I1999" s="3" t="s">
         <v>8257</v>
       </c>
     </row>
-    <row r="2000" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2000" s="6" t="s">
+    <row r="2000" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2000" s="3" t="s">
         <v>8258</v>
       </c>
-      <c r="B2000" s="5">
+      <c r="B2000" s="4">
         <v>24386551</v>
       </c>
-      <c r="C2000" s="6" t="s">
+      <c r="C2000" s="3" t="s">
         <v>8259</v>
       </c>
-      <c r="D2000" s="6" t="s">
+      <c r="D2000" s="3" t="s">
         <v>8233</v>
       </c>
-      <c r="F2000" s="6" t="s">
+      <c r="F2000" s="3" t="s">
         <v>8236</v>
       </c>
-      <c r="G2000" s="6" t="s">
+      <c r="G2000" s="3" t="s">
         <v>8237</v>
       </c>
-      <c r="H2000" s="6" t="s">
+      <c r="H2000" s="3" t="s">
         <v>8260</v>
       </c>
-      <c r="I2000" s="6" t="s">
+      <c r="I2000" s="3" t="s">
         <v>8261</v>
       </c>
     </row>
-    <row r="2001" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2001" s="6" t="s">
+    <row r="2001" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2001" s="3" t="s">
         <v>8262</v>
       </c>
-      <c r="B2001" s="5">
+      <c r="B2001" s="4">
         <v>16708380</v>
       </c>
-      <c r="C2001" s="6" t="s">
+      <c r="C2001" s="3" t="s">
         <v>8263</v>
       </c>
-      <c r="D2001" s="6" t="s">
+      <c r="D2001" s="3" t="s">
         <v>8233</v>
       </c>
-      <c r="F2001" s="6" t="s">
+      <c r="F2001" s="3" t="s">
         <v>8236</v>
       </c>
-      <c r="G2001" s="6" t="s">
+      <c r="G2001" s="3" t="s">
         <v>8237</v>
       </c>
-      <c r="H2001" s="6" t="s">
+      <c r="H2001" s="3" t="s">
         <v>8264</v>
       </c>
-      <c r="I2001" s="6" t="s">
+      <c r="I2001" s="3" t="s">
         <v>8265</v>
       </c>
     </row>
-    <row r="2002" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2002" s="6" t="s">
+    <row r="2002" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2002" s="3" t="s">
         <v>8266</v>
       </c>
-      <c r="B2002" s="5">
+      <c r="B2002" s="4">
         <v>84900976</v>
       </c>
-      <c r="C2002" s="6" t="s">
+      <c r="C2002" s="3" t="s">
         <v>8267</v>
       </c>
-      <c r="D2002" s="6" t="s">
+      <c r="D2002" s="3" t="s">
         <v>8233</v>
       </c>
-      <c r="F2002" s="6" t="s">
+      <c r="F2002" s="3" t="s">
         <v>8236</v>
       </c>
-      <c r="G2002" s="6" t="s">
+      <c r="G2002" s="3" t="s">
         <v>8237</v>
       </c>
-      <c r="H2002" s="6" t="s">
+      <c r="H2002" s="3" t="s">
         <v>8268</v>
       </c>
-      <c r="I2002" s="6" t="s">
+      <c r="I2002" s="3" t="s">
         <v>8249</v>
       </c>
     </row>
-    <row r="2003" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2003" s="6" t="s">
+    <row r="2003" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2003" s="3" t="s">
         <v>8269</v>
       </c>
-      <c r="B2003" s="5">
+      <c r="B2003" s="4">
         <v>28911280</v>
       </c>
-      <c r="C2003" s="6" t="s">
+      <c r="C2003" s="3" t="s">
         <v>8270</v>
       </c>
-      <c r="D2003" s="6" t="s">
+      <c r="D2003" s="3" t="s">
         <v>8271</v>
       </c>
-      <c r="F2003" s="6" t="s">
+      <c r="F2003" s="3" t="s">
         <v>8272</v>
       </c>
-      <c r="G2003" s="6" t="s">
+      <c r="G2003" s="3" t="s">
         <v>8273</v>
       </c>
-      <c r="H2003" s="6" t="s">
+      <c r="H2003" s="3" t="s">
         <v>8274</v>
       </c>
-      <c r="I2003" s="6" t="s">
+      <c r="I2003" s="3" t="s">
         <v>8275</v>
       </c>
     </row>
-    <row r="2004" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2004" s="6" t="s">
+    <row r="2004" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2004" s="3" t="s">
         <v>8276</v>
       </c>
-      <c r="B2004" s="5">
+      <c r="B2004" s="4">
         <v>24288502</v>
       </c>
-      <c r="C2004" s="6" t="s">
+      <c r="C2004" s="3" t="s">
         <v>8277</v>
       </c>
-      <c r="D2004" s="6" t="s">
+      <c r="D2004" s="3" t="s">
         <v>8271</v>
       </c>
-      <c r="F2004" s="6" t="s">
+      <c r="F2004" s="3" t="s">
         <v>8272</v>
       </c>
-      <c r="G2004" s="6" t="s">
+      <c r="G2004" s="3" t="s">
         <v>8273</v>
       </c>
-      <c r="H2004" s="6" t="s">
+      <c r="H2004" s="3" t="s">
         <v>8278</v>
       </c>
-      <c r="I2004" s="6" t="s">
+      <c r="I2004" s="3" t="s">
         <v>8279</v>
       </c>
     </row>
-    <row r="2005" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2005" s="6" t="s">
+    <row r="2005" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2005" s="3" t="s">
         <v>8280</v>
       </c>
-      <c r="B2005" s="5">
+      <c r="B2005" s="4">
         <v>25043293</v>
       </c>
-      <c r="C2005" s="6" t="s">
+      <c r="C2005" s="3" t="s">
         <v>8281</v>
       </c>
-      <c r="D2005" s="6" t="s">
+      <c r="D2005" s="3" t="s">
         <v>8282</v>
       </c>
-      <c r="F2005" s="6" t="s">
+      <c r="F2005" s="3" t="s">
         <v>8272</v>
       </c>
-      <c r="G2005" s="6" t="s">
+      <c r="G2005" s="3" t="s">
         <v>8273</v>
       </c>
-      <c r="H2005" s="6" t="s">
+      <c r="H2005" s="3" t="s">
         <v>8283</v>
       </c>
-      <c r="I2005" s="6" t="s">
+      <c r="I2005" s="3" t="s">
         <v>8284</v>
       </c>
     </row>
-    <row r="2006" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2006" s="6" t="s">
+    <row r="2006" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2006" s="3" t="s">
         <v>8285</v>
       </c>
-      <c r="B2006" s="5">
+      <c r="B2006" s="4">
         <v>89163174</v>
       </c>
-      <c r="C2006" s="6" t="s">
+      <c r="C2006" s="3" t="s">
         <v>8286</v>
       </c>
-      <c r="D2006" s="6" t="s">
+      <c r="D2006" s="3" t="s">
         <v>8271</v>
       </c>
-      <c r="F2006" s="6" t="s">
+      <c r="F2006" s="3" t="s">
         <v>8272</v>
       </c>
-      <c r="G2006" s="6" t="s">
+      <c r="G2006" s="3" t="s">
         <v>8273</v>
       </c>
-      <c r="H2006" s="6" t="s">
+      <c r="H2006" s="3" t="s">
         <v>8287</v>
       </c>
-      <c r="I2006" s="6" t="s">
+      <c r="I2006" s="3" t="s">
         <v>8288</v>
       </c>
     </row>
-    <row r="2007" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2007" s="6" t="s">
+    <row r="2007" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2007" s="3" t="s">
         <v>8289</v>
       </c>
-      <c r="B2007" s="5">
+      <c r="B2007" s="4">
         <v>82639301</v>
       </c>
-      <c r="C2007" s="6" t="s">
+      <c r="C2007" s="3" t="s">
         <v>8290</v>
       </c>
-      <c r="D2007" s="6" t="s">
+      <c r="D2007" s="3" t="s">
         <v>8271</v>
       </c>
-      <c r="F2007" s="6" t="s">
+      <c r="F2007" s="3" t="s">
         <v>8272</v>
       </c>
-      <c r="G2007" s="6" t="s">
+      <c r="G2007" s="3" t="s">
         <v>8273</v>
       </c>
-      <c r="H2007" s="6" t="s">
+      <c r="H2007" s="3" t="s">
         <v>8291</v>
       </c>
-      <c r="I2007" s="6" t="s">
+      <c r="I2007" s="3" t="s">
         <v>8314</v>
       </c>
     </row>
-    <row r="2008" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2008" s="6" t="s">
+    <row r="2008" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2008" s="3" t="s">
         <v>8292</v>
       </c>
-      <c r="B2008" s="5">
+      <c r="B2008" s="4">
         <v>70585126</v>
       </c>
-      <c r="C2008" s="6" t="s">
+      <c r="C2008" s="3" t="s">
         <v>8293</v>
       </c>
-      <c r="D2008" s="6" t="s">
+      <c r="D2008" s="3" t="s">
         <v>8271</v>
       </c>
-      <c r="F2008" s="6" t="s">
+      <c r="F2008" s="3" t="s">
         <v>8272</v>
       </c>
-      <c r="G2008" s="6" t="s">
+      <c r="G2008" s="3" t="s">
         <v>8273</v>
       </c>
-      <c r="H2008" s="6" t="s">
+      <c r="H2008" s="3" t="s">
         <v>8294</v>
       </c>
-      <c r="I2008" s="6" t="s">
+      <c r="I2008" s="3" t="s">
         <v>8313</v>
       </c>
     </row>
-    <row r="2009" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2009" s="6" t="s">
+    <row r="2009" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2009" s="3" t="s">
         <v>8295</v>
       </c>
-      <c r="B2009" s="5">
+      <c r="B2009" s="4">
         <v>56659456</v>
       </c>
-      <c r="C2009" s="6" t="s">
+      <c r="C2009" s="3" t="s">
         <v>8296</v>
       </c>
-      <c r="D2009" s="6" t="s">
+      <c r="D2009" s="3" t="s">
         <v>8271</v>
       </c>
-      <c r="F2009" s="6" t="s">
+      <c r="F2009" s="3" t="s">
         <v>8272</v>
       </c>
-      <c r="G2009" s="6" t="s">
+      <c r="G2009" s="3" t="s">
         <v>8273</v>
       </c>
-      <c r="H2009" s="6" t="s">
+      <c r="H2009" s="3" t="s">
         <v>8308</v>
       </c>
-      <c r="I2009" s="6" t="s">
+      <c r="I2009" s="3" t="s">
         <v>8279</v>
       </c>
     </row>
-    <row r="2010" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2010" s="6" t="s">
+    <row r="2010" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2010" s="3" t="s">
         <v>8297</v>
       </c>
-      <c r="B2010" s="5">
+      <c r="B2010" s="4">
         <v>73693417</v>
       </c>
-      <c r="C2010" s="6" t="s">
+      <c r="C2010" s="3" t="s">
         <v>8298</v>
       </c>
-      <c r="D2010" s="6" t="s">
+      <c r="D2010" s="3" t="s">
         <v>8271</v>
       </c>
-      <c r="F2010" s="6" t="s">
+      <c r="F2010" s="3" t="s">
         <v>8272</v>
       </c>
-      <c r="G2010" s="6" t="s">
+      <c r="G2010" s="3" t="s">
         <v>8273</v>
       </c>
-      <c r="H2010" s="6" t="s">
+      <c r="H2010" s="3" t="s">
         <v>8311</v>
       </c>
-      <c r="I2010" s="6" t="s">
+      <c r="I2010" s="3" t="s">
         <v>8312</v>
       </c>
     </row>
-    <row r="2011" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2011" s="6" t="s">
+    <row r="2011" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2011" s="3" t="s">
         <v>8299</v>
       </c>
-      <c r="B2011" s="5">
+      <c r="B2011" s="4">
         <v>54782327</v>
       </c>
-      <c r="C2011" s="6" t="s">
+      <c r="C2011" s="3" t="s">
         <v>8300</v>
       </c>
-      <c r="D2011" s="6" t="s">
+      <c r="D2011" s="3" t="s">
         <v>8301</v>
       </c>
-      <c r="F2011" s="6" t="s">
+      <c r="F2011" s="3" t="s">
         <v>8272</v>
       </c>
-      <c r="G2011" s="6" t="s">
+      <c r="G2011" s="3" t="s">
         <v>8273</v>
       </c>
-      <c r="H2011" s="6" t="s">
+      <c r="H2011" s="3" t="s">
         <v>8302</v>
       </c>
-      <c r="I2011" s="6" t="s">
+      <c r="I2011" s="3" t="s">
         <v>8315</v>
       </c>
     </row>
-    <row r="2012" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2012" s="6" t="s">
+    <row r="2012" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2012" s="3" t="s">
         <v>8303</v>
       </c>
-      <c r="B2012" s="5">
+      <c r="B2012" s="4">
         <v>28426484</v>
       </c>
-      <c r="C2012" s="6" t="s">
+      <c r="C2012" s="3" t="s">
         <v>8304</v>
       </c>
-      <c r="D2012" s="6" t="s">
+      <c r="D2012" s="3" t="s">
         <v>8271</v>
       </c>
-      <c r="F2012" s="6" t="s">
+      <c r="F2012" s="3" t="s">
         <v>8272</v>
       </c>
-      <c r="G2012" s="6" t="s">
+      <c r="G2012" s="3" t="s">
         <v>8273</v>
       </c>
-      <c r="H2012" s="6" t="s">
+      <c r="H2012" s="3" t="s">
         <v>8305</v>
       </c>
-      <c r="I2012" s="6" t="s">
+      <c r="I2012" s="3" t="s">
         <v>8284</v>
       </c>
     </row>
-    <row r="2013" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2013" s="6" t="s">
+    <row r="2013" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2013" s="3" t="s">
         <v>8306</v>
       </c>
-      <c r="B2013" s="5">
+      <c r="B2013" s="4">
         <v>80086182</v>
       </c>
-      <c r="C2013" s="6" t="s">
+      <c r="C2013" s="3" t="s">
         <v>8307</v>
       </c>
-      <c r="D2013" s="6" t="s">
+      <c r="D2013" s="3" t="s">
         <v>8271</v>
       </c>
-      <c r="F2013" s="6" t="s">
+      <c r="F2013" s="3" t="s">
         <v>8272</v>
       </c>
-      <c r="G2013" s="6" t="s">
+      <c r="G2013" s="3" t="s">
         <v>8273</v>
       </c>
-      <c r="H2013" s="6" t="s">
+      <c r="H2013" s="3" t="s">
         <v>8310</v>
       </c>
-      <c r="I2013" s="6" t="s">
+      <c r="I2013" s="3" t="s">
         <v>8309</v>
       </c>
     </row>
-    <row r="2014" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2014" s="6" t="s">
+    <row r="2014" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2014" s="3" t="s">
         <v>8321</v>
       </c>
-      <c r="B2014" s="5">
+      <c r="B2014" s="4">
         <v>52259079</v>
       </c>
-      <c r="C2014" s="6" t="s">
+      <c r="C2014" s="3" t="s">
         <v>8322</v>
       </c>
-      <c r="D2014" s="6" t="s">
+      <c r="D2014" s="3" t="s">
         <v>8316</v>
       </c>
-      <c r="F2014" s="6" t="s">
+      <c r="F2014" s="3" t="s">
         <v>8323</v>
       </c>
-      <c r="G2014" s="6" t="s">
+      <c r="G2014" s="3" t="s">
         <v>8324</v>
       </c>
-      <c r="H2014" s="6" t="s">
+      <c r="H2014" s="3" t="s">
         <v>8325</v>
       </c>
-      <c r="I2014" s="6" t="s">
+      <c r="I2014" s="3" t="s">
         <v>8326</v>
       </c>
     </row>
-    <row r="2015" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2015" s="6" t="s">
+    <row r="2015" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2015" s="3" t="s">
         <v>8327</v>
       </c>
-      <c r="B2015" s="5">
+      <c r="B2015" s="4">
         <v>86828303</v>
       </c>
-      <c r="C2015" s="6" t="s">
+      <c r="C2015" s="3" t="s">
         <v>8328</v>
       </c>
-      <c r="D2015" s="6" t="s">
+      <c r="D2015" s="3" t="s">
         <v>8317</v>
       </c>
-      <c r="F2015" s="6" t="s">
+      <c r="F2015" s="3" t="s">
         <v>8323</v>
       </c>
-      <c r="G2015" s="6" t="s">
+      <c r="G2015" s="3" t="s">
         <v>8329</v>
       </c>
-      <c r="H2015" s="6" t="s">
+      <c r="H2015" s="3" t="s">
         <v>8330</v>
       </c>
-      <c r="I2015" s="6" t="s">
+      <c r="I2015" s="3" t="s">
         <v>8331</v>
       </c>
     </row>
-    <row r="2016" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2016" s="6" t="s">
+    <row r="2016" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2016" s="3" t="s">
         <v>8332</v>
       </c>
-      <c r="B2016" s="5">
+      <c r="B2016" s="4">
         <v>27457023</v>
       </c>
-      <c r="C2016" s="6" t="s">
+      <c r="C2016" s="3" t="s">
         <v>8333</v>
       </c>
-      <c r="D2016" s="6" t="s">
+      <c r="D2016" s="3" t="s">
         <v>8317</v>
       </c>
-      <c r="F2016" s="6" t="s">
+      <c r="F2016" s="3" t="s">
         <v>8323</v>
       </c>
-      <c r="G2016" s="6" t="s">
+      <c r="G2016" s="3" t="s">
         <v>8324</v>
       </c>
-      <c r="H2016" s="6" t="s">
+      <c r="H2016" s="3" t="s">
         <v>8334</v>
       </c>
-      <c r="I2016" s="6" t="s">
+      <c r="I2016" s="3" t="s">
         <v>8326</v>
       </c>
     </row>
-    <row r="2017" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2017" s="6" t="s">
+    <row r="2017" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2017" s="3" t="s">
         <v>8335</v>
       </c>
-      <c r="B2017" s="5">
+      <c r="B2017" s="4">
         <v>23503047</v>
       </c>
-      <c r="C2017" s="6" t="s">
+      <c r="C2017" s="3" t="s">
         <v>8336</v>
       </c>
-      <c r="D2017" s="6" t="s">
+      <c r="D2017" s="3" t="s">
         <v>8317</v>
       </c>
-      <c r="F2017" s="6" t="s">
+      <c r="F2017" s="3" t="s">
         <v>8323</v>
       </c>
-      <c r="G2017" s="6" t="s">
+      <c r="G2017" s="3" t="s">
         <v>8329</v>
       </c>
-      <c r="H2017" s="6" t="s">
+      <c r="H2017" s="3" t="s">
         <v>8337</v>
       </c>
-      <c r="I2017" s="6" t="s">
+      <c r="I2017" s="3" t="s">
         <v>8338</v>
       </c>
     </row>
-    <row r="2018" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2018" s="6" t="s">
+    <row r="2018" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2018" s="3" t="s">
         <v>8339</v>
       </c>
-      <c r="B2018" s="5">
+      <c r="B2018" s="4">
         <v>43704649</v>
       </c>
-      <c r="C2018" s="6" t="s">
+      <c r="C2018" s="3" t="s">
         <v>8340</v>
       </c>
-      <c r="D2018" s="6" t="s">
+      <c r="D2018" s="3" t="s">
         <v>8317</v>
       </c>
-      <c r="F2018" s="6" t="s">
+      <c r="F2018" s="3" t="s">
         <v>8323</v>
       </c>
-      <c r="G2018" s="6" t="s">
+      <c r="G2018" s="3" t="s">
         <v>8324</v>
       </c>
-      <c r="H2018" s="6" t="s">
+      <c r="H2018" s="3" t="s">
         <v>8341</v>
       </c>
-      <c r="I2018" s="6" t="s">
+      <c r="I2018" s="3" t="s">
         <v>8342</v>
       </c>
     </row>
-    <row r="2019" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2019" s="6" t="s">
+    <row r="2019" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2019" s="3" t="s">
         <v>8343</v>
       </c>
-      <c r="B2019" s="5">
+      <c r="B2019" s="4">
         <v>53740840</v>
       </c>
-      <c r="C2019" s="6" t="s">
+      <c r="C2019" s="3" t="s">
         <v>8344</v>
       </c>
-      <c r="D2019" s="6" t="s">
+      <c r="D2019" s="3" t="s">
         <v>8317</v>
       </c>
-      <c r="F2019" s="6" t="s">
+      <c r="F2019" s="3" t="s">
         <v>8323</v>
       </c>
-      <c r="G2019" s="6" t="s">
+      <c r="G2019" s="3" t="s">
         <v>8324</v>
       </c>
-      <c r="H2019" s="6" t="s">
+      <c r="H2019" s="3" t="s">
         <v>8345</v>
       </c>
-      <c r="I2019" s="6" t="s">
+      <c r="I2019" s="3" t="s">
         <v>8346</v>
       </c>
     </row>
-    <row r="2020" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2020" s="6" t="s">
+    <row r="2020" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2020" s="3" t="s">
         <v>8347</v>
       </c>
-      <c r="B2020" s="5">
+      <c r="B2020" s="4">
         <v>56619737</v>
       </c>
-      <c r="C2020" s="6" t="s">
+      <c r="C2020" s="3" t="s">
         <v>8348</v>
       </c>
-      <c r="D2020" s="6" t="s">
+      <c r="D2020" s="3" t="s">
         <v>8317</v>
       </c>
-      <c r="F2020" s="6" t="s">
+      <c r="F2020" s="3" t="s">
         <v>8323</v>
       </c>
-      <c r="G2020" s="6" t="s">
+      <c r="G2020" s="3" t="s">
         <v>8324</v>
       </c>
-      <c r="H2020" s="6" t="s">
+      <c r="H2020" s="3" t="s">
         <v>8349</v>
       </c>
-      <c r="I2020" s="6" t="s">
+      <c r="I2020" s="3" t="s">
         <v>8326</v>
       </c>
     </row>
-    <row r="2021" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2021" s="6" t="s">
+    <row r="2021" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2021" s="3" t="s">
         <v>8350</v>
       </c>
-      <c r="B2021" s="5">
+      <c r="B2021" s="4">
         <v>24808757</v>
       </c>
-      <c r="C2021" s="6" t="s">
+      <c r="C2021" s="3" t="s">
         <v>8351</v>
       </c>
-      <c r="D2021" s="6" t="s">
+      <c r="D2021" s="3" t="s">
         <v>8317</v>
       </c>
-      <c r="F2021" s="6" t="s">
+      <c r="F2021" s="3" t="s">
         <v>8323</v>
       </c>
-      <c r="G2021" s="6" t="s">
+      <c r="G2021" s="3" t="s">
         <v>8324</v>
       </c>
-      <c r="H2021" s="6" t="s">
+      <c r="H2021" s="3" t="s">
         <v>8352</v>
       </c>
-      <c r="I2021" s="6" t="s">
+      <c r="I2021" s="3" t="s">
         <v>8353</v>
       </c>
     </row>
-    <row r="2022" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2022" s="6" t="s">
+    <row r="2022" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2022" s="3" t="s">
         <v>8354</v>
       </c>
-      <c r="B2022" s="5">
+      <c r="B2022" s="4">
         <v>27472283</v>
       </c>
-      <c r="C2022" s="6" t="s">
+      <c r="C2022" s="3" t="s">
         <v>8355</v>
       </c>
-      <c r="D2022" s="6" t="s">
+      <c r="D2022" s="3" t="s">
         <v>8318</v>
       </c>
-      <c r="F2022" s="6" t="s">
+      <c r="F2022" s="3" t="s">
         <v>8323</v>
       </c>
-      <c r="G2022" s="6" t="s">
+      <c r="G2022" s="3" t="s">
         <v>8324</v>
       </c>
-      <c r="H2022" s="6" t="s">
+      <c r="H2022" s="3" t="s">
         <v>8356</v>
       </c>
-      <c r="I2022" s="6" t="s">
+      <c r="I2022" s="3" t="s">
         <v>8326</v>
       </c>
     </row>
-    <row r="2023" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2023" s="6" t="s">
+    <row r="2023" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2023" s="3" t="s">
         <v>8359</v>
       </c>
-      <c r="B2023" s="5">
+      <c r="B2023" s="4">
         <v>29033965</v>
       </c>
-      <c r="C2023" s="6" t="s">
+      <c r="C2023" s="3" t="s">
         <v>8360</v>
       </c>
-      <c r="D2023" s="6" t="s">
+      <c r="D2023" s="3" t="s">
         <v>8357</v>
       </c>
-      <c r="F2023" s="6" t="s">
+      <c r="F2023" s="3" t="s">
         <v>8361</v>
       </c>
-      <c r="G2023" s="6" t="s">
+      <c r="G2023" s="3" t="s">
         <v>8362</v>
       </c>
-      <c r="H2023" s="6" t="s">
+      <c r="H2023" s="3" t="s">
         <v>8376</v>
       </c>
-      <c r="I2023" s="6" t="s">
+      <c r="I2023" s="3" t="s">
         <v>8375</v>
       </c>
     </row>
-    <row r="2024" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2024" s="6" t="s">
+    <row r="2024" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2024" s="3" t="s">
         <v>8363</v>
       </c>
-      <c r="B2024" s="5">
+      <c r="B2024" s="4">
         <v>53594184</v>
       </c>
-      <c r="C2024" s="6" t="s">
+      <c r="C2024" s="3" t="s">
         <v>8364</v>
       </c>
-      <c r="D2024" s="6" t="s">
+      <c r="D2024" s="3" t="s">
         <v>8358</v>
       </c>
-      <c r="F2024" s="6" t="s">
+      <c r="F2024" s="3" t="s">
         <v>8361</v>
       </c>
-      <c r="G2024" s="6" t="s">
+      <c r="G2024" s="3" t="s">
         <v>8362</v>
       </c>
-      <c r="H2024" s="6" t="s">
+      <c r="H2024" s="3" t="s">
         <v>8377</v>
       </c>
-      <c r="I2024" s="6" t="s">
+      <c r="I2024" s="3" t="s">
         <v>8378</v>
       </c>
     </row>
-    <row r="2025" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2025" s="6" t="s">
+    <row r="2025" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2025" s="3" t="s">
         <v>8365</v>
       </c>
-      <c r="B2025" s="5">
+      <c r="B2025" s="4">
         <v>42622374</v>
       </c>
-      <c r="C2025" s="6" t="s">
+      <c r="C2025" s="3" t="s">
         <v>8366</v>
       </c>
-      <c r="D2025" s="6" t="s">
+      <c r="D2025" s="3" t="s">
         <v>8357</v>
       </c>
-      <c r="F2025" s="6" t="s">
+      <c r="F2025" s="3" t="s">
         <v>8361</v>
       </c>
-      <c r="G2025" s="6" t="s">
+      <c r="G2025" s="3" t="s">
         <v>8362</v>
       </c>
-      <c r="H2025" s="6" t="s">
+      <c r="H2025" s="3" t="s">
         <v>8367</v>
       </c>
-      <c r="I2025" s="6" t="s">
+      <c r="I2025" s="3" t="s">
         <v>8379</v>
       </c>
     </row>
-    <row r="2026" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2026" s="6" t="s">
+    <row r="2026" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2026" s="3" t="s">
         <v>8368</v>
       </c>
-      <c r="B2026" s="5">
+      <c r="B2026" s="4">
         <v>96002575</v>
       </c>
-      <c r="C2026" s="6" t="s">
+      <c r="C2026" s="3" t="s">
         <v>8369</v>
       </c>
-      <c r="D2026" s="6" t="s">
+      <c r="D2026" s="3" t="s">
         <v>8357</v>
       </c>
-      <c r="F2026" s="6" t="s">
+      <c r="F2026" s="3" t="s">
         <v>8361</v>
       </c>
-      <c r="G2026" s="6" t="s">
+      <c r="G2026" s="3" t="s">
         <v>8362</v>
       </c>
-      <c r="H2026" s="6" t="s">
+      <c r="H2026" s="3" t="s">
         <v>8381</v>
       </c>
-      <c r="I2026" s="20" t="s">
+      <c r="I2026" s="8" t="s">
         <v>8380</v>
       </c>
     </row>
-    <row r="2027" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2027" s="6" t="s">
+    <row r="2027" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2027" s="3" t="s">
         <v>8382</v>
       </c>
-      <c r="B2027" s="5">
+      <c r="B2027" s="4">
         <v>89672698</v>
       </c>
-      <c r="C2027" s="6" t="s">
+      <c r="C2027" s="3" t="s">
         <v>8383</v>
       </c>
-      <c r="D2027" s="6" t="s">
+      <c r="D2027" s="3" t="s">
         <v>8373</v>
       </c>
-      <c r="F2027" s="6" t="s">
+      <c r="F2027" s="3" t="s">
         <v>8384</v>
       </c>
-      <c r="G2027" s="6" t="s">
+      <c r="G2027" s="3" t="s">
         <v>8403</v>
       </c>
-      <c r="H2027" s="22" t="s">
+      <c r="H2027" s="13" t="s">
         <v>8413</v>
       </c>
-      <c r="I2027" s="20" t="s">
+      <c r="I2027" s="8" t="s">
         <v>8404</v>
       </c>
     </row>
-    <row r="2028" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2028" s="6" t="s">
+    <row r="2028" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2028" s="3" t="s">
         <v>8386</v>
       </c>
-      <c r="B2028" s="5">
+      <c r="B2028" s="4">
         <v>55794222</v>
       </c>
-      <c r="C2028" s="6" t="s">
+      <c r="C2028" s="3" t="s">
         <v>8387</v>
       </c>
-      <c r="D2028" s="6" t="s">
+      <c r="D2028" s="3" t="s">
         <v>8374</v>
       </c>
-      <c r="F2028" s="6" t="s">
+      <c r="F2028" s="3" t="s">
         <v>8384</v>
       </c>
-      <c r="G2028" s="6" t="s">
+      <c r="G2028" s="3" t="s">
         <v>8385</v>
       </c>
-      <c r="H2028" s="6" t="s">
+      <c r="H2028" s="3" t="s">
         <v>8411</v>
       </c>
-      <c r="I2028" s="20" t="s">
+      <c r="I2028" s="8" t="s">
         <v>8410</v>
       </c>
     </row>
-    <row r="2029" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2029" s="6" t="s">
+    <row r="2029" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2029" s="3" t="s">
         <v>8388</v>
       </c>
-      <c r="B2029" s="5">
+      <c r="B2029" s="4">
         <v>27774061</v>
       </c>
-      <c r="C2029" s="6" t="s">
+      <c r="C2029" s="3" t="s">
         <v>8370</v>
       </c>
-      <c r="D2029" s="6" t="s">
+      <c r="D2029" s="3" t="s">
         <v>8374</v>
       </c>
-      <c r="F2029" s="6" t="s">
+      <c r="F2029" s="3" t="s">
         <v>8384</v>
       </c>
-      <c r="G2029" s="6" t="s">
+      <c r="G2029" s="3" t="s">
         <v>8385</v>
       </c>
-      <c r="H2029" s="6" t="s">
+      <c r="H2029" s="3" t="s">
         <v>8389</v>
       </c>
-      <c r="I2029" s="20" t="s">
+      <c r="I2029" s="8" t="s">
         <v>8409</v>
       </c>
     </row>
-    <row r="2030" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2030" s="6" t="s">
+    <row r="2030" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2030" s="3" t="s">
         <v>8390</v>
       </c>
-      <c r="B2030" s="5">
+      <c r="B2030" s="4">
         <v>66652410</v>
       </c>
-      <c r="C2030" s="6" t="s">
+      <c r="C2030" s="3" t="s">
         <v>8371</v>
       </c>
-      <c r="D2030" s="6" t="s">
+      <c r="D2030" s="3" t="s">
         <v>8374</v>
       </c>
-      <c r="F2030" s="6" t="s">
+      <c r="F2030" s="3" t="s">
         <v>8384</v>
       </c>
-      <c r="G2030" s="6" t="s">
+      <c r="G2030" s="3" t="s">
         <v>8385</v>
       </c>
-      <c r="H2030" s="6" t="s">
+      <c r="H2030" s="3" t="s">
         <v>8391</v>
       </c>
-      <c r="I2030" s="20" t="s">
+      <c r="I2030" s="8" t="s">
         <v>8408</v>
       </c>
     </row>
-    <row r="2031" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2031" s="6" t="s">
+    <row r="2031" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2031" s="3" t="s">
         <v>8392</v>
       </c>
-      <c r="B2031" s="5">
+      <c r="B2031" s="4">
         <v>25171389</v>
       </c>
-      <c r="C2031" s="6" t="s">
+      <c r="C2031" s="3" t="s">
         <v>8393</v>
       </c>
-      <c r="D2031" s="6" t="s">
+      <c r="D2031" s="3" t="s">
         <v>8374</v>
       </c>
-      <c r="F2031" s="6" t="s">
+      <c r="F2031" s="3" t="s">
         <v>8384</v>
       </c>
-      <c r="G2031" s="6" t="s">
+      <c r="G2031" s="3" t="s">
         <v>8385</v>
       </c>
-      <c r="H2031" s="6" t="s">
+      <c r="H2031" s="3" t="s">
         <v>8394</v>
       </c>
-      <c r="I2031" s="20" t="s">
+      <c r="I2031" s="8" t="s">
         <v>8407</v>
       </c>
     </row>
-    <row r="2032" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2032" s="6" t="s">
+    <row r="2032" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2032" s="3" t="s">
         <v>8395</v>
       </c>
-      <c r="B2032" s="5">
+      <c r="B2032" s="4">
         <v>55731769</v>
       </c>
-      <c r="C2032" s="6" t="s">
+      <c r="C2032" s="3" t="s">
         <v>8396</v>
       </c>
-      <c r="D2032" s="6" t="s">
+      <c r="D2032" s="3" t="s">
         <v>8374</v>
       </c>
-      <c r="F2032" s="6" t="s">
+      <c r="F2032" s="3" t="s">
         <v>8384</v>
       </c>
-      <c r="G2032" s="6" t="s">
+      <c r="G2032" s="3" t="s">
         <v>8385</v>
       </c>
-      <c r="H2032" s="6" t="s">
+      <c r="H2032" s="3" t="s">
         <v>8397</v>
       </c>
-      <c r="I2032" s="20" t="s">
+      <c r="I2032" s="8" t="s">
         <v>8406</v>
       </c>
     </row>
-    <row r="2033" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2033" s="6" t="s">
+    <row r="2033" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2033" s="3" t="s">
         <v>8398</v>
       </c>
-      <c r="B2033" s="5">
+      <c r="B2033" s="4">
         <v>16444732</v>
       </c>
-      <c r="C2033" s="6" t="s">
+      <c r="C2033" s="3" t="s">
         <v>8399</v>
       </c>
-      <c r="D2033" s="6" t="s">
+      <c r="D2033" s="3" t="s">
         <v>8374</v>
       </c>
-      <c r="F2033" s="6" t="s">
+      <c r="F2033" s="3" t="s">
         <v>8384</v>
       </c>
-      <c r="G2033" s="6" t="s">
+      <c r="G2033" s="3" t="s">
         <v>8385</v>
       </c>
-      <c r="H2033" s="6" t="s">
+      <c r="H2033" s="3" t="s">
         <v>8400</v>
       </c>
-      <c r="I2033" s="20" t="s">
+      <c r="I2033" s="8" t="s">
         <v>8412</v>
       </c>
     </row>
-    <row r="2034" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2034" s="6" t="s">
+    <row r="2034" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2034" s="3" t="s">
         <v>8401</v>
       </c>
-      <c r="B2034" s="5">
+      <c r="B2034" s="4">
         <v>94025314</v>
       </c>
-      <c r="C2034" s="6" t="s">
+      <c r="C2034" s="3" t="s">
         <v>8372</v>
       </c>
-      <c r="D2034" s="6" t="s">
+      <c r="D2034" s="3" t="s">
         <v>8374</v>
       </c>
-      <c r="F2034" s="6" t="s">
+      <c r="F2034" s="3" t="s">
         <v>8384</v>
       </c>
-      <c r="G2034" s="6" t="s">
+      <c r="G2034" s="3" t="s">
         <v>8385</v>
       </c>
-      <c r="H2034" s="6" t="s">
+      <c r="H2034" s="3" t="s">
         <v>8402</v>
       </c>
-      <c r="I2034" s="20" t="s">
+      <c r="I2034" s="8" t="s">
         <v>8405</v>
       </c>
     </row>
-    <row r="2035" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2035" s="6" t="s">
+    <row r="2035" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2035" s="3" t="s">
         <v>8418</v>
       </c>
-      <c r="B2035" s="5">
+      <c r="B2035" s="4">
         <v>35928595</v>
       </c>
-      <c r="C2035" s="6" t="s">
+      <c r="C2035" s="3" t="s">
         <v>8419</v>
       </c>
-      <c r="D2035" s="6" t="s">
+      <c r="D2035" s="3" t="s">
         <v>8420</v>
       </c>
-      <c r="F2035" s="6" t="s">
+      <c r="F2035" s="3" t="s">
         <v>8421</v>
       </c>
-      <c r="G2035" s="6" t="s">
+      <c r="G2035" s="3" t="s">
         <v>8422</v>
       </c>
-      <c r="H2035" s="6" t="s">
+      <c r="H2035" s="3" t="s">
         <v>8423</v>
       </c>
-      <c r="I2035" s="20" t="s">
+      <c r="I2035" s="8" t="s">
         <v>8424</v>
       </c>
     </row>
-    <row r="2036" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2036" s="6" t="s">
+    <row r="2036" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2036" s="3" t="s">
         <v>8425</v>
       </c>
-      <c r="B2036" s="5">
+      <c r="B2036" s="4">
         <v>57132939</v>
       </c>
-      <c r="C2036" s="6" t="s">
+      <c r="C2036" s="3" t="s">
         <v>8426</v>
       </c>
-      <c r="D2036" s="6" t="s">
+      <c r="D2036" s="3" t="s">
         <v>8420</v>
       </c>
-      <c r="F2036" s="6" t="s">
+      <c r="F2036" s="3" t="s">
         <v>8421</v>
       </c>
-      <c r="G2036" s="6" t="s">
+      <c r="G2036" s="3" t="s">
         <v>8422</v>
       </c>
-      <c r="H2036" s="6" t="s">
+      <c r="H2036" s="3" t="s">
         <v>8427</v>
       </c>
-      <c r="I2036" s="20" t="s">
+      <c r="I2036" s="8" t="s">
         <v>8428</v>
       </c>
     </row>
-    <row r="2037" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2037" s="6" t="s">
+    <row r="2037" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2037" s="3" t="s">
         <v>8429</v>
       </c>
-      <c r="B2037" s="5">
+      <c r="B2037" s="4">
         <v>28112723</v>
       </c>
-      <c r="C2037" s="6" t="s">
+      <c r="C2037" s="3" t="s">
         <v>8430</v>
       </c>
-      <c r="D2037" s="6" t="s">
+      <c r="D2037" s="3" t="s">
         <v>8420</v>
       </c>
-      <c r="F2037" s="6" t="s">
+      <c r="F2037" s="3" t="s">
         <v>8421</v>
       </c>
-      <c r="G2037" s="6" t="s">
+      <c r="G2037" s="3" t="s">
         <v>8431</v>
       </c>
-      <c r="H2037" s="6" t="s">
+      <c r="H2037" s="3" t="s">
         <v>8432</v>
       </c>
-      <c r="I2037" s="20" t="s">
+      <c r="I2037" s="8" t="s">
         <v>8433</v>
       </c>
     </row>
-    <row r="2038" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2038" s="6" t="s">
+    <row r="2038" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2038" s="3" t="s">
         <v>8434</v>
       </c>
-      <c r="B2038" s="5">
+      <c r="B2038" s="4">
         <v>90784186</v>
       </c>
-      <c r="C2038" s="6" t="s">
+      <c r="C2038" s="3" t="s">
         <v>8435</v>
       </c>
-      <c r="D2038" s="6" t="s">
+      <c r="D2038" s="3" t="s">
         <v>8420</v>
       </c>
-      <c r="F2038" s="6" t="s">
+      <c r="F2038" s="3" t="s">
         <v>8421</v>
       </c>
-      <c r="G2038" s="6" t="s">
+      <c r="G2038" s="3" t="s">
         <v>8422</v>
       </c>
-      <c r="H2038" s="6" t="s">
+      <c r="H2038" s="3" t="s">
         <v>8436</v>
       </c>
-      <c r="I2038" s="20" t="s">
+      <c r="I2038" s="8" t="s">
         <v>8437</v>
       </c>
     </row>
-    <row r="2039" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2039" s="6" t="s">
+    <row r="2039" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2039" s="3" t="s">
         <v>8438</v>
       </c>
-      <c r="B2039" s="5">
+      <c r="B2039" s="4">
         <v>28877776</v>
       </c>
-      <c r="C2039" s="6" t="s">
+      <c r="C2039" s="3" t="s">
         <v>8439</v>
       </c>
-      <c r="D2039" s="6" t="s">
+      <c r="D2039" s="3" t="s">
         <v>8420</v>
       </c>
-      <c r="F2039" s="6" t="s">
+      <c r="F2039" s="3" t="s">
         <v>8421</v>
       </c>
-      <c r="G2039" s="6" t="s">
+      <c r="G2039" s="3" t="s">
         <v>8422</v>
       </c>
-      <c r="H2039" s="6" t="s">
+      <c r="H2039" s="3" t="s">
         <v>8440</v>
       </c>
-      <c r="I2039" s="20"/>
-    </row>
-    <row r="2040" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2040" s="6" t="s">
+      <c r="I2039" s="8"/>
+    </row>
+    <row r="2040" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2040" s="3" t="s">
         <v>8441</v>
       </c>
-      <c r="B2040" s="5">
+      <c r="B2040" s="4">
         <v>16541523</v>
       </c>
-      <c r="C2040" s="6" t="s">
+      <c r="C2040" s="3" t="s">
         <v>8442</v>
       </c>
-      <c r="D2040" s="6" t="s">
+      <c r="D2040" s="3" t="s">
         <v>8420</v>
       </c>
-      <c r="F2040" s="6" t="s">
+      <c r="F2040" s="3" t="s">
         <v>8421</v>
       </c>
-      <c r="G2040" s="6" t="s">
+      <c r="G2040" s="3" t="s">
         <v>8422</v>
       </c>
-      <c r="H2040" s="6" t="s">
+      <c r="H2040" s="3" t="s">
         <v>8443</v>
       </c>
-      <c r="I2040" s="20" t="s">
+      <c r="I2040" s="8" t="s">
         <v>8437</v>
       </c>
     </row>
-    <row r="2041" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2041" s="6" t="s">
+    <row r="2041" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2041" s="3" t="s">
         <v>8444</v>
       </c>
-      <c r="B2041" s="5">
+      <c r="B2041" s="4">
         <v>12733681</v>
       </c>
-      <c r="C2041" s="6" t="s">
+      <c r="C2041" s="3" t="s">
         <v>8445</v>
       </c>
-      <c r="D2041" s="6" t="s">
+      <c r="D2041" s="3" t="s">
         <v>8420</v>
       </c>
-      <c r="F2041" s="6" t="s">
+      <c r="F2041" s="3" t="s">
         <v>8421</v>
       </c>
-      <c r="G2041" s="6" t="s">
+      <c r="G2041" s="3" t="s">
         <v>8422</v>
       </c>
-      <c r="H2041" s="6" t="s">
+      <c r="H2041" s="3" t="s">
         <v>8446</v>
       </c>
-      <c r="I2041" s="20" t="s">
+      <c r="I2041" s="8" t="s">
         <v>8447</v>
       </c>
     </row>
-    <row r="2042" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2042" s="6" t="s">
+    <row r="2042" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2042" s="3" t="s">
         <v>8448</v>
       </c>
-      <c r="B2042" s="5">
+      <c r="B2042" s="4">
         <v>34783798</v>
       </c>
-      <c r="C2042" s="6" t="s">
+      <c r="C2042" s="3" t="s">
         <v>8449</v>
       </c>
-      <c r="D2042" s="6" t="s">
+      <c r="D2042" s="3" t="s">
         <v>8420</v>
       </c>
-      <c r="F2042" s="6" t="s">
+      <c r="F2042" s="3" t="s">
         <v>8421</v>
       </c>
-      <c r="G2042" s="6" t="s">
+      <c r="G2042" s="3" t="s">
         <v>8422</v>
       </c>
-      <c r="H2042" s="6" t="s">
+      <c r="H2042" s="3" t="s">
         <v>8450</v>
       </c>
-      <c r="I2042" s="20"/>
-    </row>
-    <row r="2043" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2043" s="6" t="s">
+      <c r="I2042" s="8"/>
+    </row>
+    <row r="2043" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2043" s="3" t="s">
         <v>8457</v>
       </c>
-      <c r="B2043" s="5">
+      <c r="B2043" s="4">
         <v>54503893</v>
       </c>
-      <c r="C2043" s="6" t="s">
+      <c r="C2043" s="3" t="s">
         <v>8458</v>
       </c>
-      <c r="D2043" s="6" t="s">
+      <c r="D2043" s="3" t="s">
         <v>8459</v>
       </c>
-      <c r="F2043" s="6" t="s">
+      <c r="F2043" s="3" t="s">
         <v>8460</v>
       </c>
-      <c r="G2043" s="6" t="s">
+      <c r="G2043" s="3" t="s">
         <v>8461</v>
       </c>
-      <c r="H2043" s="6" t="s">
+      <c r="H2043" s="3" t="s">
         <v>8462</v>
       </c>
-      <c r="I2043" s="20" t="s">
+      <c r="I2043" s="8" t="s">
         <v>8451</v>
       </c>
     </row>
-    <row r="2044" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2044" s="6" t="s">
+    <row r="2044" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2044" s="3" t="s">
         <v>8463</v>
       </c>
-      <c r="B2044" s="5">
+      <c r="B2044" s="4">
         <v>13004319</v>
       </c>
-      <c r="C2044" s="6" t="s">
+      <c r="C2044" s="3" t="s">
         <v>8464</v>
       </c>
-      <c r="D2044" s="6" t="s">
+      <c r="D2044" s="3" t="s">
         <v>8465</v>
       </c>
-      <c r="F2044" s="6" t="s">
+      <c r="F2044" s="3" t="s">
         <v>8460</v>
       </c>
-      <c r="G2044" s="6" t="s">
+      <c r="G2044" s="3" t="s">
         <v>8461</v>
       </c>
-      <c r="H2044" s="6" t="s">
+      <c r="H2044" s="3" t="s">
         <v>8466</v>
       </c>
-      <c r="I2044" s="20" t="s">
+      <c r="I2044" s="8" t="s">
         <v>8452</v>
       </c>
     </row>
-    <row r="2045" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2045" s="6" t="s">
+    <row r="2045" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2045" s="3" t="s">
         <v>8467</v>
       </c>
-      <c r="B2045" s="5">
+      <c r="B2045" s="4">
         <v>35892013</v>
       </c>
-      <c r="C2045" s="6" t="s">
+      <c r="C2045" s="3" t="s">
         <v>8468</v>
       </c>
-      <c r="D2045" s="6" t="s">
+      <c r="D2045" s="3" t="s">
         <v>8469</v>
       </c>
-      <c r="F2045" s="6" t="s">
+      <c r="F2045" s="3" t="s">
         <v>8460</v>
       </c>
-      <c r="G2045" s="6" t="s">
+      <c r="G2045" s="3" t="s">
         <v>8461</v>
       </c>
-      <c r="H2045" s="6" t="s">
+      <c r="H2045" s="3" t="s">
         <v>8470</v>
       </c>
-      <c r="I2045" s="20" t="s">
+      <c r="I2045" s="8" t="s">
         <v>8453</v>
       </c>
     </row>
-    <row r="2046" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2046" s="6" t="s">
+    <row r="2046" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2046" s="3" t="s">
         <v>8471</v>
       </c>
-      <c r="B2046" s="5">
+      <c r="B2046" s="4">
         <v>54138621</v>
       </c>
-      <c r="C2046" s="6" t="s">
+      <c r="C2046" s="3" t="s">
         <v>8472</v>
       </c>
-      <c r="D2046" s="6" t="s">
+      <c r="D2046" s="3" t="s">
         <v>8465</v>
       </c>
-      <c r="F2046" s="6" t="s">
+      <c r="F2046" s="3" t="s">
         <v>8460</v>
       </c>
-      <c r="G2046" s="6" t="s">
+      <c r="G2046" s="3" t="s">
         <v>8461</v>
       </c>
-      <c r="H2046" s="6" t="s">
+      <c r="H2046" s="3" t="s">
         <v>8473</v>
       </c>
-      <c r="I2046" s="20" t="s">
+      <c r="I2046" s="8" t="s">
         <v>8454</v>
       </c>
     </row>
-    <row r="2047" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2047" s="6" t="s">
+    <row r="2047" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2047" s="3" t="s">
         <v>8474</v>
       </c>
-      <c r="B2047" s="5">
+      <c r="B2047" s="4">
         <v>96770218</v>
       </c>
-      <c r="C2047" s="6" t="s">
+      <c r="C2047" s="3" t="s">
         <v>8475</v>
       </c>
-      <c r="D2047" s="6" t="s">
+      <c r="D2047" s="3" t="s">
         <v>8465</v>
       </c>
-      <c r="F2047" s="6" t="s">
+      <c r="F2047" s="3" t="s">
         <v>8460</v>
       </c>
-      <c r="G2047" s="6" t="s">
+      <c r="G2047" s="3" t="s">
         <v>8461</v>
       </c>
-      <c r="H2047" s="6" t="s">
+      <c r="H2047" s="3" t="s">
         <v>8476</v>
       </c>
-      <c r="I2047" s="20" t="s">
+      <c r="I2047" s="8" t="s">
         <v>8455</v>
       </c>
     </row>
-    <row r="2048" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2048" s="6" t="s">
+    <row r="2048" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2048" s="3" t="s">
         <v>8477</v>
       </c>
-      <c r="B2048" s="5">
+      <c r="B2048" s="4">
         <v>79962796</v>
       </c>
-      <c r="C2048" s="6" t="s">
+      <c r="C2048" s="3" t="s">
         <v>8478</v>
       </c>
-      <c r="D2048" s="6" t="s">
+      <c r="D2048" s="3" t="s">
         <v>8465</v>
       </c>
-      <c r="F2048" s="6" t="s">
+      <c r="F2048" s="3" t="s">
         <v>8460</v>
       </c>
-      <c r="G2048" s="6" t="s">
+      <c r="G2048" s="3" t="s">
         <v>8461</v>
       </c>
-      <c r="H2048" s="6" t="s">
+      <c r="H2048" s="3" t="s">
         <v>8479</v>
       </c>
-      <c r="I2048" s="20" t="s">
+      <c r="I2048" s="8" t="s">
         <v>8456</v>
       </c>
     </row>
-    <row r="2049" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2049" s="6" t="s">
+    <row r="2049" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2049" s="3" t="s">
         <v>8480</v>
       </c>
-      <c r="B2049" s="5">
+      <c r="B2049" s="4">
         <v>54398652</v>
       </c>
-      <c r="C2049" s="6" t="s">
+      <c r="C2049" s="3" t="s">
         <v>8481</v>
       </c>
-      <c r="D2049" s="6" t="s">
+      <c r="D2049" s="3" t="s">
         <v>8482</v>
       </c>
-      <c r="F2049" s="6" t="s">
+      <c r="F2049" s="3" t="s">
         <v>8460</v>
       </c>
-      <c r="G2049" s="6" t="s">
+      <c r="G2049" s="3" t="s">
         <v>8461</v>
       </c>
-      <c r="H2049" s="6" t="s">
+      <c r="H2049" s="3" t="s">
         <v>8483</v>
       </c>
-      <c r="I2049" s="20" t="s">
+      <c r="I2049" s="8" t="s">
         <v>8454</v>
       </c>
     </row>
@@ -72215,493 +72128,493 @@
         <v>8486</v>
       </c>
     </row>
-    <row r="2051" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2051" s="6" t="s">
+    <row r="2051" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2051" s="3" t="s">
         <v>8488</v>
       </c>
-      <c r="B2051" s="5">
+      <c r="B2051" s="4">
         <v>79838241</v>
       </c>
-      <c r="C2051" s="6" t="s">
+      <c r="C2051" s="3" t="s">
         <v>8489</v>
       </c>
-      <c r="D2051" s="6" t="s">
+      <c r="D2051" s="3" t="s">
         <v>8490</v>
       </c>
-      <c r="F2051" s="6" t="s">
+      <c r="F2051" s="3" t="s">
         <v>8491</v>
       </c>
-      <c r="G2051" s="6" t="s">
+      <c r="G2051" s="3" t="s">
         <v>8492</v>
       </c>
-      <c r="I2051" s="20"/>
-    </row>
-    <row r="2052" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2052" s="6" t="s">
+      <c r="I2051" s="8"/>
+    </row>
+    <row r="2052" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2052" s="3" t="s">
         <v>8493</v>
       </c>
-      <c r="B2052" s="5">
+      <c r="B2052" s="4">
         <v>24926184</v>
       </c>
-      <c r="C2052" s="6" t="s">
+      <c r="C2052" s="3" t="s">
         <v>8494</v>
       </c>
-      <c r="D2052" s="6" t="s">
+      <c r="D2052" s="3" t="s">
         <v>8490</v>
       </c>
-      <c r="F2052" s="6" t="s">
+      <c r="F2052" s="3" t="s">
         <v>8491</v>
       </c>
-      <c r="G2052" s="6" t="s">
+      <c r="G2052" s="3" t="s">
         <v>8492</v>
       </c>
-      <c r="H2052" s="6" t="s">
+      <c r="H2052" s="3" t="s">
         <v>8495</v>
       </c>
-      <c r="I2052" s="20" t="s">
+      <c r="I2052" s="8" t="s">
         <v>8496</v>
       </c>
     </row>
-    <row r="2053" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2053" s="6" t="s">
+    <row r="2053" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2053" s="3" t="s">
         <v>8497</v>
       </c>
-      <c r="B2053" s="5">
+      <c r="B2053" s="4">
         <v>93369894</v>
       </c>
-      <c r="C2053" s="6" t="s">
+      <c r="C2053" s="3" t="s">
         <v>8498</v>
       </c>
-      <c r="D2053" s="6" t="s">
+      <c r="D2053" s="3" t="s">
         <v>8490</v>
       </c>
-      <c r="F2053" s="6" t="s">
+      <c r="F2053" s="3" t="s">
         <v>8491</v>
       </c>
-      <c r="G2053" s="6" t="s">
+      <c r="G2053" s="3" t="s">
         <v>8492</v>
       </c>
-      <c r="I2053" s="20"/>
-    </row>
-    <row r="2054" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2054" s="6" t="s">
+      <c r="I2053" s="8"/>
+    </row>
+    <row r="2054" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2054" s="3" t="s">
         <v>8499</v>
       </c>
-      <c r="B2054" s="5">
+      <c r="B2054" s="4">
         <v>29166887</v>
       </c>
-      <c r="C2054" s="6" t="s">
+      <c r="C2054" s="3" t="s">
         <v>8500</v>
       </c>
-      <c r="D2054" s="6" t="s">
+      <c r="D2054" s="3" t="s">
         <v>8490</v>
       </c>
-      <c r="F2054" s="6" t="s">
+      <c r="F2054" s="3" t="s">
         <v>8491</v>
       </c>
-      <c r="G2054" s="6" t="s">
+      <c r="G2054" s="3" t="s">
         <v>8492</v>
       </c>
-      <c r="I2054" s="20"/>
-    </row>
-    <row r="2055" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2055" s="6" t="s">
+      <c r="I2054" s="8"/>
+    </row>
+    <row r="2055" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2055" s="3" t="s">
         <v>8501</v>
       </c>
-      <c r="B2055" s="5">
+      <c r="B2055" s="4">
         <v>54014332</v>
       </c>
-      <c r="C2055" s="6" t="s">
+      <c r="C2055" s="3" t="s">
         <v>8502</v>
       </c>
-      <c r="D2055" s="6" t="s">
+      <c r="D2055" s="3" t="s">
         <v>8490</v>
       </c>
-      <c r="F2055" s="6" t="s">
+      <c r="F2055" s="3" t="s">
         <v>8491</v>
       </c>
-      <c r="G2055" s="6" t="s">
+      <c r="G2055" s="3" t="s">
         <v>8492</v>
       </c>
-      <c r="H2055" s="6" t="s">
+      <c r="H2055" s="3" t="s">
         <v>8503</v>
       </c>
-      <c r="I2055" s="20" t="s">
+      <c r="I2055" s="8" t="s">
         <v>8504</v>
       </c>
     </row>
-    <row r="2056" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2056" s="6" t="s">
+    <row r="2056" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2056" s="3" t="s">
         <v>8505</v>
       </c>
-      <c r="B2056" s="5">
+      <c r="B2056" s="4">
         <v>25089142</v>
       </c>
-      <c r="C2056" s="6" t="s">
+      <c r="C2056" s="3" t="s">
         <v>8506</v>
       </c>
-      <c r="D2056" s="6" t="s">
+      <c r="D2056" s="3" t="s">
         <v>8507</v>
       </c>
-      <c r="F2056" s="6" t="s">
+      <c r="F2056" s="3" t="s">
         <v>8491</v>
       </c>
-      <c r="G2056" s="6" t="s">
+      <c r="G2056" s="3" t="s">
         <v>8492</v>
       </c>
-      <c r="H2056" s="6" t="s">
+      <c r="H2056" s="3" t="s">
         <v>8508</v>
       </c>
-      <c r="I2056" s="20" t="s">
+      <c r="I2056" s="8" t="s">
         <v>8509</v>
       </c>
     </row>
-    <row r="2057" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2057" s="6" t="s">
+    <row r="2057" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2057" s="3" t="s">
         <v>8510</v>
       </c>
-      <c r="B2057" s="5">
+      <c r="B2057" s="4">
         <v>70634323</v>
       </c>
-      <c r="C2057" s="6" t="s">
+      <c r="C2057" s="3" t="s">
         <v>8511</v>
       </c>
-      <c r="D2057" s="6" t="s">
+      <c r="D2057" s="3" t="s">
         <v>8490</v>
       </c>
-      <c r="F2057" s="6" t="s">
+      <c r="F2057" s="3" t="s">
         <v>8491</v>
       </c>
-      <c r="G2057" s="6" t="s">
+      <c r="G2057" s="3" t="s">
         <v>8492</v>
       </c>
-      <c r="H2057" s="6" t="s">
+      <c r="H2057" s="3" t="s">
         <v>8512</v>
       </c>
-      <c r="I2057" s="20" t="s">
+      <c r="I2057" s="8" t="s">
         <v>8513</v>
       </c>
     </row>
-    <row r="2058" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2058" s="6" t="s">
+    <row r="2058" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2058" s="3" t="s">
         <v>8514</v>
       </c>
-      <c r="B2058" s="5">
+      <c r="B2058" s="4">
         <v>54726923</v>
       </c>
-      <c r="C2058" s="6" t="s">
+      <c r="C2058" s="3" t="s">
         <v>8515</v>
       </c>
-      <c r="D2058" s="6" t="s">
+      <c r="D2058" s="3" t="s">
         <v>8490</v>
       </c>
-      <c r="F2058" s="6" t="s">
+      <c r="F2058" s="3" t="s">
         <v>8491</v>
       </c>
-      <c r="G2058" s="6" t="s">
+      <c r="G2058" s="3" t="s">
         <v>8492</v>
       </c>
-      <c r="H2058" s="6" t="s">
+      <c r="H2058" s="3" t="s">
         <v>8516</v>
       </c>
-      <c r="I2058" s="20" t="s">
+      <c r="I2058" s="8" t="s">
         <v>8517</v>
       </c>
     </row>
-    <row r="2059" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2059" s="6" t="s">
+    <row r="2059" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2059" s="3" t="s">
         <v>8521</v>
       </c>
-      <c r="B2059" s="5">
+      <c r="B2059" s="4">
         <v>96799025</v>
       </c>
-      <c r="C2059" s="6" t="s">
+      <c r="C2059" s="3" t="s">
         <v>8522</v>
       </c>
-      <c r="D2059" s="6" t="s">
+      <c r="D2059" s="3" t="s">
         <v>8523</v>
       </c>
-      <c r="F2059" s="6" t="s">
+      <c r="F2059" s="3" t="s">
         <v>8524</v>
       </c>
-      <c r="G2059" s="6" t="s">
+      <c r="G2059" s="3" t="s">
         <v>8525</v>
       </c>
-      <c r="I2059" s="20"/>
-    </row>
-    <row r="2060" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2060" s="6" t="s">
+      <c r="I2059" s="8"/>
+    </row>
+    <row r="2060" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2060" s="3" t="s">
         <v>8526</v>
       </c>
-      <c r="B2060" s="5">
+      <c r="B2060" s="4">
         <v>82914313</v>
       </c>
-      <c r="C2060" s="6" t="s">
+      <c r="C2060" s="3" t="s">
         <v>8527</v>
       </c>
-      <c r="D2060" s="6" t="s">
+      <c r="D2060" s="3" t="s">
         <v>8523</v>
       </c>
-      <c r="F2060" s="6" t="s">
+      <c r="F2060" s="3" t="s">
         <v>8524</v>
       </c>
-      <c r="G2060" s="6" t="s">
+      <c r="G2060" s="3" t="s">
         <v>8525</v>
       </c>
-      <c r="H2060" s="6" t="s">
+      <c r="H2060" s="3" t="s">
         <v>8519</v>
       </c>
-      <c r="I2060" s="20" t="s">
+      <c r="I2060" s="8" t="s">
         <v>8520</v>
       </c>
     </row>
-    <row r="2061" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2061" s="6" t="s">
+    <row r="2061" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2061" s="3" t="s">
         <v>8528</v>
       </c>
-      <c r="B2061" s="5">
+      <c r="B2061" s="4">
         <v>28043986</v>
       </c>
-      <c r="C2061" s="6" t="s">
+      <c r="C2061" s="3" t="s">
         <v>8529</v>
       </c>
-      <c r="D2061" s="6" t="s">
+      <c r="D2061" s="3" t="s">
         <v>8523</v>
       </c>
-      <c r="F2061" s="6" t="s">
+      <c r="F2061" s="3" t="s">
         <v>8524</v>
       </c>
-      <c r="G2061" s="6" t="s">
+      <c r="G2061" s="3" t="s">
         <v>8525</v>
       </c>
-      <c r="H2061" s="6" t="s">
+      <c r="H2061" s="3" t="s">
         <v>8530</v>
       </c>
-      <c r="I2061" s="20" t="s">
+      <c r="I2061" s="8" t="s">
         <v>8531</v>
       </c>
     </row>
-    <row r="2062" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2062" s="6" t="s">
+    <row r="2062" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2062" s="3" t="s">
         <v>8532</v>
       </c>
-      <c r="B2062" s="5">
+      <c r="B2062" s="4">
         <v>89396770</v>
       </c>
-      <c r="C2062" s="6" t="s">
+      <c r="C2062" s="3" t="s">
         <v>8533</v>
       </c>
-      <c r="D2062" s="6" t="s">
+      <c r="D2062" s="3" t="s">
         <v>8523</v>
       </c>
-      <c r="F2062" s="6" t="s">
+      <c r="F2062" s="3" t="s">
         <v>8524</v>
       </c>
-      <c r="G2062" s="6" t="s">
+      <c r="G2062" s="3" t="s">
         <v>8525</v>
       </c>
-      <c r="H2062" s="6" t="s">
+      <c r="H2062" s="3" t="s">
         <v>8534</v>
       </c>
-      <c r="I2062" s="20" t="s">
+      <c r="I2062" s="8" t="s">
         <v>8535</v>
       </c>
     </row>
-    <row r="2063" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2063" s="6" t="s">
+    <row r="2063" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2063" s="3" t="s">
         <v>8536</v>
       </c>
-      <c r="B2063" s="5" t="s">
+      <c r="B2063" s="4" t="s">
         <v>8518</v>
       </c>
-      <c r="C2063" s="6" t="s">
+      <c r="C2063" s="3" t="s">
         <v>8537</v>
       </c>
-      <c r="D2063" s="6" t="s">
+      <c r="D2063" s="3" t="s">
         <v>8538</v>
       </c>
-      <c r="F2063" s="6" t="s">
+      <c r="F2063" s="3" t="s">
         <v>8539</v>
       </c>
-      <c r="G2063" s="6" t="s">
+      <c r="G2063" s="3" t="s">
         <v>8540</v>
       </c>
-      <c r="I2063" s="20"/>
-    </row>
-    <row r="2064" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2064" s="6" t="s">
+      <c r="I2063" s="8"/>
+    </row>
+    <row r="2064" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2064" s="3" t="s">
         <v>8541</v>
       </c>
-      <c r="B2064" s="5">
+      <c r="B2064" s="4">
         <v>83483376</v>
       </c>
-      <c r="C2064" s="6" t="s">
+      <c r="C2064" s="3" t="s">
         <v>8542</v>
       </c>
-      <c r="D2064" s="6" t="s">
+      <c r="D2064" s="3" t="s">
         <v>8543</v>
       </c>
-      <c r="F2064" s="6" t="s">
+      <c r="F2064" s="3" t="s">
         <v>8544</v>
       </c>
-      <c r="G2064" s="6" t="s">
+      <c r="G2064" s="3" t="s">
         <v>8545</v>
       </c>
-      <c r="I2064" s="20"/>
-    </row>
-    <row r="2065" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2065" s="6" t="s">
+      <c r="I2064" s="8"/>
+    </row>
+    <row r="2065" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2065" s="3" t="s">
         <v>8546</v>
       </c>
-      <c r="B2065" s="5">
+      <c r="B2065" s="4">
         <v>28339685</v>
       </c>
-      <c r="C2065" s="6" t="s">
+      <c r="C2065" s="3" t="s">
         <v>8547</v>
       </c>
-      <c r="D2065" s="6" t="s">
+      <c r="D2065" s="3" t="s">
         <v>8543</v>
       </c>
-      <c r="F2065" s="6" t="s">
+      <c r="F2065" s="3" t="s">
         <v>8544</v>
       </c>
-      <c r="G2065" s="6" t="s">
+      <c r="G2065" s="3" t="s">
         <v>8545</v>
       </c>
-      <c r="H2065" s="6" t="s">
+      <c r="H2065" s="3" t="s">
         <v>8548</v>
       </c>
-      <c r="I2065" s="20" t="s">
+      <c r="I2065" s="8" t="s">
         <v>8549</v>
       </c>
     </row>
-    <row r="2066" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2066" s="6" t="s">
+    <row r="2066" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2066" s="3" t="s">
         <v>8550</v>
       </c>
-      <c r="B2066" s="5">
+      <c r="B2066" s="4">
         <v>59214274</v>
       </c>
-      <c r="C2066" s="6" t="s">
+      <c r="C2066" s="3" t="s">
         <v>8551</v>
       </c>
-      <c r="D2066" s="6" t="s">
+      <c r="D2066" s="3" t="s">
         <v>8543</v>
       </c>
-      <c r="F2066" s="6" t="s">
+      <c r="F2066" s="3" t="s">
         <v>8544</v>
       </c>
-      <c r="G2066" s="6" t="s">
+      <c r="G2066" s="3" t="s">
         <v>8545</v>
       </c>
-      <c r="H2066" s="6" t="s">
+      <c r="H2066" s="3" t="s">
         <v>8552</v>
       </c>
-      <c r="I2066" s="20" t="s">
+      <c r="I2066" s="8" t="s">
         <v>8553</v>
       </c>
     </row>
-    <row r="2067" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2067" s="6" t="s">
+    <row r="2067" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2067" s="3" t="s">
         <v>8554</v>
       </c>
-      <c r="B2067" s="5">
+      <c r="B2067" s="4">
         <v>53137700</v>
       </c>
-      <c r="C2067" s="6" t="s">
+      <c r="C2067" s="3" t="s">
         <v>8555</v>
       </c>
-      <c r="D2067" s="6" t="s">
+      <c r="D2067" s="3" t="s">
         <v>8543</v>
       </c>
-      <c r="F2067" s="6" t="s">
+      <c r="F2067" s="3" t="s">
         <v>8544</v>
       </c>
-      <c r="G2067" s="6" t="s">
+      <c r="G2067" s="3" t="s">
         <v>8545</v>
       </c>
-      <c r="H2067" s="6" t="s">
+      <c r="H2067" s="3" t="s">
         <v>8556</v>
       </c>
-      <c r="I2067" s="20" t="s">
+      <c r="I2067" s="8" t="s">
         <v>8557</v>
       </c>
     </row>
-    <row r="2068" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2068" s="6" t="s">
+    <row r="2068" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2068" s="3" t="s">
         <v>8558</v>
       </c>
-      <c r="B2068" s="5">
+      <c r="B2068" s="4">
         <v>84070747</v>
       </c>
-      <c r="C2068" s="6" t="s">
+      <c r="C2068" s="3" t="s">
         <v>8559</v>
       </c>
-      <c r="D2068" s="6" t="s">
+      <c r="D2068" s="3" t="s">
         <v>8523</v>
       </c>
-      <c r="F2068" s="6" t="s">
+      <c r="F2068" s="3" t="s">
         <v>8524</v>
       </c>
-      <c r="G2068" s="6" t="s">
+      <c r="G2068" s="3" t="s">
         <v>8525</v>
       </c>
-      <c r="H2068" s="6" t="s">
+      <c r="H2068" s="3" t="s">
         <v>8560</v>
       </c>
-      <c r="I2068" s="20" t="s">
+      <c r="I2068" s="8" t="s">
         <v>8561</v>
       </c>
     </row>
-    <row r="2069" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2069" s="6" t="s">
+    <row r="2069" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2069" s="3" t="s">
         <v>8562</v>
       </c>
-      <c r="B2069" s="5">
+      <c r="B2069" s="4">
         <v>54135526</v>
       </c>
-      <c r="C2069" s="6" t="s">
+      <c r="C2069" s="3" t="s">
         <v>8563</v>
       </c>
-      <c r="D2069" s="6" t="s">
+      <c r="D2069" s="3" t="s">
         <v>8523</v>
       </c>
-      <c r="F2069" s="6" t="s">
+      <c r="F2069" s="3" t="s">
         <v>8524</v>
       </c>
-      <c r="G2069" s="6" t="s">
+      <c r="G2069" s="3" t="s">
         <v>8525</v>
       </c>
-      <c r="H2069" s="6" t="s">
+      <c r="H2069" s="3" t="s">
         <v>8564</v>
       </c>
-      <c r="I2069" s="20" t="s">
+      <c r="I2069" s="8" t="s">
         <v>8565</v>
       </c>
     </row>
-    <row r="2070" spans="1:9" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2070" s="6" t="s">
+    <row r="2070" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2070" s="3" t="s">
         <v>8566</v>
       </c>
-      <c r="B2070" s="5">
+      <c r="B2070" s="4">
         <v>16766959</v>
       </c>
-      <c r="C2070" s="6" t="s">
+      <c r="C2070" s="3" t="s">
         <v>8567</v>
       </c>
-      <c r="D2070" s="6" t="s">
+      <c r="D2070" s="3" t="s">
         <v>8523</v>
       </c>
-      <c r="F2070" s="6" t="s">
+      <c r="F2070" s="3" t="s">
         <v>8524</v>
       </c>
-      <c r="G2070" s="6" t="s">
+      <c r="G2070" s="3" t="s">
         <v>8525</v>
       </c>
-      <c r="H2070" s="6" t="s">
+      <c r="H2070" s="3" t="s">
         <v>8568</v>
       </c>
-      <c r="I2070" s="20" t="s">
+      <c r="I2070" s="8" t="s">
         <v>8569</v>
       </c>
     </row>
@@ -73001,7 +72914,7 @@
       <c r="B2088" s="4">
         <v>81464351</v>
       </c>
-      <c r="C2088" s="3" t="s">
+      <c r="C2088" s="6" t="s">
         <v>8641</v>
       </c>
       <c r="D2088" s="3" t="s">
@@ -73018,7 +72931,7 @@
       <c r="B2089" s="4">
         <v>81464351</v>
       </c>
-      <c r="C2089" s="3" t="s">
+      <c r="C2089" s="6" t="s">
         <v>8642</v>
       </c>
       <c r="D2089" s="3" t="s">
@@ -73443,7 +73356,7 @@
       <c r="B2114" s="4">
         <v>70552666</v>
       </c>
-      <c r="C2114" s="3" t="s">
+      <c r="C2114" s="6" t="s">
         <v>8665</v>
       </c>
       <c r="D2114" s="3" t="s">
@@ -73460,7 +73373,7 @@
       <c r="B2115" s="4">
         <v>70552666</v>
       </c>
-      <c r="C2115" s="3" t="s">
+      <c r="C2115" s="6" t="s">
         <v>8666</v>
       </c>
       <c r="D2115" s="3" t="s">
@@ -73676,7 +73589,7 @@
       <c r="G2127" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H2127" s="13" t="s">
+      <c r="H2127" s="7" t="s">
         <v>8728</v>
       </c>
       <c r="I2127" s="3" t="s">
@@ -73702,7 +73615,7 @@
       <c r="G2128" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H2128" s="13" t="s">
+      <c r="H2128" s="7" t="s">
         <v>8736</v>
       </c>
       <c r="I2128" s="3" t="s">
@@ -73728,7 +73641,7 @@
       <c r="G2129" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H2129" s="13" t="s">
+      <c r="H2129" s="7" t="s">
         <v>8732</v>
       </c>
       <c r="I2129" s="3" t="s">
@@ -73754,7 +73667,7 @@
       <c r="G2130" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H2130" s="13" t="s">
+      <c r="H2130" s="7" t="s">
         <v>8730</v>
       </c>
       <c r="I2130" s="3" t="s">
@@ -73780,7 +73693,7 @@
       <c r="G2131" s="3" t="s">
         <v>3581</v>
       </c>
-      <c r="H2131" s="13" t="s">
+      <c r="H2131" s="7" t="s">
         <v>8734</v>
       </c>
       <c r="I2131" s="3" t="s">
@@ -74135,7 +74048,7 @@
       <c r="G2145" s="3" t="s">
         <v>8799</v>
       </c>
-      <c r="H2145" s="13" t="s">
+      <c r="H2145" s="7" t="s">
         <v>8806</v>
       </c>
     </row>
@@ -75118,7 +75031,7 @@
       <c r="I2188" s="3" t="s">
         <v>8953</v>
       </c>
-      <c r="J2188" s="21" t="s">
+      <c r="J2188" s="13" t="s">
         <v>8947</v>
       </c>
     </row>
@@ -75144,7 +75057,7 @@
       <c r="I2189" s="3" t="s">
         <v>8953</v>
       </c>
-      <c r="J2189" s="21" t="s">
+      <c r="J2189" s="13" t="s">
         <v>8947</v>
       </c>
     </row>

--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="4755" windowWidth="11055" windowHeight="4785"/>
+    <workbookView xWindow="-15" yWindow="4800" windowWidth="11055" windowHeight="4740"/>
   </bookViews>
   <sheets>
     <sheet name="順豐出口" sheetId="4" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12462" uniqueCount="8997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12522" uniqueCount="9025">
   <si>
     <t>麒安科技有限公司</t>
   </si>
@@ -31766,6 +31766,94 @@
   </si>
   <si>
     <t>119.05.23</t>
+  </si>
+  <si>
+    <t>華辰皮件有限公司</t>
+  </si>
+  <si>
+    <t>麥立得有限公司</t>
+  </si>
+  <si>
+    <t>七友科技股份有限公司</t>
+  </si>
+  <si>
+    <t>特通科技有限公司</t>
+  </si>
+  <si>
+    <t>萊凌科技股份有限公司</t>
+  </si>
+  <si>
+    <t>裕乘股份有限公司</t>
+  </si>
+  <si>
+    <t>毫米波科技股份有限公司</t>
+  </si>
+  <si>
+    <t>奧川科技有限公司</t>
+  </si>
+  <si>
+    <t>祥群興業有限公司</t>
+  </si>
+  <si>
+    <t>相求精工有限公司</t>
+  </si>
+  <si>
+    <t>正道工業股份有限公司</t>
+  </si>
+  <si>
+    <t>永傑數位科技有限公司</t>
+  </si>
+  <si>
+    <t>114業二09160</t>
+  </si>
+  <si>
+    <t>114業二09161</t>
+  </si>
+  <si>
+    <t>114業二09162</t>
+  </si>
+  <si>
+    <t>114業二09163</t>
+  </si>
+  <si>
+    <t>114業二09164</t>
+  </si>
+  <si>
+    <t>114業二09165</t>
+  </si>
+  <si>
+    <t>114業二09166</t>
+  </si>
+  <si>
+    <t>114業二09167</t>
+  </si>
+  <si>
+    <t>114業二09168</t>
+  </si>
+  <si>
+    <t>114業二09169</t>
+  </si>
+  <si>
+    <t>114業二09170</t>
+  </si>
+  <si>
+    <t>114業二09171</t>
+  </si>
+  <si>
+    <t>119.05.26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119.05.31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>118.05.26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114.05.29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -31904,7 +31992,37 @@
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -32243,7 +32361,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:J2196"/>
+  <dimension ref="A1:J2204"/>
   <sheetFormatPr defaultRowHeight="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="64" style="3" bestFit="1" customWidth="1"/>
@@ -75368,24 +75486,267 @@
         <v>8996</v>
       </c>
     </row>
-    <row r="2196" spans="2:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2196" s="3"/>
-      <c r="C2196" s="4"/>
+    <row r="2193" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2193" s="3" t="s">
+        <v>8997</v>
+      </c>
+      <c r="B2193" s="3">
+        <v>42986698</v>
+      </c>
+      <c r="C2193" s="3" t="s">
+        <v>9009</v>
+      </c>
+      <c r="D2193" s="3" t="s">
+        <v>9021</v>
+      </c>
+      <c r="F2193" s="3" t="s">
+        <v>9024</v>
+      </c>
+      <c r="G2193" s="3" t="s">
+        <v>8896</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2194" s="3" t="s">
+        <v>8998</v>
+      </c>
+      <c r="B2194" s="3">
+        <v>90704368</v>
+      </c>
+      <c r="C2194" s="3" t="s">
+        <v>9010</v>
+      </c>
+      <c r="D2194" s="3" t="s">
+        <v>9021</v>
+      </c>
+      <c r="F2194" s="3" t="s">
+        <v>9024</v>
+      </c>
+      <c r="G2194" s="3" t="s">
+        <v>8896</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2195" s="3" t="s">
+        <v>8999</v>
+      </c>
+      <c r="B2195" s="3">
+        <v>70603601</v>
+      </c>
+      <c r="C2195" s="3" t="s">
+        <v>9011</v>
+      </c>
+      <c r="D2195" s="3" t="s">
+        <v>9021</v>
+      </c>
+      <c r="F2195" s="3" t="s">
+        <v>9024</v>
+      </c>
+      <c r="G2195" s="3" t="s">
+        <v>8896</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2196" s="3" t="s">
+        <v>9000</v>
+      </c>
+      <c r="B2196" s="3">
+        <v>28648704</v>
+      </c>
+      <c r="C2196" s="3" t="s">
+        <v>9012</v>
+      </c>
+      <c r="D2196" s="3" t="s">
+        <v>9021</v>
+      </c>
+      <c r="F2196" s="3" t="s">
+        <v>9024</v>
+      </c>
+      <c r="G2196" s="3" t="s">
+        <v>8896</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2197" s="3" t="s">
+        <v>9001</v>
+      </c>
+      <c r="B2197" s="3">
+        <v>83465481</v>
+      </c>
+      <c r="C2197" s="3" t="s">
+        <v>9013</v>
+      </c>
+      <c r="D2197" s="3" t="s">
+        <v>9022</v>
+      </c>
+      <c r="F2197" s="3" t="s">
+        <v>9024</v>
+      </c>
+      <c r="G2197" s="3" t="s">
+        <v>8896</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2198" s="3" t="s">
+        <v>9002</v>
+      </c>
+      <c r="B2198" s="3">
+        <v>16682184</v>
+      </c>
+      <c r="C2198" s="3" t="s">
+        <v>9014</v>
+      </c>
+      <c r="D2198" s="3" t="s">
+        <v>9022</v>
+      </c>
+      <c r="F2198" s="3" t="s">
+        <v>9024</v>
+      </c>
+      <c r="G2198" s="3" t="s">
+        <v>8896</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2199" s="3" t="s">
+        <v>9003</v>
+      </c>
+      <c r="B2199" s="3">
+        <v>50984309</v>
+      </c>
+      <c r="C2199" s="3" t="s">
+        <v>9015</v>
+      </c>
+      <c r="D2199" s="3" t="s">
+        <v>9021</v>
+      </c>
+      <c r="F2199" s="3" t="s">
+        <v>9024</v>
+      </c>
+      <c r="G2199" s="3" t="s">
+        <v>8896</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2200" s="3" t="s">
+        <v>9004</v>
+      </c>
+      <c r="B2200" s="3">
+        <v>93581973</v>
+      </c>
+      <c r="C2200" s="3" t="s">
+        <v>9016</v>
+      </c>
+      <c r="D2200" s="3" t="s">
+        <v>9021</v>
+      </c>
+      <c r="F2200" s="3" t="s">
+        <v>9024</v>
+      </c>
+      <c r="G2200" s="3" t="s">
+        <v>8896</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2201" s="3" t="s">
+        <v>9005</v>
+      </c>
+      <c r="B2201" s="3">
+        <v>97208961</v>
+      </c>
+      <c r="C2201" s="3" t="s">
+        <v>9017</v>
+      </c>
+      <c r="D2201" s="3" t="s">
+        <v>9021</v>
+      </c>
+      <c r="F2201" s="3" t="s">
+        <v>9024</v>
+      </c>
+      <c r="G2201" s="3" t="s">
+        <v>8896</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2202" s="3" t="s">
+        <v>9006</v>
+      </c>
+      <c r="B2202" s="3">
+        <v>90403222</v>
+      </c>
+      <c r="C2202" s="3" t="s">
+        <v>9018</v>
+      </c>
+      <c r="D2202" s="3" t="s">
+        <v>9021</v>
+      </c>
+      <c r="F2202" s="3" t="s">
+        <v>9024</v>
+      </c>
+      <c r="G2202" s="3" t="s">
+        <v>8896</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2203" s="3" t="s">
+        <v>9007</v>
+      </c>
+      <c r="B2203" s="3">
+        <v>68193807</v>
+      </c>
+      <c r="C2203" s="3" t="s">
+        <v>9019</v>
+      </c>
+      <c r="D2203" s="3" t="s">
+        <v>9021</v>
+      </c>
+      <c r="F2203" s="3" t="s">
+        <v>9024</v>
+      </c>
+      <c r="G2203" s="3" t="s">
+        <v>8896</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2204" s="3" t="s">
+        <v>9008</v>
+      </c>
+      <c r="B2204" s="3">
+        <v>53620900</v>
+      </c>
+      <c r="C2204" s="3" t="s">
+        <v>9020</v>
+      </c>
+      <c r="D2204" s="3" t="s">
+        <v>9023</v>
+      </c>
+      <c r="F2204" s="3" t="s">
+        <v>9024</v>
+      </c>
+      <c r="G2204" s="3" t="s">
+        <v>8896</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J2182"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A2189 A2197:A1048576 B2196 A2193:A2195">
+  <conditionalFormatting sqref="A1:A2189 A2205:A1048576">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B2189 B2205:B1048576">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C2192 C2205:C1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2190">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B2189 B2197:B1048576 C2196 B2193:B2195">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  <conditionalFormatting sqref="B2193:B2204">
+    <cfRule type="duplicateValues" dxfId="2" priority="3" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C2195 C2197:C1048576 D2196">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2190">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="B2193:B2204">
+    <cfRule type="duplicateValues" dxfId="1" priority="1" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1110:G1120 G234:G594 G596:G623 G171:G232 G625:G1107 G2170 G2:G169">

--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62170C6-F04D-4358-9DE2-418D69B55331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CACD7A9-7F51-4812-8157-BC30FE0DCE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12665" uniqueCount="9079">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12709" uniqueCount="9101">
   <si>
     <t>麒安科技有限公司</t>
   </si>
@@ -32004,6 +32004,76 @@
   </si>
   <si>
     <t>167/曾小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>倢通科技股份有限公司</t>
+  </si>
+  <si>
+    <t>新廣業股份有限公司中科分公司</t>
+  </si>
+  <si>
+    <t>貝登堡國際股份有限公司</t>
+  </si>
+  <si>
+    <t>佳凌科技股份有限公司</t>
+  </si>
+  <si>
+    <t>蘊榮科技股份有限公司</t>
+  </si>
+  <si>
+    <t>聯鎰電子股份有限公司</t>
+  </si>
+  <si>
+    <t>華瑞功率電子股份有限公司</t>
+  </si>
+  <si>
+    <t>康聚醫學科技股份有限公司</t>
+  </si>
+  <si>
+    <t>114業二11233</t>
+  </si>
+  <si>
+    <t>114業二11234</t>
+  </si>
+  <si>
+    <t>114業二11235</t>
+  </si>
+  <si>
+    <t>114業二11236</t>
+  </si>
+  <si>
+    <t>114業二11237</t>
+  </si>
+  <si>
+    <t>114業二11238</t>
+  </si>
+  <si>
+    <t>114業二11239</t>
+  </si>
+  <si>
+    <t>114業二11240</t>
+  </si>
+  <si>
+    <t>119.07.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>117.07.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114.07.16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>綠色科技股份有限公司</t>
+  </si>
+  <si>
+    <t>114業二11242</t>
+  </si>
+  <si>
+    <t>119.07.15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -32152,7 +32222,37 @@
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -32544,7 +32644,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:N2231"/>
+  <dimension ref="A1:N2239"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21.9" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="79" style="3" customWidth="1"/>
@@ -76490,9 +76590,6 @@
       <c r="D2225" s="3" t="s">
         <v>9044</v>
       </c>
-      <c r="E2225" s="3" t="s">
-        <v>3131</v>
-      </c>
       <c r="F2225" s="3" t="s">
         <v>9052</v>
       </c>
@@ -76560,7 +76657,7 @@
         <v>9057</v>
       </c>
       <c r="D2228" s="3" t="s">
-        <v>9076</v>
+        <v>9098</v>
       </c>
       <c r="E2228" s="3" t="s">
         <v>3131</v>
@@ -76577,7 +76674,7 @@
         <v>9059</v>
       </c>
       <c r="D2229" s="3" t="s">
-        <v>9077</v>
+        <v>9099</v>
       </c>
       <c r="E2229" s="3" t="s">
         <v>3131</v>
@@ -76594,40 +76691,224 @@
         <v>9061</v>
       </c>
       <c r="D2230" s="3" t="s">
-        <v>9078</v>
+        <v>9100</v>
       </c>
       <c r="E2230" s="3" t="s">
         <v>3131</v>
       </c>
     </row>
-    <row r="2231" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2231" spans="1:9" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2231" s="3" t="s">
+        <v>9076</v>
+      </c>
+      <c r="B2231" s="4">
+        <v>80572199</v>
+      </c>
+      <c r="C2231" s="3" t="s">
+        <v>9084</v>
+      </c>
+      <c r="D2231" s="3" t="s">
+        <v>9092</v>
+      </c>
+      <c r="F2231" s="3" t="s">
+        <v>9094</v>
+      </c>
+      <c r="G2231" s="3" t="s">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:9" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2232" s="3" t="s">
+        <v>9077</v>
+      </c>
+      <c r="B2232" s="4">
+        <v>94163126</v>
+      </c>
+      <c r="C2232" s="3" t="s">
+        <v>9085</v>
+      </c>
+      <c r="D2232" s="3" t="s">
+        <v>9092</v>
+      </c>
+      <c r="F2232" s="3" t="s">
+        <v>9094</v>
+      </c>
+      <c r="G2232" s="3" t="s">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:9" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2233" s="3" t="s">
+        <v>9078</v>
+      </c>
+      <c r="B2233" s="4">
+        <v>84748403</v>
+      </c>
+      <c r="C2233" s="3" t="s">
+        <v>9086</v>
+      </c>
+      <c r="D2233" s="3" t="s">
+        <v>9093</v>
+      </c>
+      <c r="F2233" s="3" t="s">
+        <v>9094</v>
+      </c>
+      <c r="G2233" s="3" t="s">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:9" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2234" s="3" t="s">
+        <v>9079</v>
+      </c>
+      <c r="B2234" s="4">
+        <v>70848492</v>
+      </c>
+      <c r="C2234" s="3" t="s">
+        <v>9087</v>
+      </c>
+      <c r="D2234" s="3" t="s">
+        <v>9092</v>
+      </c>
+      <c r="F2234" s="3" t="s">
+        <v>9094</v>
+      </c>
+      <c r="G2234" s="3" t="s">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:9" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2235" s="3" t="s">
+        <v>9080</v>
+      </c>
+      <c r="B2235" s="4">
+        <v>16265929</v>
+      </c>
+      <c r="C2235" s="3" t="s">
+        <v>9088</v>
+      </c>
+      <c r="D2235" s="3" t="s">
+        <v>9092</v>
+      </c>
+      <c r="F2235" s="3" t="s">
+        <v>9094</v>
+      </c>
+      <c r="G2235" s="3" t="s">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:9" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2236" s="3" t="s">
+        <v>9081</v>
+      </c>
+      <c r="B2236" s="4">
+        <v>12831732</v>
+      </c>
+      <c r="C2236" s="3" t="s">
+        <v>9089</v>
+      </c>
+      <c r="D2236" s="3" t="s">
+        <v>9092</v>
+      </c>
+      <c r="F2236" s="3" t="s">
+        <v>9094</v>
+      </c>
+      <c r="G2236" s="3" t="s">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:9" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2237" s="3" t="s">
+        <v>9082</v>
+      </c>
+      <c r="B2237" s="4">
+        <v>53701712</v>
+      </c>
+      <c r="C2237" s="3" t="s">
+        <v>9090</v>
+      </c>
+      <c r="D2237" s="3" t="s">
+        <v>9092</v>
+      </c>
+      <c r="F2237" s="3" t="s">
+        <v>9094</v>
+      </c>
+      <c r="G2237" s="3" t="s">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:9" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2238" s="3" t="s">
+        <v>9083</v>
+      </c>
+      <c r="B2238" s="4">
+        <v>64861742</v>
+      </c>
+      <c r="C2238" s="3" t="s">
+        <v>9091</v>
+      </c>
+      <c r="D2238" s="3" t="s">
+        <v>9092</v>
+      </c>
+      <c r="F2238" s="3" t="s">
+        <v>9094</v>
+      </c>
+      <c r="G2238" s="3" t="s">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:9" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2239" s="3" t="s">
+        <v>9095</v>
+      </c>
+      <c r="B2239" s="4">
+        <v>80280685</v>
+      </c>
+      <c r="C2239" s="3" t="s">
+        <v>9096</v>
+      </c>
+      <c r="D2239" s="3" t="s">
+        <v>9097</v>
+      </c>
+      <c r="F2239" s="3" t="s">
+        <v>9094</v>
+      </c>
+      <c r="G2239" s="3" t="s">
+        <v>3420</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="H1:H2216" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2219">
-    <cfRule type="duplicateValues" dxfId="8" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="7" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+  <conditionalFormatting sqref="C1:C2230 C2240:C1048576">
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2202:C2212">
-    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2214:C2218">
-    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2220:C2226">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2229:C1048576 C1:C2219">
-    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+  <conditionalFormatting sqref="C2229:C2230 C1:C2219 C2240:C1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2229:C1048576 C2213 C2:C2201">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  <conditionalFormatting sqref="C2229:C2230 C2213 C2:C2201 C2240:C1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2231:C2239">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1065:G1075 G189:G549 G551:G578 G126:G187 G580:G1062 G2124 G2:G124" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13059" uniqueCount="9271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13081" uniqueCount="9288">
   <si>
     <t>麒安科技有限公司</t>
   </si>
@@ -32706,6 +32706,64 @@
   </si>
   <si>
     <t>118.07.18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>裕鋮股份有限公司</t>
+  </si>
+  <si>
+    <t>美商構光科技股份有限公司台灣分公司</t>
+  </si>
+  <si>
+    <t>擎亞電子股份有限公司</t>
+  </si>
+  <si>
+    <t>00198581</t>
+  </si>
+  <si>
+    <t>114業二16697</t>
+  </si>
+  <si>
+    <t>114業二16696</t>
+  </si>
+  <si>
+    <t>114業二16695</t>
+  </si>
+  <si>
+    <t>119.09.16</t>
+  </si>
+  <si>
+    <t>117.09.16</t>
+  </si>
+  <si>
+    <t>118.09.16</t>
+  </si>
+  <si>
+    <t>114.09.18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-366-3836</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>簡小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-577-1609</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>202/張先生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2655-7699</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>396/周小姐</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -33327,7 +33385,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:N2265"/>
+  <dimension ref="A1:N2268"/>
   <sheetFormatPr defaultRowHeight="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="79" style="3" customWidth="1"/>
@@ -78936,6 +78994,84 @@
       </c>
       <c r="E2265" t="s">
         <v>8989</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2266" s="3" t="s">
+        <v>9271</v>
+      </c>
+      <c r="B2266" s="4" t="s">
+        <v>9274</v>
+      </c>
+      <c r="C2266" s="3" t="s">
+        <v>9277</v>
+      </c>
+      <c r="D2266" s="3" t="s">
+        <v>9278</v>
+      </c>
+      <c r="F2266" s="3" t="s">
+        <v>9281</v>
+      </c>
+      <c r="G2266" s="3" t="s">
+        <v>3212</v>
+      </c>
+      <c r="H2266" s="3" t="s">
+        <v>9282</v>
+      </c>
+      <c r="I2266" s="3" t="s">
+        <v>9283</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2267" s="3" t="s">
+        <v>9272</v>
+      </c>
+      <c r="B2267" s="4">
+        <v>90009713</v>
+      </c>
+      <c r="C2267" s="3" t="s">
+        <v>9276</v>
+      </c>
+      <c r="D2267" s="3" t="s">
+        <v>9279</v>
+      </c>
+      <c r="F2267" s="3" t="s">
+        <v>9281</v>
+      </c>
+      <c r="G2267" s="3" t="s">
+        <v>3212</v>
+      </c>
+      <c r="H2267" s="3" t="s">
+        <v>9284</v>
+      </c>
+      <c r="I2267" s="3" t="s">
+        <v>9285</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2268" s="3" t="s">
+        <v>9273</v>
+      </c>
+      <c r="B2268" s="4">
+        <v>16099112</v>
+      </c>
+      <c r="C2268" s="3" t="s">
+        <v>9275</v>
+      </c>
+      <c r="D2268" s="3" t="s">
+        <v>9280</v>
+      </c>
+      <c r="F2268" s="3" t="s">
+        <v>9281</v>
+      </c>
+      <c r="G2268" s="3" t="s">
+        <v>3212</v>
+      </c>
+      <c r="H2268" s="3" t="s">
+        <v>9286</v>
+      </c>
+      <c r="I2268" s="3" t="s">
+        <v>9287</v>
       </c>
     </row>
   </sheetData>

--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13369" uniqueCount="9438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13550" uniqueCount="9521">
   <si>
     <t>麒安科技有限公司</t>
   </si>
@@ -33309,6 +33309,273 @@
   <si>
     <t>117.11.11</t>
   </si>
+  <si>
+    <t>03-666-3456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114.11.20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>500819/彭小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>07-607-6655</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22/羅小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2322-1791</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12/楊小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2218-5452</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>866048/鄭小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>04-2527-4061</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>04-2532-6399</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-8919-1566</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>336/林小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2269-5353</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14/林小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>確認方式</t>
+  </si>
+  <si>
+    <t>委任書處理</t>
+  </si>
+  <si>
+    <t>委任人統編</t>
+  </si>
+  <si>
+    <t>委任人名稱</t>
+  </si>
+  <si>
+    <t>監管編號</t>
+  </si>
+  <si>
+    <t>報關業者箱號</t>
+  </si>
+  <si>
+    <t>受任人名稱</t>
+  </si>
+  <si>
+    <t>關別</t>
+  </si>
+  <si>
+    <t>海空運別</t>
+  </si>
+  <si>
+    <t>進出口別</t>
+  </si>
+  <si>
+    <t>報單號碼</t>
+  </si>
+  <si>
+    <t>委任起始日</t>
+  </si>
+  <si>
+    <t>委任截止日</t>
+  </si>
+  <si>
+    <t>委任核准文號</t>
+  </si>
+  <si>
+    <t>建檔日期時間</t>
+  </si>
+  <si>
+    <t>同意由報關業者傳送出口檢附文件</t>
+  </si>
+  <si>
+    <t>同意由報關業者傳送進口檢附文件</t>
+  </si>
+  <si>
+    <t>E.已建立委任關係</t>
+  </si>
+  <si>
+    <t>查看</t>
+  </si>
+  <si>
+    <t>汎星半導體股份有限公司</t>
+  </si>
+  <si>
+    <t>台灣順豐速運股份有限公司</t>
+  </si>
+  <si>
+    <t>臺北關</t>
+  </si>
+  <si>
+    <t>115/01/01</t>
+  </si>
+  <si>
+    <t>119/12/31</t>
+  </si>
+  <si>
+    <t>WBBL2025118515</t>
+  </si>
+  <si>
+    <t>114/11/19 16:42:23</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>英屬開曼群島商澄和股份有限公司台灣分公司</t>
+  </si>
+  <si>
+    <t>114/11/19</t>
+  </si>
+  <si>
+    <t>119/11/18</t>
+  </si>
+  <si>
+    <t>WBBL2025118437</t>
+  </si>
+  <si>
+    <t>114/11/18 10:22:11</t>
+  </si>
+  <si>
+    <t>英屬安吉拉商星端國際有限公司台灣分公司</t>
+  </si>
+  <si>
+    <t>114/11/11</t>
+  </si>
+  <si>
+    <t>119/11/11</t>
+  </si>
+  <si>
+    <t>WBBL2025118279</t>
+  </si>
+  <si>
+    <t>114/11/10 11:17:50</t>
+  </si>
+  <si>
+    <t>美商畢真有限公司台灣分公司</t>
+  </si>
+  <si>
+    <t>114/11/07</t>
+  </si>
+  <si>
+    <t>119/11/06</t>
+  </si>
+  <si>
+    <t>WBBL2025118189</t>
+  </si>
+  <si>
+    <t>114/11/05 18:24:57</t>
+  </si>
+  <si>
+    <t>禾瑞貿易股份有限公司</t>
+  </si>
+  <si>
+    <t>114/11/05</t>
+  </si>
+  <si>
+    <t>119/11/04</t>
+  </si>
+  <si>
+    <t>WBBL2025118131</t>
+  </si>
+  <si>
+    <t>114/11/04 15:51:03</t>
+  </si>
+  <si>
+    <t>114/10/15</t>
+  </si>
+  <si>
+    <t>119/10/14</t>
+  </si>
+  <si>
+    <t>114/10/14 12:44:16</t>
+  </si>
+  <si>
+    <t>114/10/01</t>
+  </si>
+  <si>
+    <t>117/12/31</t>
+  </si>
+  <si>
+    <t>114/09/30 16:16:56</t>
+  </si>
+  <si>
+    <t>台灣羅伯特博世股份有限公司</t>
+  </si>
+  <si>
+    <t>114/09/20</t>
+  </si>
+  <si>
+    <t>119/09/19</t>
+  </si>
+  <si>
+    <t>WBBL2025097208</t>
+  </si>
+  <si>
+    <t>114/09/19 13:55:59</t>
+  </si>
+  <si>
+    <t>114/09/17</t>
+  </si>
+  <si>
+    <t>117/09/16</t>
+  </si>
+  <si>
+    <t>114/09/16 16:39:37</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>119/09/17</t>
+  </si>
+  <si>
+    <t>114/09/16 14:08:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>線上申請</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -33318,7 +33585,7 @@
     <numFmt numFmtId="176" formatCode="_ &quot;¥&quot;* #,##0.00_ ;_ &quot;¥&quot;* \-#,##0.00_ ;_ &quot;¥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="新細明體"/>
@@ -33405,21 +33672,89 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12.7"/>
+      <color rgb="FF2E6E9E"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.7"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="14.4"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F4F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFEFFC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEC88"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -33435,7 +33770,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -33487,13 +33822,69 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="貨幣" xfId="2" builtinId="4"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -33865,7 +34256,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:N2301"/>
+  <dimension ref="A1:AA2339"/>
   <sheetFormatPr defaultRowHeight="22" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="79" style="3" customWidth="1"/>
@@ -33876,15 +34267,19 @@
     <col min="6" max="6" width="15.625" style="3" customWidth="1"/>
     <col min="7" max="7" width="13" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="16.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.375" style="3" customWidth="1"/>
     <col min="10" max="10" width="67.375" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="13.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9" style="3"/>
+    <col min="13" max="13" width="24.5" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.125" style="3" customWidth="1"/>
     <col min="15" max="15" width="23.375" style="3" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="24.625" style="3" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="23.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="3"/>
+    <col min="18" max="21" width="9" style="3"/>
+    <col min="22" max="22" width="14.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -80600,6 +80995,18 @@
       <c r="D2293" s="3" t="s">
         <v>9435</v>
       </c>
+      <c r="F2293" s="3" t="s">
+        <v>9439</v>
+      </c>
+      <c r="G2293" s="3" t="s">
+        <v>3050</v>
+      </c>
+      <c r="H2293" s="3" t="s">
+        <v>9451</v>
+      </c>
+      <c r="I2293" s="3" t="s">
+        <v>9452</v>
+      </c>
     </row>
     <row r="2294" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2294" s="3" t="s">
@@ -80614,6 +81021,9 @@
       <c r="D2294" s="3" t="s">
         <v>9435</v>
       </c>
+      <c r="F2294" s="3" t="s">
+        <v>9439</v>
+      </c>
     </row>
     <row r="2295" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2295" s="3" t="s">
@@ -80628,6 +81038,18 @@
       <c r="D2295" s="3" t="s">
         <v>9436</v>
       </c>
+      <c r="F2295" s="3" t="s">
+        <v>9439</v>
+      </c>
+      <c r="G2295" s="3" t="s">
+        <v>3050</v>
+      </c>
+      <c r="H2295" s="3" t="s">
+        <v>9438</v>
+      </c>
+      <c r="I2295" s="3" t="s">
+        <v>9440</v>
+      </c>
     </row>
     <row r="2296" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2296" s="3" t="s">
@@ -80642,6 +81064,18 @@
       <c r="D2296" s="3" t="s">
         <v>9435</v>
       </c>
+      <c r="F2296" s="3" t="s">
+        <v>9439</v>
+      </c>
+      <c r="G2296" s="3" t="s">
+        <v>3050</v>
+      </c>
+      <c r="H2296" s="3" t="s">
+        <v>9441</v>
+      </c>
+      <c r="I2296" s="3" t="s">
+        <v>9442</v>
+      </c>
     </row>
     <row r="2297" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2297" s="3" t="s">
@@ -80656,6 +81090,18 @@
       <c r="D2297" s="3" t="s">
         <v>9435</v>
       </c>
+      <c r="F2297" s="3" t="s">
+        <v>9439</v>
+      </c>
+      <c r="G2297" s="3" t="s">
+        <v>3050</v>
+      </c>
+      <c r="H2297" s="3" t="s">
+        <v>9449</v>
+      </c>
+      <c r="I2297" s="3" t="s">
+        <v>9450</v>
+      </c>
     </row>
     <row r="2298" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2298" s="3" t="s">
@@ -80670,6 +81116,18 @@
       <c r="D2298" s="3" t="s">
         <v>9437</v>
       </c>
+      <c r="F2298" s="3" t="s">
+        <v>9439</v>
+      </c>
+      <c r="G2298" s="3" t="s">
+        <v>3050</v>
+      </c>
+      <c r="H2298" s="3" t="s">
+        <v>9447</v>
+      </c>
+      <c r="I2298" s="3" t="s">
+        <v>9448</v>
+      </c>
     </row>
     <row r="2299" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2299" s="3" t="s">
@@ -80684,6 +81142,18 @@
       <c r="D2299" s="3" t="s">
         <v>9435</v>
       </c>
+      <c r="F2299" s="3" t="s">
+        <v>9439</v>
+      </c>
+      <c r="G2299" s="3" t="s">
+        <v>3050</v>
+      </c>
+      <c r="H2299" s="3" t="s">
+        <v>9445</v>
+      </c>
+      <c r="I2299" s="3" t="s">
+        <v>9446</v>
+      </c>
     </row>
     <row r="2300" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2300" s="3" t="s">
@@ -80698,6 +81168,18 @@
       <c r="D2300" s="3" t="s">
         <v>9435</v>
       </c>
+      <c r="F2300" s="3" t="s">
+        <v>9439</v>
+      </c>
+      <c r="G2300" s="3" t="s">
+        <v>3050</v>
+      </c>
+      <c r="H2300" s="3" t="s">
+        <v>9453</v>
+      </c>
+      <c r="I2300" s="3" t="s">
+        <v>9454</v>
+      </c>
     </row>
     <row r="2301" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2301" s="3" t="s">
@@ -80712,29 +81194,711 @@
       <c r="D2301" s="3" t="s">
         <v>9435</v>
       </c>
+      <c r="F2301" s="3" t="s">
+        <v>9439</v>
+      </c>
+      <c r="G2301" s="3" t="s">
+        <v>3050</v>
+      </c>
+      <c r="H2301" s="3" t="s">
+        <v>9443</v>
+      </c>
+      <c r="I2301" s="3" t="s">
+        <v>9444</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2302" s="3" t="s">
+        <v>9474</v>
+      </c>
+      <c r="B2302" s="4">
+        <v>90039651</v>
+      </c>
+      <c r="C2302" s="3" t="s">
+        <v>9479</v>
+      </c>
+      <c r="D2302" s="3" t="s">
+        <v>9478</v>
+      </c>
+      <c r="E2302" s="3" t="s">
+        <v>9520</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2303" s="3" t="s">
+        <v>9482</v>
+      </c>
+      <c r="B2303" s="4">
+        <v>59060539</v>
+      </c>
+      <c r="C2303" s="3" t="s">
+        <v>9485</v>
+      </c>
+      <c r="D2303" s="3" t="s">
+        <v>9484</v>
+      </c>
+      <c r="E2303" s="3" t="s">
+        <v>9520</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2304" s="3" t="s">
+        <v>9487</v>
+      </c>
+      <c r="B2304" s="4">
+        <v>24807384</v>
+      </c>
+      <c r="C2304" s="3" t="s">
+        <v>9490</v>
+      </c>
+      <c r="D2304" s="3" t="s">
+        <v>9489</v>
+      </c>
+      <c r="E2304" s="3" t="s">
+        <v>9520</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2305" s="3" t="s">
+        <v>9492</v>
+      </c>
+      <c r="B2305" s="4">
+        <v>60600762</v>
+      </c>
+      <c r="C2305" s="3" t="s">
+        <v>9495</v>
+      </c>
+      <c r="D2305" s="3" t="s">
+        <v>9494</v>
+      </c>
+      <c r="E2305" s="3" t="s">
+        <v>9520</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2306" s="3" t="s">
+        <v>9497</v>
+      </c>
+      <c r="B2306" s="4">
+        <v>25156394</v>
+      </c>
+      <c r="C2306" s="3" t="s">
+        <v>9500</v>
+      </c>
+      <c r="D2306" s="3" t="s">
+        <v>9499</v>
+      </c>
+      <c r="E2306" s="3" t="s">
+        <v>9520</v>
+      </c>
+    </row>
+    <row r="2327" spans="10:27" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J2327" s="28" t="s">
+        <v>9519</v>
+      </c>
+      <c r="K2327" s="17"/>
+      <c r="L2327" s="17"/>
+      <c r="M2327" s="17"/>
+      <c r="N2327" s="17"/>
+      <c r="O2327" s="17"/>
+      <c r="P2327" s="17"/>
+      <c r="Q2327" s="17"/>
+      <c r="R2327" s="17"/>
+      <c r="S2327" s="17"/>
+      <c r="T2327" s="17"/>
+      <c r="U2327" s="17"/>
+      <c r="V2327" s="17"/>
+      <c r="W2327" s="17"/>
+      <c r="X2327" s="17"/>
+      <c r="Y2327" s="17"/>
+      <c r="Z2327" s="17"/>
+      <c r="AA2327" s="17"/>
+    </row>
+    <row r="2328" spans="10:27" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J2328" s="28"/>
+      <c r="K2328" s="18" t="s">
+        <v>9455</v>
+      </c>
+      <c r="L2328" s="18" t="s">
+        <v>9456</v>
+      </c>
+      <c r="M2328" s="18" t="s">
+        <v>9457</v>
+      </c>
+      <c r="N2328" s="18" t="s">
+        <v>9458</v>
+      </c>
+      <c r="O2328" s="18" t="s">
+        <v>9459</v>
+      </c>
+      <c r="P2328" s="18" t="s">
+        <v>9460</v>
+      </c>
+      <c r="Q2328" s="18" t="s">
+        <v>9461</v>
+      </c>
+      <c r="R2328" s="18" t="s">
+        <v>9462</v>
+      </c>
+      <c r="S2328" s="18" t="s">
+        <v>9463</v>
+      </c>
+      <c r="T2328" s="18" t="s">
+        <v>9464</v>
+      </c>
+      <c r="U2328" s="18" t="s">
+        <v>9465</v>
+      </c>
+      <c r="V2328" s="18" t="s">
+        <v>9466</v>
+      </c>
+      <c r="W2328" s="18" t="s">
+        <v>9467</v>
+      </c>
+      <c r="X2328" s="18" t="s">
+        <v>9468</v>
+      </c>
+      <c r="Y2328" s="18" t="s">
+        <v>9469</v>
+      </c>
+      <c r="Z2328" s="18" t="s">
+        <v>9470</v>
+      </c>
+      <c r="AA2328" s="18" t="s">
+        <v>9471</v>
+      </c>
+    </row>
+    <row r="2329" spans="10:27" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J2329" s="19"/>
+      <c r="K2329" s="19"/>
+      <c r="L2329" s="19"/>
+      <c r="M2329" s="19"/>
+      <c r="N2329" s="19"/>
+      <c r="O2329" s="19"/>
+      <c r="P2329" s="19"/>
+      <c r="Q2329" s="19"/>
+      <c r="R2329" s="19"/>
+      <c r="S2329" s="19"/>
+      <c r="T2329" s="19"/>
+      <c r="U2329" s="19"/>
+      <c r="V2329" s="19"/>
+      <c r="W2329" s="19"/>
+      <c r="X2329" s="19"/>
+      <c r="Y2329" s="19"/>
+      <c r="Z2329" s="19"/>
+      <c r="AA2329" s="19"/>
+    </row>
+    <row r="2330" spans="10:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J2330" s="20">
+        <v>1</v>
+      </c>
+      <c r="K2330" s="21" t="s">
+        <v>9472</v>
+      </c>
+      <c r="L2330" s="21" t="s">
+        <v>9473</v>
+      </c>
+      <c r="M2330" s="21">
+        <v>90039651</v>
+      </c>
+      <c r="N2330" s="22" t="s">
+        <v>9474</v>
+      </c>
+      <c r="O2330" s="21"/>
+      <c r="P2330" s="21">
+        <v>696</v>
+      </c>
+      <c r="Q2330" s="22" t="s">
+        <v>9475</v>
+      </c>
+      <c r="R2330" s="21" t="s">
+        <v>9476</v>
+      </c>
+      <c r="S2330" s="21"/>
+      <c r="T2330" s="21"/>
+      <c r="U2330" s="21"/>
+      <c r="V2330" s="21" t="s">
+        <v>9477</v>
+      </c>
+      <c r="W2330" s="21" t="s">
+        <v>9478</v>
+      </c>
+      <c r="X2330" s="21" t="s">
+        <v>9479</v>
+      </c>
+      <c r="Y2330" s="21" t="s">
+        <v>9480</v>
+      </c>
+      <c r="Z2330" s="21" t="s">
+        <v>9481</v>
+      </c>
+      <c r="AA2330" s="21" t="s">
+        <v>9481</v>
+      </c>
+    </row>
+    <row r="2331" spans="10:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J2331" s="20">
+        <v>2</v>
+      </c>
+      <c r="K2331" s="23" t="s">
+        <v>9472</v>
+      </c>
+      <c r="L2331" s="23" t="s">
+        <v>9473</v>
+      </c>
+      <c r="M2331" s="23">
+        <v>59060539</v>
+      </c>
+      <c r="N2331" s="24" t="s">
+        <v>9482</v>
+      </c>
+      <c r="O2331" s="23"/>
+      <c r="P2331" s="23">
+        <v>696</v>
+      </c>
+      <c r="Q2331" s="24" t="s">
+        <v>9475</v>
+      </c>
+      <c r="R2331" s="23" t="s">
+        <v>9476</v>
+      </c>
+      <c r="S2331" s="23"/>
+      <c r="T2331" s="23"/>
+      <c r="U2331" s="23"/>
+      <c r="V2331" s="23" t="s">
+        <v>9483</v>
+      </c>
+      <c r="W2331" s="23" t="s">
+        <v>9484</v>
+      </c>
+      <c r="X2331" s="23" t="s">
+        <v>9485</v>
+      </c>
+      <c r="Y2331" s="23" t="s">
+        <v>9486</v>
+      </c>
+      <c r="Z2331" s="23" t="s">
+        <v>9481</v>
+      </c>
+      <c r="AA2331" s="23" t="s">
+        <v>9481</v>
+      </c>
+    </row>
+    <row r="2332" spans="10:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J2332" s="20">
+        <v>3</v>
+      </c>
+      <c r="K2332" s="23" t="s">
+        <v>9472</v>
+      </c>
+      <c r="L2332" s="23" t="s">
+        <v>9473</v>
+      </c>
+      <c r="M2332" s="23">
+        <v>24807384</v>
+      </c>
+      <c r="N2332" s="24" t="s">
+        <v>9487</v>
+      </c>
+      <c r="O2332" s="23"/>
+      <c r="P2332" s="23">
+        <v>696</v>
+      </c>
+      <c r="Q2332" s="24" t="s">
+        <v>9475</v>
+      </c>
+      <c r="R2332" s="23" t="s">
+        <v>9476</v>
+      </c>
+      <c r="S2332" s="23"/>
+      <c r="T2332" s="23"/>
+      <c r="U2332" s="23"/>
+      <c r="V2332" s="23" t="s">
+        <v>9488</v>
+      </c>
+      <c r="W2332" s="23" t="s">
+        <v>9489</v>
+      </c>
+      <c r="X2332" s="23" t="s">
+        <v>9490</v>
+      </c>
+      <c r="Y2332" s="23" t="s">
+        <v>9491</v>
+      </c>
+      <c r="Z2332" s="23" t="s">
+        <v>9481</v>
+      </c>
+      <c r="AA2332" s="23" t="s">
+        <v>9481</v>
+      </c>
+    </row>
+    <row r="2333" spans="10:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J2333" s="20">
+        <v>4</v>
+      </c>
+      <c r="K2333" s="23" t="s">
+        <v>9472</v>
+      </c>
+      <c r="L2333" s="23" t="s">
+        <v>9473</v>
+      </c>
+      <c r="M2333" s="23">
+        <v>60600762</v>
+      </c>
+      <c r="N2333" s="24" t="s">
+        <v>9492</v>
+      </c>
+      <c r="O2333" s="23"/>
+      <c r="P2333" s="23">
+        <v>696</v>
+      </c>
+      <c r="Q2333" s="24" t="s">
+        <v>9475</v>
+      </c>
+      <c r="R2333" s="23" t="s">
+        <v>9476</v>
+      </c>
+      <c r="S2333" s="23"/>
+      <c r="T2333" s="23"/>
+      <c r="U2333" s="23"/>
+      <c r="V2333" s="23" t="s">
+        <v>9493</v>
+      </c>
+      <c r="W2333" s="23" t="s">
+        <v>9494</v>
+      </c>
+      <c r="X2333" s="23" t="s">
+        <v>9495</v>
+      </c>
+      <c r="Y2333" s="23" t="s">
+        <v>9496</v>
+      </c>
+      <c r="Z2333" s="23" t="s">
+        <v>9481</v>
+      </c>
+      <c r="AA2333" s="23" t="s">
+        <v>9481</v>
+      </c>
+    </row>
+    <row r="2334" spans="10:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J2334" s="20">
+        <v>5</v>
+      </c>
+      <c r="K2334" s="23" t="s">
+        <v>9472</v>
+      </c>
+      <c r="L2334" s="23" t="s">
+        <v>9473</v>
+      </c>
+      <c r="M2334" s="23">
+        <v>25156394</v>
+      </c>
+      <c r="N2334" s="24" t="s">
+        <v>9497</v>
+      </c>
+      <c r="O2334" s="23"/>
+      <c r="P2334" s="23">
+        <v>696</v>
+      </c>
+      <c r="Q2334" s="24" t="s">
+        <v>9475</v>
+      </c>
+      <c r="R2334" s="23" t="s">
+        <v>9476</v>
+      </c>
+      <c r="S2334" s="23"/>
+      <c r="T2334" s="23"/>
+      <c r="U2334" s="23"/>
+      <c r="V2334" s="23" t="s">
+        <v>9498</v>
+      </c>
+      <c r="W2334" s="23" t="s">
+        <v>9499</v>
+      </c>
+      <c r="X2334" s="23" t="s">
+        <v>9500</v>
+      </c>
+      <c r="Y2334" s="23" t="s">
+        <v>9501</v>
+      </c>
+      <c r="Z2334" s="23" t="s">
+        <v>9481</v>
+      </c>
+      <c r="AA2334" s="23" t="s">
+        <v>9481</v>
+      </c>
+    </row>
+    <row r="2335" spans="10:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J2335" s="20">
+        <v>6</v>
+      </c>
+      <c r="K2335" s="23" t="s">
+        <v>9472</v>
+      </c>
+      <c r="L2335" s="23" t="s">
+        <v>9473</v>
+      </c>
+      <c r="M2335" s="23">
+        <v>42869468</v>
+      </c>
+      <c r="N2335" s="24" t="s">
+        <v>9280</v>
+      </c>
+      <c r="O2335" s="23"/>
+      <c r="P2335" s="23">
+        <v>696</v>
+      </c>
+      <c r="Q2335" s="24" t="s">
+        <v>9475</v>
+      </c>
+      <c r="R2335" s="23" t="s">
+        <v>9476</v>
+      </c>
+      <c r="S2335" s="23"/>
+      <c r="T2335" s="23"/>
+      <c r="U2335" s="23"/>
+      <c r="V2335" s="23" t="s">
+        <v>9502</v>
+      </c>
+      <c r="W2335" s="23" t="s">
+        <v>9503</v>
+      </c>
+      <c r="X2335" s="23" t="s">
+        <v>9281</v>
+      </c>
+      <c r="Y2335" s="23" t="s">
+        <v>9504</v>
+      </c>
+      <c r="Z2335" s="23" t="s">
+        <v>9481</v>
+      </c>
+      <c r="AA2335" s="23" t="s">
+        <v>9481</v>
+      </c>
+    </row>
+    <row r="2336" spans="10:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J2336" s="20">
+        <v>7</v>
+      </c>
+      <c r="K2336" s="23" t="s">
+        <v>9472</v>
+      </c>
+      <c r="L2336" s="23" t="s">
+        <v>9473</v>
+      </c>
+      <c r="M2336" s="23">
+        <v>53750425</v>
+      </c>
+      <c r="N2336" s="24" t="s">
+        <v>9282</v>
+      </c>
+      <c r="O2336" s="23"/>
+      <c r="P2336" s="23">
+        <v>696</v>
+      </c>
+      <c r="Q2336" s="24" t="s">
+        <v>9475</v>
+      </c>
+      <c r="R2336" s="23" t="s">
+        <v>9476</v>
+      </c>
+      <c r="S2336" s="23"/>
+      <c r="T2336" s="23"/>
+      <c r="U2336" s="23"/>
+      <c r="V2336" s="23" t="s">
+        <v>9505</v>
+      </c>
+      <c r="W2336" s="23" t="s">
+        <v>9506</v>
+      </c>
+      <c r="X2336" s="23" t="s">
+        <v>9283</v>
+      </c>
+      <c r="Y2336" s="23" t="s">
+        <v>9507</v>
+      </c>
+      <c r="Z2336" s="23" t="s">
+        <v>9481</v>
+      </c>
+      <c r="AA2336" s="23" t="s">
+        <v>9481</v>
+      </c>
+    </row>
+    <row r="2337" spans="10:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J2337" s="20">
+        <v>8</v>
+      </c>
+      <c r="K2337" s="23" t="s">
+        <v>9472</v>
+      </c>
+      <c r="L2337" s="23" t="s">
+        <v>9473</v>
+      </c>
+      <c r="M2337" s="23">
+        <v>80272572</v>
+      </c>
+      <c r="N2337" s="24" t="s">
+        <v>9508</v>
+      </c>
+      <c r="O2337" s="23"/>
+      <c r="P2337" s="23">
+        <v>696</v>
+      </c>
+      <c r="Q2337" s="24" t="s">
+        <v>9475</v>
+      </c>
+      <c r="R2337" s="23" t="s">
+        <v>9476</v>
+      </c>
+      <c r="S2337" s="23"/>
+      <c r="T2337" s="23"/>
+      <c r="U2337" s="23"/>
+      <c r="V2337" s="23" t="s">
+        <v>9509</v>
+      </c>
+      <c r="W2337" s="23" t="s">
+        <v>9510</v>
+      </c>
+      <c r="X2337" s="23" t="s">
+        <v>9511</v>
+      </c>
+      <c r="Y2337" s="23" t="s">
+        <v>9512</v>
+      </c>
+      <c r="Z2337" s="23" t="s">
+        <v>9481</v>
+      </c>
+      <c r="AA2337" s="23" t="s">
+        <v>9481</v>
+      </c>
+    </row>
+    <row r="2338" spans="10:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J2338" s="20">
+        <v>9</v>
+      </c>
+      <c r="K2338" s="23" t="s">
+        <v>9472</v>
+      </c>
+      <c r="L2338" s="23" t="s">
+        <v>9473</v>
+      </c>
+      <c r="M2338" s="23">
+        <v>52706730</v>
+      </c>
+      <c r="N2338" s="24" t="s">
+        <v>9088</v>
+      </c>
+      <c r="O2338" s="23"/>
+      <c r="P2338" s="23">
+        <v>696</v>
+      </c>
+      <c r="Q2338" s="24" t="s">
+        <v>9475</v>
+      </c>
+      <c r="R2338" s="23" t="s">
+        <v>9476</v>
+      </c>
+      <c r="S2338" s="23"/>
+      <c r="T2338" s="23"/>
+      <c r="U2338" s="23"/>
+      <c r="V2338" s="23" t="s">
+        <v>9513</v>
+      </c>
+      <c r="W2338" s="23" t="s">
+        <v>9514</v>
+      </c>
+      <c r="X2338" s="23" t="s">
+        <v>9089</v>
+      </c>
+      <c r="Y2338" s="23" t="s">
+        <v>9515</v>
+      </c>
+      <c r="Z2338" s="23" t="s">
+        <v>9516</v>
+      </c>
+      <c r="AA2338" s="23" t="s">
+        <v>9516</v>
+      </c>
+    </row>
+    <row r="2339" spans="10:27" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J2339" s="25">
+        <v>10</v>
+      </c>
+      <c r="K2339" s="26" t="s">
+        <v>9472</v>
+      </c>
+      <c r="L2339" s="26" t="s">
+        <v>9473</v>
+      </c>
+      <c r="M2339" s="26">
+        <v>52582885</v>
+      </c>
+      <c r="N2339" s="27" t="s">
+        <v>9090</v>
+      </c>
+      <c r="O2339" s="26"/>
+      <c r="P2339" s="26">
+        <v>696</v>
+      </c>
+      <c r="Q2339" s="27" t="s">
+        <v>9475</v>
+      </c>
+      <c r="R2339" s="26" t="s">
+        <v>9476</v>
+      </c>
+      <c r="S2339" s="26"/>
+      <c r="T2339" s="26"/>
+      <c r="U2339" s="26"/>
+      <c r="V2339" s="26" t="s">
+        <v>9513</v>
+      </c>
+      <c r="W2339" s="26" t="s">
+        <v>9517</v>
+      </c>
+      <c r="X2339" s="26" t="s">
+        <v>9091</v>
+      </c>
+      <c r="Y2339" s="26" t="s">
+        <v>9518</v>
+      </c>
+      <c r="Z2339" s="26" t="s">
+        <v>9481</v>
+      </c>
+      <c r="AA2339" s="26" t="s">
+        <v>9481</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="H1:H2089"/>
+  <mergeCells count="1">
+    <mergeCell ref="J2327:J2328"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B2162:B2171">
-    <cfRule type="duplicateValues" dxfId="6" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2162:B2171">
-    <cfRule type="duplicateValues" dxfId="5" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2162:B2171">
-    <cfRule type="duplicateValues" dxfId="4" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2148:E2150">
+    <cfRule type="duplicateValues" dxfId="5" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2148:E2150">
+    <cfRule type="duplicateValues" dxfId="4" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2148:E2150">
     <cfRule type="duplicateValues" dxfId="3" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2148:E2150">
-    <cfRule type="duplicateValues" dxfId="2" priority="16"/>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2148:E2150">
-    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+  <conditionalFormatting sqref="D2302:D2311 C1:C2301 C2312:C1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
+  <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">

--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20416"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.66.23.230\886wa\◆進口相關查詢資料庫◆(不要移動)\◆新委任書-出口◆\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A338D160-CAA0-4F1A-A2CB-ED349E0D6B94}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="5580" windowWidth="11055" windowHeight="3975"/>
+    <workbookView xWindow="-15" yWindow="5580" windowWidth="11055" windowHeight="3975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="順豐出口" sheetId="4" r:id="rId1"/>
@@ -18,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13519" uniqueCount="9418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13480" uniqueCount="9422">
   <si>
     <t>麒安科技有限公司</t>
   </si>
@@ -33107,147 +33113,171 @@
     <t>119.12.08</t>
   </si>
   <si>
-    <t>E.已建立委任關係</t>
-  </si>
-  <si>
-    <t>查看</t>
-  </si>
-  <si>
     <t>月村科技股份有限公司</t>
   </si>
   <si>
-    <t>台灣順豐速運股份有限公司</t>
-  </si>
-  <si>
-    <t>臺北關</t>
-  </si>
-  <si>
-    <t>115/01/13</t>
-  </si>
-  <si>
-    <t>120/01/12</t>
-  </si>
-  <si>
     <t>WBBL2026014659</t>
   </si>
   <si>
-    <t>115/01/12 13:29:38</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>佳昂科技股份有限公司</t>
   </si>
   <si>
-    <t>115/01/08</t>
-  </si>
-  <si>
-    <t>120/01/07</t>
-  </si>
-  <si>
     <t>WBBL2026014148</t>
   </si>
   <si>
-    <t>115/01/07 11:02:32</t>
-  </si>
-  <si>
     <t>台灣數位串流有限公司</t>
   </si>
   <si>
-    <t>115/01/06</t>
-  </si>
-  <si>
-    <t>120/01/06</t>
-  </si>
-  <si>
     <t>WBBL2026014015</t>
   </si>
   <si>
-    <t>115/01/05 18:26:21</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>115/01/03</t>
-  </si>
-  <si>
-    <t>120/01/03</t>
-  </si>
-  <si>
-    <t>115/01/02 17:13:44</t>
-  </si>
-  <si>
-    <t>114/12/24</t>
-  </si>
-  <si>
-    <t>118/12/31</t>
-  </si>
-  <si>
-    <t>114/12/23 10:23:08</t>
-  </si>
-  <si>
-    <t>114/12/22</t>
-  </si>
-  <si>
-    <t>119/12/22</t>
-  </si>
-  <si>
-    <t>114/12/21 06:04:56</t>
-  </si>
-  <si>
-    <t>114/12/18</t>
-  </si>
-  <si>
-    <t>119/12/18</t>
-  </si>
-  <si>
-    <t>114/12/17 15:37:32</t>
-  </si>
-  <si>
-    <t>114/12/09</t>
-  </si>
-  <si>
-    <t>119/12/08</t>
-  </si>
-  <si>
-    <t>114/12/08 10:50:13</t>
-  </si>
-  <si>
-    <t>115/01/01</t>
-  </si>
-  <si>
-    <t>117/12/31</t>
-  </si>
-  <si>
-    <t>114/12/04 17:12:46</t>
-  </si>
-  <si>
-    <t>114/12/04</t>
-  </si>
-  <si>
-    <t>119/12/03</t>
-  </si>
-  <si>
-    <t>114/12/03 16:27:26</t>
-  </si>
-  <si>
     <t>120.01.12</t>
   </si>
   <si>
     <t>120.01.07</t>
+  </si>
+  <si>
+    <t>台灣科百特股份有限公司</t>
+  </si>
+  <si>
+    <t>貫一興業股份有限公司</t>
+  </si>
+  <si>
+    <t>八光實業股份有限公司</t>
+  </si>
+  <si>
+    <t>台灣鈣鈦礦科技股份有限公司</t>
+  </si>
+  <si>
+    <t>永瀚實業有限公司</t>
+  </si>
+  <si>
+    <t>笠菖實業有限公司</t>
+  </si>
+  <si>
+    <t>兆盈興業股份有限公司</t>
+  </si>
+  <si>
+    <t>開發工業股份有限公司</t>
+  </si>
+  <si>
+    <t>漢德威自動化科技股份有限公司</t>
+  </si>
+  <si>
+    <t>友嘉科技股份有限公司</t>
+  </si>
+  <si>
+    <t>揚全股份有限公司</t>
+  </si>
+  <si>
+    <t>115業二00024</t>
+  </si>
+  <si>
+    <t>115業二00025</t>
+  </si>
+  <si>
+    <t>115業二00026</t>
+  </si>
+  <si>
+    <t>115業二00027</t>
+  </si>
+  <si>
+    <t>115業二00028</t>
+  </si>
+  <si>
+    <t>115業二00029</t>
+  </si>
+  <si>
+    <t>115業二00030</t>
+  </si>
+  <si>
+    <t>115業二01609</t>
+  </si>
+  <si>
+    <t>115業二01610</t>
+  </si>
+  <si>
+    <t>115業二01611</t>
+  </si>
+  <si>
+    <t>115業二01612</t>
+  </si>
+  <si>
+    <t>115業二01613</t>
+  </si>
+  <si>
+    <t>120.01.13</t>
+  </si>
+  <si>
+    <t>117.01.07</t>
+  </si>
+  <si>
+    <t>120.01.11</t>
+  </si>
+  <si>
+    <t>115.01.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電話</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-5600-101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>06-2795-522</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>823/顏小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-8698-1136</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-6589760</t>
+  </si>
+  <si>
+    <t>120/廖小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-553-5736</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2651-0070</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>謝小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-8687-4045</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>郵件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>winni.yang@jointek.com.tw</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="_ &quot;¥&quot;* #,##0.00_ ;_ &quot;¥&quot;* \-#,##0.00_ ;_ &quot;¥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="新細明體"/>
@@ -33340,65 +33370,19 @@
       <family val="1"/>
       <charset val="136"/>
     </font>
-    <font>
-      <sz val="14.4"/>
-      <color rgb="FF000000"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="14.4"/>
-      <color rgb="FFFF0000"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFDFD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFEFFC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -33416,7 +33400,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -33473,30 +33457,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -33691,7 +33651,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -33724,9 +33684,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -33759,6 +33736,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -33934,9 +33928,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:W2301"/>
+  <dimension ref="A1:N2292"/>
   <sheetFormatPr defaultRowHeight="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="79" style="3" customWidth="1"/>
@@ -80981,7 +80975,7 @@
         <v>9368</v>
       </c>
     </row>
-    <row r="2273" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2273" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2273" s="3" t="s">
         <v>9363</v>
       </c>
@@ -80995,7 +80989,7 @@
         <v>9368</v>
       </c>
     </row>
-    <row r="2274" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2274" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2274" s="3" t="s">
         <v>9364</v>
       </c>
@@ -81009,7 +81003,7 @@
         <v>9369</v>
       </c>
     </row>
-    <row r="2275" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2275" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2275" s="3" t="s">
         <v>9365</v>
       </c>
@@ -81023,7 +81017,7 @@
         <v>9368</v>
       </c>
     </row>
-    <row r="2276" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2276" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2276" s="3" t="s">
         <v>9366</v>
       </c>
@@ -81037,7 +81031,7 @@
         <v>9368</v>
       </c>
     </row>
-    <row r="2277" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2277" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2277" s="3" t="s">
         <v>9367</v>
       </c>
@@ -81051,533 +81045,323 @@
         <v>9368</v>
       </c>
     </row>
-    <row r="2278" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2278" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2278" s="3" t="s">
-        <v>9376</v>
+        <v>9374</v>
       </c>
       <c r="B2278" s="4">
         <v>16492781</v>
       </c>
       <c r="C2278" s="3" t="s">
-        <v>9381</v>
+        <v>9375</v>
       </c>
       <c r="D2278" s="3" t="s">
-        <v>9416</v>
-      </c>
-    </row>
-    <row r="2279" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9380</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2279" s="3" t="s">
-        <v>9384</v>
+        <v>9376</v>
       </c>
       <c r="B2279" s="4">
         <v>82995167</v>
       </c>
       <c r="C2279" s="3" t="s">
-        <v>9387</v>
+        <v>9377</v>
       </c>
       <c r="D2279" s="3" t="s">
-        <v>9417</v>
-      </c>
-    </row>
-    <row r="2280" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9381</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2280" s="3" t="s">
-        <v>9389</v>
+        <v>9378</v>
       </c>
       <c r="B2280" s="4">
         <v>83569021</v>
       </c>
       <c r="C2280" s="3" t="s">
-        <v>9392</v>
+        <v>9379</v>
       </c>
       <c r="D2280" s="3" t="s">
         <v>9368</v>
       </c>
     </row>
-    <row r="2291" spans="6:23" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F2291" s="19">
-        <v>1</v>
-      </c>
-      <c r="G2291" s="20" t="s">
-        <v>9374</v>
-      </c>
-      <c r="H2291" s="20" t="s">
-        <v>9375</v>
-      </c>
-      <c r="I2291" s="20">
-        <v>16492781</v>
-      </c>
-      <c r="J2291" s="21" t="s">
-        <v>9376</v>
-      </c>
-      <c r="K2291" s="20"/>
-      <c r="L2291" s="20">
-        <v>696</v>
-      </c>
-      <c r="M2291" s="21" t="s">
-        <v>9377</v>
-      </c>
-      <c r="N2291" s="20" t="s">
-        <v>9378</v>
-      </c>
-      <c r="O2291" s="20"/>
-      <c r="P2291" s="20"/>
-      <c r="Q2291" s="20"/>
-      <c r="R2291" s="20" t="s">
-        <v>9379</v>
-      </c>
-      <c r="S2291" s="25" t="s">
-        <v>9380</v>
-      </c>
-      <c r="T2291" s="20" t="s">
+    <row r="2281" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2281" s="3" t="s">
+        <v>9382</v>
+      </c>
+      <c r="B2281" s="4">
+        <v>42970921</v>
+      </c>
+      <c r="C2281" s="3" t="s">
+        <v>9393</v>
+      </c>
+      <c r="D2281" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2281" s="3" t="s">
+        <v>9408</v>
+      </c>
+      <c r="G2281" s="3" t="s">
+        <v>9409</v>
+      </c>
+      <c r="H2281" s="3" t="s">
+        <v>9410</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2282" s="3" t="s">
+        <v>9383</v>
+      </c>
+      <c r="B2282" s="4">
+        <v>86770196</v>
+      </c>
+      <c r="C2282" s="3" t="s">
+        <v>9394</v>
+      </c>
+      <c r="D2282" s="3" t="s">
+        <v>3869</v>
+      </c>
+      <c r="F2282" s="3" t="s">
+        <v>9408</v>
+      </c>
+      <c r="G2282" s="3" t="s">
+        <v>9409</v>
+      </c>
+      <c r="H2282" s="3" t="s">
+        <v>9411</v>
+      </c>
+      <c r="I2282" s="3" t="s">
+        <v>9412</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2283" s="3" t="s">
+        <v>9384</v>
+      </c>
+      <c r="B2283" s="4">
+        <v>30965162</v>
+      </c>
+      <c r="C2283" s="3" t="s">
+        <v>9395</v>
+      </c>
+      <c r="D2283" s="3" t="s">
+        <v>9405</v>
+      </c>
+      <c r="F2283" s="3" t="s">
+        <v>9408</v>
+      </c>
+      <c r="G2283" s="3" t="s">
+        <v>9409</v>
+      </c>
+      <c r="H2283" s="3" t="s">
+        <v>9413</v>
+      </c>
+      <c r="I2283" s="3" t="s">
+        <v>9415</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2284" s="3" t="s">
+        <v>9385</v>
+      </c>
+      <c r="B2284" s="4">
+        <v>90871999</v>
+      </c>
+      <c r="C2284" s="3" t="s">
+        <v>9396</v>
+      </c>
+      <c r="D2284" s="3" t="s">
+        <v>9405</v>
+      </c>
+      <c r="F2284" s="3" t="s">
+        <v>9408</v>
+      </c>
+      <c r="G2284" s="3" t="s">
+        <v>9409</v>
+      </c>
+      <c r="H2284" s="3" t="s">
+        <v>9414</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2285" s="3" t="s">
+        <v>6597</v>
+      </c>
+      <c r="B2285" s="4">
+        <v>28618687</v>
+      </c>
+      <c r="C2285" s="3" t="s">
+        <v>9397</v>
+      </c>
+      <c r="D2285" s="3" t="s">
+        <v>9406</v>
+      </c>
+      <c r="F2285" s="3" t="s">
+        <v>9408</v>
+      </c>
+      <c r="G2285" s="3" t="s">
+        <v>9409</v>
+      </c>
+      <c r="H2285" s="3" t="s">
+        <v>9416</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2286" s="3" t="s">
+        <v>9386</v>
+      </c>
+      <c r="B2286" s="4">
+        <v>54185335</v>
+      </c>
+      <c r="C2286" s="3" t="s">
+        <v>9398</v>
+      </c>
+      <c r="D2286" s="3" t="s">
         <v>9381</v>
       </c>
-      <c r="U2291" s="20" t="s">
-        <v>9382</v>
-      </c>
-      <c r="V2291" s="20" t="s">
-        <v>9383</v>
-      </c>
-      <c r="W2291" s="20" t="s">
-        <v>9383</v>
-      </c>
-    </row>
-    <row r="2292" spans="6:23" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F2292" s="19">
-        <v>2</v>
-      </c>
-      <c r="G2292" s="20" t="s">
-        <v>9374</v>
-      </c>
-      <c r="H2292" s="20" t="s">
-        <v>9375</v>
-      </c>
-      <c r="I2292" s="20">
-        <v>82995167</v>
-      </c>
-      <c r="J2292" s="21" t="s">
-        <v>9384</v>
-      </c>
-      <c r="K2292" s="20"/>
-      <c r="L2292" s="20">
-        <v>696</v>
-      </c>
-      <c r="M2292" s="21" t="s">
-        <v>9377</v>
-      </c>
-      <c r="N2292" s="20" t="s">
-        <v>9378</v>
-      </c>
-      <c r="O2292" s="20"/>
-      <c r="P2292" s="20"/>
-      <c r="Q2292" s="20"/>
-      <c r="R2292" s="20" t="s">
-        <v>9385</v>
-      </c>
-      <c r="S2292" s="25" t="s">
-        <v>9386</v>
-      </c>
-      <c r="T2292" s="20" t="s">
+      <c r="F2286" s="3" t="s">
+        <v>9408</v>
+      </c>
+      <c r="G2286" s="3" t="s">
+        <v>9409</v>
+      </c>
+      <c r="H2286" s="3" t="s">
+        <v>9417</v>
+      </c>
+      <c r="I2286" s="3" t="s">
+        <v>9418</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2287" s="3" t="s">
         <v>9387</v>
       </c>
-      <c r="U2292" s="20" t="s">
+      <c r="B2287" s="4">
+        <v>80473873</v>
+      </c>
+      <c r="C2287" s="3" t="s">
+        <v>9399</v>
+      </c>
+      <c r="D2287" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2287" s="3" t="s">
+        <v>9408</v>
+      </c>
+      <c r="G2287" s="3" t="s">
+        <v>9409</v>
+      </c>
+      <c r="H2287" s="3" t="s">
+        <v>9419</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2288" s="3" t="s">
         <v>9388</v>
       </c>
-      <c r="V2292" s="20" t="s">
-        <v>9383</v>
-      </c>
-      <c r="W2292" s="20" t="s">
-        <v>9383</v>
-      </c>
-    </row>
-    <row r="2293" spans="6:23" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F2293" s="19">
-        <v>3</v>
-      </c>
-      <c r="G2293" s="20" t="s">
-        <v>9374</v>
-      </c>
-      <c r="H2293" s="20" t="s">
-        <v>9375</v>
-      </c>
-      <c r="I2293" s="20">
-        <v>83569021</v>
-      </c>
-      <c r="J2293" s="21" t="s">
+      <c r="B2288" s="4">
+        <v>24613063</v>
+      </c>
+      <c r="C2288" s="3" t="s">
+        <v>9400</v>
+      </c>
+      <c r="D2288" s="3" t="s">
+        <v>9405</v>
+      </c>
+      <c r="F2288" s="3" t="s">
+        <v>9408</v>
+      </c>
+      <c r="G2288" s="3" t="s">
+        <v>9420</v>
+      </c>
+      <c r="J2288" s="3" t="s">
+        <v>9421</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2289" s="3" t="s">
         <v>9389</v>
       </c>
-      <c r="K2293" s="20"/>
-      <c r="L2293" s="20">
-        <v>696</v>
-      </c>
-      <c r="M2293" s="21" t="s">
-        <v>9377</v>
-      </c>
-      <c r="N2293" s="20" t="s">
-        <v>9378</v>
-      </c>
-      <c r="O2293" s="20"/>
-      <c r="P2293" s="20"/>
-      <c r="Q2293" s="20"/>
-      <c r="R2293" s="20" t="s">
+      <c r="B2289" s="4">
+        <v>85305524</v>
+      </c>
+      <c r="C2289" s="3" t="s">
+        <v>9401</v>
+      </c>
+      <c r="D2289" s="3" t="s">
+        <v>9407</v>
+      </c>
+      <c r="F2289" s="3" t="s">
+        <v>9408</v>
+      </c>
+      <c r="G2289" s="3" t="s">
+        <v>9409</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2290" s="3" t="s">
         <v>9390</v>
       </c>
-      <c r="S2293" s="25" t="s">
+      <c r="B2290" s="4">
+        <v>53591829</v>
+      </c>
+      <c r="C2290" s="3" t="s">
+        <v>9402</v>
+      </c>
+      <c r="D2290" s="3" t="s">
+        <v>9405</v>
+      </c>
+      <c r="F2290" s="3" t="s">
+        <v>9408</v>
+      </c>
+      <c r="G2290" s="3" t="s">
+        <v>9409</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2291" s="3" t="s">
         <v>9391</v>
       </c>
-      <c r="T2293" s="20" t="s">
+      <c r="B2291" s="4">
+        <v>96978717</v>
+      </c>
+      <c r="C2291" s="3" t="s">
+        <v>9403</v>
+      </c>
+      <c r="D2291" s="3" t="s">
+        <v>9405</v>
+      </c>
+      <c r="F2291" s="3" t="s">
+        <v>9408</v>
+      </c>
+      <c r="G2291" s="3" t="s">
+        <v>9409</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2292" s="3" t="s">
         <v>9392</v>
       </c>
-      <c r="U2293" s="20" t="s">
-        <v>9393</v>
-      </c>
-      <c r="V2293" s="20" t="s">
-        <v>9394</v>
-      </c>
-      <c r="W2293" s="20" t="s">
-        <v>9394</v>
-      </c>
-    </row>
-    <row r="2294" spans="6:23" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F2294" s="19">
-        <v>4</v>
-      </c>
-      <c r="G2294" s="20" t="s">
-        <v>9374</v>
-      </c>
-      <c r="H2294" s="20" t="s">
-        <v>9375</v>
-      </c>
-      <c r="I2294" s="20">
-        <v>54172710</v>
-      </c>
-      <c r="J2294" s="21" t="s">
-        <v>9342</v>
-      </c>
-      <c r="K2294" s="20"/>
-      <c r="L2294" s="20">
-        <v>696</v>
-      </c>
-      <c r="M2294" s="21" t="s">
-        <v>9377</v>
-      </c>
-      <c r="N2294" s="20" t="s">
-        <v>9378</v>
-      </c>
-      <c r="O2294" s="20"/>
-      <c r="P2294" s="20"/>
-      <c r="Q2294" s="20"/>
-      <c r="R2294" s="20" t="s">
-        <v>9395</v>
-      </c>
-      <c r="S2294" s="25" t="s">
-        <v>9396</v>
-      </c>
-      <c r="T2294" s="20" t="s">
-        <v>9343</v>
-      </c>
-      <c r="U2294" s="20" t="s">
-        <v>9397</v>
-      </c>
-      <c r="V2294" s="20" t="s">
-        <v>9383</v>
-      </c>
-      <c r="W2294" s="20" t="s">
-        <v>9383</v>
-      </c>
-    </row>
-    <row r="2295" spans="6:23" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F2295" s="19">
-        <v>5</v>
-      </c>
-      <c r="G2295" s="20" t="s">
-        <v>9374</v>
-      </c>
-      <c r="H2295" s="20" t="s">
-        <v>9375</v>
-      </c>
-      <c r="I2295" s="20">
-        <v>83362859</v>
-      </c>
-      <c r="J2295" s="21" t="s">
-        <v>9344</v>
-      </c>
-      <c r="K2295" s="20"/>
-      <c r="L2295" s="20">
-        <v>696</v>
-      </c>
-      <c r="M2295" s="21" t="s">
-        <v>9377</v>
-      </c>
-      <c r="N2295" s="20" t="s">
-        <v>9378</v>
-      </c>
-      <c r="O2295" s="20"/>
-      <c r="P2295" s="20"/>
-      <c r="Q2295" s="20"/>
-      <c r="R2295" s="20" t="s">
-        <v>9398</v>
-      </c>
-      <c r="S2295" s="25" t="s">
-        <v>9399</v>
-      </c>
-      <c r="T2295" s="20" t="s">
-        <v>9345</v>
-      </c>
-      <c r="U2295" s="20" t="s">
-        <v>9400</v>
-      </c>
-      <c r="V2295" s="20" t="s">
-        <v>9394</v>
-      </c>
-      <c r="W2295" s="20" t="s">
-        <v>9394</v>
-      </c>
-    </row>
-    <row r="2296" spans="6:23" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F2296" s="19">
-        <v>6</v>
-      </c>
-      <c r="G2296" s="20" t="s">
-        <v>9374</v>
-      </c>
-      <c r="H2296" s="20" t="s">
-        <v>9375</v>
-      </c>
-      <c r="I2296" s="20">
-        <v>80295202</v>
-      </c>
-      <c r="J2296" s="21" t="s">
-        <v>9346</v>
-      </c>
-      <c r="K2296" s="20"/>
-      <c r="L2296" s="20">
-        <v>696</v>
-      </c>
-      <c r="M2296" s="21" t="s">
-        <v>9377</v>
-      </c>
-      <c r="N2296" s="20" t="s">
-        <v>9378</v>
-      </c>
-      <c r="O2296" s="20"/>
-      <c r="P2296" s="20"/>
-      <c r="Q2296" s="20"/>
-      <c r="R2296" s="20" t="s">
-        <v>9401</v>
-      </c>
-      <c r="S2296" s="25" t="s">
-        <v>9402</v>
-      </c>
-      <c r="T2296" s="20" t="s">
-        <v>9347</v>
-      </c>
-      <c r="U2296" s="20" t="s">
-        <v>9403</v>
-      </c>
-      <c r="V2296" s="20" t="s">
-        <v>9394</v>
-      </c>
-      <c r="W2296" s="20" t="s">
-        <v>9394</v>
-      </c>
-    </row>
-    <row r="2297" spans="6:23" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F2297" s="19">
-        <v>7</v>
-      </c>
-      <c r="G2297" s="20" t="s">
-        <v>9374</v>
-      </c>
-      <c r="H2297" s="20" t="s">
-        <v>9375</v>
-      </c>
-      <c r="I2297" s="20">
-        <v>53621915</v>
-      </c>
-      <c r="J2297" s="21" t="s">
-        <v>9348</v>
-      </c>
-      <c r="K2297" s="20"/>
-      <c r="L2297" s="20">
-        <v>696</v>
-      </c>
-      <c r="M2297" s="21" t="s">
-        <v>9377</v>
-      </c>
-      <c r="N2297" s="20" t="s">
-        <v>9378</v>
-      </c>
-      <c r="O2297" s="20"/>
-      <c r="P2297" s="20"/>
-      <c r="Q2297" s="20"/>
-      <c r="R2297" s="20" t="s">
+      <c r="B2292" s="4">
+        <v>22426557</v>
+      </c>
+      <c r="C2292" s="3" t="s">
         <v>9404</v>
       </c>
-      <c r="S2297" s="25" t="s">
-        <v>9405</v>
-      </c>
-      <c r="T2297" s="20" t="s">
-        <v>9349</v>
-      </c>
-      <c r="U2297" s="20" t="s">
-        <v>9406</v>
-      </c>
-      <c r="V2297" s="20" t="s">
-        <v>9383</v>
-      </c>
-      <c r="W2297" s="20" t="s">
-        <v>9383</v>
-      </c>
-    </row>
-    <row r="2298" spans="6:23" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F2298" s="19">
-        <v>8</v>
-      </c>
-      <c r="G2298" s="20" t="s">
-        <v>9374</v>
-      </c>
-      <c r="H2298" s="20" t="s">
-        <v>9375</v>
-      </c>
-      <c r="I2298" s="20">
-        <v>28548091</v>
-      </c>
-      <c r="J2298" s="21" t="s">
-        <v>9350</v>
-      </c>
-      <c r="K2298" s="20"/>
-      <c r="L2298" s="20">
-        <v>696</v>
-      </c>
-      <c r="M2298" s="21" t="s">
-        <v>9377</v>
-      </c>
-      <c r="N2298" s="20" t="s">
-        <v>9378</v>
-      </c>
-      <c r="O2298" s="20"/>
-      <c r="P2298" s="20"/>
-      <c r="Q2298" s="20"/>
-      <c r="R2298" s="20" t="s">
-        <v>9407</v>
-      </c>
-      <c r="S2298" s="25" t="s">
+      <c r="D2292" s="3" t="s">
+        <v>7146</v>
+      </c>
+      <c r="F2292" s="3" t="s">
         <v>9408</v>
       </c>
-      <c r="T2298" s="20" t="s">
-        <v>9351</v>
-      </c>
-      <c r="U2298" s="20" t="s">
+      <c r="G2292" s="3" t="s">
         <v>9409</v>
       </c>
-      <c r="V2298" s="20" t="s">
-        <v>9394</v>
-      </c>
-      <c r="W2298" s="20" t="s">
-        <v>9394</v>
-      </c>
-    </row>
-    <row r="2299" spans="6:23" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F2299" s="19">
-        <v>9</v>
-      </c>
-      <c r="G2299" s="20" t="s">
-        <v>9374</v>
-      </c>
-      <c r="H2299" s="20" t="s">
-        <v>9375</v>
-      </c>
-      <c r="I2299" s="20">
-        <v>84899112</v>
-      </c>
-      <c r="J2299" s="21" t="s">
-        <v>9166</v>
-      </c>
-      <c r="K2299" s="20"/>
-      <c r="L2299" s="20">
-        <v>696</v>
-      </c>
-      <c r="M2299" s="21" t="s">
-        <v>9377</v>
-      </c>
-      <c r="N2299" s="20" t="s">
-        <v>9378</v>
-      </c>
-      <c r="O2299" s="20"/>
-      <c r="P2299" s="20"/>
-      <c r="Q2299" s="20"/>
-      <c r="R2299" s="20" t="s">
-        <v>9410</v>
-      </c>
-      <c r="S2299" s="25" t="s">
-        <v>9411</v>
-      </c>
-      <c r="T2299" s="20" t="s">
-        <v>9167</v>
-      </c>
-      <c r="U2299" s="20" t="s">
-        <v>9412</v>
-      </c>
-      <c r="V2299" s="20" t="s">
-        <v>9394</v>
-      </c>
-      <c r="W2299" s="20" t="s">
-        <v>9394</v>
-      </c>
-    </row>
-    <row r="2300" spans="6:23" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F2300" s="22">
-        <v>10</v>
-      </c>
-      <c r="G2300" s="23" t="s">
-        <v>9374</v>
-      </c>
-      <c r="H2300" s="23" t="s">
-        <v>9375</v>
-      </c>
-      <c r="I2300" s="23">
-        <v>30901647</v>
-      </c>
-      <c r="J2300" s="24" t="s">
-        <v>9143</v>
-      </c>
-      <c r="K2300" s="23"/>
-      <c r="L2300" s="23">
-        <v>696</v>
-      </c>
-      <c r="M2300" s="24" t="s">
-        <v>9377</v>
-      </c>
-      <c r="N2300" s="23" t="s">
-        <v>9378</v>
-      </c>
-      <c r="O2300" s="23"/>
-      <c r="P2300" s="23"/>
-      <c r="Q2300" s="23"/>
-      <c r="R2300" s="23" t="s">
-        <v>9413</v>
-      </c>
-      <c r="S2300" s="26" t="s">
-        <v>9414</v>
-      </c>
-      <c r="T2300" s="23" t="s">
-        <v>9144</v>
-      </c>
-      <c r="U2300" s="23" t="s">
-        <v>9415</v>
-      </c>
-      <c r="V2300" s="23" t="s">
-        <v>9394</v>
-      </c>
-      <c r="W2300" s="23" t="s">
-        <v>9394</v>
-      </c>
-    </row>
-    <row r="2301" spans="6:23" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="S2301" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="H1:H1983"/>
+  <autoFilter ref="H1:H1983" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B2056:B2065">
     <cfRule type="duplicateValues" dxfId="12" priority="59"/>
@@ -81615,16 +81399,16 @@
     <cfRule type="duplicateValues" dxfId="0" priority="6" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G832:G842 G318:G345 G347:G829 G1891 G2:G316">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G832:G842 G318:G345 G347:G829 G1891 G2:G316" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"電話,Mail"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="J1123" r:id="rId1"/>
-    <hyperlink ref="J1383" r:id="rId2"/>
-    <hyperlink ref="J1904" r:id="rId3"/>
-    <hyperlink ref="J1905" r:id="rId4"/>
-    <hyperlink ref="J2069" r:id="rId5"/>
+    <hyperlink ref="J1123" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="J1383" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="J1904" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="J1905" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="J2069" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
@@ -81633,7 +81417,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>

--- a/Export_format/出口長委登記表.xlsx
+++ b/Export_format/出口長委登記表.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20416"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.66.23.230\886wa\◆進口相關查詢資料庫◆(不要移動)\◆新委任書-出口◆\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEBBC53-12AC-48B2-A03E-D2D02668EC77}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="5655" windowWidth="11055" windowHeight="3900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15" yWindow="5655" windowWidth="11055" windowHeight="3900"/>
   </bookViews>
   <sheets>
     <sheet name="順豐出口" sheetId="4" r:id="rId1"/>
@@ -24,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13562" uniqueCount="9445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13645" uniqueCount="9488">
   <si>
     <t>麒安科技有限公司</t>
   </si>
@@ -33326,11 +33320,151 @@
   <si>
     <t>7726/彭小姐</t>
   </si>
+  <si>
+    <t>全磊微機電股份有限公司</t>
+  </si>
+  <si>
+    <t>聯碩電器股份有限公司</t>
+  </si>
+  <si>
+    <t>三全科技股份有限公司</t>
+  </si>
+  <si>
+    <t>上暘光學股份有限公司</t>
+  </si>
+  <si>
+    <t>青木科技股份有限公司</t>
+  </si>
+  <si>
+    <t>勞蘇企業社</t>
+  </si>
+  <si>
+    <t>昇佳電子股份有限公司</t>
+  </si>
+  <si>
+    <t>友通資訊股份有限公司</t>
+  </si>
+  <si>
+    <t>120.02.10</t>
+  </si>
+  <si>
+    <t>115業二03586</t>
+  </si>
+  <si>
+    <t>115業二03587</t>
+  </si>
+  <si>
+    <t>115業二03588</t>
+  </si>
+  <si>
+    <t>115業二03589</t>
+  </si>
+  <si>
+    <t>115業二03590</t>
+  </si>
+  <si>
+    <t>115業二03591</t>
+  </si>
+  <si>
+    <t>115業二03592</t>
+  </si>
+  <si>
+    <t>115業二03593</t>
+  </si>
+  <si>
+    <t>115.02.12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-563-2161</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6666/吳小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-396-1188</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2659-3636</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>洪小姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-355-5685</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>04-2568-4128</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0989-476-953</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2697-2986</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>WBBL2026022265</t>
+  </si>
+  <si>
+    <t>藝鏡國際股份有限公司</t>
+  </si>
+  <si>
+    <t>WBBL2026020940</t>
+  </si>
+  <si>
+    <t>艾維克科技股份有限公司</t>
+  </si>
+  <si>
+    <t>WBBL2026020483</t>
+  </si>
+  <si>
+    <t>聖曼德服裝有限公司</t>
+  </si>
+  <si>
+    <t>WBBL2026017893</t>
+  </si>
+  <si>
+    <t>WBBL2026016755</t>
+  </si>
+  <si>
+    <t>麗臺科技股份有限公司</t>
+  </si>
+  <si>
+    <t>WBBL2026016087</t>
+  </si>
+  <si>
+    <t>01180613</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>120.03.18</t>
+  </si>
+  <si>
+    <t>120.02.04</t>
+  </si>
+  <si>
+    <t>120.01.26</t>
+  </si>
+  <si>
+    <t>121.07.10</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="_ &quot;¥&quot;* #,##0.00_ ;_ &quot;¥&quot;* \-#,##0.00_ ;_ &quot;¥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
@@ -33709,7 +33843,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -33742,26 +33876,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -33794,23 +33911,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -33986,9 +34086,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:U2291"/>
+  <dimension ref="A1:U2319"/>
   <sheetFormatPr defaultRowHeight="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="79" style="3" customWidth="1"/>
@@ -81771,6 +81871,334 @@
       </c>
       <c r="I2291" s="3" t="s">
         <v>9444</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2292" s="3" t="s">
+        <v>9445</v>
+      </c>
+      <c r="B2292" s="4">
+        <v>86124830</v>
+      </c>
+      <c r="C2292" s="3" t="s">
+        <v>9454</v>
+      </c>
+      <c r="D2292" s="3" t="s">
+        <v>9453</v>
+      </c>
+      <c r="F2292" s="3" t="s">
+        <v>9462</v>
+      </c>
+      <c r="G2292" s="3" t="s">
+        <v>2613</v>
+      </c>
+      <c r="H2292" s="3" t="s">
+        <v>9463</v>
+      </c>
+      <c r="I2292" s="3" t="s">
+        <v>9464</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2293" s="3" t="s">
+        <v>9446</v>
+      </c>
+      <c r="B2293" s="4">
+        <v>28587431</v>
+      </c>
+      <c r="C2293" s="3" t="s">
+        <v>9455</v>
+      </c>
+      <c r="D2293" s="3" t="s">
+        <v>9039</v>
+      </c>
+      <c r="F2293" s="3" t="s">
+        <v>9462</v>
+      </c>
+      <c r="G2293" s="3" t="s">
+        <v>2613</v>
+      </c>
+      <c r="H2293" s="3" t="s">
+        <v>9465</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2294" s="3" t="s">
+        <v>9447</v>
+      </c>
+      <c r="B2294" s="4">
+        <v>84133454</v>
+      </c>
+      <c r="C2294" s="3" t="s">
+        <v>9456</v>
+      </c>
+      <c r="D2294" s="3" t="s">
+        <v>9453</v>
+      </c>
+      <c r="F2294" s="3" t="s">
+        <v>9462</v>
+      </c>
+      <c r="G2294" s="3" t="s">
+        <v>2613</v>
+      </c>
+      <c r="H2294" s="3" t="s">
+        <v>9466</v>
+      </c>
+      <c r="I2294" s="3" t="s">
+        <v>9467</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2295" s="3" t="s">
+        <v>9448</v>
+      </c>
+      <c r="B2295" s="4">
+        <v>53490527</v>
+      </c>
+      <c r="C2295" s="3" t="s">
+        <v>9457</v>
+      </c>
+      <c r="D2295" s="3" t="s">
+        <v>9453</v>
+      </c>
+      <c r="F2295" s="3" t="s">
+        <v>9462</v>
+      </c>
+      <c r="G2295" s="3" t="s">
+        <v>2613</v>
+      </c>
+      <c r="H2295" s="3" t="s">
+        <v>9468</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2296" s="3" t="s">
+        <v>9449</v>
+      </c>
+      <c r="B2296" s="4">
+        <v>83010243</v>
+      </c>
+      <c r="C2296" s="3" t="s">
+        <v>9458</v>
+      </c>
+      <c r="D2296" s="3" t="s">
+        <v>9453</v>
+      </c>
+      <c r="F2296" s="3" t="s">
+        <v>9462</v>
+      </c>
+      <c r="G2296" s="3" t="s">
+        <v>2613</v>
+      </c>
+      <c r="H2296" s="3" t="s">
+        <v>9469</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2297" s="3" t="s">
+        <v>9450</v>
+      </c>
+      <c r="B2297" s="4">
+        <v>91425738</v>
+      </c>
+      <c r="C2297" s="3" t="s">
+        <v>9459</v>
+      </c>
+      <c r="D2297" s="3" t="s">
+        <v>9453</v>
+      </c>
+      <c r="F2297" s="3" t="s">
+        <v>9462</v>
+      </c>
+      <c r="G2297" s="3" t="s">
+        <v>2613</v>
+      </c>
+      <c r="H2297" s="3" t="s">
+        <v>9470</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2298" s="3" t="s">
+        <v>9451</v>
+      </c>
+      <c r="B2298" s="4">
+        <v>25079572</v>
+      </c>
+      <c r="C2298" s="3" t="s">
+        <v>9460</v>
+      </c>
+      <c r="D2298" s="3" t="s">
+        <v>8082</v>
+      </c>
+      <c r="F2298" s="3" t="s">
+        <v>9462</v>
+      </c>
+      <c r="G2298" s="3" t="s">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2299" s="3" t="s">
+        <v>9452</v>
+      </c>
+      <c r="B2299" s="4">
+        <v>30950652</v>
+      </c>
+      <c r="C2299" s="3" t="s">
+        <v>9461</v>
+      </c>
+      <c r="D2299" s="3" t="s">
+        <v>9453</v>
+      </c>
+      <c r="F2299" s="3" t="s">
+        <v>9462</v>
+      </c>
+      <c r="G2299" s="3" t="s">
+        <v>2613</v>
+      </c>
+      <c r="H2299" s="3" t="s">
+        <v>9471</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2300" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2300" s="5" t="s">
+        <v>9483</v>
+      </c>
+      <c r="C2300" s="3" t="s">
+        <v>9473</v>
+      </c>
+      <c r="D2300" s="3" t="s">
+        <v>9484</v>
+      </c>
+      <c r="E2300" s="3" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2301" s="3" t="s">
+        <v>9474</v>
+      </c>
+      <c r="B2301" s="4">
+        <v>53243511</v>
+      </c>
+      <c r="C2301" s="3" t="s">
+        <v>9475</v>
+      </c>
+      <c r="D2301" s="3" t="s">
+        <v>9412</v>
+      </c>
+      <c r="E2301" s="3" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2302" s="3" t="s">
+        <v>9476</v>
+      </c>
+      <c r="B2302" s="4">
+        <v>29087808</v>
+      </c>
+      <c r="C2302" s="3" t="s">
+        <v>9477</v>
+      </c>
+      <c r="D2302" s="3" t="s">
+        <v>9485</v>
+      </c>
+      <c r="E2302" s="3" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2303" s="3" t="s">
+        <v>9478</v>
+      </c>
+      <c r="B2303" s="4">
+        <v>54336621</v>
+      </c>
+      <c r="C2303" s="3" t="s">
+        <v>9479</v>
+      </c>
+      <c r="D2303" s="3" t="s">
+        <v>9486</v>
+      </c>
+      <c r="E2303" s="3" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2304" s="3" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B2304" s="4">
+        <v>53529585</v>
+      </c>
+      <c r="C2304" s="3" t="s">
+        <v>9480</v>
+      </c>
+      <c r="D2304" s="3" t="s">
+        <v>9487</v>
+      </c>
+      <c r="E2304" s="3" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2305" s="3" t="s">
+        <v>9481</v>
+      </c>
+      <c r="B2305" s="4">
+        <v>22325002</v>
+      </c>
+      <c r="C2305" s="3" t="s">
+        <v>9482</v>
+      </c>
+      <c r="D2305" s="3" t="s">
+        <v>9326</v>
+      </c>
+      <c r="E2305" s="3" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2306" s="3" t="s">
+        <v>9304</v>
+      </c>
+      <c r="B2306" s="4">
+        <v>11332202</v>
+      </c>
+      <c r="C2306" s="3" t="s">
+        <v>9306</v>
+      </c>
+      <c r="D2306" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="E2306" s="3" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2307" s="3" t="s">
+        <v>9310</v>
+      </c>
+      <c r="B2307" s="4">
+        <v>29187736</v>
+      </c>
+      <c r="C2307" s="3" t="s">
+        <v>9312</v>
+      </c>
+      <c r="D2307" s="3" t="s">
+        <v>9326</v>
+      </c>
+      <c r="E2307" s="3" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E2319" s="3" t="s">
+        <v>9472</v>
       </c>
     </row>
   </sheetData>
@@ -81811,16 +82239,16 @@
     <cfRule type="duplicateValues" dxfId="0" priority="6" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G795:G805 G281:G308 G310:G792 G1854 G2:G279" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G795:G805 G281:G308 G310:G792 G1854 G2:G279">
       <formula1>"電話,Mail"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="J1086" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="J1346" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="J1867" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="J1868" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="J2032" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="J1086" r:id="rId1"/>
+    <hyperlink ref="J1346" r:id="rId2"/>
+    <hyperlink ref="J1867" r:id="rId3"/>
+    <hyperlink ref="J1868" r:id="rId4"/>
+    <hyperlink ref="J2032" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
@@ -81829,7 +82257,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
